--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6346AA13-45CF-4995-9D67-C6DFC433D96A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9F957B-4B03-4D4A-9E5B-3DFD995A1DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -92,31 +93,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_ "/>
-    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -124,7 +125,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -132,7 +133,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -140,35 +141,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -176,7 +177,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -184,14 +185,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -199,14 +200,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -214,7 +215,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -222,20 +223,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -244,7 +245,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -602,7 +603,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -610,92 +611,92 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -713,7 +714,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3847,6 +3848,9 @@
                 <c:pt idx="1030">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="1031">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6948,6 +6952,9 @@
                 </c:pt>
                 <c:pt idx="1030">
                   <c:v>68.52</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>68.36</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7124,7 +7131,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7132,6 +7138,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -7164,7 +7171,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10306,6 +10313,9 @@
                 <c:pt idx="1030">
                   <c:v>46107</c:v>
                 </c:pt>
+                <c:pt idx="1031">
+                  <c:v>46114</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13407,6 +13417,9 @@
                 </c:pt>
                 <c:pt idx="1030">
                   <c:v>47.03</c:v>
+                </c:pt>
+                <c:pt idx="1031">
+                  <c:v>55.64</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13488,6 +13501,7 @@
         <c:axId val="1271699984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -13563,7 +13577,7 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr rtl="0">
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -13582,7 +13596,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13590,6 +13603,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -14816,9 +14830,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14856,7 +14870,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -14962,7 +14976,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15104,7 +15118,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15112,24 +15126,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1032"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K1033"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.75" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.26953125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.90625" style="10"/>
+    <col min="11" max="11" width="21.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15164,7 +15178,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>38903</v>
       </c>
@@ -15215,7 +15229,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="15">
         <v>38910</v>
       </c>
@@ -15266,7 +15280,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>38903</v>
       </c>
@@ -15302,7 +15316,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>38910</v>
       </c>
@@ -15338,7 +15352,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
         <v>38917</v>
       </c>
@@ -15374,7 +15388,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>38924</v>
       </c>
@@ -15410,7 +15424,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>38931</v>
       </c>
@@ -15446,7 +15460,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>38938</v>
       </c>
@@ -15482,7 +15496,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>38945</v>
       </c>
@@ -15518,7 +15532,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>38952</v>
       </c>
@@ -15554,7 +15568,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
         <v>38959</v>
       </c>
@@ -15590,7 +15604,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
         <v>38966</v>
       </c>
@@ -15626,7 +15640,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>38973</v>
       </c>
@@ -15662,7 +15676,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
         <v>38980</v>
       </c>
@@ -15698,7 +15712,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
         <v>38987</v>
       </c>
@@ -15734,7 +15748,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
         <v>38994</v>
       </c>
@@ -15770,7 +15784,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>39001</v>
       </c>
@@ -15806,7 +15820,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
         <v>39008</v>
       </c>
@@ -15842,7 +15856,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>39015</v>
       </c>
@@ -15878,7 +15892,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
         <v>39022</v>
       </c>
@@ -15914,7 +15928,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
         <v>39029</v>
       </c>
@@ -15950,7 +15964,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
         <v>39036</v>
       </c>
@@ -15986,7 +16000,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
         <v>39043</v>
       </c>
@@ -16022,7 +16036,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
         <v>39050</v>
       </c>
@@ -16058,7 +16072,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
         <v>39057</v>
       </c>
@@ -16094,7 +16108,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
         <v>39064</v>
       </c>
@@ -16130,7 +16144,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
         <v>39071</v>
       </c>
@@ -16166,7 +16180,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
         <v>39078</v>
       </c>
@@ -16202,7 +16216,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
         <v>39085</v>
       </c>
@@ -16238,7 +16252,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
         <v>39092</v>
       </c>
@@ -16274,7 +16288,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
         <v>39099</v>
       </c>
@@ -16310,7 +16324,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>39106</v>
       </c>
@@ -16346,7 +16360,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>39113</v>
       </c>
@@ -16382,7 +16396,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>39120</v>
       </c>
@@ -16418,7 +16432,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>39127</v>
       </c>
@@ -16454,7 +16468,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>39134</v>
       </c>
@@ -16490,7 +16504,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>39141</v>
       </c>
@@ -16526,7 +16540,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
         <v>39148</v>
       </c>
@@ -16562,7 +16576,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>39155</v>
       </c>
@@ -16598,7 +16612,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>39162</v>
       </c>
@@ -16634,7 +16648,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>39169</v>
       </c>
@@ -16670,7 +16684,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="15">
         <v>39176</v>
       </c>
@@ -16706,7 +16720,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="15">
         <v>39183</v>
       </c>
@@ -16742,7 +16756,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
         <v>39190</v>
       </c>
@@ -16778,7 +16792,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="15">
         <v>39197</v>
       </c>
@@ -16814,7 +16828,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="15">
         <v>39204</v>
       </c>
@@ -16850,7 +16864,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>39211</v>
       </c>
@@ -16886,7 +16900,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="15">
         <v>39218</v>
       </c>
@@ -16922,7 +16936,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="15">
         <v>39225</v>
       </c>
@@ -16958,7 +16972,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="15">
         <v>39232</v>
       </c>
@@ -16994,7 +17008,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>39239</v>
       </c>
@@ -17030,7 +17044,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="15">
         <v>39246</v>
       </c>
@@ -17066,7 +17080,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="15">
         <v>39253</v>
       </c>
@@ -17102,7 +17116,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="15">
         <v>39260</v>
       </c>
@@ -17138,7 +17152,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="15">
         <v>39268</v>
       </c>
@@ -17174,7 +17188,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>39274</v>
       </c>
@@ -17210,7 +17224,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="15">
         <v>39281</v>
       </c>
@@ -17246,7 +17260,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>39288</v>
       </c>
@@ -17282,7 +17296,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
         <v>39295</v>
       </c>
@@ -17318,7 +17332,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>39302</v>
       </c>
@@ -17354,7 +17368,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>39309</v>
       </c>
@@ -17390,7 +17404,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="15">
         <v>39316</v>
       </c>
@@ -17426,7 +17440,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="15">
         <v>39323</v>
       </c>
@@ -17462,7 +17476,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="15">
         <v>39330</v>
       </c>
@@ -17498,7 +17512,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="15">
         <v>39337</v>
       </c>
@@ -17534,7 +17548,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>39344</v>
       </c>
@@ -17585,7 +17599,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="15">
         <v>39351</v>
       </c>
@@ -17621,7 +17635,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>39358</v>
       </c>
@@ -17657,7 +17671,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="15">
         <v>39365</v>
       </c>
@@ -17693,7 +17707,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="15">
         <v>39372</v>
       </c>
@@ -17729,7 +17743,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="15">
         <v>39379</v>
       </c>
@@ -17765,7 +17779,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>39386</v>
       </c>
@@ -17801,7 +17815,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="15">
         <v>39393</v>
       </c>
@@ -17837,7 +17851,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
         <v>39400</v>
       </c>
@@ -17873,7 +17887,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="15">
         <v>39407</v>
       </c>
@@ -17909,7 +17923,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>39414</v>
       </c>
@@ -17945,7 +17959,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="15">
         <v>39421</v>
       </c>
@@ -17981,7 +17995,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="15">
         <v>39428</v>
       </c>
@@ -18017,7 +18031,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="15">
         <v>39435</v>
       </c>
@@ -18053,7 +18067,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="15">
         <v>39442</v>
       </c>
@@ -18089,7 +18103,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="15">
         <v>39449</v>
       </c>
@@ -18125,7 +18139,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="15">
         <v>39456</v>
       </c>
@@ -18161,7 +18175,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="15">
         <v>39463</v>
       </c>
@@ -18197,7 +18211,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="15">
         <v>39470</v>
       </c>
@@ -18233,7 +18247,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="15">
         <v>39477</v>
       </c>
@@ -18269,7 +18283,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="15">
         <v>39484</v>
       </c>
@@ -18305,7 +18319,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="15">
         <v>39491</v>
       </c>
@@ -18341,7 +18355,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="15">
         <v>39498</v>
       </c>
@@ -18377,7 +18391,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="15">
         <v>39505</v>
       </c>
@@ -18413,7 +18427,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="15">
         <v>39512</v>
       </c>
@@ -18449,7 +18463,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="15">
         <v>39519</v>
       </c>
@@ -18485,7 +18499,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="15">
         <v>39526</v>
       </c>
@@ -18521,7 +18535,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="15">
         <v>39533</v>
       </c>
@@ -18557,7 +18571,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="15">
         <v>39540</v>
       </c>
@@ -18593,7 +18607,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="15">
         <v>39547</v>
       </c>
@@ -18629,7 +18643,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="15">
         <v>39554</v>
       </c>
@@ -18665,7 +18679,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="15">
         <v>39561</v>
       </c>
@@ -18701,7 +18715,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>39569</v>
       </c>
@@ -18737,7 +18751,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="15">
         <v>39575</v>
       </c>
@@ -18773,7 +18787,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="15">
         <v>39582</v>
       </c>
@@ -18809,7 +18823,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="15">
         <v>39589</v>
       </c>
@@ -18845,7 +18859,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="15">
         <v>39596</v>
       </c>
@@ -18881,7 +18895,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="15">
         <v>39603</v>
       </c>
@@ -18917,7 +18931,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="15">
         <v>39610</v>
       </c>
@@ -18953,7 +18967,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1">
+    <row r="106" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15">
         <v>39617</v>
       </c>
@@ -18989,7 +19003,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="15">
         <v>39624</v>
       </c>
@@ -19025,7 +19039,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="15">
         <v>39631</v>
       </c>
@@ -19061,7 +19075,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1">
+    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15">
         <v>39638</v>
       </c>
@@ -19097,7 +19111,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="15">
         <v>39645</v>
       </c>
@@ -19133,7 +19147,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="15">
         <v>39652</v>
       </c>
@@ -19169,7 +19183,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="15">
         <v>39659</v>
       </c>
@@ -19205,7 +19219,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="15">
         <v>39666</v>
       </c>
@@ -19241,7 +19255,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="15">
         <v>39673</v>
       </c>
@@ -19277,7 +19291,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="15">
         <v>39681</v>
       </c>
@@ -19313,7 +19327,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="15">
         <v>39687</v>
       </c>
@@ -19349,7 +19363,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="15">
         <v>39694</v>
       </c>
@@ -19385,7 +19399,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="15">
         <v>39701</v>
       </c>
@@ -19421,7 +19435,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="15">
         <v>39708</v>
       </c>
@@ -19457,7 +19471,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="15">
         <v>39715</v>
       </c>
@@ -19493,7 +19507,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="15">
         <v>39722</v>
       </c>
@@ -19529,7 +19543,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="15">
         <v>39729</v>
       </c>
@@ -19565,7 +19579,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="15">
         <v>39736</v>
       </c>
@@ -19601,7 +19615,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="15">
         <v>39743</v>
       </c>
@@ -19637,7 +19651,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="15">
         <v>39750</v>
       </c>
@@ -19673,7 +19687,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="15">
         <v>39757</v>
       </c>
@@ -19709,7 +19723,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="15">
         <v>39764</v>
       </c>
@@ -19745,7 +19759,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="15">
         <v>39771</v>
       </c>
@@ -19781,7 +19795,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="15">
         <v>39778</v>
       </c>
@@ -19817,7 +19831,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="15">
         <v>39785</v>
       </c>
@@ -19853,7 +19867,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="15">
         <v>39792</v>
       </c>
@@ -19904,7 +19918,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="15">
         <v>39799</v>
       </c>
@@ -19940,7 +19954,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="15">
         <v>39806</v>
       </c>
@@ -19976,7 +19990,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="15">
         <v>39813</v>
       </c>
@@ -20012,7 +20026,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="15">
         <v>39820</v>
       </c>
@@ -20048,7 +20062,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="15">
         <v>39827</v>
       </c>
@@ -20084,7 +20098,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="15">
         <v>39834</v>
       </c>
@@ -20120,7 +20134,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="15">
         <v>39841</v>
       </c>
@@ -20156,7 +20170,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="15">
         <v>39848</v>
       </c>
@@ -20192,7 +20206,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="15">
         <v>39855</v>
       </c>
@@ -20228,7 +20242,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="15">
         <v>39862</v>
       </c>
@@ -20264,7 +20278,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="15">
         <v>39869</v>
       </c>
@@ -20300,7 +20314,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="15">
         <v>39876</v>
       </c>
@@ -20336,7 +20350,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="15">
         <v>39883</v>
       </c>
@@ -20372,7 +20386,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="15">
         <v>39890</v>
       </c>
@@ -20408,7 +20422,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="15">
         <v>39897</v>
       </c>
@@ -20444,7 +20458,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="15">
         <v>39904</v>
       </c>
@@ -20480,7 +20494,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="15">
         <v>39911</v>
       </c>
@@ -20516,7 +20530,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="15">
         <v>39918</v>
       </c>
@@ -20552,7 +20566,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="15">
         <v>39925</v>
       </c>
@@ -20588,7 +20602,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="15">
         <v>39932</v>
       </c>
@@ -20624,7 +20638,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="15">
         <v>39939</v>
       </c>
@@ -20660,7 +20674,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="15">
         <v>39946</v>
       </c>
@@ -20696,7 +20710,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="15">
         <v>39953</v>
       </c>
@@ -20732,7 +20746,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="15">
         <v>39960</v>
       </c>
@@ -20768,7 +20782,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="15">
         <v>39967</v>
       </c>
@@ -20804,7 +20818,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="15">
         <v>39974</v>
       </c>
@@ -20840,7 +20854,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="15">
         <v>39981</v>
       </c>
@@ -20876,7 +20890,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="15">
         <v>39988</v>
       </c>
@@ -20912,7 +20926,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="15">
         <v>39995</v>
       </c>
@@ -20948,7 +20962,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="15">
         <v>40002</v>
       </c>
@@ -20984,7 +20998,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="15">
         <v>40009</v>
       </c>
@@ -21020,7 +21034,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="15">
         <v>40016</v>
       </c>
@@ -21056,7 +21070,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="15">
         <v>40023</v>
       </c>
@@ -21092,7 +21106,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="15">
         <v>40030</v>
       </c>
@@ -21128,7 +21142,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="15">
         <v>40037</v>
       </c>
@@ -21164,7 +21178,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="15">
         <v>40044</v>
       </c>
@@ -21200,7 +21214,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="15">
         <v>40051</v>
       </c>
@@ -21236,7 +21250,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="15">
         <v>40058</v>
       </c>
@@ -21272,7 +21286,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="15">
         <v>40065</v>
       </c>
@@ -21308,7 +21322,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="15">
         <v>40072</v>
       </c>
@@ -21344,7 +21358,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="15">
         <v>40079</v>
       </c>
@@ -21380,7 +21394,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="15">
         <v>40086</v>
       </c>
@@ -21416,7 +21430,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="15">
         <v>40093</v>
       </c>
@@ -21452,7 +21466,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="15">
         <v>40100</v>
       </c>
@@ -21488,7 +21502,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="15">
         <v>40107</v>
       </c>
@@ -21524,7 +21538,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="15">
         <v>40114</v>
       </c>
@@ -21560,7 +21574,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="15">
         <v>40121</v>
       </c>
@@ -21596,7 +21610,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="15">
         <v>40128</v>
       </c>
@@ -21632,7 +21646,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="15">
         <v>40135</v>
       </c>
@@ -21668,7 +21682,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="15">
         <v>40142</v>
       </c>
@@ -21704,7 +21718,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="15">
         <v>40149</v>
       </c>
@@ -21740,7 +21754,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="15">
         <v>40156</v>
       </c>
@@ -21776,7 +21790,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="15">
         <v>40163</v>
       </c>
@@ -21812,7 +21826,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="15">
         <v>40170</v>
       </c>
@@ -21848,7 +21862,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="15">
         <v>40177</v>
       </c>
@@ -21884,7 +21898,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="15">
         <v>40184</v>
       </c>
@@ -21920,7 +21934,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="15">
         <v>40191</v>
       </c>
@@ -21956,7 +21970,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="15">
         <v>40198</v>
       </c>
@@ -21992,7 +22006,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="15">
         <v>40205</v>
       </c>
@@ -22028,7 +22042,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="15">
         <v>40212</v>
       </c>
@@ -22064,7 +22078,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="15">
         <v>40219</v>
       </c>
@@ -22100,7 +22114,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="15">
         <v>40226</v>
       </c>
@@ -22136,7 +22150,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="15">
         <v>40233</v>
       </c>
@@ -22172,7 +22186,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="15">
         <v>40240</v>
       </c>
@@ -22223,7 +22237,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="15">
         <v>40247</v>
       </c>
@@ -22259,7 +22273,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="15">
         <v>40254</v>
       </c>
@@ -22295,7 +22309,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="15">
         <v>40261</v>
       </c>
@@ -22331,7 +22345,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="15">
         <v>40268</v>
       </c>
@@ -22367,7 +22381,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="15">
         <v>40275</v>
       </c>
@@ -22403,7 +22417,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="15">
         <v>40282</v>
       </c>
@@ -22439,7 +22453,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="15">
         <v>40289</v>
       </c>
@@ -22475,7 +22489,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="15">
         <v>40296</v>
       </c>
@@ -22511,7 +22525,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="15">
         <v>40303</v>
       </c>
@@ -22547,7 +22561,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="15">
         <v>40310</v>
       </c>
@@ -22583,7 +22597,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="15">
         <v>40317</v>
       </c>
@@ -22619,7 +22633,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="15">
         <v>40324</v>
       </c>
@@ -22655,7 +22669,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="15">
         <v>40331</v>
       </c>
@@ -22691,7 +22705,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="15">
         <v>40338</v>
       </c>
@@ -22727,7 +22741,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="15">
         <v>40345</v>
       </c>
@@ -22763,7 +22777,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="15">
         <v>40352</v>
       </c>
@@ -22799,7 +22813,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="15">
         <v>40359</v>
       </c>
@@ -22835,7 +22849,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="15">
         <v>40366</v>
       </c>
@@ -22871,7 +22885,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="15">
         <v>40373</v>
       </c>
@@ -22907,7 +22921,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="15">
         <v>40380</v>
       </c>
@@ -22943,7 +22957,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="15">
         <v>40387</v>
       </c>
@@ -22979,7 +22993,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="15">
         <v>40394</v>
       </c>
@@ -23015,7 +23029,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="15">
         <v>40401</v>
       </c>
@@ -23051,7 +23065,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="15">
         <v>40408</v>
       </c>
@@ -23087,7 +23101,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="15">
         <v>40415</v>
       </c>
@@ -23123,7 +23137,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="15">
         <v>40422</v>
       </c>
@@ -23159,7 +23173,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="15">
         <v>40429</v>
       </c>
@@ -23195,7 +23209,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="15">
         <v>40436</v>
       </c>
@@ -23231,7 +23245,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="15">
         <v>40443</v>
       </c>
@@ -23267,7 +23281,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="15">
         <v>40450</v>
       </c>
@@ -23303,7 +23317,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="15">
         <v>40457</v>
       </c>
@@ -23339,7 +23353,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="15">
         <v>40464</v>
       </c>
@@ -23375,7 +23389,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="15">
         <v>40471</v>
       </c>
@@ -23411,7 +23425,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="15">
         <v>40478</v>
       </c>
@@ -23447,7 +23461,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="15">
         <v>40485</v>
       </c>
@@ -23483,7 +23497,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="15">
         <v>40493</v>
       </c>
@@ -23519,7 +23533,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="15">
         <v>40499</v>
       </c>
@@ -23555,7 +23569,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="15">
         <v>40506</v>
       </c>
@@ -23591,7 +23605,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="15">
         <v>40513</v>
       </c>
@@ -23627,7 +23641,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="15">
         <v>40520</v>
       </c>
@@ -23663,7 +23677,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="15">
         <v>40527</v>
       </c>
@@ -23699,7 +23713,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="15">
         <v>40534</v>
       </c>
@@ -23735,7 +23749,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="15">
         <v>40541</v>
       </c>
@@ -23771,7 +23785,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="15">
         <v>40548</v>
       </c>
@@ -23807,7 +23821,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="15">
         <v>40555</v>
       </c>
@@ -23843,7 +23857,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="15">
         <v>40562</v>
       </c>
@@ -23879,7 +23893,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="15">
         <v>40569</v>
       </c>
@@ -23915,7 +23929,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="15">
         <v>40576</v>
       </c>
@@ -23951,7 +23965,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="15">
         <v>40583</v>
       </c>
@@ -23987,7 +24001,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="15">
         <v>40590</v>
       </c>
@@ -24023,7 +24037,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="15">
         <v>40597</v>
       </c>
@@ -24059,7 +24073,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="15">
         <v>40604</v>
       </c>
@@ -24095,7 +24109,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="15">
         <v>40611</v>
       </c>
@@ -24131,7 +24145,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="15">
         <v>40618</v>
       </c>
@@ -24167,7 +24181,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="15">
         <v>40625</v>
       </c>
@@ -24203,7 +24217,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="15">
         <v>40632</v>
       </c>
@@ -24239,7 +24253,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="15">
         <v>40639</v>
       </c>
@@ -24275,7 +24289,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="15">
         <v>40646</v>
       </c>
@@ -24311,7 +24325,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="15">
         <v>40653</v>
       </c>
@@ -24347,7 +24361,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="15">
         <v>40660</v>
       </c>
@@ -24383,7 +24397,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="15">
         <v>40667</v>
       </c>
@@ -24419,7 +24433,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="15">
         <v>40674</v>
       </c>
@@ -24455,7 +24469,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="15">
         <v>40681</v>
       </c>
@@ -24491,7 +24505,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="15">
         <v>40688</v>
       </c>
@@ -24542,7 +24556,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="15">
         <v>40695</v>
       </c>
@@ -24578,7 +24592,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="15">
         <v>40702</v>
       </c>
@@ -24614,7 +24628,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="15">
         <v>40709</v>
       </c>
@@ -24650,7 +24664,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="15">
         <v>40716</v>
       </c>
@@ -24686,7 +24700,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="15">
         <v>40723</v>
       </c>
@@ -24722,7 +24736,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="15">
         <v>40730</v>
       </c>
@@ -24758,7 +24772,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="15">
         <v>40737</v>
       </c>
@@ -24794,7 +24808,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="15">
         <v>40744</v>
       </c>
@@ -24830,7 +24844,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="15">
         <v>40751</v>
       </c>
@@ -24866,7 +24880,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="15">
         <v>40758</v>
       </c>
@@ -24902,7 +24916,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="15">
         <v>40765</v>
       </c>
@@ -24938,7 +24952,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="15">
         <v>40772</v>
       </c>
@@ -24974,7 +24988,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="15">
         <v>40779</v>
       </c>
@@ -25010,7 +25024,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="15">
         <v>40786</v>
       </c>
@@ -25046,7 +25060,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="15">
         <v>40793</v>
       </c>
@@ -25082,7 +25096,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="15">
         <v>40800</v>
       </c>
@@ -25118,7 +25132,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="15">
         <v>40807</v>
       </c>
@@ -25154,7 +25168,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="15">
         <v>40814</v>
       </c>
@@ -25190,7 +25204,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="15">
         <v>40821</v>
       </c>
@@ -25226,7 +25240,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="15">
         <v>40828</v>
       </c>
@@ -25262,7 +25276,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="15">
         <v>40835</v>
       </c>
@@ -25298,7 +25312,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="15">
         <v>40842</v>
       </c>
@@ -25334,7 +25348,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="15">
         <v>40849</v>
       </c>
@@ -25370,7 +25384,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="15">
         <v>40856</v>
       </c>
@@ -25406,7 +25420,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="15">
         <v>40863</v>
       </c>
@@ -25442,7 +25456,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="15">
         <v>40870</v>
       </c>
@@ -25478,7 +25492,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="15">
         <v>40877</v>
       </c>
@@ -25514,7 +25528,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="15">
         <v>40884</v>
       </c>
@@ -25550,7 +25564,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="15">
         <v>40891</v>
       </c>
@@ -25586,7 +25600,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="15">
         <v>40898</v>
       </c>
@@ -25622,7 +25636,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="15">
         <v>40905</v>
       </c>
@@ -25658,7 +25672,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="15">
         <v>40912</v>
       </c>
@@ -25694,7 +25708,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="15">
         <v>40919</v>
       </c>
@@ -25730,7 +25744,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="15">
         <v>40926</v>
       </c>
@@ -25766,7 +25780,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="15">
         <v>40933</v>
       </c>
@@ -25802,7 +25816,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="15">
         <v>40940</v>
       </c>
@@ -25838,7 +25852,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="15">
         <v>40947</v>
       </c>
@@ -25874,7 +25888,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="15">
         <v>40954</v>
       </c>
@@ -25910,7 +25924,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="15">
         <v>40961</v>
       </c>
@@ -25946,7 +25960,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="15">
         <v>40968</v>
       </c>
@@ -25982,7 +25996,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="15">
         <v>40975</v>
       </c>
@@ -26018,7 +26032,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="15">
         <v>40982</v>
       </c>
@@ -26054,7 +26068,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="15">
         <v>40989</v>
       </c>
@@ -26090,7 +26104,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="15">
         <v>40996</v>
       </c>
@@ -26126,7 +26140,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="15">
         <v>41003</v>
       </c>
@@ -26162,7 +26176,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="15">
         <v>41010</v>
       </c>
@@ -26198,7 +26212,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="15">
         <v>41017</v>
       </c>
@@ -26234,7 +26248,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="15">
         <v>41024</v>
       </c>
@@ -26270,7 +26284,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="15">
         <v>41031</v>
       </c>
@@ -26306,7 +26320,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="15">
         <v>41038</v>
       </c>
@@ -26342,7 +26356,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="15">
         <v>41045</v>
       </c>
@@ -26378,7 +26392,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="15">
         <v>41052</v>
       </c>
@@ -26414,7 +26428,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="15">
         <v>41059</v>
       </c>
@@ -26450,7 +26464,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="15">
         <v>41066</v>
       </c>
@@ -26486,7 +26500,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="15">
         <v>41073</v>
       </c>
@@ -26522,7 +26536,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="15">
         <v>41080</v>
       </c>
@@ -26558,7 +26572,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="15">
         <v>41087</v>
       </c>
@@ -26594,7 +26608,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="15">
         <v>41095</v>
       </c>
@@ -26630,7 +26644,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="15">
         <v>41101</v>
       </c>
@@ -26666,7 +26680,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="15">
         <v>41108</v>
       </c>
@@ -26702,7 +26716,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="15">
         <v>41115</v>
       </c>
@@ -26738,7 +26752,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="15">
         <v>41122</v>
       </c>
@@ -26774,7 +26788,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="15">
         <v>41129</v>
       </c>
@@ -26810,7 +26824,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="15">
         <v>41136</v>
       </c>
@@ -26861,7 +26875,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="15">
         <v>41143</v>
       </c>
@@ -26897,7 +26911,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="15">
         <v>41150</v>
       </c>
@@ -26933,7 +26947,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="15">
         <v>41157</v>
       </c>
@@ -26969,7 +26983,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="15">
         <v>41164</v>
       </c>
@@ -27005,7 +27019,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="15">
         <v>41171</v>
       </c>
@@ -27041,7 +27055,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="15">
         <v>41178</v>
       </c>
@@ -27077,7 +27091,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="15">
         <v>41185</v>
       </c>
@@ -27113,7 +27127,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="15">
         <v>41192</v>
       </c>
@@ -27149,7 +27163,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="15">
         <v>41199</v>
       </c>
@@ -27185,7 +27199,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="15">
         <v>41206</v>
       </c>
@@ -27221,7 +27235,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="15">
         <v>41213</v>
       </c>
@@ -27257,7 +27271,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="15">
         <v>41220</v>
       </c>
@@ -27293,7 +27307,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="15">
         <v>41227</v>
       </c>
@@ -27329,7 +27343,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="15">
         <v>41234</v>
       </c>
@@ -27365,7 +27379,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="15">
         <v>41241</v>
       </c>
@@ -27401,7 +27415,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="15">
         <v>41248</v>
       </c>
@@ -27437,7 +27451,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="15">
         <v>41255</v>
       </c>
@@ -27473,7 +27487,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="15">
         <v>41262</v>
       </c>
@@ -27509,7 +27523,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="15">
         <v>41269</v>
       </c>
@@ -27545,7 +27559,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="15">
         <v>41276</v>
       </c>
@@ -27581,7 +27595,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="15">
         <v>41283</v>
       </c>
@@ -27617,7 +27631,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="15">
         <v>41290</v>
       </c>
@@ -27653,7 +27667,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="15">
         <v>41297</v>
       </c>
@@ -27689,7 +27703,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="15">
         <v>41304</v>
       </c>
@@ -27725,7 +27739,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="15">
         <v>41311</v>
       </c>
@@ -27761,7 +27775,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="15">
         <v>41318</v>
       </c>
@@ -27797,7 +27811,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="15">
         <v>41325</v>
       </c>
@@ -27833,7 +27847,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="15">
         <v>41332</v>
       </c>
@@ -27869,7 +27883,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="15">
         <v>41339</v>
       </c>
@@ -27905,7 +27919,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="15">
         <v>41346</v>
       </c>
@@ -27941,7 +27955,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="15">
         <v>41353</v>
       </c>
@@ -27977,7 +27991,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="15">
         <v>41360</v>
       </c>
@@ -28013,7 +28027,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="15">
         <v>41367</v>
       </c>
@@ -28049,7 +28063,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="15">
         <v>41374</v>
       </c>
@@ -28085,7 +28099,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="15">
         <v>41381</v>
       </c>
@@ -28121,7 +28135,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="15">
         <v>41388</v>
       </c>
@@ -28157,7 +28171,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="15">
         <v>41395</v>
       </c>
@@ -28193,7 +28207,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="15">
         <v>41402</v>
       </c>
@@ -28229,7 +28243,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="15">
         <v>41409</v>
       </c>
@@ -28265,7 +28279,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="15">
         <v>41416</v>
       </c>
@@ -28301,7 +28315,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="15">
         <v>41423</v>
       </c>
@@ -28337,7 +28351,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="15">
         <v>41430</v>
       </c>
@@ -28373,7 +28387,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="15">
         <v>41437</v>
       </c>
@@ -28409,7 +28423,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="15">
         <v>41444</v>
       </c>
@@ -28445,7 +28459,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="15">
         <v>41451</v>
       </c>
@@ -28481,7 +28495,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="15">
         <v>41458</v>
       </c>
@@ -28517,7 +28531,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="15">
         <v>41465</v>
       </c>
@@ -28553,7 +28567,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="15">
         <v>41472</v>
       </c>
@@ -28589,7 +28603,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="15">
         <v>41479</v>
       </c>
@@ -28625,7 +28639,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="15">
         <v>41486</v>
       </c>
@@ -28661,7 +28675,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="15">
         <v>41493</v>
       </c>
@@ -28697,7 +28711,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="15">
         <v>41500</v>
       </c>
@@ -28733,7 +28747,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="15">
         <v>41507</v>
       </c>
@@ -28769,7 +28783,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="15">
         <v>41514</v>
       </c>
@@ -28805,7 +28819,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="15">
         <v>41521</v>
       </c>
@@ -28841,7 +28855,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="15">
         <v>41528</v>
       </c>
@@ -28877,7 +28891,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="15">
         <v>41535</v>
       </c>
@@ -28913,7 +28927,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="15">
         <v>41542</v>
       </c>
@@ -28949,7 +28963,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="15">
         <v>41549</v>
       </c>
@@ -28985,7 +28999,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="15">
         <v>41556</v>
       </c>
@@ -29021,7 +29035,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="15">
         <v>41563</v>
       </c>
@@ -29057,7 +29071,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="15">
         <v>41570</v>
       </c>
@@ -29093,7 +29107,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="15">
         <v>41577</v>
       </c>
@@ -29129,7 +29143,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="15">
         <v>41584</v>
       </c>
@@ -29180,7 +29194,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="15">
         <v>41591</v>
       </c>
@@ -29216,7 +29230,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="15">
         <v>41598</v>
       </c>
@@ -29252,7 +29266,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="15">
         <v>41605</v>
       </c>
@@ -29288,7 +29302,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="15">
         <v>41612</v>
       </c>
@@ -29324,7 +29338,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="15">
         <v>41619</v>
       </c>
@@ -29360,7 +29374,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="15">
         <v>41626</v>
       </c>
@@ -29396,7 +29410,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="15">
         <v>41634</v>
       </c>
@@ -29432,7 +29446,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="15">
         <v>41641</v>
       </c>
@@ -29468,7 +29482,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="15">
         <v>41647</v>
       </c>
@@ -29504,7 +29518,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="15">
         <v>41654</v>
       </c>
@@ -29540,7 +29554,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="15">
         <v>41661</v>
       </c>
@@ -29576,7 +29590,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="15">
         <v>41668</v>
       </c>
@@ -29612,7 +29626,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="15">
         <v>41675</v>
       </c>
@@ -29648,7 +29662,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="15">
         <v>41682</v>
       </c>
@@ -29684,7 +29698,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="15">
         <v>41689</v>
       </c>
@@ -29720,7 +29734,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="15">
         <v>41696</v>
       </c>
@@ -29756,7 +29770,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="15">
         <v>41703</v>
       </c>
@@ -29792,7 +29806,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="15">
         <v>41710</v>
       </c>
@@ -29828,7 +29842,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="15">
         <v>41716</v>
       </c>
@@ -29864,7 +29878,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="15">
         <v>41717</v>
       </c>
@@ -29900,7 +29914,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="15">
         <v>41724</v>
       </c>
@@ -29936,7 +29950,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="15">
         <v>41731</v>
       </c>
@@ -29972,7 +29986,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="15">
         <v>41738</v>
       </c>
@@ -30008,7 +30022,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="15">
         <v>41745</v>
       </c>
@@ -30044,7 +30058,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="15">
         <v>41752</v>
       </c>
@@ -30080,7 +30094,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="15">
         <v>41759</v>
       </c>
@@ -30116,7 +30130,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="15">
         <v>41766</v>
       </c>
@@ -30152,7 +30166,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="15">
         <v>41773</v>
       </c>
@@ -30188,7 +30202,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="15">
         <v>41780</v>
       </c>
@@ -30224,7 +30238,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="15">
         <v>41787</v>
       </c>
@@ -30260,7 +30274,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="15">
         <v>41794</v>
       </c>
@@ -30296,7 +30310,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="15">
         <v>41801</v>
       </c>
@@ -30332,7 +30346,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="15">
         <v>41808</v>
       </c>
@@ -30368,7 +30382,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="15">
         <v>41815</v>
       </c>
@@ -30404,7 +30418,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="15">
         <v>41822</v>
       </c>
@@ -30440,7 +30454,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="15">
         <v>41829</v>
       </c>
@@ -30476,7 +30490,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="15">
         <v>41836</v>
       </c>
@@ -30512,7 +30526,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="15">
         <v>41843</v>
       </c>
@@ -30548,7 +30562,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="15">
         <v>41850</v>
       </c>
@@ -30584,7 +30598,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" s="15">
         <v>41857</v>
       </c>
@@ -30620,7 +30634,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" s="15">
         <v>41864</v>
       </c>
@@ -30656,7 +30670,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="15">
         <v>41871</v>
       </c>
@@ -30692,7 +30706,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" s="15">
         <v>41878</v>
       </c>
@@ -30728,7 +30742,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" s="15">
         <v>41885</v>
       </c>
@@ -30764,7 +30778,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" s="15">
         <v>41892</v>
       </c>
@@ -30800,7 +30814,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" s="15">
         <v>41899</v>
       </c>
@@ -30836,7 +30850,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" s="15">
         <v>41906</v>
       </c>
@@ -30872,7 +30886,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435" s="15">
         <v>41913</v>
       </c>
@@ -30908,7 +30922,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436" s="15">
         <v>41920</v>
       </c>
@@ -30944,7 +30958,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437" s="15">
         <v>41927</v>
       </c>
@@ -30980,7 +30994,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438" s="15">
         <v>41934</v>
       </c>
@@ -31016,7 +31030,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439" s="15">
         <v>41941</v>
       </c>
@@ -31052,7 +31066,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440" s="15">
         <v>41948</v>
       </c>
@@ -31088,7 +31102,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441" s="15">
         <v>41955</v>
       </c>
@@ -31124,7 +31138,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442" s="15">
         <v>41962</v>
       </c>
@@ -31160,7 +31174,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443" s="15">
         <v>41968</v>
       </c>
@@ -31196,7 +31210,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444" s="15">
         <v>41976</v>
       </c>
@@ -31232,7 +31246,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445" s="15">
         <v>41983</v>
       </c>
@@ -31268,7 +31282,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446" s="15">
         <v>41990</v>
       </c>
@@ -31304,7 +31318,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447" s="15">
         <v>41997</v>
       </c>
@@ -31340,7 +31354,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448" s="15">
         <v>42004</v>
       </c>
@@ -31376,7 +31390,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449" s="15">
         <v>42011</v>
       </c>
@@ -31412,7 +31426,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450" s="15">
         <v>42018</v>
       </c>
@@ -31448,7 +31462,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451" s="15">
         <v>42025</v>
       </c>
@@ -31499,7 +31513,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" s="15">
         <v>42032</v>
       </c>
@@ -31535,7 +31549,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" s="15">
         <v>42039</v>
       </c>
@@ -31571,7 +31585,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" s="15">
         <v>42046</v>
       </c>
@@ -31607,7 +31621,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" s="15">
         <v>42053</v>
       </c>
@@ -31643,7 +31657,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456" s="15">
         <v>42060</v>
       </c>
@@ -31679,7 +31693,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457" s="15">
         <v>42067</v>
       </c>
@@ -31715,7 +31729,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458" s="15">
         <v>42074</v>
       </c>
@@ -31751,7 +31765,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459" s="15">
         <v>42088</v>
       </c>
@@ -31787,7 +31801,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460" s="15">
         <v>42095</v>
       </c>
@@ -31823,7 +31837,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461" s="15">
         <v>42102</v>
       </c>
@@ -31859,7 +31873,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462" s="15">
         <v>42109</v>
       </c>
@@ -31895,7 +31909,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463" s="15">
         <v>42116</v>
       </c>
@@ -31931,7 +31945,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464" s="15">
         <v>42123</v>
       </c>
@@ -31967,7 +31981,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465" s="15">
         <v>42130</v>
       </c>
@@ -32003,7 +32017,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466" s="15">
         <v>42137</v>
       </c>
@@ -32039,7 +32053,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467" s="15">
         <v>42144</v>
       </c>
@@ -32075,7 +32089,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" s="15">
         <v>42151</v>
       </c>
@@ -32111,7 +32125,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" s="15">
         <v>42158</v>
       </c>
@@ -32147,7 +32161,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" s="15">
         <v>42165</v>
       </c>
@@ -32183,7 +32197,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471" s="15">
         <v>42172</v>
       </c>
@@ -32219,7 +32233,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" s="15">
         <v>42179</v>
       </c>
@@ -32255,7 +32269,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" s="15">
         <v>42186</v>
       </c>
@@ -32291,7 +32305,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" s="15">
         <v>42193</v>
       </c>
@@ -32327,7 +32341,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475" s="15">
         <v>42200</v>
       </c>
@@ -32363,7 +32377,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" s="15">
         <v>42207</v>
       </c>
@@ -32399,7 +32413,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" s="15">
         <v>42214</v>
       </c>
@@ -32435,7 +32449,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" s="15">
         <v>42221</v>
       </c>
@@ -32471,7 +32485,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479" s="15">
         <v>42228</v>
       </c>
@@ -32507,7 +32521,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" s="15">
         <v>42235</v>
       </c>
@@ -32543,7 +32557,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" s="15">
         <v>42242</v>
       </c>
@@ -32579,7 +32593,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" s="15">
         <v>42249</v>
       </c>
@@ -32615,7 +32629,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" s="15">
         <v>42256</v>
       </c>
@@ -32651,7 +32665,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" s="15">
         <v>42263</v>
       </c>
@@ -32687,7 +32701,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" s="15">
         <v>42270</v>
       </c>
@@ -32723,7 +32737,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" s="15">
         <v>42277</v>
       </c>
@@ -32759,7 +32773,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487" s="15">
         <v>42284</v>
       </c>
@@ -32795,7 +32809,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" s="15">
         <v>42291</v>
       </c>
@@ -32831,7 +32845,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" s="15">
         <v>42298</v>
       </c>
@@ -32867,7 +32881,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" s="15">
         <v>42305</v>
       </c>
@@ -32903,7 +32917,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491" s="15">
         <v>42312</v>
       </c>
@@ -32939,7 +32953,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" s="15">
         <v>42319</v>
       </c>
@@ -32975,7 +32989,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" s="15">
         <v>42326</v>
       </c>
@@ -33011,7 +33025,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="15">
         <v>42333</v>
       </c>
@@ -33047,7 +33061,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" s="15">
         <v>42340</v>
       </c>
@@ -33083,7 +33097,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" s="15">
         <v>42347</v>
       </c>
@@ -33119,7 +33133,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" s="15">
         <v>42354</v>
       </c>
@@ -33155,7 +33169,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" s="15">
         <v>42361</v>
       </c>
@@ -33191,7 +33205,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" s="15">
         <v>42368</v>
       </c>
@@ -33227,7 +33241,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500" s="15">
         <v>42375</v>
       </c>
@@ -33263,7 +33277,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501" s="15">
         <v>42382</v>
       </c>
@@ -33299,7 +33313,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502" s="15">
         <v>42396</v>
       </c>
@@ -33335,7 +33349,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503" s="15">
         <v>42403</v>
       </c>
@@ -33371,7 +33385,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504" s="15">
         <v>42410</v>
       </c>
@@ -33407,7 +33421,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505" s="15">
         <v>42417</v>
       </c>
@@ -33443,7 +33457,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A506" s="15">
         <v>42424</v>
       </c>
@@ -33479,7 +33493,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A507" s="15">
         <v>42431</v>
       </c>
@@ -33515,7 +33529,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A508" s="15">
         <v>42438</v>
       </c>
@@ -33551,7 +33565,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A509" s="15">
         <v>42445</v>
       </c>
@@ -33587,7 +33601,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A510" s="15">
         <v>42452</v>
       </c>
@@ -33623,7 +33637,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A511" s="15">
         <v>42459</v>
       </c>
@@ -33659,7 +33673,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A512" s="15">
         <v>42466</v>
       </c>
@@ -33695,7 +33709,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513" s="15">
         <v>42473</v>
       </c>
@@ -33731,7 +33745,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514" s="15">
         <v>42480</v>
       </c>
@@ -33767,7 +33781,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515" s="15">
         <v>42487</v>
       </c>
@@ -33818,7 +33832,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516" s="15">
         <v>42494</v>
       </c>
@@ -33854,7 +33868,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517" s="15">
         <v>42501</v>
       </c>
@@ -33890,7 +33904,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518" s="15">
         <v>42508</v>
       </c>
@@ -33926,7 +33940,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519" s="15">
         <v>42515</v>
       </c>
@@ -33962,7 +33976,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520" s="15">
         <v>42522</v>
       </c>
@@ -33998,7 +34012,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521" s="15">
         <v>42529</v>
       </c>
@@ -34034,7 +34048,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522" s="15">
         <v>42536</v>
       </c>
@@ -34070,7 +34084,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523" s="15">
         <v>42543</v>
       </c>
@@ -34106,7 +34120,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524" s="15">
         <v>42550</v>
       </c>
@@ -34142,7 +34156,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525" s="15">
         <v>42557</v>
       </c>
@@ -34178,7 +34192,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526" s="15">
         <v>42564</v>
       </c>
@@ -34214,7 +34228,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" s="15">
         <v>42571</v>
       </c>
@@ -34250,7 +34264,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" s="15">
         <v>42578</v>
       </c>
@@ -34286,7 +34300,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" s="15">
         <v>42585</v>
       </c>
@@ -34322,7 +34336,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" s="15">
         <v>42592</v>
       </c>
@@ -34358,7 +34372,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" s="15">
         <v>42599</v>
       </c>
@@ -34394,7 +34408,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" s="15">
         <v>42606</v>
       </c>
@@ -34430,7 +34444,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" s="15">
         <v>42613</v>
       </c>
@@ -34466,7 +34480,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A534" s="15">
         <v>42620</v>
       </c>
@@ -34502,7 +34516,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" s="15">
         <v>42627</v>
       </c>
@@ -34538,7 +34552,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" s="15">
         <v>42634</v>
       </c>
@@ -34574,7 +34588,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" s="15">
         <v>42641</v>
       </c>
@@ -34610,7 +34624,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" s="15">
         <v>42648</v>
       </c>
@@ -34646,7 +34660,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" s="15">
         <v>42655</v>
       </c>
@@ -34682,7 +34696,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" s="15">
         <v>42662</v>
       </c>
@@ -34718,7 +34732,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" s="15">
         <v>42669</v>
       </c>
@@ -34754,7 +34768,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" s="15">
         <v>42676</v>
       </c>
@@ -34790,7 +34804,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" s="15">
         <v>42683</v>
       </c>
@@ -34826,7 +34840,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" s="15">
         <v>42689</v>
       </c>
@@ -34862,7 +34876,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" s="15">
         <v>42697</v>
       </c>
@@ -34898,7 +34912,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A546" s="15">
         <v>42704</v>
       </c>
@@ -34934,7 +34948,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" s="15">
         <v>42711</v>
       </c>
@@ -34970,7 +34984,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" s="15">
         <v>42718</v>
       </c>
@@ -35006,7 +35020,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" s="15">
         <v>42725</v>
       </c>
@@ -35042,7 +35056,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A550" s="15">
         <v>42732</v>
       </c>
@@ -35078,7 +35092,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" s="15">
         <v>42739</v>
       </c>
@@ -35114,7 +35128,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" s="15">
         <v>42746</v>
       </c>
@@ -35150,7 +35164,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" s="15">
         <v>42753</v>
       </c>
@@ -35186,7 +35200,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554" s="15">
         <v>42760</v>
       </c>
@@ -35222,7 +35236,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" s="15">
         <v>42767</v>
       </c>
@@ -35258,7 +35272,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" s="15">
         <v>42774</v>
       </c>
@@ -35294,7 +35308,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" s="15">
         <v>42781</v>
       </c>
@@ -35330,7 +35344,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" s="15">
         <v>42788</v>
       </c>
@@ -35366,7 +35380,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" s="15">
         <v>42795</v>
       </c>
@@ -35402,7 +35416,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" s="15">
         <v>42802</v>
       </c>
@@ -35438,7 +35452,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" s="15">
         <v>42809</v>
       </c>
@@ -35474,7 +35488,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" s="15">
         <v>42816</v>
       </c>
@@ -35510,7 +35524,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" s="15">
         <v>42823</v>
       </c>
@@ -35546,7 +35560,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A564" s="15">
         <v>42830</v>
       </c>
@@ -35582,7 +35596,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" s="15">
         <v>42837</v>
       </c>
@@ -35618,7 +35632,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" s="15">
         <v>42844</v>
       </c>
@@ -35654,7 +35668,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" s="15">
         <v>42851</v>
       </c>
@@ -35690,7 +35704,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" s="15">
         <v>42858</v>
       </c>
@@ -35726,7 +35740,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A569" s="15">
         <v>42865</v>
       </c>
@@ -35762,7 +35776,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" s="15">
         <v>42872</v>
       </c>
@@ -35798,7 +35812,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" s="15">
         <v>42879</v>
       </c>
@@ -35834,7 +35848,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" s="15">
         <v>42886</v>
       </c>
@@ -35870,7 +35884,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A573" s="15">
         <v>42893</v>
       </c>
@@ -35906,7 +35920,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A574" s="15">
         <v>42900</v>
       </c>
@@ -35942,7 +35956,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A575" s="15">
         <v>42907</v>
       </c>
@@ -35978,7 +35992,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A576" s="15">
         <v>42914</v>
       </c>
@@ -36014,7 +36028,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577" s="15">
         <v>42921</v>
       </c>
@@ -36050,7 +36064,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A578" s="15">
         <v>42928</v>
       </c>
@@ -36086,7 +36100,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A579" s="15">
         <v>42935</v>
       </c>
@@ -36137,7 +36151,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A580" s="15">
         <v>42942</v>
       </c>
@@ -36173,7 +36187,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A581" s="15">
         <v>42949</v>
       </c>
@@ -36209,7 +36223,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A582" s="15">
         <v>42956</v>
       </c>
@@ -36245,7 +36259,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A583" s="15">
         <v>42963</v>
       </c>
@@ -36281,7 +36295,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A584" s="15">
         <v>42970</v>
       </c>
@@ -36317,7 +36331,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A585" s="15">
         <v>42977</v>
       </c>
@@ -36353,7 +36367,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A586" s="15">
         <v>42984</v>
       </c>
@@ -36389,7 +36403,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587" s="15">
         <v>42991</v>
       </c>
@@ -36425,7 +36439,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A588" s="15">
         <v>42998</v>
       </c>
@@ -36461,7 +36475,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A589" s="15">
         <v>43005</v>
       </c>
@@ -36497,7 +36511,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A590" s="15">
         <v>43012</v>
       </c>
@@ -36533,7 +36547,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A591" s="15">
         <v>43019</v>
       </c>
@@ -36569,7 +36583,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A592" s="15">
         <v>43026</v>
       </c>
@@ -36605,7 +36619,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A593" s="15">
         <v>43033</v>
       </c>
@@ -36641,7 +36655,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A594" s="15">
         <v>43040</v>
       </c>
@@ -36677,7 +36691,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A595" s="15">
         <v>43047</v>
       </c>
@@ -36713,7 +36727,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A596" s="15">
         <v>43054</v>
       </c>
@@ -36749,7 +36763,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" s="15">
         <v>43061</v>
       </c>
@@ -36785,7 +36799,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" s="15">
         <v>43068</v>
       </c>
@@ -36821,7 +36835,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" s="15">
         <v>43075</v>
       </c>
@@ -36857,7 +36871,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A600" s="15">
         <v>43082</v>
       </c>
@@ -36893,7 +36907,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" s="15">
         <v>43089</v>
       </c>
@@ -36929,7 +36943,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" s="15">
         <v>43096</v>
       </c>
@@ -36965,7 +36979,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" s="15">
         <v>43103</v>
       </c>
@@ -37001,7 +37015,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" s="15">
         <v>43110</v>
       </c>
@@ -37037,7 +37051,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A605" s="15">
         <v>43117</v>
       </c>
@@ -37073,7 +37087,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A606" s="15">
         <v>43124</v>
       </c>
@@ -37109,7 +37123,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A607" s="15">
         <v>43131</v>
       </c>
@@ -37145,7 +37159,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A608" s="15">
         <v>43138</v>
       </c>
@@ -37181,7 +37195,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A609" s="15">
         <v>43145</v>
       </c>
@@ -37217,7 +37231,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610" s="15">
         <v>43152</v>
       </c>
@@ -37253,7 +37267,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A611" s="15">
         <v>43159</v>
       </c>
@@ -37289,7 +37303,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A612" s="15">
         <v>43166</v>
       </c>
@@ -37325,7 +37339,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613" s="15">
         <v>43173</v>
       </c>
@@ -37361,7 +37375,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A614" s="15">
         <v>43180</v>
       </c>
@@ -37397,7 +37411,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A615" s="15">
         <v>43187</v>
       </c>
@@ -37433,7 +37447,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A616" s="15">
         <v>43194</v>
       </c>
@@ -37469,7 +37483,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A617" s="15">
         <v>43201</v>
       </c>
@@ -37505,7 +37519,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A618" s="15">
         <v>43208</v>
       </c>
@@ -37541,7 +37555,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A619" s="15">
         <v>43215</v>
       </c>
@@ -37577,7 +37591,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A620" s="15">
         <v>43222</v>
       </c>
@@ -37613,7 +37627,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A621" s="15">
         <v>43229</v>
       </c>
@@ -37649,7 +37663,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A622" s="15">
         <v>43236</v>
       </c>
@@ -37685,7 +37699,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" s="15">
         <v>43243</v>
       </c>
@@ -37721,7 +37735,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" s="15">
         <v>43250</v>
       </c>
@@ -37757,7 +37771,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" s="15">
         <v>43257</v>
       </c>
@@ -37793,7 +37807,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" s="15">
         <v>43264</v>
       </c>
@@ -37829,7 +37843,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" s="15">
         <v>43271</v>
       </c>
@@ -37865,7 +37879,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" s="15">
         <v>43278</v>
       </c>
@@ -37901,7 +37915,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" s="15">
         <v>43285</v>
       </c>
@@ -37937,7 +37951,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" s="15">
         <v>43292</v>
       </c>
@@ -37973,7 +37987,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A631" s="15">
         <v>43299</v>
       </c>
@@ -38009,7 +38023,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" s="15">
         <v>43306</v>
       </c>
@@ -38045,7 +38059,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" s="15">
         <v>43313</v>
       </c>
@@ -38081,7 +38095,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" s="15">
         <v>43320</v>
       </c>
@@ -38117,7 +38131,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" s="15">
         <v>43327</v>
       </c>
@@ -38153,7 +38167,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" s="15">
         <v>43334</v>
       </c>
@@ -38189,7 +38203,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" s="15">
         <v>43341</v>
       </c>
@@ -38225,7 +38239,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" s="15">
         <v>43348</v>
       </c>
@@ -38261,7 +38275,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A639" s="15">
         <v>43355</v>
       </c>
@@ -38297,7 +38311,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A640" s="15">
         <v>43362</v>
       </c>
@@ -38333,7 +38347,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A641" s="15">
         <v>43369</v>
       </c>
@@ -38369,7 +38383,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A642" s="15">
         <v>43376</v>
       </c>
@@ -38405,7 +38419,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A643" s="15">
         <v>43383</v>
       </c>
@@ -38456,7 +38470,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A644" s="15">
         <v>43391</v>
       </c>
@@ -38492,7 +38506,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A645" s="15">
         <v>43397</v>
       </c>
@@ -38528,7 +38542,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646" s="15">
         <v>43404</v>
       </c>
@@ -38564,7 +38578,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A647" s="15">
         <v>43411</v>
       </c>
@@ -38600,7 +38614,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A648" s="15">
         <v>43418</v>
       </c>
@@ -38636,7 +38650,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649" s="15">
         <v>43425</v>
       </c>
@@ -38672,7 +38686,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A650" s="15">
         <v>43432</v>
       </c>
@@ -38708,7 +38722,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A651" s="15">
         <v>43439</v>
       </c>
@@ -38744,7 +38758,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A652" s="15">
         <v>43446</v>
       </c>
@@ -38780,7 +38794,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A653" s="15">
         <v>43453</v>
       </c>
@@ -38816,7 +38830,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A654" s="15">
         <v>43460</v>
       </c>
@@ -38852,7 +38866,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A655" s="15">
         <v>43467</v>
       </c>
@@ -38888,7 +38902,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A656" s="15">
         <v>43474</v>
       </c>
@@ -38924,7 +38938,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A657" s="15">
         <v>43481</v>
       </c>
@@ -38960,7 +38974,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A658" s="15">
         <v>43488</v>
       </c>
@@ -38996,7 +39010,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A659" s="15">
         <v>43495</v>
       </c>
@@ -39032,7 +39046,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A660" s="15">
         <v>43502</v>
       </c>
@@ -39068,7 +39082,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A661" s="15">
         <v>43509</v>
       </c>
@@ -39104,7 +39118,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A662" s="15">
         <v>43516</v>
       </c>
@@ -39140,7 +39154,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A663" s="15">
         <v>43523</v>
       </c>
@@ -39176,7 +39190,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A664" s="15">
         <v>43530</v>
       </c>
@@ -39212,7 +39226,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A665" s="15">
         <v>43537</v>
       </c>
@@ -39248,7 +39262,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A666" s="15">
         <v>43544</v>
       </c>
@@ -39284,7 +39298,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A667" s="15">
         <v>43551</v>
       </c>
@@ -39320,7 +39334,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A668" s="15">
         <v>43558</v>
       </c>
@@ -39356,7 +39370,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A669" s="15">
         <v>43565</v>
       </c>
@@ -39392,7 +39406,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A670" s="15">
         <v>43572</v>
       </c>
@@ -39428,7 +39442,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A671" s="15">
         <v>43579</v>
       </c>
@@ -39464,7 +39478,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A672" s="15">
         <v>43586</v>
       </c>
@@ -39500,7 +39514,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A673" s="15">
         <v>43593</v>
       </c>
@@ -39536,7 +39550,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A674" s="15">
         <v>43600</v>
       </c>
@@ -39572,7 +39586,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A675" s="15">
         <v>43607</v>
       </c>
@@ -39608,7 +39622,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A676" s="15">
         <v>43614</v>
       </c>
@@ -39644,7 +39658,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677" s="15">
         <v>43621</v>
       </c>
@@ -39680,7 +39694,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678" s="15">
         <v>43628</v>
       </c>
@@ -39716,7 +39730,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679" s="15">
         <v>43635</v>
       </c>
@@ -39752,7 +39766,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680" s="15">
         <v>43642</v>
       </c>
@@ -39788,7 +39802,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681" s="15">
         <v>43649</v>
       </c>
@@ -39824,7 +39838,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" s="15">
         <v>43656</v>
       </c>
@@ -39860,7 +39874,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" s="15">
         <v>43663</v>
       </c>
@@ -39896,7 +39910,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" s="15">
         <v>43670</v>
       </c>
@@ -39932,7 +39946,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" s="15">
         <v>43677</v>
       </c>
@@ -39968,7 +39982,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" s="15">
         <v>43684</v>
       </c>
@@ -40004,7 +40018,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A687" s="15">
         <v>43691</v>
       </c>
@@ -40040,7 +40054,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688" s="15">
         <v>43698</v>
       </c>
@@ -40076,7 +40090,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A689" s="15">
         <v>43705</v>
       </c>
@@ -40112,7 +40126,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A690" s="15">
         <v>43712</v>
       </c>
@@ -40148,7 +40162,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A691" s="15">
         <v>43719</v>
       </c>
@@ -40184,7 +40198,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A692" s="15">
         <v>43726</v>
       </c>
@@ -40220,7 +40234,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A693" s="15">
         <v>43733</v>
       </c>
@@ -40256,7 +40270,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A694" s="15">
         <v>43740</v>
       </c>
@@ -40292,7 +40306,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A695" s="15">
         <v>43747</v>
       </c>
@@ -40328,7 +40342,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A696" s="15">
         <v>43754</v>
       </c>
@@ -40364,7 +40378,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A697" s="15">
         <v>43761</v>
       </c>
@@ -40400,7 +40414,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A698" s="15">
         <v>43768</v>
       </c>
@@ -40436,7 +40450,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A699" s="15">
         <v>43775</v>
       </c>
@@ -40472,7 +40486,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A700" s="15">
         <v>43782</v>
       </c>
@@ -40508,7 +40522,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A701" s="15">
         <v>43789</v>
       </c>
@@ -40544,7 +40558,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" s="15">
         <v>43796</v>
       </c>
@@ -40580,7 +40594,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" s="15">
         <v>43803</v>
       </c>
@@ -40616,7 +40630,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" s="15">
         <v>43810</v>
       </c>
@@ -40652,7 +40666,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" s="15">
         <v>43817</v>
       </c>
@@ -40688,7 +40702,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" s="15">
         <v>43824</v>
       </c>
@@ -40724,7 +40738,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" s="15">
         <v>43831</v>
       </c>
@@ -40775,7 +40789,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" s="15">
         <v>43838</v>
       </c>
@@ -40811,7 +40825,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A709" s="15">
         <v>43845</v>
       </c>
@@ -40847,7 +40861,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A710" s="15">
         <v>43852</v>
       </c>
@@ -40883,7 +40897,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A711" s="15">
         <v>43859</v>
       </c>
@@ -40919,7 +40933,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A712" s="15">
         <v>43866</v>
       </c>
@@ -40955,7 +40969,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A713" s="15">
         <v>43873</v>
       </c>
@@ -40991,7 +41005,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A714" s="15">
         <v>43880</v>
       </c>
@@ -41027,7 +41041,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A715" s="15">
         <v>43887</v>
       </c>
@@ -41063,7 +41077,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A716" s="15">
         <v>43894</v>
       </c>
@@ -41099,7 +41113,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A717" s="15">
         <v>43901</v>
       </c>
@@ -41135,7 +41149,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A718" s="15">
         <v>43908</v>
       </c>
@@ -41171,7 +41185,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A719" s="15">
         <v>43915</v>
       </c>
@@ -41207,7 +41221,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A720" s="15">
         <v>43922</v>
       </c>
@@ -41243,7 +41257,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A721" s="15">
         <v>43929</v>
       </c>
@@ -41279,7 +41293,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A722" s="15">
         <v>43936</v>
       </c>
@@ -41315,7 +41329,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A723" s="15">
         <v>43943</v>
       </c>
@@ -41351,7 +41365,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A724" s="15">
         <v>43950</v>
       </c>
@@ -41387,7 +41401,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A725" s="15">
         <v>43957</v>
       </c>
@@ -41423,7 +41437,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A726" s="15">
         <v>43964</v>
       </c>
@@ -41459,7 +41473,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A727" s="15">
         <v>43971</v>
       </c>
@@ -41495,7 +41509,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A728" s="15">
         <v>43978</v>
       </c>
@@ -41531,7 +41545,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A729" s="15">
         <v>43985</v>
       </c>
@@ -41567,7 +41581,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A730" s="15">
         <v>43992</v>
       </c>
@@ -41603,7 +41617,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A731" s="15">
         <v>43999</v>
       </c>
@@ -41639,7 +41653,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A732" s="15">
         <v>44006</v>
       </c>
@@ -41675,7 +41689,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A733" s="15">
         <v>44013</v>
       </c>
@@ -41711,7 +41725,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A734" s="15">
         <v>44020</v>
       </c>
@@ -41747,7 +41761,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A735" s="15">
         <v>44027</v>
       </c>
@@ -41783,7 +41797,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A736" s="15">
         <v>44034</v>
       </c>
@@ -41819,7 +41833,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A737" s="15">
         <v>44041</v>
       </c>
@@ -41855,7 +41869,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A738" s="15">
         <v>44048</v>
       </c>
@@ -41891,7 +41905,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A739" s="15">
         <v>44055</v>
       </c>
@@ -41927,7 +41941,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A740" s="15">
         <v>44062</v>
       </c>
@@ -41963,7 +41977,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A741" s="15">
         <v>44069</v>
       </c>
@@ -41999,7 +42013,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A742" s="15">
         <v>44076</v>
       </c>
@@ -42035,7 +42049,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A743" s="15">
         <v>44083</v>
       </c>
@@ -42071,7 +42085,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A744" s="15">
         <v>44090</v>
       </c>
@@ -42107,7 +42121,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A745" s="15">
         <v>44097</v>
       </c>
@@ -42143,7 +42157,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A746" s="15">
         <v>44104</v>
       </c>
@@ -42179,7 +42193,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A747" s="15">
         <v>44111</v>
       </c>
@@ -42215,7 +42229,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A748" s="15">
         <v>44118</v>
       </c>
@@ -42251,7 +42265,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A749" s="15">
         <v>44125</v>
       </c>
@@ -42287,7 +42301,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A750" s="15">
         <v>44132</v>
       </c>
@@ -42323,7 +42337,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A751" s="15">
         <v>44139</v>
       </c>
@@ -42359,7 +42373,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A752" s="15">
         <v>44146</v>
       </c>
@@ -42395,7 +42409,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A753" s="15">
         <v>44153</v>
       </c>
@@ -42431,7 +42445,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A754" s="15">
         <v>44160</v>
       </c>
@@ -42467,7 +42481,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A755" s="15">
         <v>44167</v>
       </c>
@@ -42503,7 +42517,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A756" s="15">
         <v>44174</v>
       </c>
@@ -42539,7 +42553,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757" s="15">
         <v>44181</v>
       </c>
@@ -42575,7 +42589,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758" s="15">
         <v>44188</v>
       </c>
@@ -42611,7 +42625,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759" s="15">
         <v>44195</v>
       </c>
@@ -42647,7 +42661,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A760" s="15">
         <v>44202</v>
       </c>
@@ -42683,7 +42697,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A761" s="15">
         <v>44209</v>
       </c>
@@ -42719,7 +42733,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762" s="15">
         <v>44216</v>
       </c>
@@ -42755,7 +42769,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763" s="15">
         <v>44223</v>
       </c>
@@ -42791,7 +42805,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A764" s="15">
         <v>44230</v>
       </c>
@@ -42827,7 +42841,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A765" s="15">
         <v>44237</v>
       </c>
@@ -42863,7 +42877,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A766" s="15">
         <v>44244</v>
       </c>
@@ -42899,7 +42913,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767" s="15">
         <v>44251</v>
       </c>
@@ -42935,7 +42949,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A768" s="15">
         <v>44258</v>
       </c>
@@ -42971,7 +42985,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A769" s="15">
         <v>44265</v>
       </c>
@@ -43007,7 +43021,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A770" s="15">
         <v>44272</v>
       </c>
@@ -43043,7 +43057,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A771" s="15">
         <v>44279</v>
       </c>
@@ -43094,7 +43108,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A772" s="15">
         <v>44286</v>
       </c>
@@ -43130,7 +43144,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A773" s="15">
         <v>44293</v>
       </c>
@@ -43166,7 +43180,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A774" s="15">
         <v>44300</v>
       </c>
@@ -43202,7 +43216,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A775" s="15">
         <v>44307</v>
       </c>
@@ -43238,7 +43252,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A776" s="15">
         <v>44314</v>
       </c>
@@ -43274,7 +43288,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A777" s="15">
         <v>44321</v>
       </c>
@@ -43310,7 +43324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A778" s="15">
         <v>44328</v>
       </c>
@@ -43346,7 +43360,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A779" s="15">
         <v>44335</v>
       </c>
@@ -43382,7 +43396,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A780" s="15">
         <v>44342</v>
       </c>
@@ -43418,7 +43432,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A781" s="15">
         <v>44349</v>
       </c>
@@ -43454,7 +43468,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A782" s="15">
         <v>44356</v>
       </c>
@@ -43490,7 +43504,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A783" s="15">
         <v>44363</v>
       </c>
@@ -43526,7 +43540,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A784" s="15">
         <v>44370</v>
       </c>
@@ -43562,7 +43576,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A785" s="15">
         <v>44377</v>
       </c>
@@ -43598,7 +43612,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A786" s="15">
         <v>44384</v>
       </c>
@@ -43634,7 +43648,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A787" s="15">
         <v>44391</v>
       </c>
@@ -43670,7 +43684,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A788" s="15">
         <v>44398</v>
       </c>
@@ -43706,7 +43720,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A789" s="15">
         <v>44405</v>
       </c>
@@ -43742,7 +43756,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A790" s="15">
         <v>44412</v>
       </c>
@@ -43778,7 +43792,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A791" s="15">
         <v>44419</v>
       </c>
@@ -43814,7 +43828,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A792" s="15">
         <v>44426</v>
       </c>
@@ -43850,7 +43864,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A793" s="15">
         <v>44433</v>
       </c>
@@ -43886,7 +43900,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A794" s="15">
         <v>44440</v>
       </c>
@@ -43922,7 +43936,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A795" s="15">
         <v>44447</v>
       </c>
@@ -43958,7 +43972,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A796" s="15">
         <v>44454</v>
       </c>
@@ -43994,7 +44008,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A797" s="15">
         <v>44461</v>
       </c>
@@ -44030,7 +44044,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A798" s="15">
         <v>44468</v>
       </c>
@@ -44066,7 +44080,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A799" s="15">
         <v>44475</v>
       </c>
@@ -44102,7 +44116,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A800" s="15">
         <v>44482</v>
       </c>
@@ -44138,7 +44152,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A801" s="15">
         <v>44489</v>
       </c>
@@ -44174,7 +44188,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A802" s="15">
         <v>44496</v>
       </c>
@@ -44210,7 +44224,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A803" s="15">
         <v>44503</v>
       </c>
@@ -44246,7 +44260,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A804" s="15">
         <v>44510</v>
       </c>
@@ -44282,7 +44296,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A805" s="15">
         <v>44517</v>
       </c>
@@ -44318,7 +44332,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A806" s="15">
         <v>44524</v>
       </c>
@@ -44354,7 +44368,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A807" s="15">
         <v>44531</v>
       </c>
@@ -44390,7 +44404,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A808" s="15">
         <v>44538</v>
       </c>
@@ -44426,7 +44440,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A809" s="15">
         <v>44545</v>
       </c>
@@ -44462,7 +44476,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A810" s="15">
         <v>44552</v>
       </c>
@@ -44498,7 +44512,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A811" s="15">
         <v>44559</v>
       </c>
@@ -44534,7 +44548,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A812" s="15">
         <v>44566</v>
       </c>
@@ -44570,7 +44584,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A813" s="15">
         <v>44573</v>
       </c>
@@ -44606,7 +44620,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A814" s="15">
         <v>44580</v>
       </c>
@@ -44642,7 +44656,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A815" s="15">
         <v>44587</v>
       </c>
@@ -44678,7 +44692,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A816" s="15">
         <v>44594</v>
       </c>
@@ -44714,7 +44728,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11">
+    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A817" s="15">
         <v>44601</v>
       </c>
@@ -44750,7 +44764,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11">
+    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A818" s="15">
         <v>44608</v>
       </c>
@@ -44786,7 +44800,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11">
+    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A819" s="15">
         <v>44615</v>
       </c>
@@ -44822,7 +44836,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11">
+    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A820" s="15">
         <v>44622</v>
       </c>
@@ -44858,7 +44872,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11">
+    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A821" s="15">
         <v>44629</v>
       </c>
@@ -44894,7 +44908,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11">
+    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A822" s="15">
         <v>44636</v>
       </c>
@@ -44930,7 +44944,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A823" s="15">
         <v>44643</v>
       </c>
@@ -44966,7 +44980,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A824" s="15">
         <v>44650</v>
       </c>
@@ -45002,7 +45016,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A825" s="15">
         <v>44657</v>
       </c>
@@ -45038,7 +45052,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A826" s="15">
         <v>44664</v>
       </c>
@@ -45074,7 +45088,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A827" s="15">
         <v>44671</v>
       </c>
@@ -45110,7 +45124,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A828" s="15">
         <v>44678</v>
       </c>
@@ -45146,7 +45160,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A829" s="15">
         <v>44685</v>
       </c>
@@ -45182,7 +45196,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A830" s="15">
         <v>44692</v>
       </c>
@@ -45218,7 +45232,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A831" s="15">
         <v>44699</v>
       </c>
@@ -45254,7 +45268,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A832" s="15">
         <v>44706</v>
       </c>
@@ -45290,7 +45304,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11">
+    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A833" s="15">
         <v>44713</v>
       </c>
@@ -45326,7 +45340,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11">
+    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A834" s="15">
         <v>44720</v>
       </c>
@@ -45362,7 +45376,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11">
+    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A835" s="15">
         <v>44727</v>
       </c>
@@ -45413,7 +45427,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11">
+    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A836" s="15">
         <v>44734</v>
       </c>
@@ -45449,7 +45463,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11">
+    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A837" s="15">
         <v>44741</v>
       </c>
@@ -45485,7 +45499,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11">
+    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A838" s="15">
         <v>44748</v>
       </c>
@@ -45521,7 +45535,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11">
+    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A839" s="15">
         <v>44755</v>
       </c>
@@ -45557,7 +45571,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11">
+    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A840" s="15">
         <v>44762</v>
       </c>
@@ -45593,7 +45607,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11">
+    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" s="15">
         <v>44769</v>
       </c>
@@ -45629,7 +45643,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11">
+    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" s="15">
         <v>44776</v>
       </c>
@@ -45665,7 +45679,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11">
+    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" s="15">
         <v>44783</v>
       </c>
@@ -45701,7 +45715,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11">
+    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A844" s="15">
         <v>44790</v>
       </c>
@@ -45737,7 +45751,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11">
+    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A845" s="15">
         <v>44797</v>
       </c>
@@ -45773,7 +45787,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11">
+    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A846" s="15">
         <v>44804</v>
       </c>
@@ -45809,7 +45823,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11">
+    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A847" s="15">
         <v>44811</v>
       </c>
@@ -45845,7 +45859,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11">
+    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A848" s="15">
         <v>44818</v>
       </c>
@@ -45881,7 +45895,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11">
+    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A849" s="15">
         <v>44825</v>
       </c>
@@ -45917,7 +45931,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11">
+    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A850" s="15">
         <v>44832</v>
       </c>
@@ -45953,7 +45967,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11">
+    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A851" s="15">
         <v>44839</v>
       </c>
@@ -45989,7 +46003,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11">
+    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A852" s="15">
         <v>44846</v>
       </c>
@@ -46025,7 +46039,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11">
+    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A853" s="15">
         <v>44853</v>
       </c>
@@ -46061,7 +46075,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11">
+    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A854" s="15">
         <v>44860</v>
       </c>
@@ -46097,7 +46111,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11">
+    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A855" s="15">
         <v>44867</v>
       </c>
@@ -46133,7 +46147,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11">
+    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A856" s="15">
         <v>44874</v>
       </c>
@@ -46169,7 +46183,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11">
+    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A857" s="15">
         <v>44881</v>
       </c>
@@ -46205,7 +46219,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11">
+    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A858" s="15">
         <v>44888</v>
       </c>
@@ -46241,7 +46255,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11">
+    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A859" s="15">
         <v>44895</v>
       </c>
@@ -46277,7 +46291,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11">
+    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A860" s="15">
         <v>44902</v>
       </c>
@@ -46313,7 +46327,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11">
+    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A861" s="15">
         <v>44909</v>
       </c>
@@ -46349,7 +46363,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11">
+    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A862" s="15">
         <v>44916</v>
       </c>
@@ -46385,7 +46399,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11">
+    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A863" s="15">
         <v>44923</v>
       </c>
@@ -46421,7 +46435,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11">
+    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A864" s="15">
         <v>44930</v>
       </c>
@@ -46457,7 +46471,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11">
+    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A865" s="15">
         <v>44937</v>
       </c>
@@ -46493,7 +46507,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11">
+    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A866" s="15">
         <v>44944</v>
       </c>
@@ -46529,7 +46543,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11">
+    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A867" s="15">
         <v>44951</v>
       </c>
@@ -46565,7 +46579,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11">
+    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A868" s="15">
         <v>44958</v>
       </c>
@@ -46601,7 +46615,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11">
+    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A869" s="15">
         <v>44965</v>
       </c>
@@ -46637,7 +46651,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11">
+    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A870" s="15">
         <v>44972</v>
       </c>
@@ -46673,7 +46687,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11">
+    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A871" s="15">
         <v>44979</v>
       </c>
@@ -46709,7 +46723,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11">
+    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" s="15">
         <v>44986</v>
       </c>
@@ -46745,7 +46759,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11">
+    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" s="15">
         <v>44993</v>
       </c>
@@ -46781,7 +46795,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11">
+    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" s="15">
         <v>45000</v>
       </c>
@@ -46817,7 +46831,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11">
+    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A875" s="15">
         <v>45007</v>
       </c>
@@ -46853,7 +46867,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11">
+    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" s="15">
         <v>45014</v>
       </c>
@@ -46889,7 +46903,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11">
+    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" s="15">
         <v>45021</v>
       </c>
@@ -46925,7 +46939,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11">
+    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" s="15">
         <v>45028</v>
       </c>
@@ -46961,7 +46975,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11">
+    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A879" s="15">
         <v>45035</v>
       </c>
@@ -46997,7 +47011,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11">
+    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" s="15">
         <v>45042</v>
       </c>
@@ -47033,7 +47047,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11">
+    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" s="15">
         <v>45049</v>
       </c>
@@ -47069,7 +47083,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11">
+    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" s="15">
         <v>45056</v>
       </c>
@@ -47105,7 +47119,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11">
+    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A883" s="15">
         <v>45063</v>
       </c>
@@ -47141,7 +47155,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" s="15">
         <v>45070</v>
       </c>
@@ -47177,7 +47191,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" s="15">
         <v>45077</v>
       </c>
@@ -47213,7 +47227,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" s="15">
         <v>45084</v>
       </c>
@@ -47249,7 +47263,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11">
+    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A887" s="15">
         <v>45091</v>
       </c>
@@ -47285,7 +47299,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11">
+    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" s="15">
         <v>45098</v>
       </c>
@@ -47321,7 +47335,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11">
+    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" s="15">
         <v>45105</v>
       </c>
@@ -47357,7 +47371,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11">
+    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" s="15">
         <v>45112</v>
       </c>
@@ -47393,7 +47407,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A891" s="15">
         <v>45119</v>
       </c>
@@ -47429,7 +47443,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11">
+    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" s="15">
         <v>45126</v>
       </c>
@@ -47465,7 +47479,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11">
+    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" s="15">
         <v>45133</v>
       </c>
@@ -47501,7 +47515,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11">
+    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" s="15">
         <v>45140</v>
       </c>
@@ -47537,7 +47551,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11">
+    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A895" s="15">
         <v>45147</v>
       </c>
@@ -47573,7 +47587,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11">
+    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A896" s="15">
         <v>45154</v>
       </c>
@@ -47609,7 +47623,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11">
+    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A897" s="15">
         <v>45161</v>
       </c>
@@ -47645,7 +47659,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A898" s="15">
         <v>45168</v>
       </c>
@@ -47681,7 +47695,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11">
+    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A899" s="15">
         <v>45175</v>
       </c>
@@ -47732,7 +47746,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11">
+    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A900" s="15">
         <v>45182</v>
       </c>
@@ -47768,7 +47782,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11">
+    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A901" s="15">
         <v>45189</v>
       </c>
@@ -47804,7 +47818,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11">
+    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A902" s="15">
         <v>45196</v>
       </c>
@@ -47840,7 +47854,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11">
+    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A903" s="15">
         <v>45203</v>
       </c>
@@ -47876,7 +47890,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11">
+    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A904" s="15">
         <v>45210</v>
       </c>
@@ -47912,7 +47926,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11">
+    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A905" s="15">
         <v>45217</v>
       </c>
@@ -47948,7 +47962,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11">
+    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A906" s="15">
         <v>45224</v>
       </c>
@@ -47984,7 +47998,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11">
+    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A907" s="15">
         <v>45231</v>
       </c>
@@ -48020,7 +48034,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11">
+    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A908" s="15">
         <v>45238</v>
       </c>
@@ -48056,7 +48070,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11">
+    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A909" s="15">
         <v>45245</v>
       </c>
@@ -48092,7 +48106,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11">
+    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A910" s="15">
         <v>45252</v>
       </c>
@@ -48128,7 +48142,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11">
+    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A911" s="15">
         <v>45259</v>
       </c>
@@ -48164,7 +48178,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11">
+    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A912" s="15">
         <v>45266</v>
       </c>
@@ -48200,7 +48214,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11">
+    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A913" s="15">
         <v>45273</v>
       </c>
@@ -48236,7 +48250,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11">
+    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A914" s="15">
         <v>45280</v>
       </c>
@@ -48272,7 +48286,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11">
+    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A915" s="15">
         <v>45287</v>
       </c>
@@ -48308,7 +48322,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11">
+    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A916" s="15">
         <v>45294</v>
       </c>
@@ -48344,7 +48358,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11">
+    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A917" s="15">
         <v>45301</v>
       </c>
@@ -48380,7 +48394,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11">
+    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A918" s="15">
         <v>45308</v>
       </c>
@@ -48416,7 +48430,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11">
+    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A919" s="15">
         <v>45315</v>
       </c>
@@ -48452,7 +48466,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11">
+    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A920" s="15">
         <v>45322</v>
       </c>
@@ -48488,7 +48502,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11">
+    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A921" s="15">
         <v>45329</v>
       </c>
@@ -48524,7 +48538,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11">
+    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A922" s="15">
         <v>45336</v>
       </c>
@@ -48560,7 +48574,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11">
+    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A923" s="15">
         <v>45343</v>
       </c>
@@ -48596,7 +48610,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11">
+    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A924" s="15">
         <v>45350</v>
       </c>
@@ -48632,7 +48646,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11">
+    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A925" s="15">
         <v>45357</v>
       </c>
@@ -48668,7 +48682,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11">
+    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A926" s="15">
         <v>45364</v>
       </c>
@@ -48704,7 +48718,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11">
+    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A927" s="15">
         <v>45371</v>
       </c>
@@ -48740,7 +48754,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11">
+    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A928" s="15">
         <v>45378</v>
       </c>
@@ -48776,7 +48790,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11">
+    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A929" s="15">
         <v>45385</v>
       </c>
@@ -48812,7 +48826,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11">
+    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A930" s="15">
         <v>45392</v>
       </c>
@@ -48848,7 +48862,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11">
+    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A931" s="15">
         <v>45399</v>
       </c>
@@ -48884,7 +48898,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11">
+    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A932" s="15">
         <v>45406</v>
       </c>
@@ -48920,7 +48934,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11">
+    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A933" s="15">
         <v>45413</v>
       </c>
@@ -48956,7 +48970,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11">
+    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A934" s="15">
         <v>45420</v>
       </c>
@@ -48992,7 +49006,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11">
+    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A935" s="15">
         <v>45427</v>
       </c>
@@ -49028,7 +49042,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11">
+    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A936" s="15">
         <v>45434</v>
       </c>
@@ -49064,7 +49078,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11">
+    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A937" s="15">
         <v>45441</v>
       </c>
@@ -49100,7 +49114,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11">
+    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A938" s="15">
         <v>45448</v>
       </c>
@@ -49136,7 +49150,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11">
+    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A939" s="15">
         <v>45455</v>
       </c>
@@ -49172,7 +49186,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11">
+    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A940" s="15">
         <v>45462</v>
       </c>
@@ -49208,7 +49222,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11">
+    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A941" s="15">
         <v>45469</v>
       </c>
@@ -49244,7 +49258,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11">
+    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A942" s="15">
         <v>45476</v>
       </c>
@@ -49280,7 +49294,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11">
+    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A943" s="15">
         <v>45483</v>
       </c>
@@ -49316,7 +49330,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11">
+    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A944" s="15">
         <v>45490</v>
       </c>
@@ -49352,7 +49366,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11">
+    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A945" s="15">
         <v>45497</v>
       </c>
@@ -49388,7 +49402,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11">
+    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A946" s="15">
         <v>45504</v>
       </c>
@@ -49424,7 +49438,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11">
+    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A947" s="15">
         <v>45511</v>
       </c>
@@ -49460,7 +49474,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11">
+    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A948" s="15">
         <v>45518</v>
       </c>
@@ -49496,7 +49510,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11">
+    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A949" s="15">
         <v>45525</v>
       </c>
@@ -49532,7 +49546,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11">
+    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A950" s="15">
         <v>45532</v>
       </c>
@@ -49568,7 +49582,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11">
+    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A951" s="15">
         <v>45539</v>
       </c>
@@ -49604,7 +49618,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11">
+    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A952" s="15">
         <v>45546</v>
       </c>
@@ -49640,7 +49654,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11">
+    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A953" s="15">
         <v>45553</v>
       </c>
@@ -49676,7 +49690,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11">
+    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A954" s="15">
         <v>45560</v>
       </c>
@@ -49712,7 +49726,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11">
+    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A955" s="15">
         <v>45567</v>
       </c>
@@ -49748,7 +49762,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11">
+    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A956" s="15">
         <v>45574</v>
       </c>
@@ -49784,7 +49798,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11">
+    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A957" s="15">
         <v>45581</v>
       </c>
@@ -49820,7 +49834,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11">
+    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A958" s="15">
         <v>45588</v>
       </c>
@@ -49856,7 +49870,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11">
+    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A959" s="15">
         <v>45595</v>
       </c>
@@ -49892,7 +49906,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11">
+    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A960" s="15">
         <v>45602</v>
       </c>
@@ -49928,7 +49942,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11">
+    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A961" s="15">
         <v>45609</v>
       </c>
@@ -49964,7 +49978,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11">
+    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A962" s="15">
         <v>45616</v>
       </c>
@@ -50000,7 +50014,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11">
+    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A963" s="15">
         <v>45623</v>
       </c>
@@ -50051,7 +50065,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11">
+    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A964" s="15">
         <v>45630</v>
       </c>
@@ -50087,7 +50101,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11">
+    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A965" s="15">
         <v>45637</v>
       </c>
@@ -50123,7 +50137,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11">
+    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A966" s="15">
         <v>45644</v>
       </c>
@@ -50159,7 +50173,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11">
+    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A967" s="15">
         <v>45651</v>
       </c>
@@ -50195,7 +50209,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11">
+    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A968" s="15">
         <v>45658</v>
       </c>
@@ -50231,7 +50245,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11">
+    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A969" s="15">
         <v>45665</v>
       </c>
@@ -50267,7 +50281,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11">
+    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A970" s="15">
         <v>45672</v>
       </c>
@@ -50303,7 +50317,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11">
+    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A971" s="15">
         <v>45679</v>
       </c>
@@ -50339,7 +50353,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11">
+    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A972" s="15">
         <v>45686</v>
       </c>
@@ -50375,7 +50389,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11">
+    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A973" s="15">
         <v>45693</v>
       </c>
@@ -50411,7 +50425,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11">
+    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A974" s="15">
         <v>45700</v>
       </c>
@@ -50447,7 +50461,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11">
+    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A975" s="15">
         <v>45707</v>
       </c>
@@ -50483,7 +50497,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11">
+    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A976" s="15">
         <v>45714</v>
       </c>
@@ -50519,7 +50533,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A977" s="15">
         <v>45721</v>
       </c>
@@ -50555,7 +50569,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A978" s="15">
         <v>45728</v>
       </c>
@@ -50591,7 +50605,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A979" s="15">
         <v>45735</v>
       </c>
@@ -50627,7 +50641,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A980" s="15">
         <v>45742</v>
       </c>
@@ -50663,7 +50677,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A981" s="15">
         <v>45749</v>
       </c>
@@ -50699,7 +50713,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A982" s="15">
         <v>45756</v>
       </c>
@@ -50735,7 +50749,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A983" s="15">
         <v>45763</v>
       </c>
@@ -50771,7 +50785,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A984" s="15">
         <v>45770</v>
       </c>
@@ -50807,7 +50821,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A985" s="15">
         <v>45777</v>
       </c>
@@ -50843,7 +50857,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A986" s="15">
         <v>45784</v>
       </c>
@@ -50879,7 +50893,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A987" s="15">
         <v>45791</v>
       </c>
@@ -50915,7 +50929,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A988" s="15">
         <v>45798</v>
       </c>
@@ -50951,7 +50965,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" s="15">
         <v>45805</v>
       </c>
@@ -50987,7 +51001,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11">
+    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" s="15">
         <v>45812</v>
       </c>
@@ -51023,7 +51037,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11">
+    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" s="15">
         <v>45819</v>
       </c>
@@ -51059,7 +51073,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" s="15">
         <v>45826</v>
       </c>
@@ -51095,7 +51109,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" s="15">
         <v>45833</v>
       </c>
@@ -51131,7 +51145,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A994" s="15">
         <v>45840</v>
       </c>
@@ -51167,7 +51181,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" s="15">
         <v>45847</v>
       </c>
@@ -51203,7 +51217,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" s="15">
         <v>45854</v>
       </c>
@@ -51239,7 +51253,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" s="15">
         <v>45861</v>
       </c>
@@ -51275,7 +51289,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" s="15">
         <v>45868</v>
       </c>
@@ -51311,7 +51325,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A999" s="15">
         <v>45875</v>
       </c>
@@ -51347,7 +51361,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1000" s="15">
         <v>45882</v>
       </c>
@@ -51383,7 +51397,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1001" s="15">
         <v>45889</v>
       </c>
@@ -51419,7 +51433,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11">
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1002" s="15">
         <v>45896</v>
       </c>
@@ -51455,7 +51469,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11">
+    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1003" s="15">
         <v>45903</v>
       </c>
@@ -51491,7 +51505,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11">
+    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1004" s="15">
         <v>45910</v>
       </c>
@@ -51527,7 +51541,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11">
+    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1005" s="15">
         <v>45917</v>
       </c>
@@ -51563,7 +51577,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11">
+    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1006" s="15">
         <v>45924</v>
       </c>
@@ -51599,7 +51613,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11">
+    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1007" s="15">
         <v>45931</v>
       </c>
@@ -51635,7 +51649,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11">
+    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1008" s="15">
         <v>45938</v>
       </c>
@@ -51671,7 +51685,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11">
+    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1009" s="15">
         <v>45945</v>
       </c>
@@ -51707,7 +51721,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11">
+    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1010" s="15">
         <v>45952</v>
       </c>
@@ -51743,7 +51757,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11">
+    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1011" s="15">
         <v>45959</v>
       </c>
@@ -51779,7 +51793,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11">
+    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1012" s="15">
         <v>45966</v>
       </c>
@@ -51815,7 +51829,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11">
+    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1013" s="15">
         <v>45973</v>
       </c>
@@ -51851,7 +51865,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11">
+    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1014" s="15">
         <v>45980</v>
       </c>
@@ -51887,7 +51901,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11">
+    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1015" s="15">
         <v>45987</v>
       </c>
@@ -51923,7 +51937,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11">
+    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1016" s="15">
         <v>45994</v>
       </c>
@@ -51959,7 +51973,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11">
+    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1017" s="15">
         <v>46001</v>
       </c>
@@ -51995,7 +52009,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11">
+    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1018" s="15">
         <v>46008</v>
       </c>
@@ -52031,7 +52045,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11">
+    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1019" s="15">
         <v>46015</v>
       </c>
@@ -52067,7 +52081,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11">
+    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1020" s="15">
         <v>46022</v>
       </c>
@@ -52103,7 +52117,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11">
+    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1021" s="15">
         <v>46029</v>
       </c>
@@ -52139,7 +52153,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11">
+    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1022" s="15">
         <v>46036</v>
       </c>
@@ -52175,7 +52189,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11">
+    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1023" s="15">
         <v>46043</v>
       </c>
@@ -52211,7 +52225,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11">
+    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1024" s="15">
         <v>46050</v>
       </c>
@@ -52247,7 +52261,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11">
+    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1025" s="15">
         <v>46057</v>
       </c>
@@ -52283,7 +52297,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11">
+    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1026" s="15">
         <v>46064</v>
       </c>
@@ -52319,7 +52333,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11">
+    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1027" s="15">
         <v>46071</v>
       </c>
@@ -52370,7 +52384,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11">
+    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1028" s="15">
         <v>46078</v>
       </c>
@@ -52406,7 +52420,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11">
+    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1029" s="15">
         <v>46085</v>
       </c>
@@ -52442,7 +52456,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11">
+    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1030" s="15">
         <v>46092</v>
       </c>
@@ -52478,7 +52492,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11">
+    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1031" s="15">
         <v>46099</v>
       </c>
@@ -52514,7 +52528,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="1032" spans="1:11">
+    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1032" s="15">
         <v>46106</v>
       </c>
@@ -52525,7 +52539,7 @@
         <v>0.41666666666666802</v>
       </c>
       <c r="D1032" s="15" t="str">
-        <f t="shared" ref="D1032" si="17">IF(
+        <f t="shared" ref="D1032:D1034" si="17">IF(
  AND(
   B1032 &gt;= IF(
          YEAR(B1032)&gt;=2007,
@@ -52565,6 +52579,42 @@
         <v>47.03</v>
       </c>
     </row>
+    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1033" s="15">
+        <v>46113</v>
+      </c>
+      <c r="B1033" s="15">
+        <v>46114</v>
+      </c>
+      <c r="C1033" s="17">
+        <v>0.41666666666667401</v>
+      </c>
+      <c r="D1033" s="15" t="str">
+        <f t="shared" si="17"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1033" s="7">
+        <v>68.36</v>
+      </c>
+      <c r="F1033" s="8">
+        <v>-100</v>
+      </c>
+      <c r="G1033" s="7">
+        <v>37</v>
+      </c>
+      <c r="H1033" s="9">
+        <v>82.5</v>
+      </c>
+      <c r="I1033" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1033" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1033" s="7">
+        <v>55.64</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52575,7 +52625,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52586,9 +52636,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52596,7 +52646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9F957B-4B03-4D4A-9E5B-3DFD995A1DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C7585D5-65BD-47F4-8FBA-634CED33CC5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3851,6 +3848,9 @@
                 <c:pt idx="1031">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="1032">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6955,6 +6955,9 @@
                 </c:pt>
                 <c:pt idx="1031">
                   <c:v>68.36</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>69.38</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7131,6 +7134,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7138,7 +7142,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10316,6 +10319,9 @@
                 <c:pt idx="1031">
                   <c:v>46114</c:v>
                 </c:pt>
+                <c:pt idx="1032">
+                  <c:v>46121</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13420,6 +13426,9 @@
                 </c:pt>
                 <c:pt idx="1031">
                   <c:v>55.64</c:v>
+                </c:pt>
+                <c:pt idx="1032">
+                  <c:v>51.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13596,6 +13605,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -13603,7 +13613,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -15126,21 +15135,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1033"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:K1034"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="15" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.25" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.19921875" style="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.25" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.3984375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.875" style="10"/>
+    <col min="11" max="11" width="21.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.8984375" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
@@ -52539,7 +52548,7 @@
         <v>0.41666666666666802</v>
       </c>
       <c r="D1032" s="15" t="str">
-        <f t="shared" ref="D1032:D1034" si="17">IF(
+        <f t="shared" ref="D1032:D1033" si="17">IF(
  AND(
   B1032 &gt;= IF(
          YEAR(B1032)&gt;=2007,
@@ -52615,6 +52624,57 @@
         <v>55.64</v>
       </c>
     </row>
+    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1034" s="15">
+        <v>46120</v>
+      </c>
+      <c r="B1034" s="15">
+        <v>46121</v>
+      </c>
+      <c r="C1034" s="17">
+        <v>0.41666666666668001</v>
+      </c>
+      <c r="D1034" s="15" t="str">
+        <f t="shared" ref="D1034" si="18">IF(
+ AND(
+  B1034 &gt;= IF(
+         YEAR(B1034)&gt;=2007,
+         DATE(YEAR(B1034),3,14)-WEEKDAY(DATE(YEAR(B1034),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1034),4,7)-WEEKDAY(DATE(YEAR(B1034),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1034 &lt;  IF(
+         YEAR(B1034)&gt;=2007,
+         DATE(YEAR(B1034),11,7)-WEEKDAY(DATE(YEAR(B1034),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1034),10,31)-WEEKDAY(DATE(YEAR(B1034),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1034" s="7">
+        <v>69.38</v>
+      </c>
+      <c r="F1034" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1034" s="7">
+        <v>37.5</v>
+      </c>
+      <c r="H1034" s="9">
+        <v>74.5</v>
+      </c>
+      <c r="I1034" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1034" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1034" s="7">
+        <v>51.31</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52625,7 +52685,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52636,9 +52696,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52646,7 +52706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC547176-F2EE-405B-AB46-70E98873E482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCEA53C-672B-4DAB-9E1D-DB9E0D84A23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -90,31 +90,31 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.00_ "/>
-    <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri Light"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="major"/>
     </font>
@@ -122,7 +122,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -130,7 +130,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -138,35 +138,35 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -174,7 +174,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -182,14 +182,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -197,14 +197,14 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -212,7 +212,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -220,20 +220,20 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -242,7 +242,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -600,7 +600,7 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -608,92 +608,92 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="166" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="21" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="21" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +711,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3854,6 +3854,9 @@
                 <c:pt idx="1033">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="1034">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6964,6 +6967,9 @@
                 </c:pt>
                 <c:pt idx="1033">
                   <c:v>79.489999999999995</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>94.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7180,7 +7186,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10331,6 +10337,9 @@
                 <c:pt idx="1033">
                   <c:v>46128</c:v>
                 </c:pt>
+                <c:pt idx="1034">
+                  <c:v>46135</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13441,6 +13450,9 @@
                 </c:pt>
                 <c:pt idx="1033">
                   <c:v>68.87</c:v>
+                </c:pt>
+                <c:pt idx="1034">
+                  <c:v>51.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14851,9 +14863,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14891,7 +14903,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -14997,7 +15009,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15139,7 +15151,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15147,24 +15159,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1035"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K1036"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.296875" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.09765625" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.36328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.3984375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.90625" style="10"/>
+    <col min="11" max="11" width="21.69921875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.8984375" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1">
+    <row r="1" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15199,7 +15211,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="15">
         <v>38903</v>
       </c>
@@ -15250,7 +15262,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="15">
         <v>38910</v>
       </c>
@@ -15301,7 +15313,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="15">
         <v>38903</v>
       </c>
@@ -15337,7 +15349,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="15">
         <v>38910</v>
       </c>
@@ -15373,7 +15385,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="15">
         <v>38917</v>
       </c>
@@ -15409,7 +15421,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="15">
         <v>38924</v>
       </c>
@@ -15445,7 +15457,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="15">
         <v>38931</v>
       </c>
@@ -15481,7 +15493,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="15">
         <v>38938</v>
       </c>
@@ -15517,7 +15529,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>38945</v>
       </c>
@@ -15553,7 +15565,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>38952</v>
       </c>
@@ -15589,7 +15601,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="15">
         <v>38959</v>
       </c>
@@ -15625,7 +15637,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="15">
         <v>38966</v>
       </c>
@@ -15661,7 +15673,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>38973</v>
       </c>
@@ -15697,7 +15709,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
         <v>38980</v>
       </c>
@@ -15733,7 +15745,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="15">
         <v>38987</v>
       </c>
@@ -15769,7 +15781,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="15">
         <v>38994</v>
       </c>
@@ -15805,7 +15817,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="15">
         <v>39001</v>
       </c>
@@ -15841,7 +15853,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="15">
         <v>39008</v>
       </c>
@@ -15877,7 +15889,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="15">
         <v>39015</v>
       </c>
@@ -15913,7 +15925,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="15">
         <v>39022</v>
       </c>
@@ -15949,7 +15961,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="15">
         <v>39029</v>
       </c>
@@ -15985,7 +15997,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="15">
         <v>39036</v>
       </c>
@@ -16021,7 +16033,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="15">
         <v>39043</v>
       </c>
@@ -16057,7 +16069,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="15">
         <v>39050</v>
       </c>
@@ -16093,7 +16105,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="15">
         <v>39057</v>
       </c>
@@ -16129,7 +16141,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="15">
         <v>39064</v>
       </c>
@@ -16165,7 +16177,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="15">
         <v>39071</v>
       </c>
@@ -16201,7 +16213,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="15">
         <v>39078</v>
       </c>
@@ -16237,7 +16249,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="15">
         <v>39085</v>
       </c>
@@ -16273,7 +16285,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="15">
         <v>39092</v>
       </c>
@@ -16309,7 +16321,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="15">
         <v>39099</v>
       </c>
@@ -16345,7 +16357,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="15">
         <v>39106</v>
       </c>
@@ -16381,7 +16393,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="15">
         <v>39113</v>
       </c>
@@ -16417,7 +16429,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="15">
         <v>39120</v>
       </c>
@@ -16453,7 +16465,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="15">
         <v>39127</v>
       </c>
@@ -16489,7 +16501,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="15">
         <v>39134</v>
       </c>
@@ -16525,7 +16537,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="15">
         <v>39141</v>
       </c>
@@ -16561,7 +16573,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="15">
         <v>39148</v>
       </c>
@@ -16597,7 +16609,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="15">
         <v>39155</v>
       </c>
@@ -16633,7 +16645,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="15">
         <v>39162</v>
       </c>
@@ -16669,7 +16681,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="15">
         <v>39169</v>
       </c>
@@ -16705,7 +16717,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="15">
         <v>39176</v>
       </c>
@@ -16741,7 +16753,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="15">
         <v>39183</v>
       </c>
@@ -16777,7 +16789,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="15">
         <v>39190</v>
       </c>
@@ -16813,7 +16825,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="15">
         <v>39197</v>
       </c>
@@ -16849,7 +16861,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="15">
         <v>39204</v>
       </c>
@@ -16885,7 +16897,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="15">
         <v>39211</v>
       </c>
@@ -16921,7 +16933,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="15">
         <v>39218</v>
       </c>
@@ -16957,7 +16969,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="15">
         <v>39225</v>
       </c>
@@ -16993,7 +17005,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="15">
         <v>39232</v>
       </c>
@@ -17029,7 +17041,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="15">
         <v>39239</v>
       </c>
@@ -17065,7 +17077,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="15">
         <v>39246</v>
       </c>
@@ -17101,7 +17113,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="15">
         <v>39253</v>
       </c>
@@ -17137,7 +17149,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="15">
         <v>39260</v>
       </c>
@@ -17173,7 +17185,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="15">
         <v>39268</v>
       </c>
@@ -17209,7 +17221,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="15">
         <v>39274</v>
       </c>
@@ -17245,7 +17257,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="15">
         <v>39281</v>
       </c>
@@ -17281,7 +17293,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="15">
         <v>39288</v>
       </c>
@@ -17317,7 +17329,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="15">
         <v>39295</v>
       </c>
@@ -17353,7 +17365,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="15">
         <v>39302</v>
       </c>
@@ -17389,7 +17401,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="15">
         <v>39309</v>
       </c>
@@ -17425,7 +17437,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="15">
         <v>39316</v>
       </c>
@@ -17461,7 +17473,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="15">
         <v>39323</v>
       </c>
@@ -17497,7 +17509,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="15">
         <v>39330</v>
       </c>
@@ -17533,7 +17545,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="15">
         <v>39337</v>
       </c>
@@ -17569,7 +17581,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="15">
         <v>39344</v>
       </c>
@@ -17620,7 +17632,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="15">
         <v>39351</v>
       </c>
@@ -17656,7 +17668,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="15">
         <v>39358</v>
       </c>
@@ -17692,7 +17704,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="15">
         <v>39365</v>
       </c>
@@ -17728,7 +17740,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="15">
         <v>39372</v>
       </c>
@@ -17764,7 +17776,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="15">
         <v>39379</v>
       </c>
@@ -17800,7 +17812,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="15">
         <v>39386</v>
       </c>
@@ -17836,7 +17848,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="15">
         <v>39393</v>
       </c>
@@ -17872,7 +17884,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="15">
         <v>39400</v>
       </c>
@@ -17908,7 +17920,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="15">
         <v>39407</v>
       </c>
@@ -17944,7 +17956,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="15">
         <v>39414</v>
       </c>
@@ -17980,7 +17992,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="15">
         <v>39421</v>
       </c>
@@ -18016,7 +18028,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="15">
         <v>39428</v>
       </c>
@@ -18052,7 +18064,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="15">
         <v>39435</v>
       </c>
@@ -18088,7 +18100,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="15">
         <v>39442</v>
       </c>
@@ -18124,7 +18136,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="15">
         <v>39449</v>
       </c>
@@ -18160,7 +18172,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="15">
         <v>39456</v>
       </c>
@@ -18196,7 +18208,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="15">
         <v>39463</v>
       </c>
@@ -18232,7 +18244,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="15">
         <v>39470</v>
       </c>
@@ -18268,7 +18280,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="15">
         <v>39477</v>
       </c>
@@ -18304,7 +18316,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="15">
         <v>39484</v>
       </c>
@@ -18340,7 +18352,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="15">
         <v>39491</v>
       </c>
@@ -18376,7 +18388,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="15">
         <v>39498</v>
       </c>
@@ -18412,7 +18424,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="15">
         <v>39505</v>
       </c>
@@ -18448,7 +18460,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="15">
         <v>39512</v>
       </c>
@@ -18484,7 +18496,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="15">
         <v>39519</v>
       </c>
@@ -18520,7 +18532,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="15">
         <v>39526</v>
       </c>
@@ -18556,7 +18568,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="15">
         <v>39533</v>
       </c>
@@ -18592,7 +18604,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="15">
         <v>39540</v>
       </c>
@@ -18628,7 +18640,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="15">
         <v>39547</v>
       </c>
@@ -18664,7 +18676,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="15">
         <v>39554</v>
       </c>
@@ -18700,7 +18712,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="15">
         <v>39561</v>
       </c>
@@ -18736,7 +18748,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="15">
         <v>39569</v>
       </c>
@@ -18772,7 +18784,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="15">
         <v>39575</v>
       </c>
@@ -18808,7 +18820,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="15">
         <v>39582</v>
       </c>
@@ -18844,7 +18856,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="15">
         <v>39589</v>
       </c>
@@ -18880,7 +18892,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="15">
         <v>39596</v>
       </c>
@@ -18916,7 +18928,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="15">
         <v>39603</v>
       </c>
@@ -18952,7 +18964,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="15">
         <v>39610</v>
       </c>
@@ -18988,7 +19000,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="11" customFormat="1">
+    <row r="106" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="15">
         <v>39617</v>
       </c>
@@ -19024,7 +19036,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="15">
         <v>39624</v>
       </c>
@@ -19060,7 +19072,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="15">
         <v>39631</v>
       </c>
@@ -19096,7 +19108,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="11" customFormat="1">
+    <row r="109" spans="1:11" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="15">
         <v>39638</v>
       </c>
@@ -19132,7 +19144,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="15">
         <v>39645</v>
       </c>
@@ -19168,7 +19180,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="15">
         <v>39652</v>
       </c>
@@ -19204,7 +19216,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="15">
         <v>39659</v>
       </c>
@@ -19240,7 +19252,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="15">
         <v>39666</v>
       </c>
@@ -19276,7 +19288,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="15">
         <v>39673</v>
       </c>
@@ -19312,7 +19324,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="15">
         <v>39681</v>
       </c>
@@ -19348,7 +19360,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="15">
         <v>39687</v>
       </c>
@@ -19384,7 +19396,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="15">
         <v>39694</v>
       </c>
@@ -19420,7 +19432,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="15">
         <v>39701</v>
       </c>
@@ -19456,7 +19468,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="15">
         <v>39708</v>
       </c>
@@ -19492,7 +19504,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="15">
         <v>39715</v>
       </c>
@@ -19528,7 +19540,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="15">
         <v>39722</v>
       </c>
@@ -19564,7 +19576,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="15">
         <v>39729</v>
       </c>
@@ -19600,7 +19612,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="15">
         <v>39736</v>
       </c>
@@ -19636,7 +19648,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="15">
         <v>39743</v>
       </c>
@@ -19672,7 +19684,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="15">
         <v>39750</v>
       </c>
@@ -19708,7 +19720,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="15">
         <v>39757</v>
       </c>
@@ -19744,7 +19756,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="15">
         <v>39764</v>
       </c>
@@ -19780,7 +19792,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="15">
         <v>39771</v>
       </c>
@@ -19816,7 +19828,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="15">
         <v>39778</v>
       </c>
@@ -19852,7 +19864,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="15">
         <v>39785</v>
       </c>
@@ -19888,7 +19900,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="15">
         <v>39792</v>
       </c>
@@ -19939,7 +19951,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="15">
         <v>39799</v>
       </c>
@@ -19975,7 +19987,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="15">
         <v>39806</v>
       </c>
@@ -20011,7 +20023,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="15">
         <v>39813</v>
       </c>
@@ -20047,7 +20059,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="15">
         <v>39820</v>
       </c>
@@ -20083,7 +20095,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="15">
         <v>39827</v>
       </c>
@@ -20119,7 +20131,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="15">
         <v>39834</v>
       </c>
@@ -20155,7 +20167,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="15">
         <v>39841</v>
       </c>
@@ -20191,7 +20203,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="15">
         <v>39848</v>
       </c>
@@ -20227,7 +20239,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="15">
         <v>39855</v>
       </c>
@@ -20263,7 +20275,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="15">
         <v>39862</v>
       </c>
@@ -20299,7 +20311,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="15">
         <v>39869</v>
       </c>
@@ -20335,7 +20347,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="15">
         <v>39876</v>
       </c>
@@ -20371,7 +20383,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="15">
         <v>39883</v>
       </c>
@@ -20407,7 +20419,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="15">
         <v>39890</v>
       </c>
@@ -20443,7 +20455,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="15">
         <v>39897</v>
       </c>
@@ -20479,7 +20491,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="15">
         <v>39904</v>
       </c>
@@ -20515,7 +20527,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="15">
         <v>39911</v>
       </c>
@@ -20551,7 +20563,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="15">
         <v>39918</v>
       </c>
@@ -20587,7 +20599,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="15">
         <v>39925</v>
       </c>
@@ -20623,7 +20635,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="15">
         <v>39932</v>
       </c>
@@ -20659,7 +20671,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="15">
         <v>39939</v>
       </c>
@@ -20695,7 +20707,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="15">
         <v>39946</v>
       </c>
@@ -20731,7 +20743,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="15">
         <v>39953</v>
       </c>
@@ -20767,7 +20779,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="15">
         <v>39960</v>
       </c>
@@ -20803,7 +20815,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="15">
         <v>39967</v>
       </c>
@@ -20839,7 +20851,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="15">
         <v>39974</v>
       </c>
@@ -20875,7 +20887,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="15">
         <v>39981</v>
       </c>
@@ -20911,7 +20923,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="15">
         <v>39988</v>
       </c>
@@ -20947,7 +20959,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="15">
         <v>39995</v>
       </c>
@@ -20983,7 +20995,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="15">
         <v>40002</v>
       </c>
@@ -21019,7 +21031,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="15">
         <v>40009</v>
       </c>
@@ -21055,7 +21067,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="15">
         <v>40016</v>
       </c>
@@ -21091,7 +21103,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="15">
         <v>40023</v>
       </c>
@@ -21127,7 +21139,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="15">
         <v>40030</v>
       </c>
@@ -21163,7 +21175,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="15">
         <v>40037</v>
       </c>
@@ -21199,7 +21211,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="15">
         <v>40044</v>
       </c>
@@ -21235,7 +21247,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="15">
         <v>40051</v>
       </c>
@@ -21271,7 +21283,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="15">
         <v>40058</v>
       </c>
@@ -21307,7 +21319,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="15">
         <v>40065</v>
       </c>
@@ -21343,7 +21355,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="15">
         <v>40072</v>
       </c>
@@ -21379,7 +21391,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="15">
         <v>40079</v>
       </c>
@@ -21415,7 +21427,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="15">
         <v>40086</v>
       </c>
@@ -21451,7 +21463,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="15">
         <v>40093</v>
       </c>
@@ -21487,7 +21499,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="15">
         <v>40100</v>
       </c>
@@ -21523,7 +21535,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="15">
         <v>40107</v>
       </c>
@@ -21559,7 +21571,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="15">
         <v>40114</v>
       </c>
@@ -21595,7 +21607,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="15">
         <v>40121</v>
       </c>
@@ -21631,7 +21643,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="15">
         <v>40128</v>
       </c>
@@ -21667,7 +21679,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="15">
         <v>40135</v>
       </c>
@@ -21703,7 +21715,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="15">
         <v>40142</v>
       </c>
@@ -21739,7 +21751,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="15">
         <v>40149</v>
       </c>
@@ -21775,7 +21787,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="15">
         <v>40156</v>
       </c>
@@ -21811,7 +21823,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="15">
         <v>40163</v>
       </c>
@@ -21847,7 +21859,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="15">
         <v>40170</v>
       </c>
@@ -21883,7 +21895,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="15">
         <v>40177</v>
       </c>
@@ -21919,7 +21931,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="15">
         <v>40184</v>
       </c>
@@ -21955,7 +21967,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="15">
         <v>40191</v>
       </c>
@@ -21991,7 +22003,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="15">
         <v>40198</v>
       </c>
@@ -22027,7 +22039,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="15">
         <v>40205</v>
       </c>
@@ -22063,7 +22075,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="15">
         <v>40212</v>
       </c>
@@ -22099,7 +22111,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="15">
         <v>40219</v>
       </c>
@@ -22135,7 +22147,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="15">
         <v>40226</v>
       </c>
@@ -22171,7 +22183,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="15">
         <v>40233</v>
       </c>
@@ -22207,7 +22219,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="15">
         <v>40240</v>
       </c>
@@ -22258,7 +22270,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="15">
         <v>40247</v>
       </c>
@@ -22294,7 +22306,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="15">
         <v>40254</v>
       </c>
@@ -22330,7 +22342,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="15">
         <v>40261</v>
       </c>
@@ -22366,7 +22378,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="15">
         <v>40268</v>
       </c>
@@ -22402,7 +22414,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="15">
         <v>40275</v>
       </c>
@@ -22438,7 +22450,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="15">
         <v>40282</v>
       </c>
@@ -22474,7 +22486,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="15">
         <v>40289</v>
       </c>
@@ -22510,7 +22522,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="15">
         <v>40296</v>
       </c>
@@ -22546,7 +22558,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="15">
         <v>40303</v>
       </c>
@@ -22582,7 +22594,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="15">
         <v>40310</v>
       </c>
@@ -22618,7 +22630,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="15">
         <v>40317</v>
       </c>
@@ -22654,7 +22666,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="15">
         <v>40324</v>
       </c>
@@ -22690,7 +22702,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="15">
         <v>40331</v>
       </c>
@@ -22726,7 +22738,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="15">
         <v>40338</v>
       </c>
@@ -22762,7 +22774,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="15">
         <v>40345</v>
       </c>
@@ -22798,7 +22810,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="15">
         <v>40352</v>
       </c>
@@ -22834,7 +22846,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="15">
         <v>40359</v>
       </c>
@@ -22870,7 +22882,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="15">
         <v>40366</v>
       </c>
@@ -22906,7 +22918,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="15">
         <v>40373</v>
       </c>
@@ -22942,7 +22954,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="15">
         <v>40380</v>
       </c>
@@ -22978,7 +22990,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="15">
         <v>40387</v>
       </c>
@@ -23014,7 +23026,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="15">
         <v>40394</v>
       </c>
@@ -23050,7 +23062,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="15">
         <v>40401</v>
       </c>
@@ -23086,7 +23098,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="15">
         <v>40408</v>
       </c>
@@ -23122,7 +23134,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="15">
         <v>40415</v>
       </c>
@@ -23158,7 +23170,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="15">
         <v>40422</v>
       </c>
@@ -23194,7 +23206,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="15">
         <v>40429</v>
       </c>
@@ -23230,7 +23242,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="15">
         <v>40436</v>
       </c>
@@ -23266,7 +23278,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="15">
         <v>40443</v>
       </c>
@@ -23302,7 +23314,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="15">
         <v>40450</v>
       </c>
@@ -23338,7 +23350,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="15">
         <v>40457</v>
       </c>
@@ -23374,7 +23386,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="15">
         <v>40464</v>
       </c>
@@ -23410,7 +23422,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="15">
         <v>40471</v>
       </c>
@@ -23446,7 +23458,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="15">
         <v>40478</v>
       </c>
@@ -23482,7 +23494,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="15">
         <v>40485</v>
       </c>
@@ -23518,7 +23530,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="15">
         <v>40493</v>
       </c>
@@ -23554,7 +23566,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="15">
         <v>40499</v>
       </c>
@@ -23590,7 +23602,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="15">
         <v>40506</v>
       </c>
@@ -23626,7 +23638,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="15">
         <v>40513</v>
       </c>
@@ -23662,7 +23674,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="15">
         <v>40520</v>
       </c>
@@ -23698,7 +23710,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="15">
         <v>40527</v>
       </c>
@@ -23734,7 +23746,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="15">
         <v>40534</v>
       </c>
@@ -23770,7 +23782,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="15">
         <v>40541</v>
       </c>
@@ -23806,7 +23818,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="15">
         <v>40548</v>
       </c>
@@ -23842,7 +23854,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="15">
         <v>40555</v>
       </c>
@@ -23878,7 +23890,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="15">
         <v>40562</v>
       </c>
@@ -23914,7 +23926,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="15">
         <v>40569</v>
       </c>
@@ -23950,7 +23962,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="15">
         <v>40576</v>
       </c>
@@ -23986,7 +23998,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="15">
         <v>40583</v>
       </c>
@@ -24022,7 +24034,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="15">
         <v>40590</v>
       </c>
@@ -24058,7 +24070,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="15">
         <v>40597</v>
       </c>
@@ -24094,7 +24106,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="15">
         <v>40604</v>
       </c>
@@ -24130,7 +24142,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="15">
         <v>40611</v>
       </c>
@@ -24166,7 +24178,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="15">
         <v>40618</v>
       </c>
@@ -24202,7 +24214,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="15">
         <v>40625</v>
       </c>
@@ -24238,7 +24250,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="15">
         <v>40632</v>
       </c>
@@ -24274,7 +24286,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="15">
         <v>40639</v>
       </c>
@@ -24310,7 +24322,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="15">
         <v>40646</v>
       </c>
@@ -24346,7 +24358,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="15">
         <v>40653</v>
       </c>
@@ -24382,7 +24394,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="15">
         <v>40660</v>
       </c>
@@ -24418,7 +24430,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="15">
         <v>40667</v>
       </c>
@@ -24454,7 +24466,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="15">
         <v>40674</v>
       </c>
@@ -24490,7 +24502,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="15">
         <v>40681</v>
       </c>
@@ -24526,7 +24538,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="15">
         <v>40688</v>
       </c>
@@ -24577,7 +24589,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="15">
         <v>40695</v>
       </c>
@@ -24613,7 +24625,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="15">
         <v>40702</v>
       </c>
@@ -24649,7 +24661,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="15">
         <v>40709</v>
       </c>
@@ -24685,7 +24697,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="15">
         <v>40716</v>
       </c>
@@ -24721,7 +24733,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="15">
         <v>40723</v>
       </c>
@@ -24757,7 +24769,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="15">
         <v>40730</v>
       </c>
@@ -24793,7 +24805,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="15">
         <v>40737</v>
       </c>
@@ -24829,7 +24841,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="15">
         <v>40744</v>
       </c>
@@ -24865,7 +24877,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="15">
         <v>40751</v>
       </c>
@@ -24901,7 +24913,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="15">
         <v>40758</v>
       </c>
@@ -24937,7 +24949,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="15">
         <v>40765</v>
       </c>
@@ -24973,7 +24985,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="15">
         <v>40772</v>
       </c>
@@ -25009,7 +25021,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="15">
         <v>40779</v>
       </c>
@@ -25045,7 +25057,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="15">
         <v>40786</v>
       </c>
@@ -25081,7 +25093,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="15">
         <v>40793</v>
       </c>
@@ -25117,7 +25129,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="15">
         <v>40800</v>
       </c>
@@ -25153,7 +25165,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="15">
         <v>40807</v>
       </c>
@@ -25189,7 +25201,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="15">
         <v>40814</v>
       </c>
@@ -25225,7 +25237,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="15">
         <v>40821</v>
       </c>
@@ -25261,7 +25273,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="15">
         <v>40828</v>
       </c>
@@ -25297,7 +25309,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="15">
         <v>40835</v>
       </c>
@@ -25333,7 +25345,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="15">
         <v>40842</v>
       </c>
@@ -25369,7 +25381,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="15">
         <v>40849</v>
       </c>
@@ -25405,7 +25417,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="15">
         <v>40856</v>
       </c>
@@ -25441,7 +25453,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="15">
         <v>40863</v>
       </c>
@@ -25477,7 +25489,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="15">
         <v>40870</v>
       </c>
@@ -25513,7 +25525,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="15">
         <v>40877</v>
       </c>
@@ -25549,7 +25561,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="15">
         <v>40884</v>
       </c>
@@ -25585,7 +25597,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="15">
         <v>40891</v>
       </c>
@@ -25621,7 +25633,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="15">
         <v>40898</v>
       </c>
@@ -25657,7 +25669,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="15">
         <v>40905</v>
       </c>
@@ -25693,7 +25705,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="15">
         <v>40912</v>
       </c>
@@ -25729,7 +25741,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="15">
         <v>40919</v>
       </c>
@@ -25765,7 +25777,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="15">
         <v>40926</v>
       </c>
@@ -25801,7 +25813,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="15">
         <v>40933</v>
       </c>
@@ -25837,7 +25849,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="15">
         <v>40940</v>
       </c>
@@ -25873,7 +25885,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="15">
         <v>40947</v>
       </c>
@@ -25909,7 +25921,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="15">
         <v>40954</v>
       </c>
@@ -25945,7 +25957,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="15">
         <v>40961</v>
       </c>
@@ -25981,7 +25993,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="15">
         <v>40968</v>
       </c>
@@ -26017,7 +26029,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="15">
         <v>40975</v>
       </c>
@@ -26053,7 +26065,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="15">
         <v>40982</v>
       </c>
@@ -26089,7 +26101,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="15">
         <v>40989</v>
       </c>
@@ -26125,7 +26137,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="15">
         <v>40996</v>
       </c>
@@ -26161,7 +26173,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="15">
         <v>41003</v>
       </c>
@@ -26197,7 +26209,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="15">
         <v>41010</v>
       </c>
@@ -26233,7 +26245,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="15">
         <v>41017</v>
       </c>
@@ -26269,7 +26281,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="15">
         <v>41024</v>
       </c>
@@ -26305,7 +26317,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="15">
         <v>41031</v>
       </c>
@@ -26341,7 +26353,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="15">
         <v>41038</v>
       </c>
@@ -26377,7 +26389,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="15">
         <v>41045</v>
       </c>
@@ -26413,7 +26425,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="15">
         <v>41052</v>
       </c>
@@ -26449,7 +26461,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="15">
         <v>41059</v>
       </c>
@@ -26485,7 +26497,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="15">
         <v>41066</v>
       </c>
@@ -26521,7 +26533,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="15">
         <v>41073</v>
       </c>
@@ -26557,7 +26569,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="15">
         <v>41080</v>
       </c>
@@ -26593,7 +26605,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="15">
         <v>41087</v>
       </c>
@@ -26629,7 +26641,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="15">
         <v>41095</v>
       </c>
@@ -26665,7 +26677,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="15">
         <v>41101</v>
       </c>
@@ -26701,7 +26713,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="15">
         <v>41108</v>
       </c>
@@ -26737,7 +26749,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="15">
         <v>41115</v>
       </c>
@@ -26773,7 +26785,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="15">
         <v>41122</v>
       </c>
@@ -26809,7 +26821,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="15">
         <v>41129</v>
       </c>
@@ -26845,7 +26857,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="15">
         <v>41136</v>
       </c>
@@ -26896,7 +26908,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="15">
         <v>41143</v>
       </c>
@@ -26932,7 +26944,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="15">
         <v>41150</v>
       </c>
@@ -26968,7 +26980,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="15">
         <v>41157</v>
       </c>
@@ -27004,7 +27016,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="15">
         <v>41164</v>
       </c>
@@ -27040,7 +27052,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="15">
         <v>41171</v>
       </c>
@@ -27076,7 +27088,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="15">
         <v>41178</v>
       </c>
@@ -27112,7 +27124,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="15">
         <v>41185</v>
       </c>
@@ -27148,7 +27160,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="15">
         <v>41192</v>
       </c>
@@ -27184,7 +27196,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="15">
         <v>41199</v>
       </c>
@@ -27220,7 +27232,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="15">
         <v>41206</v>
       </c>
@@ -27256,7 +27268,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="15">
         <v>41213</v>
       </c>
@@ -27292,7 +27304,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="15">
         <v>41220</v>
       </c>
@@ -27328,7 +27340,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="15">
         <v>41227</v>
       </c>
@@ -27364,7 +27376,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="15">
         <v>41234</v>
       </c>
@@ -27400,7 +27412,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="15">
         <v>41241</v>
       </c>
@@ -27436,7 +27448,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="15">
         <v>41248</v>
       </c>
@@ -27472,7 +27484,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="15">
         <v>41255</v>
       </c>
@@ -27508,7 +27520,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="15">
         <v>41262</v>
       </c>
@@ -27544,7 +27556,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="15">
         <v>41269</v>
       </c>
@@ -27580,7 +27592,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="15">
         <v>41276</v>
       </c>
@@ -27616,7 +27628,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="15">
         <v>41283</v>
       </c>
@@ -27652,7 +27664,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="15">
         <v>41290</v>
       </c>
@@ -27688,7 +27700,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="15">
         <v>41297</v>
       </c>
@@ -27724,7 +27736,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="15">
         <v>41304</v>
       </c>
@@ -27760,7 +27772,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="15">
         <v>41311</v>
       </c>
@@ -27796,7 +27808,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="15">
         <v>41318</v>
       </c>
@@ -27832,7 +27844,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="15">
         <v>41325</v>
       </c>
@@ -27868,7 +27880,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="15">
         <v>41332</v>
       </c>
@@ -27904,7 +27916,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="15">
         <v>41339</v>
       </c>
@@ -27940,7 +27952,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="15">
         <v>41346</v>
       </c>
@@ -27976,7 +27988,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="15">
         <v>41353</v>
       </c>
@@ -28012,7 +28024,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="15">
         <v>41360</v>
       </c>
@@ -28048,7 +28060,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="15">
         <v>41367</v>
       </c>
@@ -28084,7 +28096,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="15">
         <v>41374</v>
       </c>
@@ -28120,7 +28132,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="15">
         <v>41381</v>
       </c>
@@ -28156,7 +28168,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="15">
         <v>41388</v>
       </c>
@@ -28192,7 +28204,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="15">
         <v>41395</v>
       </c>
@@ -28228,7 +28240,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="15">
         <v>41402</v>
       </c>
@@ -28264,7 +28276,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="15">
         <v>41409</v>
       </c>
@@ -28300,7 +28312,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="15">
         <v>41416</v>
       </c>
@@ -28336,7 +28348,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="15">
         <v>41423</v>
       </c>
@@ -28372,7 +28384,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="15">
         <v>41430</v>
       </c>
@@ -28408,7 +28420,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="15">
         <v>41437</v>
       </c>
@@ -28444,7 +28456,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="15">
         <v>41444</v>
       </c>
@@ -28480,7 +28492,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="15">
         <v>41451</v>
       </c>
@@ -28516,7 +28528,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="15">
         <v>41458</v>
       </c>
@@ -28552,7 +28564,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="15">
         <v>41465</v>
       </c>
@@ -28588,7 +28600,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="15">
         <v>41472</v>
       </c>
@@ -28624,7 +28636,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="15">
         <v>41479</v>
       </c>
@@ -28660,7 +28672,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="15">
         <v>41486</v>
       </c>
@@ -28696,7 +28708,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="15">
         <v>41493</v>
       </c>
@@ -28732,7 +28744,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="15">
         <v>41500</v>
       </c>
@@ -28768,7 +28780,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="15">
         <v>41507</v>
       </c>
@@ -28804,7 +28816,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="15">
         <v>41514</v>
       </c>
@@ -28840,7 +28852,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="15">
         <v>41521</v>
       </c>
@@ -28876,7 +28888,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="15">
         <v>41528</v>
       </c>
@@ -28912,7 +28924,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="15">
         <v>41535</v>
       </c>
@@ -28948,7 +28960,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="15">
         <v>41542</v>
       </c>
@@ -28984,7 +28996,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="15">
         <v>41549</v>
       </c>
@@ -29020,7 +29032,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="15">
         <v>41556</v>
       </c>
@@ -29056,7 +29068,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="15">
         <v>41563</v>
       </c>
@@ -29092,7 +29104,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="15">
         <v>41570</v>
       </c>
@@ -29128,7 +29140,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="15">
         <v>41577</v>
       </c>
@@ -29164,7 +29176,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="15">
         <v>41584</v>
       </c>
@@ -29215,7 +29227,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="15">
         <v>41591</v>
       </c>
@@ -29251,7 +29263,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="15">
         <v>41598</v>
       </c>
@@ -29287,7 +29299,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="15">
         <v>41605</v>
       </c>
@@ -29323,7 +29335,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="15">
         <v>41612</v>
       </c>
@@ -29359,7 +29371,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="15">
         <v>41619</v>
       </c>
@@ -29395,7 +29407,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="15">
         <v>41626</v>
       </c>
@@ -29431,7 +29443,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="15">
         <v>41634</v>
       </c>
@@ -29467,7 +29479,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="15">
         <v>41641</v>
       </c>
@@ -29503,7 +29515,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="15">
         <v>41647</v>
       </c>
@@ -29539,7 +29551,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="15">
         <v>41654</v>
       </c>
@@ -29575,7 +29587,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="15">
         <v>41661</v>
       </c>
@@ -29611,7 +29623,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="15">
         <v>41668</v>
       </c>
@@ -29647,7 +29659,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="15">
         <v>41675</v>
       </c>
@@ -29683,7 +29695,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="15">
         <v>41682</v>
       </c>
@@ -29719,7 +29731,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="15">
         <v>41689</v>
       </c>
@@ -29755,7 +29767,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="15">
         <v>41696</v>
       </c>
@@ -29791,7 +29803,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="15">
         <v>41703</v>
       </c>
@@ -29827,7 +29839,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="15">
         <v>41710</v>
       </c>
@@ -29863,7 +29875,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="15">
         <v>41716</v>
       </c>
@@ -29899,7 +29911,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="15">
         <v>41717</v>
       </c>
@@ -29935,7 +29947,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="15">
         <v>41724</v>
       </c>
@@ -29971,7 +29983,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="15">
         <v>41731</v>
       </c>
@@ -30007,7 +30019,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="15">
         <v>41738</v>
       </c>
@@ -30043,7 +30055,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="15">
         <v>41745</v>
       </c>
@@ -30079,7 +30091,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="15">
         <v>41752</v>
       </c>
@@ -30115,7 +30127,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="15">
         <v>41759</v>
       </c>
@@ -30151,7 +30163,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="15">
         <v>41766</v>
       </c>
@@ -30187,7 +30199,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="15">
         <v>41773</v>
       </c>
@@ -30223,7 +30235,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="15">
         <v>41780</v>
       </c>
@@ -30259,7 +30271,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="15">
         <v>41787</v>
       </c>
@@ -30295,7 +30307,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="15">
         <v>41794</v>
       </c>
@@ -30331,7 +30343,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="15">
         <v>41801</v>
       </c>
@@ -30367,7 +30379,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="15">
         <v>41808</v>
       </c>
@@ -30403,7 +30415,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="15">
         <v>41815</v>
       </c>
@@ -30439,7 +30451,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="15">
         <v>41822</v>
       </c>
@@ -30475,7 +30487,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="15">
         <v>41829</v>
       </c>
@@ -30511,7 +30523,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="15">
         <v>41836</v>
       </c>
@@ -30547,7 +30559,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="15">
         <v>41843</v>
       </c>
@@ -30583,7 +30595,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="15">
         <v>41850</v>
       </c>
@@ -30619,7 +30631,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" s="15">
         <v>41857</v>
       </c>
@@ -30655,7 +30667,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" s="15">
         <v>41864</v>
       </c>
@@ -30691,7 +30703,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="15">
         <v>41871</v>
       </c>
@@ -30727,7 +30739,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" s="15">
         <v>41878</v>
       </c>
@@ -30763,7 +30775,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" s="15">
         <v>41885</v>
       </c>
@@ -30799,7 +30811,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" s="15">
         <v>41892</v>
       </c>
@@ -30835,7 +30847,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" s="15">
         <v>41899</v>
       </c>
@@ -30871,7 +30883,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" s="15">
         <v>41906</v>
       </c>
@@ -30907,7 +30919,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435" s="15">
         <v>41913</v>
       </c>
@@ -30943,7 +30955,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436" s="15">
         <v>41920</v>
       </c>
@@ -30979,7 +30991,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437" s="15">
         <v>41927</v>
       </c>
@@ -31015,7 +31027,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438" s="15">
         <v>41934</v>
       </c>
@@ -31051,7 +31063,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439" s="15">
         <v>41941</v>
       </c>
@@ -31087,7 +31099,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440" s="15">
         <v>41948</v>
       </c>
@@ -31123,7 +31135,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441" s="15">
         <v>41955</v>
       </c>
@@ -31159,7 +31171,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442" s="15">
         <v>41962</v>
       </c>
@@ -31195,7 +31207,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443" s="15">
         <v>41968</v>
       </c>
@@ -31231,7 +31243,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444" s="15">
         <v>41976</v>
       </c>
@@ -31267,7 +31279,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445" s="15">
         <v>41983</v>
       </c>
@@ -31303,7 +31315,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446" s="15">
         <v>41990</v>
       </c>
@@ -31339,7 +31351,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447" s="15">
         <v>41997</v>
       </c>
@@ -31375,7 +31387,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448" s="15">
         <v>42004</v>
       </c>
@@ -31411,7 +31423,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449" s="15">
         <v>42011</v>
       </c>
@@ -31447,7 +31459,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450" s="15">
         <v>42018</v>
       </c>
@@ -31483,7 +31495,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451" s="15">
         <v>42025</v>
       </c>
@@ -31534,7 +31546,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" s="15">
         <v>42032</v>
       </c>
@@ -31570,7 +31582,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" s="15">
         <v>42039</v>
       </c>
@@ -31606,7 +31618,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" s="15">
         <v>42046</v>
       </c>
@@ -31642,7 +31654,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" s="15">
         <v>42053</v>
       </c>
@@ -31678,7 +31690,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456" s="15">
         <v>42060</v>
       </c>
@@ -31714,7 +31726,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457" s="15">
         <v>42067</v>
       </c>
@@ -31750,7 +31762,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458" s="15">
         <v>42074</v>
       </c>
@@ -31786,7 +31798,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459" s="15">
         <v>42088</v>
       </c>
@@ -31822,7 +31834,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460" s="15">
         <v>42095</v>
       </c>
@@ -31858,7 +31870,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461" s="15">
         <v>42102</v>
       </c>
@@ -31894,7 +31906,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462" s="15">
         <v>42109</v>
       </c>
@@ -31930,7 +31942,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463" s="15">
         <v>42116</v>
       </c>
@@ -31966,7 +31978,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464" s="15">
         <v>42123</v>
       </c>
@@ -32002,7 +32014,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465" s="15">
         <v>42130</v>
       </c>
@@ -32038,7 +32050,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466" s="15">
         <v>42137</v>
       </c>
@@ -32074,7 +32086,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467" s="15">
         <v>42144</v>
       </c>
@@ -32110,7 +32122,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" s="15">
         <v>42151</v>
       </c>
@@ -32146,7 +32158,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" s="15">
         <v>42158</v>
       </c>
@@ -32182,7 +32194,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" s="15">
         <v>42165</v>
       </c>
@@ -32218,7 +32230,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471" s="15">
         <v>42172</v>
       </c>
@@ -32254,7 +32266,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" s="15">
         <v>42179</v>
       </c>
@@ -32290,7 +32302,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" s="15">
         <v>42186</v>
       </c>
@@ -32326,7 +32338,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" s="15">
         <v>42193</v>
       </c>
@@ -32362,7 +32374,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475" s="15">
         <v>42200</v>
       </c>
@@ -32398,7 +32410,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" s="15">
         <v>42207</v>
       </c>
@@ -32434,7 +32446,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" s="15">
         <v>42214</v>
       </c>
@@ -32470,7 +32482,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" s="15">
         <v>42221</v>
       </c>
@@ -32506,7 +32518,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479" s="15">
         <v>42228</v>
       </c>
@@ -32542,7 +32554,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" s="15">
         <v>42235</v>
       </c>
@@ -32578,7 +32590,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" s="15">
         <v>42242</v>
       </c>
@@ -32614,7 +32626,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" s="15">
         <v>42249</v>
       </c>
@@ -32650,7 +32662,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" s="15">
         <v>42256</v>
       </c>
@@ -32686,7 +32698,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" s="15">
         <v>42263</v>
       </c>
@@ -32722,7 +32734,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" s="15">
         <v>42270</v>
       </c>
@@ -32758,7 +32770,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" s="15">
         <v>42277</v>
       </c>
@@ -32794,7 +32806,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487" s="15">
         <v>42284</v>
       </c>
@@ -32830,7 +32842,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" s="15">
         <v>42291</v>
       </c>
@@ -32866,7 +32878,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" s="15">
         <v>42298</v>
       </c>
@@ -32902,7 +32914,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" s="15">
         <v>42305</v>
       </c>
@@ -32938,7 +32950,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491" s="15">
         <v>42312</v>
       </c>
@@ -32974,7 +32986,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" s="15">
         <v>42319</v>
       </c>
@@ -33010,7 +33022,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" s="15">
         <v>42326</v>
       </c>
@@ -33046,7 +33058,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="15">
         <v>42333</v>
       </c>
@@ -33082,7 +33094,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" s="15">
         <v>42340</v>
       </c>
@@ -33118,7 +33130,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" s="15">
         <v>42347</v>
       </c>
@@ -33154,7 +33166,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" s="15">
         <v>42354</v>
       </c>
@@ -33190,7 +33202,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" s="15">
         <v>42361</v>
       </c>
@@ -33226,7 +33238,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" s="15">
         <v>42368</v>
       </c>
@@ -33262,7 +33274,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500" s="15">
         <v>42375</v>
       </c>
@@ -33298,7 +33310,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501" s="15">
         <v>42382</v>
       </c>
@@ -33334,7 +33346,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502" s="15">
         <v>42396</v>
       </c>
@@ -33370,7 +33382,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503" s="15">
         <v>42403</v>
       </c>
@@ -33406,7 +33418,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504" s="15">
         <v>42410</v>
       </c>
@@ -33442,7 +33454,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505" s="15">
         <v>42417</v>
       </c>
@@ -33478,7 +33490,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A506" s="15">
         <v>42424</v>
       </c>
@@ -33514,7 +33526,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A507" s="15">
         <v>42431</v>
       </c>
@@ -33550,7 +33562,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A508" s="15">
         <v>42438</v>
       </c>
@@ -33586,7 +33598,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A509" s="15">
         <v>42445</v>
       </c>
@@ -33622,7 +33634,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A510" s="15">
         <v>42452</v>
       </c>
@@ -33658,7 +33670,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A511" s="15">
         <v>42459</v>
       </c>
@@ -33694,7 +33706,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A512" s="15">
         <v>42466</v>
       </c>
@@ -33730,7 +33742,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513" s="15">
         <v>42473</v>
       </c>
@@ -33766,7 +33778,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514" s="15">
         <v>42480</v>
       </c>
@@ -33802,7 +33814,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515" s="15">
         <v>42487</v>
       </c>
@@ -33853,7 +33865,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516" s="15">
         <v>42494</v>
       </c>
@@ -33889,7 +33901,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517" s="15">
         <v>42501</v>
       </c>
@@ -33925,7 +33937,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518" s="15">
         <v>42508</v>
       </c>
@@ -33961,7 +33973,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519" s="15">
         <v>42515</v>
       </c>
@@ -33997,7 +34009,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520" s="15">
         <v>42522</v>
       </c>
@@ -34033,7 +34045,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521" s="15">
         <v>42529</v>
       </c>
@@ -34069,7 +34081,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522" s="15">
         <v>42536</v>
       </c>
@@ -34105,7 +34117,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523" s="15">
         <v>42543</v>
       </c>
@@ -34141,7 +34153,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524" s="15">
         <v>42550</v>
       </c>
@@ -34177,7 +34189,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525" s="15">
         <v>42557</v>
       </c>
@@ -34213,7 +34225,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526" s="15">
         <v>42564</v>
       </c>
@@ -34249,7 +34261,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" s="15">
         <v>42571</v>
       </c>
@@ -34285,7 +34297,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" s="15">
         <v>42578</v>
       </c>
@@ -34321,7 +34333,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" s="15">
         <v>42585</v>
       </c>
@@ -34357,7 +34369,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" s="15">
         <v>42592</v>
       </c>
@@ -34393,7 +34405,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" s="15">
         <v>42599</v>
       </c>
@@ -34429,7 +34441,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" s="15">
         <v>42606</v>
       </c>
@@ -34465,7 +34477,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" s="15">
         <v>42613</v>
       </c>
@@ -34501,7 +34513,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A534" s="15">
         <v>42620</v>
       </c>
@@ -34537,7 +34549,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" s="15">
         <v>42627</v>
       </c>
@@ -34573,7 +34585,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" s="15">
         <v>42634</v>
       </c>
@@ -34609,7 +34621,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" s="15">
         <v>42641</v>
       </c>
@@ -34645,7 +34657,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" s="15">
         <v>42648</v>
       </c>
@@ -34681,7 +34693,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" s="15">
         <v>42655</v>
       </c>
@@ -34717,7 +34729,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" s="15">
         <v>42662</v>
       </c>
@@ -34753,7 +34765,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" s="15">
         <v>42669</v>
       </c>
@@ -34789,7 +34801,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" s="15">
         <v>42676</v>
       </c>
@@ -34825,7 +34837,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" s="15">
         <v>42683</v>
       </c>
@@ -34861,7 +34873,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" s="15">
         <v>42689</v>
       </c>
@@ -34897,7 +34909,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" s="15">
         <v>42697</v>
       </c>
@@ -34933,7 +34945,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A546" s="15">
         <v>42704</v>
       </c>
@@ -34969,7 +34981,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" s="15">
         <v>42711</v>
       </c>
@@ -35005,7 +35017,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" s="15">
         <v>42718</v>
       </c>
@@ -35041,7 +35053,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" s="15">
         <v>42725</v>
       </c>
@@ -35077,7 +35089,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A550" s="15">
         <v>42732</v>
       </c>
@@ -35113,7 +35125,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" s="15">
         <v>42739</v>
       </c>
@@ -35149,7 +35161,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" s="15">
         <v>42746</v>
       </c>
@@ -35185,7 +35197,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" s="15">
         <v>42753</v>
       </c>
@@ -35221,7 +35233,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554" s="15">
         <v>42760</v>
       </c>
@@ -35257,7 +35269,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" s="15">
         <v>42767</v>
       </c>
@@ -35293,7 +35305,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" s="15">
         <v>42774</v>
       </c>
@@ -35329,7 +35341,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" s="15">
         <v>42781</v>
       </c>
@@ -35365,7 +35377,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" s="15">
         <v>42788</v>
       </c>
@@ -35401,7 +35413,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" s="15">
         <v>42795</v>
       </c>
@@ -35437,7 +35449,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" s="15">
         <v>42802</v>
       </c>
@@ -35473,7 +35485,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" s="15">
         <v>42809</v>
       </c>
@@ -35509,7 +35521,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" s="15">
         <v>42816</v>
       </c>
@@ -35545,7 +35557,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" s="15">
         <v>42823</v>
       </c>
@@ -35581,7 +35593,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A564" s="15">
         <v>42830</v>
       </c>
@@ -35617,7 +35629,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" s="15">
         <v>42837</v>
       </c>
@@ -35653,7 +35665,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" s="15">
         <v>42844</v>
       </c>
@@ -35689,7 +35701,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" s="15">
         <v>42851</v>
       </c>
@@ -35725,7 +35737,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" s="15">
         <v>42858</v>
       </c>
@@ -35761,7 +35773,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A569" s="15">
         <v>42865</v>
       </c>
@@ -35797,7 +35809,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" s="15">
         <v>42872</v>
       </c>
@@ -35833,7 +35845,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" s="15">
         <v>42879</v>
       </c>
@@ -35869,7 +35881,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" s="15">
         <v>42886</v>
       </c>
@@ -35905,7 +35917,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A573" s="15">
         <v>42893</v>
       </c>
@@ -35941,7 +35953,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A574" s="15">
         <v>42900</v>
       </c>
@@ -35977,7 +35989,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A575" s="15">
         <v>42907</v>
       </c>
@@ -36013,7 +36025,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A576" s="15">
         <v>42914</v>
       </c>
@@ -36049,7 +36061,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577" s="15">
         <v>42921</v>
       </c>
@@ -36085,7 +36097,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A578" s="15">
         <v>42928</v>
       </c>
@@ -36121,7 +36133,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A579" s="15">
         <v>42935</v>
       </c>
@@ -36172,7 +36184,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A580" s="15">
         <v>42942</v>
       </c>
@@ -36208,7 +36220,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A581" s="15">
         <v>42949</v>
       </c>
@@ -36244,7 +36256,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A582" s="15">
         <v>42956</v>
       </c>
@@ -36280,7 +36292,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A583" s="15">
         <v>42963</v>
       </c>
@@ -36316,7 +36328,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A584" s="15">
         <v>42970</v>
       </c>
@@ -36352,7 +36364,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A585" s="15">
         <v>42977</v>
       </c>
@@ -36388,7 +36400,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A586" s="15">
         <v>42984</v>
       </c>
@@ -36424,7 +36436,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587" s="15">
         <v>42991</v>
       </c>
@@ -36460,7 +36472,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A588" s="15">
         <v>42998</v>
       </c>
@@ -36496,7 +36508,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A589" s="15">
         <v>43005</v>
       </c>
@@ -36532,7 +36544,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A590" s="15">
         <v>43012</v>
       </c>
@@ -36568,7 +36580,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A591" s="15">
         <v>43019</v>
       </c>
@@ -36604,7 +36616,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A592" s="15">
         <v>43026</v>
       </c>
@@ -36640,7 +36652,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A593" s="15">
         <v>43033</v>
       </c>
@@ -36676,7 +36688,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A594" s="15">
         <v>43040</v>
       </c>
@@ -36712,7 +36724,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A595" s="15">
         <v>43047</v>
       </c>
@@ -36748,7 +36760,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A596" s="15">
         <v>43054</v>
       </c>
@@ -36784,7 +36796,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" s="15">
         <v>43061</v>
       </c>
@@ -36820,7 +36832,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" s="15">
         <v>43068</v>
       </c>
@@ -36856,7 +36868,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" s="15">
         <v>43075</v>
       </c>
@@ -36892,7 +36904,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A600" s="15">
         <v>43082</v>
       </c>
@@ -36928,7 +36940,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" s="15">
         <v>43089</v>
       </c>
@@ -36964,7 +36976,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" s="15">
         <v>43096</v>
       </c>
@@ -37000,7 +37012,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" s="15">
         <v>43103</v>
       </c>
@@ -37036,7 +37048,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" s="15">
         <v>43110</v>
       </c>
@@ -37072,7 +37084,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A605" s="15">
         <v>43117</v>
       </c>
@@ -37108,7 +37120,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A606" s="15">
         <v>43124</v>
       </c>
@@ -37144,7 +37156,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A607" s="15">
         <v>43131</v>
       </c>
@@ -37180,7 +37192,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A608" s="15">
         <v>43138</v>
       </c>
@@ -37216,7 +37228,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A609" s="15">
         <v>43145</v>
       </c>
@@ -37252,7 +37264,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610" s="15">
         <v>43152</v>
       </c>
@@ -37288,7 +37300,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A611" s="15">
         <v>43159</v>
       </c>
@@ -37324,7 +37336,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A612" s="15">
         <v>43166</v>
       </c>
@@ -37360,7 +37372,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613" s="15">
         <v>43173</v>
       </c>
@@ -37396,7 +37408,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A614" s="15">
         <v>43180</v>
       </c>
@@ -37432,7 +37444,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A615" s="15">
         <v>43187</v>
       </c>
@@ -37468,7 +37480,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A616" s="15">
         <v>43194</v>
       </c>
@@ -37504,7 +37516,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A617" s="15">
         <v>43201</v>
       </c>
@@ -37540,7 +37552,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A618" s="15">
         <v>43208</v>
       </c>
@@ -37576,7 +37588,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A619" s="15">
         <v>43215</v>
       </c>
@@ -37612,7 +37624,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A620" s="15">
         <v>43222</v>
       </c>
@@ -37648,7 +37660,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A621" s="15">
         <v>43229</v>
       </c>
@@ -37684,7 +37696,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A622" s="15">
         <v>43236</v>
       </c>
@@ -37720,7 +37732,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" s="15">
         <v>43243</v>
       </c>
@@ -37756,7 +37768,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" s="15">
         <v>43250</v>
       </c>
@@ -37792,7 +37804,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" s="15">
         <v>43257</v>
       </c>
@@ -37828,7 +37840,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" s="15">
         <v>43264</v>
       </c>
@@ -37864,7 +37876,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" s="15">
         <v>43271</v>
       </c>
@@ -37900,7 +37912,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" s="15">
         <v>43278</v>
       </c>
@@ -37936,7 +37948,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" s="15">
         <v>43285</v>
       </c>
@@ -37972,7 +37984,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" s="15">
         <v>43292</v>
       </c>
@@ -38008,7 +38020,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A631" s="15">
         <v>43299</v>
       </c>
@@ -38044,7 +38056,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" s="15">
         <v>43306</v>
       </c>
@@ -38080,7 +38092,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" s="15">
         <v>43313</v>
       </c>
@@ -38116,7 +38128,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" s="15">
         <v>43320</v>
       </c>
@@ -38152,7 +38164,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" s="15">
         <v>43327</v>
       </c>
@@ -38188,7 +38200,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" s="15">
         <v>43334</v>
       </c>
@@ -38224,7 +38236,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" s="15">
         <v>43341</v>
       </c>
@@ -38260,7 +38272,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" s="15">
         <v>43348</v>
       </c>
@@ -38296,7 +38308,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A639" s="15">
         <v>43355</v>
       </c>
@@ -38332,7 +38344,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A640" s="15">
         <v>43362</v>
       </c>
@@ -38368,7 +38380,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A641" s="15">
         <v>43369</v>
       </c>
@@ -38404,7 +38416,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A642" s="15">
         <v>43376</v>
       </c>
@@ -38440,7 +38452,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A643" s="15">
         <v>43383</v>
       </c>
@@ -38491,7 +38503,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A644" s="15">
         <v>43391</v>
       </c>
@@ -38527,7 +38539,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A645" s="15">
         <v>43397</v>
       </c>
@@ -38563,7 +38575,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646" s="15">
         <v>43404</v>
       </c>
@@ -38599,7 +38611,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A647" s="15">
         <v>43411</v>
       </c>
@@ -38635,7 +38647,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A648" s="15">
         <v>43418</v>
       </c>
@@ -38671,7 +38683,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649" s="15">
         <v>43425</v>
       </c>
@@ -38707,7 +38719,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A650" s="15">
         <v>43432</v>
       </c>
@@ -38743,7 +38755,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A651" s="15">
         <v>43439</v>
       </c>
@@ -38779,7 +38791,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A652" s="15">
         <v>43446</v>
       </c>
@@ -38815,7 +38827,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A653" s="15">
         <v>43453</v>
       </c>
@@ -38851,7 +38863,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A654" s="15">
         <v>43460</v>
       </c>
@@ -38887,7 +38899,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A655" s="15">
         <v>43467</v>
       </c>
@@ -38923,7 +38935,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A656" s="15">
         <v>43474</v>
       </c>
@@ -38959,7 +38971,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A657" s="15">
         <v>43481</v>
       </c>
@@ -38995,7 +39007,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A658" s="15">
         <v>43488</v>
       </c>
@@ -39031,7 +39043,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A659" s="15">
         <v>43495</v>
       </c>
@@ -39067,7 +39079,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A660" s="15">
         <v>43502</v>
       </c>
@@ -39103,7 +39115,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A661" s="15">
         <v>43509</v>
       </c>
@@ -39139,7 +39151,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A662" s="15">
         <v>43516</v>
       </c>
@@ -39175,7 +39187,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A663" s="15">
         <v>43523</v>
       </c>
@@ -39211,7 +39223,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A664" s="15">
         <v>43530</v>
       </c>
@@ -39247,7 +39259,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A665" s="15">
         <v>43537</v>
       </c>
@@ -39283,7 +39295,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A666" s="15">
         <v>43544</v>
       </c>
@@ -39319,7 +39331,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A667" s="15">
         <v>43551</v>
       </c>
@@ -39355,7 +39367,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A668" s="15">
         <v>43558</v>
       </c>
@@ -39391,7 +39403,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A669" s="15">
         <v>43565</v>
       </c>
@@ -39427,7 +39439,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A670" s="15">
         <v>43572</v>
       </c>
@@ -39463,7 +39475,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A671" s="15">
         <v>43579</v>
       </c>
@@ -39499,7 +39511,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A672" s="15">
         <v>43586</v>
       </c>
@@ -39535,7 +39547,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A673" s="15">
         <v>43593</v>
       </c>
@@ -39571,7 +39583,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A674" s="15">
         <v>43600</v>
       </c>
@@ -39607,7 +39619,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A675" s="15">
         <v>43607</v>
       </c>
@@ -39643,7 +39655,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A676" s="15">
         <v>43614</v>
       </c>
@@ -39679,7 +39691,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677" s="15">
         <v>43621</v>
       </c>
@@ -39715,7 +39727,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678" s="15">
         <v>43628</v>
       </c>
@@ -39751,7 +39763,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679" s="15">
         <v>43635</v>
       </c>
@@ -39787,7 +39799,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680" s="15">
         <v>43642</v>
       </c>
@@ -39823,7 +39835,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681" s="15">
         <v>43649</v>
       </c>
@@ -39859,7 +39871,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" s="15">
         <v>43656</v>
       </c>
@@ -39895,7 +39907,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" s="15">
         <v>43663</v>
       </c>
@@ -39931,7 +39943,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" s="15">
         <v>43670</v>
       </c>
@@ -39967,7 +39979,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" s="15">
         <v>43677</v>
       </c>
@@ -40003,7 +40015,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" s="15">
         <v>43684</v>
       </c>
@@ -40039,7 +40051,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A687" s="15">
         <v>43691</v>
       </c>
@@ -40075,7 +40087,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688" s="15">
         <v>43698</v>
       </c>
@@ -40111,7 +40123,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A689" s="15">
         <v>43705</v>
       </c>
@@ -40147,7 +40159,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A690" s="15">
         <v>43712</v>
       </c>
@@ -40183,7 +40195,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A691" s="15">
         <v>43719</v>
       </c>
@@ -40219,7 +40231,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A692" s="15">
         <v>43726</v>
       </c>
@@ -40255,7 +40267,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A693" s="15">
         <v>43733</v>
       </c>
@@ -40291,7 +40303,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A694" s="15">
         <v>43740</v>
       </c>
@@ -40327,7 +40339,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A695" s="15">
         <v>43747</v>
       </c>
@@ -40363,7 +40375,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A696" s="15">
         <v>43754</v>
       </c>
@@ -40399,7 +40411,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A697" s="15">
         <v>43761</v>
       </c>
@@ -40435,7 +40447,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A698" s="15">
         <v>43768</v>
       </c>
@@ -40471,7 +40483,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A699" s="15">
         <v>43775</v>
       </c>
@@ -40507,7 +40519,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A700" s="15">
         <v>43782</v>
       </c>
@@ -40543,7 +40555,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A701" s="15">
         <v>43789</v>
       </c>
@@ -40579,7 +40591,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" s="15">
         <v>43796</v>
       </c>
@@ -40615,7 +40627,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" s="15">
         <v>43803</v>
       </c>
@@ -40651,7 +40663,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" s="15">
         <v>43810</v>
       </c>
@@ -40687,7 +40699,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" s="15">
         <v>43817</v>
       </c>
@@ -40723,7 +40735,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" s="15">
         <v>43824</v>
       </c>
@@ -40759,7 +40771,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" s="15">
         <v>43831</v>
       </c>
@@ -40810,7 +40822,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" s="15">
         <v>43838</v>
       </c>
@@ -40846,7 +40858,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A709" s="15">
         <v>43845</v>
       </c>
@@ -40882,7 +40894,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A710" s="15">
         <v>43852</v>
       </c>
@@ -40918,7 +40930,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A711" s="15">
         <v>43859</v>
       </c>
@@ -40954,7 +40966,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A712" s="15">
         <v>43866</v>
       </c>
@@ -40990,7 +41002,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A713" s="15">
         <v>43873</v>
       </c>
@@ -41026,7 +41038,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A714" s="15">
         <v>43880</v>
       </c>
@@ -41062,7 +41074,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A715" s="15">
         <v>43887</v>
       </c>
@@ -41098,7 +41110,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A716" s="15">
         <v>43894</v>
       </c>
@@ -41134,7 +41146,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A717" s="15">
         <v>43901</v>
       </c>
@@ -41170,7 +41182,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A718" s="15">
         <v>43908</v>
       </c>
@@ -41206,7 +41218,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A719" s="15">
         <v>43915</v>
       </c>
@@ -41242,7 +41254,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A720" s="15">
         <v>43922</v>
       </c>
@@ -41278,7 +41290,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A721" s="15">
         <v>43929</v>
       </c>
@@ -41314,7 +41326,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A722" s="15">
         <v>43936</v>
       </c>
@@ -41350,7 +41362,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A723" s="15">
         <v>43943</v>
       </c>
@@ -41386,7 +41398,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A724" s="15">
         <v>43950</v>
       </c>
@@ -41422,7 +41434,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A725" s="15">
         <v>43957</v>
       </c>
@@ -41458,7 +41470,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A726" s="15">
         <v>43964</v>
       </c>
@@ -41494,7 +41506,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A727" s="15">
         <v>43971</v>
       </c>
@@ -41530,7 +41542,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A728" s="15">
         <v>43978</v>
       </c>
@@ -41566,7 +41578,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A729" s="15">
         <v>43985</v>
       </c>
@@ -41602,7 +41614,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A730" s="15">
         <v>43992</v>
       </c>
@@ -41638,7 +41650,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A731" s="15">
         <v>43999</v>
       </c>
@@ -41674,7 +41686,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A732" s="15">
         <v>44006</v>
       </c>
@@ -41710,7 +41722,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A733" s="15">
         <v>44013</v>
       </c>
@@ -41746,7 +41758,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A734" s="15">
         <v>44020</v>
       </c>
@@ -41782,7 +41794,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A735" s="15">
         <v>44027</v>
       </c>
@@ -41818,7 +41830,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A736" s="15">
         <v>44034</v>
       </c>
@@ -41854,7 +41866,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A737" s="15">
         <v>44041</v>
       </c>
@@ -41890,7 +41902,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A738" s="15">
         <v>44048</v>
       </c>
@@ -41926,7 +41938,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A739" s="15">
         <v>44055</v>
       </c>
@@ -41962,7 +41974,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A740" s="15">
         <v>44062</v>
       </c>
@@ -41998,7 +42010,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A741" s="15">
         <v>44069</v>
       </c>
@@ -42034,7 +42046,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A742" s="15">
         <v>44076</v>
       </c>
@@ -42070,7 +42082,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A743" s="15">
         <v>44083</v>
       </c>
@@ -42106,7 +42118,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A744" s="15">
         <v>44090</v>
       </c>
@@ -42142,7 +42154,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A745" s="15">
         <v>44097</v>
       </c>
@@ -42178,7 +42190,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A746" s="15">
         <v>44104</v>
       </c>
@@ -42214,7 +42226,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A747" s="15">
         <v>44111</v>
       </c>
@@ -42250,7 +42262,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A748" s="15">
         <v>44118</v>
       </c>
@@ -42286,7 +42298,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A749" s="15">
         <v>44125</v>
       </c>
@@ -42322,7 +42334,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A750" s="15">
         <v>44132</v>
       </c>
@@ -42358,7 +42370,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A751" s="15">
         <v>44139</v>
       </c>
@@ -42394,7 +42406,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A752" s="15">
         <v>44146</v>
       </c>
@@ -42430,7 +42442,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A753" s="15">
         <v>44153</v>
       </c>
@@ -42466,7 +42478,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A754" s="15">
         <v>44160</v>
       </c>
@@ -42502,7 +42514,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A755" s="15">
         <v>44167</v>
       </c>
@@ -42538,7 +42550,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A756" s="15">
         <v>44174</v>
       </c>
@@ -42574,7 +42586,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757" s="15">
         <v>44181</v>
       </c>
@@ -42610,7 +42622,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758" s="15">
         <v>44188</v>
       </c>
@@ -42646,7 +42658,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759" s="15">
         <v>44195</v>
       </c>
@@ -42682,7 +42694,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A760" s="15">
         <v>44202</v>
       </c>
@@ -42718,7 +42730,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A761" s="15">
         <v>44209</v>
       </c>
@@ -42754,7 +42766,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762" s="15">
         <v>44216</v>
       </c>
@@ -42790,7 +42802,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763" s="15">
         <v>44223</v>
       </c>
@@ -42826,7 +42838,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A764" s="15">
         <v>44230</v>
       </c>
@@ -42862,7 +42874,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A765" s="15">
         <v>44237</v>
       </c>
@@ -42898,7 +42910,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A766" s="15">
         <v>44244</v>
       </c>
@@ -42934,7 +42946,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767" s="15">
         <v>44251</v>
       </c>
@@ -42970,7 +42982,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A768" s="15">
         <v>44258</v>
       </c>
@@ -43006,7 +43018,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A769" s="15">
         <v>44265</v>
       </c>
@@ -43042,7 +43054,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A770" s="15">
         <v>44272</v>
       </c>
@@ -43078,7 +43090,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A771" s="15">
         <v>44279</v>
       </c>
@@ -43129,7 +43141,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A772" s="15">
         <v>44286</v>
       </c>
@@ -43165,7 +43177,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A773" s="15">
         <v>44293</v>
       </c>
@@ -43201,7 +43213,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A774" s="15">
         <v>44300</v>
       </c>
@@ -43237,7 +43249,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A775" s="15">
         <v>44307</v>
       </c>
@@ -43273,7 +43285,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A776" s="15">
         <v>44314</v>
       </c>
@@ -43309,7 +43321,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A777" s="15">
         <v>44321</v>
       </c>
@@ -43345,7 +43357,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A778" s="15">
         <v>44328</v>
       </c>
@@ -43381,7 +43393,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A779" s="15">
         <v>44335</v>
       </c>
@@ -43417,7 +43429,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A780" s="15">
         <v>44342</v>
       </c>
@@ -43453,7 +43465,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A781" s="15">
         <v>44349</v>
       </c>
@@ -43489,7 +43501,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A782" s="15">
         <v>44356</v>
       </c>
@@ -43525,7 +43537,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A783" s="15">
         <v>44363</v>
       </c>
@@ -43561,7 +43573,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A784" s="15">
         <v>44370</v>
       </c>
@@ -43597,7 +43609,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A785" s="15">
         <v>44377</v>
       </c>
@@ -43633,7 +43645,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A786" s="15">
         <v>44384</v>
       </c>
@@ -43669,7 +43681,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A787" s="15">
         <v>44391</v>
       </c>
@@ -43705,7 +43717,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A788" s="15">
         <v>44398</v>
       </c>
@@ -43741,7 +43753,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A789" s="15">
         <v>44405</v>
       </c>
@@ -43777,7 +43789,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A790" s="15">
         <v>44412</v>
       </c>
@@ -43813,7 +43825,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A791" s="15">
         <v>44419</v>
       </c>
@@ -43849,7 +43861,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A792" s="15">
         <v>44426</v>
       </c>
@@ -43885,7 +43897,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A793" s="15">
         <v>44433</v>
       </c>
@@ -43921,7 +43933,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A794" s="15">
         <v>44440</v>
       </c>
@@ -43957,7 +43969,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A795" s="15">
         <v>44447</v>
       </c>
@@ -43993,7 +44005,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A796" s="15">
         <v>44454</v>
       </c>
@@ -44029,7 +44041,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A797" s="15">
         <v>44461</v>
       </c>
@@ -44065,7 +44077,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A798" s="15">
         <v>44468</v>
       </c>
@@ -44101,7 +44113,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A799" s="15">
         <v>44475</v>
       </c>
@@ -44137,7 +44149,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A800" s="15">
         <v>44482</v>
       </c>
@@ -44173,7 +44185,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A801" s="15">
         <v>44489</v>
       </c>
@@ -44209,7 +44221,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A802" s="15">
         <v>44496</v>
       </c>
@@ -44245,7 +44257,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A803" s="15">
         <v>44503</v>
       </c>
@@ -44281,7 +44293,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A804" s="15">
         <v>44510</v>
       </c>
@@ -44317,7 +44329,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A805" s="15">
         <v>44517</v>
       </c>
@@ -44353,7 +44365,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A806" s="15">
         <v>44524</v>
       </c>
@@ -44389,7 +44401,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A807" s="15">
         <v>44531</v>
       </c>
@@ -44425,7 +44437,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A808" s="15">
         <v>44538</v>
       </c>
@@ -44461,7 +44473,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A809" s="15">
         <v>44545</v>
       </c>
@@ -44497,7 +44509,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A810" s="15">
         <v>44552</v>
       </c>
@@ -44533,7 +44545,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A811" s="15">
         <v>44559</v>
       </c>
@@ -44569,7 +44581,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A812" s="15">
         <v>44566</v>
       </c>
@@ -44605,7 +44617,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A813" s="15">
         <v>44573</v>
       </c>
@@ -44641,7 +44653,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A814" s="15">
         <v>44580</v>
       </c>
@@ -44677,7 +44689,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A815" s="15">
         <v>44587</v>
       </c>
@@ -44713,7 +44725,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A816" s="15">
         <v>44594</v>
       </c>
@@ -44749,7 +44761,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11">
+    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A817" s="15">
         <v>44601</v>
       </c>
@@ -44785,7 +44797,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11">
+    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A818" s="15">
         <v>44608</v>
       </c>
@@ -44821,7 +44833,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11">
+    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A819" s="15">
         <v>44615</v>
       </c>
@@ -44857,7 +44869,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11">
+    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A820" s="15">
         <v>44622</v>
       </c>
@@ -44893,7 +44905,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11">
+    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A821" s="15">
         <v>44629</v>
       </c>
@@ -44929,7 +44941,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11">
+    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A822" s="15">
         <v>44636</v>
       </c>
@@ -44965,7 +44977,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A823" s="15">
         <v>44643</v>
       </c>
@@ -45001,7 +45013,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A824" s="15">
         <v>44650</v>
       </c>
@@ -45037,7 +45049,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A825" s="15">
         <v>44657</v>
       </c>
@@ -45073,7 +45085,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A826" s="15">
         <v>44664</v>
       </c>
@@ -45109,7 +45121,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A827" s="15">
         <v>44671</v>
       </c>
@@ -45145,7 +45157,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A828" s="15">
         <v>44678</v>
       </c>
@@ -45181,7 +45193,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A829" s="15">
         <v>44685</v>
       </c>
@@ -45217,7 +45229,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A830" s="15">
         <v>44692</v>
       </c>
@@ -45253,7 +45265,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A831" s="15">
         <v>44699</v>
       </c>
@@ -45289,7 +45301,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A832" s="15">
         <v>44706</v>
       </c>
@@ -45325,7 +45337,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11">
+    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A833" s="15">
         <v>44713</v>
       </c>
@@ -45361,7 +45373,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11">
+    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A834" s="15">
         <v>44720</v>
       </c>
@@ -45397,7 +45409,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11">
+    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A835" s="15">
         <v>44727</v>
       </c>
@@ -45448,7 +45460,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11">
+    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A836" s="15">
         <v>44734</v>
       </c>
@@ -45484,7 +45496,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11">
+    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A837" s="15">
         <v>44741</v>
       </c>
@@ -45520,7 +45532,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11">
+    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A838" s="15">
         <v>44748</v>
       </c>
@@ -45556,7 +45568,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11">
+    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A839" s="15">
         <v>44755</v>
       </c>
@@ -45592,7 +45604,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11">
+    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A840" s="15">
         <v>44762</v>
       </c>
@@ -45628,7 +45640,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11">
+    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" s="15">
         <v>44769</v>
       </c>
@@ -45664,7 +45676,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11">
+    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" s="15">
         <v>44776</v>
       </c>
@@ -45700,7 +45712,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11">
+    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" s="15">
         <v>44783</v>
       </c>
@@ -45736,7 +45748,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11">
+    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A844" s="15">
         <v>44790</v>
       </c>
@@ -45772,7 +45784,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11">
+    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A845" s="15">
         <v>44797</v>
       </c>
@@ -45808,7 +45820,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11">
+    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A846" s="15">
         <v>44804</v>
       </c>
@@ -45844,7 +45856,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11">
+    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A847" s="15">
         <v>44811</v>
       </c>
@@ -45880,7 +45892,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11">
+    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A848" s="15">
         <v>44818</v>
       </c>
@@ -45916,7 +45928,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11">
+    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A849" s="15">
         <v>44825</v>
       </c>
@@ -45952,7 +45964,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11">
+    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A850" s="15">
         <v>44832</v>
       </c>
@@ -45988,7 +46000,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11">
+    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A851" s="15">
         <v>44839</v>
       </c>
@@ -46024,7 +46036,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11">
+    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A852" s="15">
         <v>44846</v>
       </c>
@@ -46060,7 +46072,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11">
+    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A853" s="15">
         <v>44853</v>
       </c>
@@ -46096,7 +46108,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11">
+    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A854" s="15">
         <v>44860</v>
       </c>
@@ -46132,7 +46144,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11">
+    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A855" s="15">
         <v>44867</v>
       </c>
@@ -46168,7 +46180,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11">
+    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A856" s="15">
         <v>44874</v>
       </c>
@@ -46204,7 +46216,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11">
+    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A857" s="15">
         <v>44881</v>
       </c>
@@ -46240,7 +46252,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11">
+    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A858" s="15">
         <v>44888</v>
       </c>
@@ -46276,7 +46288,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11">
+    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A859" s="15">
         <v>44895</v>
       </c>
@@ -46312,7 +46324,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11">
+    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A860" s="15">
         <v>44902</v>
       </c>
@@ -46348,7 +46360,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11">
+    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A861" s="15">
         <v>44909</v>
       </c>
@@ -46384,7 +46396,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11">
+    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A862" s="15">
         <v>44916</v>
       </c>
@@ -46420,7 +46432,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11">
+    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A863" s="15">
         <v>44923</v>
       </c>
@@ -46456,7 +46468,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11">
+    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A864" s="15">
         <v>44930</v>
       </c>
@@ -46492,7 +46504,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11">
+    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A865" s="15">
         <v>44937</v>
       </c>
@@ -46528,7 +46540,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11">
+    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A866" s="15">
         <v>44944</v>
       </c>
@@ -46564,7 +46576,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11">
+    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A867" s="15">
         <v>44951</v>
       </c>
@@ -46600,7 +46612,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11">
+    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A868" s="15">
         <v>44958</v>
       </c>
@@ -46636,7 +46648,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11">
+    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A869" s="15">
         <v>44965</v>
       </c>
@@ -46672,7 +46684,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11">
+    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A870" s="15">
         <v>44972</v>
       </c>
@@ -46708,7 +46720,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11">
+    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A871" s="15">
         <v>44979</v>
       </c>
@@ -46744,7 +46756,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11">
+    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" s="15">
         <v>44986</v>
       </c>
@@ -46780,7 +46792,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11">
+    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" s="15">
         <v>44993</v>
       </c>
@@ -46816,7 +46828,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11">
+    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" s="15">
         <v>45000</v>
       </c>
@@ -46852,7 +46864,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11">
+    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A875" s="15">
         <v>45007</v>
       </c>
@@ -46888,7 +46900,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11">
+    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" s="15">
         <v>45014</v>
       </c>
@@ -46924,7 +46936,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11">
+    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" s="15">
         <v>45021</v>
       </c>
@@ -46960,7 +46972,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11">
+    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" s="15">
         <v>45028</v>
       </c>
@@ -46996,7 +47008,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11">
+    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A879" s="15">
         <v>45035</v>
       </c>
@@ -47032,7 +47044,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11">
+    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" s="15">
         <v>45042</v>
       </c>
@@ -47068,7 +47080,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11">
+    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" s="15">
         <v>45049</v>
       </c>
@@ -47104,7 +47116,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11">
+    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" s="15">
         <v>45056</v>
       </c>
@@ -47140,7 +47152,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11">
+    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A883" s="15">
         <v>45063</v>
       </c>
@@ -47176,7 +47188,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" s="15">
         <v>45070</v>
       </c>
@@ -47212,7 +47224,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" s="15">
         <v>45077</v>
       </c>
@@ -47248,7 +47260,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" s="15">
         <v>45084</v>
       </c>
@@ -47284,7 +47296,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11">
+    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A887" s="15">
         <v>45091</v>
       </c>
@@ -47320,7 +47332,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11">
+    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" s="15">
         <v>45098</v>
       </c>
@@ -47356,7 +47368,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11">
+    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" s="15">
         <v>45105</v>
       </c>
@@ -47392,7 +47404,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11">
+    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" s="15">
         <v>45112</v>
       </c>
@@ -47428,7 +47440,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A891" s="15">
         <v>45119</v>
       </c>
@@ -47464,7 +47476,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11">
+    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" s="15">
         <v>45126</v>
       </c>
@@ -47500,7 +47512,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11">
+    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" s="15">
         <v>45133</v>
       </c>
@@ -47536,7 +47548,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11">
+    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" s="15">
         <v>45140</v>
       </c>
@@ -47572,7 +47584,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11">
+    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A895" s="15">
         <v>45147</v>
       </c>
@@ -47608,7 +47620,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11">
+    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A896" s="15">
         <v>45154</v>
       </c>
@@ -47644,7 +47656,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11">
+    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A897" s="15">
         <v>45161</v>
       </c>
@@ -47680,7 +47692,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A898" s="15">
         <v>45168</v>
       </c>
@@ -47716,7 +47728,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11">
+    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A899" s="15">
         <v>45175</v>
       </c>
@@ -47767,7 +47779,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11">
+    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A900" s="15">
         <v>45182</v>
       </c>
@@ -47803,7 +47815,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11">
+    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A901" s="15">
         <v>45189</v>
       </c>
@@ -47839,7 +47851,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11">
+    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A902" s="15">
         <v>45196</v>
       </c>
@@ -47875,7 +47887,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11">
+    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A903" s="15">
         <v>45203</v>
       </c>
@@ -47911,7 +47923,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11">
+    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A904" s="15">
         <v>45210</v>
       </c>
@@ -47947,7 +47959,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11">
+    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A905" s="15">
         <v>45217</v>
       </c>
@@ -47983,7 +47995,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11">
+    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A906" s="15">
         <v>45224</v>
       </c>
@@ -48019,7 +48031,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11">
+    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A907" s="15">
         <v>45231</v>
       </c>
@@ -48055,7 +48067,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11">
+    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A908" s="15">
         <v>45238</v>
       </c>
@@ -48091,7 +48103,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11">
+    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A909" s="15">
         <v>45245</v>
       </c>
@@ -48127,7 +48139,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11">
+    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A910" s="15">
         <v>45252</v>
       </c>
@@ -48163,7 +48175,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11">
+    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A911" s="15">
         <v>45259</v>
       </c>
@@ -48199,7 +48211,7 @@
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11">
+    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A912" s="15">
         <v>45266</v>
       </c>
@@ -48235,7 +48247,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11">
+    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A913" s="15">
         <v>45273</v>
       </c>
@@ -48271,7 +48283,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11">
+    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A914" s="15">
         <v>45280</v>
       </c>
@@ -48307,7 +48319,7 @@
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11">
+    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A915" s="15">
         <v>45287</v>
       </c>
@@ -48343,7 +48355,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11">
+    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A916" s="15">
         <v>45294</v>
       </c>
@@ -48379,7 +48391,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11">
+    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A917" s="15">
         <v>45301</v>
       </c>
@@ -48415,7 +48427,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11">
+    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A918" s="15">
         <v>45308</v>
       </c>
@@ -48451,7 +48463,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11">
+    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A919" s="15">
         <v>45315</v>
       </c>
@@ -48487,7 +48499,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11">
+    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A920" s="15">
         <v>45322</v>
       </c>
@@ -48523,7 +48535,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11">
+    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A921" s="15">
         <v>45329</v>
       </c>
@@ -48559,7 +48571,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11">
+    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A922" s="15">
         <v>45336</v>
       </c>
@@ -48595,7 +48607,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11">
+    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A923" s="15">
         <v>45343</v>
       </c>
@@ -48631,7 +48643,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11">
+    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A924" s="15">
         <v>45350</v>
       </c>
@@ -48667,7 +48679,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11">
+    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A925" s="15">
         <v>45357</v>
       </c>
@@ -48703,7 +48715,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11">
+    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A926" s="15">
         <v>45364</v>
       </c>
@@ -48739,7 +48751,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11">
+    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A927" s="15">
         <v>45371</v>
       </c>
@@ -48775,7 +48787,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11">
+    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A928" s="15">
         <v>45378</v>
       </c>
@@ -48811,7 +48823,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11">
+    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A929" s="15">
         <v>45385</v>
       </c>
@@ -48847,7 +48859,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11">
+    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A930" s="15">
         <v>45392</v>
       </c>
@@ -48883,7 +48895,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11">
+    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A931" s="15">
         <v>45399</v>
       </c>
@@ -48919,7 +48931,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11">
+    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A932" s="15">
         <v>45406</v>
       </c>
@@ -48955,7 +48967,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11">
+    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A933" s="15">
         <v>45413</v>
       </c>
@@ -48991,7 +49003,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11">
+    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A934" s="15">
         <v>45420</v>
       </c>
@@ -49027,7 +49039,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11">
+    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A935" s="15">
         <v>45427</v>
       </c>
@@ -49063,7 +49075,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11">
+    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A936" s="15">
         <v>45434</v>
       </c>
@@ -49099,7 +49111,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11">
+    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A937" s="15">
         <v>45441</v>
       </c>
@@ -49135,7 +49147,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11">
+    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A938" s="15">
         <v>45448</v>
       </c>
@@ -49171,7 +49183,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11">
+    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A939" s="15">
         <v>45455</v>
       </c>
@@ -49207,7 +49219,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11">
+    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A940" s="15">
         <v>45462</v>
       </c>
@@ -49243,7 +49255,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11">
+    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A941" s="15">
         <v>45469</v>
       </c>
@@ -49279,7 +49291,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11">
+    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A942" s="15">
         <v>45476</v>
       </c>
@@ -49315,7 +49327,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11">
+    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A943" s="15">
         <v>45483</v>
       </c>
@@ -49351,7 +49363,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11">
+    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A944" s="15">
         <v>45490</v>
       </c>
@@ -49387,7 +49399,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11">
+    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A945" s="15">
         <v>45497</v>
       </c>
@@ -49423,7 +49435,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11">
+    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A946" s="15">
         <v>45504</v>
       </c>
@@ -49459,7 +49471,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11">
+    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A947" s="15">
         <v>45511</v>
       </c>
@@ -49495,7 +49507,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11">
+    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A948" s="15">
         <v>45518</v>
       </c>
@@ -49531,7 +49543,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11">
+    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A949" s="15">
         <v>45525</v>
       </c>
@@ -49567,7 +49579,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11">
+    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A950" s="15">
         <v>45532</v>
       </c>
@@ -49603,7 +49615,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11">
+    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A951" s="15">
         <v>45539</v>
       </c>
@@ -49639,7 +49651,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11">
+    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A952" s="15">
         <v>45546</v>
       </c>
@@ -49675,7 +49687,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11">
+    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A953" s="15">
         <v>45553</v>
       </c>
@@ -49711,7 +49723,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11">
+    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A954" s="15">
         <v>45560</v>
       </c>
@@ -49747,7 +49759,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11">
+    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A955" s="15">
         <v>45567</v>
       </c>
@@ -49783,7 +49795,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11">
+    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A956" s="15">
         <v>45574</v>
       </c>
@@ -49819,7 +49831,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11">
+    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A957" s="15">
         <v>45581</v>
       </c>
@@ -49855,7 +49867,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11">
+    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A958" s="15">
         <v>45588</v>
       </c>
@@ -49891,7 +49903,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11">
+    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A959" s="15">
         <v>45595</v>
       </c>
@@ -49927,7 +49939,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11">
+    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A960" s="15">
         <v>45602</v>
       </c>
@@ -49963,7 +49975,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11">
+    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A961" s="15">
         <v>45609</v>
       </c>
@@ -49999,7 +50011,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11">
+    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A962" s="15">
         <v>45616</v>
       </c>
@@ -50035,7 +50047,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11">
+    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A963" s="15">
         <v>45623</v>
       </c>
@@ -50086,7 +50098,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11">
+    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A964" s="15">
         <v>45630</v>
       </c>
@@ -50122,7 +50134,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11">
+    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A965" s="15">
         <v>45637</v>
       </c>
@@ -50158,7 +50170,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11">
+    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A966" s="15">
         <v>45644</v>
       </c>
@@ -50194,7 +50206,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11">
+    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A967" s="15">
         <v>45651</v>
       </c>
@@ -50230,7 +50242,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11">
+    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A968" s="15">
         <v>45658</v>
       </c>
@@ -50266,7 +50278,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11">
+    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A969" s="15">
         <v>45665</v>
       </c>
@@ -50302,7 +50314,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11">
+    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A970" s="15">
         <v>45672</v>
       </c>
@@ -50338,7 +50350,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11">
+    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A971" s="15">
         <v>45679</v>
       </c>
@@ -50374,7 +50386,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11">
+    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A972" s="15">
         <v>45686</v>
       </c>
@@ -50410,7 +50422,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11">
+    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A973" s="15">
         <v>45693</v>
       </c>
@@ -50446,7 +50458,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11">
+    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A974" s="15">
         <v>45700</v>
       </c>
@@ -50482,7 +50494,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11">
+    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A975" s="15">
         <v>45707</v>
       </c>
@@ -50518,7 +50530,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11">
+    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A976" s="15">
         <v>45714</v>
       </c>
@@ -50554,7 +50566,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A977" s="15">
         <v>45721</v>
       </c>
@@ -50590,7 +50602,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A978" s="15">
         <v>45728</v>
       </c>
@@ -50626,7 +50638,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A979" s="15">
         <v>45735</v>
       </c>
@@ -50662,7 +50674,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A980" s="15">
         <v>45742</v>
       </c>
@@ -50698,7 +50710,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A981" s="15">
         <v>45749</v>
       </c>
@@ -50734,7 +50746,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A982" s="15">
         <v>45756</v>
       </c>
@@ -50770,7 +50782,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A983" s="15">
         <v>45763</v>
       </c>
@@ -50806,7 +50818,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A984" s="15">
         <v>45770</v>
       </c>
@@ -50842,7 +50854,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A985" s="15">
         <v>45777</v>
       </c>
@@ -50878,7 +50890,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A986" s="15">
         <v>45784</v>
       </c>
@@ -50914,7 +50926,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A987" s="15">
         <v>45791</v>
       </c>
@@ -50950,7 +50962,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A988" s="15">
         <v>45798</v>
       </c>
@@ -50986,7 +50998,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" s="15">
         <v>45805</v>
       </c>
@@ -51022,7 +51034,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11">
+    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" s="15">
         <v>45812</v>
       </c>
@@ -51058,7 +51070,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11">
+    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" s="15">
         <v>45819</v>
       </c>
@@ -51094,7 +51106,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" s="15">
         <v>45826</v>
       </c>
@@ -51130,7 +51142,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" s="15">
         <v>45833</v>
       </c>
@@ -51166,7 +51178,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A994" s="15">
         <v>45840</v>
       </c>
@@ -51202,7 +51214,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" s="15">
         <v>45847</v>
       </c>
@@ -51238,7 +51250,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" s="15">
         <v>45854</v>
       </c>
@@ -51274,7 +51286,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" s="15">
         <v>45861</v>
       </c>
@@ -51310,7 +51322,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" s="15">
         <v>45868</v>
       </c>
@@ -51346,7 +51358,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A999" s="15">
         <v>45875</v>
       </c>
@@ -51382,7 +51394,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1000" s="15">
         <v>45882</v>
       </c>
@@ -51418,7 +51430,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1001" s="15">
         <v>45889</v>
       </c>
@@ -51454,7 +51466,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11">
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1002" s="15">
         <v>45896</v>
       </c>
@@ -51490,7 +51502,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11">
+    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1003" s="15">
         <v>45903</v>
       </c>
@@ -51526,7 +51538,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11">
+    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1004" s="15">
         <v>45910</v>
       </c>
@@ -51562,7 +51574,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11">
+    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1005" s="15">
         <v>45917</v>
       </c>
@@ -51598,7 +51610,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11">
+    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1006" s="15">
         <v>45924</v>
       </c>
@@ -51634,7 +51646,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11">
+    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1007" s="15">
         <v>45931</v>
       </c>
@@ -51670,7 +51682,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11">
+    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1008" s="15">
         <v>45938</v>
       </c>
@@ -51706,7 +51718,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11">
+    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1009" s="15">
         <v>45945</v>
       </c>
@@ -51742,7 +51754,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11">
+    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1010" s="15">
         <v>45952</v>
       </c>
@@ -51778,7 +51790,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11">
+    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1011" s="15">
         <v>45959</v>
       </c>
@@ -51814,7 +51826,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11">
+    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1012" s="15">
         <v>45966</v>
       </c>
@@ -51850,7 +51862,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11">
+    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1013" s="15">
         <v>45973</v>
       </c>
@@ -51886,7 +51898,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11">
+    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1014" s="15">
         <v>45980</v>
       </c>
@@ -51922,7 +51934,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11">
+    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1015" s="15">
         <v>45987</v>
       </c>
@@ -51958,7 +51970,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11">
+    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1016" s="15">
         <v>45994</v>
       </c>
@@ -51994,7 +52006,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11">
+    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1017" s="15">
         <v>46001</v>
       </c>
@@ -52030,7 +52042,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11">
+    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1018" s="15">
         <v>46008</v>
       </c>
@@ -52066,7 +52078,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11">
+    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1019" s="15">
         <v>46015</v>
       </c>
@@ -52102,7 +52114,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11">
+    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1020" s="15">
         <v>46022</v>
       </c>
@@ -52138,7 +52150,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11">
+    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1021" s="15">
         <v>46029</v>
       </c>
@@ -52174,7 +52186,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11">
+    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1022" s="15">
         <v>46036</v>
       </c>
@@ -52210,7 +52222,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11">
+    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1023" s="15">
         <v>46043</v>
       </c>
@@ -52246,7 +52258,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11">
+    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1024" s="15">
         <v>46050</v>
       </c>
@@ -52282,7 +52294,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11">
+    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1025" s="15">
         <v>46057</v>
       </c>
@@ -52318,7 +52330,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11">
+    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1026" s="15">
         <v>46064</v>
       </c>
@@ -52354,7 +52366,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11">
+    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1027" s="15">
         <v>46071</v>
       </c>
@@ -52405,7 +52417,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11">
+    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1028" s="15">
         <v>46078</v>
       </c>
@@ -52441,7 +52453,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11">
+    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1029" s="15">
         <v>46085</v>
       </c>
@@ -52477,7 +52489,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11">
+    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1030" s="15">
         <v>46092</v>
       </c>
@@ -52513,7 +52525,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11">
+    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1031" s="15">
         <v>46099</v>
       </c>
@@ -52549,7 +52561,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="1032" spans="1:11">
+    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1032" s="15">
         <v>46106</v>
       </c>
@@ -52600,7 +52612,7 @@
         <v>47.03</v>
       </c>
     </row>
-    <row r="1033" spans="1:11">
+    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1033" s="15">
         <v>46113</v>
       </c>
@@ -52636,7 +52648,7 @@
         <v>55.64</v>
       </c>
     </row>
-    <row r="1034" spans="1:11">
+    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1034" s="15">
         <v>46120</v>
       </c>
@@ -52647,7 +52659,7 @@
         <v>0.41666666666668001</v>
       </c>
       <c r="D1034" s="15" t="str">
-        <f t="shared" ref="D1034:D1035" si="18">IF(
+        <f t="shared" ref="D1034:D1036" si="18">IF(
  AND(
   B1034 &gt;= IF(
          YEAR(B1034)&gt;=2007,
@@ -52687,7 +52699,7 @@
         <v>51.31</v>
       </c>
     </row>
-    <row r="1035" spans="1:11">
+    <row r="1035" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1035" s="15">
         <v>46127</v>
       </c>
@@ -52721,6 +52733,42 @@
       </c>
       <c r="K1035" s="7">
         <v>68.87</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1036" s="15">
+        <v>46134</v>
+      </c>
+      <c r="B1036" s="15">
+        <v>46135</v>
+      </c>
+      <c r="C1036" s="17">
+        <v>0.416666666666692</v>
+      </c>
+      <c r="D1036" s="15" t="str">
+        <f t="shared" si="18"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1036" s="7">
+        <v>94.15</v>
+      </c>
+      <c r="F1036" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1036" s="7">
+        <v>80</v>
+      </c>
+      <c r="H1036" s="9">
+        <v>100</v>
+      </c>
+      <c r="I1036" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1036" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1036" s="7">
+        <v>51.9</v>
       </c>
     </row>
   </sheetData>
@@ -52733,7 +52781,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52744,9 +52792,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -52754,7 +52802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDCEA53C-672B-4DAB-9E1D-DB9E0D84A23A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8EA0616-2DC9-44BB-8339-51A76115A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3857,6 +3857,12 @@
                 <c:pt idx="1034">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="1035">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6970,6 +6976,12 @@
                 </c:pt>
                 <c:pt idx="1034">
                   <c:v>94.15</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>93.79</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>96.67</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10340,6 +10352,12 @@
                 <c:pt idx="1034">
                   <c:v>46135</c:v>
                 </c:pt>
+                <c:pt idx="1035">
+                  <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>46149</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13453,6 +13471,12 @@
                 </c:pt>
                 <c:pt idx="1034">
                   <c:v>51.9</c:v>
+                </c:pt>
+                <c:pt idx="1035">
+                  <c:v>48.61</c:v>
+                </c:pt>
+                <c:pt idx="1036">
+                  <c:v>43.28</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15159,7 +15183,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1036"/>
+  <dimension ref="A1:K1038"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.69921875" style="15" bestFit="1" customWidth="1"/>
@@ -52769,6 +52793,93 @@
       </c>
       <c r="K1036" s="7">
         <v>51.9</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1037" s="15">
+        <v>46141</v>
+      </c>
+      <c r="B1037" s="15">
+        <v>46142</v>
+      </c>
+      <c r="C1037" s="17">
+        <v>0.41666666666669799</v>
+      </c>
+      <c r="D1037" s="15" t="str">
+        <f t="shared" ref="D1037:D1038" si="19">IF(
+ AND(
+  B1037 &gt;= IF(
+         YEAR(B1037)&gt;=2007,
+         DATE(YEAR(B1037),3,14)-WEEKDAY(DATE(YEAR(B1037),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1037),4,7)-WEEKDAY(DATE(YEAR(B1037),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1037 &lt;  IF(
+         YEAR(B1037)&gt;=2007,
+         DATE(YEAR(B1037),11,7)-WEEKDAY(DATE(YEAR(B1037),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1037),10,31)-WEEKDAY(DATE(YEAR(B1037),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1037" s="7">
+        <v>93.79</v>
+      </c>
+      <c r="F1037" s="8">
+        <v>-50</v>
+      </c>
+      <c r="G1037" s="7">
+        <v>80</v>
+      </c>
+      <c r="H1037" s="9">
+        <v>100</v>
+      </c>
+      <c r="I1037" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1037" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1037" s="7">
+        <v>48.61</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1038" s="15">
+        <v>46148</v>
+      </c>
+      <c r="B1038" s="15">
+        <v>46149</v>
+      </c>
+      <c r="C1038" s="17">
+        <v>0.41666666666670399</v>
+      </c>
+      <c r="D1038" s="15" t="str">
+        <f t="shared" si="19"/>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1038" s="7">
+        <v>96.67</v>
+      </c>
+      <c r="F1038" s="8">
+        <v>0</v>
+      </c>
+      <c r="G1038" s="7">
+        <v>87.5</v>
+      </c>
+      <c r="H1038" s="9">
+        <v>100</v>
+      </c>
+      <c r="I1038" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1038" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1038" s="7">
+        <v>43.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC4C067B-3E3C-4719-9AB4-09C37BF1CA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A41448-21E9-47DC-9546-E8FA93381990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -650,50 +650,50 @@
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +711,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3866,6 +3866,9 @@
                 <c:pt idx="1037">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="1038">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -6988,6 +6991,9 @@
                 </c:pt>
                 <c:pt idx="1037">
                   <c:v>77.34</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>82.02</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7204,7 +7210,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -10367,6 +10373,9 @@
                 <c:pt idx="1037">
                   <c:v>46156</c:v>
                 </c:pt>
+                <c:pt idx="1038">
+                  <c:v>46163</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13489,6 +13498,9 @@
                 </c:pt>
                 <c:pt idx="1037">
                   <c:v>68.17</c:v>
+                </c:pt>
+                <c:pt idx="1038">
+                  <c:v>55.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -14899,9 +14911,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14939,7 +14951,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15045,7 +15057,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15187,7 +15199,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15195,21 +15207,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1039"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6"/>
+  <dimension ref="A1:K1040"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6328125" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="10"/>
+    <col min="11" max="11" width="21.6328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1">
@@ -52930,6 +52942,57 @@
         <v>68.17</v>
       </c>
     </row>
+    <row r="1040" spans="1:11">
+      <c r="A1040" s="15">
+        <v>46162</v>
+      </c>
+      <c r="B1040" s="15">
+        <v>46163</v>
+      </c>
+      <c r="C1040" s="17">
+        <v>0.41666666666671598</v>
+      </c>
+      <c r="D1040" s="15" t="str">
+        <f t="shared" ref="D1040" si="20">IF(
+ AND(
+  B1040 &gt;= IF(
+         YEAR(B1040)&gt;=2007,
+         DATE(YEAR(B1040),3,14)-WEEKDAY(DATE(YEAR(B1040),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1040),4,7)-WEEKDAY(DATE(YEAR(B1040),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1040 &lt;  IF(
+         YEAR(B1040)&gt;=2007,
+         DATE(YEAR(B1040),11,7)-WEEKDAY(DATE(YEAR(B1040),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1040),10,31)-WEEKDAY(DATE(YEAR(B1040),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1040" s="7">
+        <v>82.02</v>
+      </c>
+      <c r="F1040" s="8">
+        <v>-100</v>
+      </c>
+      <c r="G1040" s="7">
+        <v>69</v>
+      </c>
+      <c r="H1040" s="9">
+        <v>96</v>
+      </c>
+      <c r="I1040" s="9">
+        <v>100</v>
+      </c>
+      <c r="J1040" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1040" s="7">
+        <v>55.01</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52940,7 +53003,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -52951,7 +53014,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5A41448-21E9-47DC-9546-E8FA93381990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -650,50 +650,50 @@
     </xf>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Comma" xfId="42" builtinId="3"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
+    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -711,7 +711,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7210,7 +7210,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14911,9 +14911,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -14951,7 +14951,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15057,7 +15057,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15199,7 +15199,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15208,20 +15208,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1040"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.6328125" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.36328125" style="17" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.453125" style="15" customWidth="1"/>
-    <col min="5" max="5" width="11.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.44140625" style="15" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.453125" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6328125" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.90625" style="10"/>
+    <col min="11" max="11" width="21.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="6" customFormat="1">
@@ -53003,7 +53003,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53014,7 +53014,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="2:3">
       <c r="B2" t="s">

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1BE83C-9FC4-4EF5-ACF9-268FB060E6E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90ABC82-169A-434B-8AD7-D273486CD01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3891,6 +3891,9 @@
                 <c:pt idx="1039">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="1040">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7019,6 +7022,9 @@
                 </c:pt>
                 <c:pt idx="1039">
                   <c:v>98.39</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>86.82</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10423,6 +10429,9 @@
                 <c:pt idx="1039">
                   <c:v>46170</c:v>
                 </c:pt>
+                <c:pt idx="1040">
+                  <c:v>46177</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13551,6 +13560,9 @@
                 </c:pt>
                 <c:pt idx="1039">
                   <c:v>47.62</c:v>
+                </c:pt>
+                <c:pt idx="1040">
+                  <c:v>72.069999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15257,7 +15269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1041"/>
+  <dimension ref="A1:K1042"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="12.6328125" style="15" bestFit="1" customWidth="1"/>
@@ -53077,6 +53089,57 @@
       </c>
       <c r="K1041" s="7">
         <v>47.62</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:11">
+      <c r="A1042" s="15">
+        <v>46176</v>
+      </c>
+      <c r="B1042" s="15">
+        <v>46177</v>
+      </c>
+      <c r="C1042" s="17">
+        <v>0.41666666666672802</v>
+      </c>
+      <c r="D1042" s="15" t="str">
+        <f t="shared" ref="D1042" si="21">IF(
+ AND(
+  B1042 &gt;= IF(
+         YEAR(B1042)&gt;=2007,
+         DATE(YEAR(B1042),3,14)-WEEKDAY(DATE(YEAR(B1042),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1042),4,7)-WEEKDAY(DATE(YEAR(B1042),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1042 &lt;  IF(
+         YEAR(B1042)&gt;=2007,
+         DATE(YEAR(B1042),11,7)-WEEKDAY(DATE(YEAR(B1042),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1042),10,31)-WEEKDAY(DATE(YEAR(B1042),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1042" s="7">
+        <v>86.82</v>
+      </c>
+      <c r="F1042" s="8">
+        <v>-200</v>
+      </c>
+      <c r="G1042" s="7">
+        <v>85.75</v>
+      </c>
+      <c r="H1042" s="9">
+        <v>95</v>
+      </c>
+      <c r="I1042" s="9">
+        <v>103.75</v>
+      </c>
+      <c r="J1042" s="9">
+        <v>200</v>
+      </c>
+      <c r="K1042" s="7">
+        <v>72.069999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data/sentiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1E85F8-AECB-4309-8B9E-AF4A2A8AD355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D44D321-7CC4-B243-BC51-721EC110B765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22160" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
     <numFmt numFmtId="166" formatCode="0.00_ "/>
     <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,7 +592,7 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -613,10 +613,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1">
@@ -628,59 +628,58 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="44">
-    <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - 강조색6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - 강조색6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - 강조색6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="강조색1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="강조색2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="강조색3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="강조색4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="강조색5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="강조색6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="경고문" xfId="14" builtinId="11" customBuiltin="1"/>
-    <cellStyle name="계산" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="나쁨" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="메모" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="보통" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="설명 텍스트" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="셀 확인" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="쉼표" xfId="42" builtinId="3"/>
-    <cellStyle name="연결된 셀" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="요약" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="입력" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="제목" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="제목 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="제목 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="제목 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="제목 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="43" builtinId="8"/>
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Comma" xfId="42" builtinId="3"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="43" builtinId="8"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -698,7 +697,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7234,7 +7233,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -14972,9 +14971,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -15012,7 +15011,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -15118,7 +15117,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -15260,7 +15259,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15269,23 +15268,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K1043"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.44140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.44140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="13"/>
+    <col min="1" max="1" width="10.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.1640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="7" customFormat="1">
+    <row r="1" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -15320,7 +15319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>38903</v>
       </c>
@@ -15371,7 +15370,7 @@
         <v>55.55</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>38910</v>
       </c>
@@ -15422,7 +15421,7 @@
         <v>47.84</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>38903</v>
       </c>
@@ -15458,7 +15457,7 @@
         <v>55.549999722194443</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>38910</v>
       </c>
@@ -15494,7 +15493,7 @@
         <v>47.838896308338889</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>38917</v>
       </c>
@@ -15530,7 +15529,7 @@
         <v>38.170438823780898</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>38924</v>
       </c>
@@ -15566,7 +15565,7 @@
         <v>33.778460222455372</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>38931</v>
       </c>
@@ -15602,7 +15601,7 @@
         <v>43.692625871599382</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>38938</v>
       </c>
@@ -15638,7 +15637,7 @@
         <v>47.483927790753583</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>38945</v>
       </c>
@@ -15674,7 +15673,7 @@
         <v>56.524684873071166</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>38952</v>
       </c>
@@ -15710,7 +15709,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>38959</v>
       </c>
@@ -15746,7 +15745,7 @@
         <v>45.170475778833321</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>38966</v>
       </c>
@@ -15782,7 +15781,7 @@
         <v>50.374290674884271</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>38973</v>
       </c>
@@ -15818,7 +15817,7 @@
         <v>56.228640389040173</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>38980</v>
       </c>
@@ -15854,7 +15853,7 @@
         <v>31.264996401726965</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>38987</v>
       </c>
@@ -15890,7 +15889,7 @@
         <v>55.807410979021469</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>38994</v>
       </c>
@@ -15926,7 +15925,7 @@
         <v>59.404629449227272</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>39001</v>
       </c>
@@ -15962,7 +15961,7 @@
         <v>59.825434763385545</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>39008</v>
       </c>
@@ -15998,7 +15997,7 @@
         <v>33.215082952435786</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>39015</v>
       </c>
@@ -16034,7 +16033,7 @@
         <v>53.121506002748077</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>39022</v>
       </c>
@@ -16070,7 +16069,7 @@
         <v>53.864396997357062</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>39029</v>
       </c>
@@ -16106,7 +16105,7 @@
         <v>46.653652879834993</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>39036</v>
       </c>
@@ -16142,7 +16141,7 @@
         <v>61.297793607386772</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>39043</v>
       </c>
@@ -16178,7 +16177,7 @@
         <v>20.824828195876073</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>39050</v>
       </c>
@@ -16214,7 +16213,7 @@
         <v>38.414042173363363</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>39057</v>
       </c>
@@ -16250,7 +16249,7 @@
         <v>58.029540018794734</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>39064</v>
       </c>
@@ -16286,7 +16285,7 @@
         <v>19.415261547359616</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>39071</v>
       </c>
@@ -16322,7 +16321,7 @@
         <v>22.354395725773102</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>39078</v>
       </c>
@@ -16358,7 +16357,7 @@
         <v>35.213204259954928</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>39085</v>
       </c>
@@ -16394,7 +16393,7 @@
         <v>32.236442245024186</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>39092</v>
       </c>
@@ -16430,7 +16429,7 @@
         <v>65.212862654704111</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="8">
         <v>39099</v>
       </c>
@@ -16466,7 +16465,7 @@
         <v>27.899999503569333</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" s="8">
         <v>39106</v>
       </c>
@@ -16502,7 +16501,7 @@
         <v>42.723911860082509</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="8">
         <v>39113</v>
       </c>
@@ -16538,7 +16537,7 @@
         <v>49.378006237595294</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" s="8">
         <v>39120</v>
       </c>
@@ -16574,7 +16573,7 @@
         <v>45.927163507298019</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="8">
         <v>39127</v>
       </c>
@@ -16610,7 +16609,7 @@
         <v>55.649805268718424</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" s="8">
         <v>39134</v>
       </c>
@@ -16646,7 +16645,7 @@
         <v>52.764818137257436</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="8">
         <v>39141</v>
       </c>
@@ -16682,7 +16681,7 @@
         <v>53.726231363347424</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" s="8">
         <v>39148</v>
       </c>
@@ -16718,7 +16717,7 @@
         <v>48.602880573068916</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" s="8">
         <v>39155</v>
       </c>
@@ -16754,7 +16753,7 @@
         <v>68.635171039352031</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" s="8">
         <v>39162</v>
       </c>
@@ -16790,7 +16789,7 @@
         <v>54.906588487696794</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="8">
         <v>39169</v>
       </c>
@@ -16826,7 +16825,7 @@
         <v>61.630606010506028</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" s="8">
         <v>39176</v>
       </c>
@@ -16862,7 +16861,7 @@
         <v>64.537968733792852</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="8">
         <v>39183</v>
       </c>
@@ -16898,7 +16897,7 @@
         <v>57.825060311252592</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="8">
         <v>39190</v>
       </c>
@@ -16934,7 +16933,7 @@
         <v>69.279479346364909</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="8">
         <v>39197</v>
       </c>
@@ -16970,7 +16969,7 @@
         <v>59.001416591157486</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A47" s="8">
         <v>39204</v>
       </c>
@@ -17006,7 +17005,7 @@
         <v>59.063995424924954</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="8">
         <v>39211</v>
       </c>
@@ -17042,7 +17041,7 @@
         <v>55.064860745205635</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A49" s="8">
         <v>39218</v>
       </c>
@@ -17078,7 +17077,7 @@
         <v>51.819247148139851</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="8">
         <v>39225</v>
       </c>
@@ -17114,7 +17113,7 @@
         <v>53.983793864455286</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="8">
         <v>39232</v>
       </c>
@@ -17150,7 +17149,7 @@
         <v>48.786852991286374</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="8">
         <v>39239</v>
       </c>
@@ -17186,7 +17185,7 @@
         <v>62.811083593759328</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A53" s="8">
         <v>39246</v>
       </c>
@@ -17222,7 +17221,7 @@
         <v>65.542340513594723</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A54" s="8">
         <v>39253</v>
       </c>
@@ -17258,7 +17257,7 @@
         <v>67.954431672633518</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A55" s="8">
         <v>39260</v>
       </c>
@@ -17294,7 +17293,7 @@
         <v>55.826175891531534</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A56" s="8">
         <v>39268</v>
       </c>
@@ -17330,7 +17329,7 @@
         <v>60.176790324426577</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A57" s="8">
         <v>39274</v>
       </c>
@@ -17366,7 +17365,7 @@
         <v>51.354938031690303</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A58" s="8">
         <v>39281</v>
       </c>
@@ -17402,7 +17401,7 @@
         <v>45.888802797874582</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A59" s="8">
         <v>39288</v>
       </c>
@@ -17438,7 +17437,7 @@
         <v>63.76609180512709</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A60" s="8">
         <v>39295</v>
       </c>
@@ -17474,7 +17473,7 @@
         <v>59.657354953098618</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A61" s="8">
         <v>39302</v>
       </c>
@@ -17510,7 +17509,7 @@
         <v>65.099669293697346</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A62" s="8">
         <v>39309</v>
       </c>
@@ -17546,7 +17545,7 @@
         <v>57.034529015325447</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A63" s="8">
         <v>39316</v>
       </c>
@@ -17582,7 +17581,7 @@
         <v>52.701658833000693</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A64" s="8">
         <v>39323</v>
       </c>
@@ -17618,7 +17617,7 @@
         <v>72.566359583555496</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A65" s="8">
         <v>39330</v>
       </c>
@@ -17654,7 +17653,7 @@
         <v>45.022968675258781</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A66" s="8">
         <v>39337</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>69.603104472428257</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A67" s="8">
         <v>39344</v>
       </c>
@@ -17741,7 +17740,7 @@
         <v>42.408304442812678</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A68" s="8">
         <v>39351</v>
       </c>
@@ -17777,7 +17776,7 @@
         <v>38.186796212286225</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A69" s="8">
         <v>39358</v>
       </c>
@@ -17813,7 +17812,7 @@
         <v>61.369548273391054</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A70" s="8">
         <v>39365</v>
       </c>
@@ -17849,7 +17848,7 @@
         <v>56.227919122877815</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A71" s="8">
         <v>39372</v>
       </c>
@@ -17885,7 +17884,7 @@
         <v>49.208363214031834</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="8">
         <v>39379</v>
       </c>
@@ -17921,7 +17920,7 @@
         <v>65.850867379966061</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A73" s="8">
         <v>39386</v>
       </c>
@@ -17957,7 +17956,7 @@
         <v>75.074716234904798</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A74" s="8">
         <v>39393</v>
       </c>
@@ -17993,7 +17992,7 @@
         <v>52.534527153195896</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" s="8">
         <v>39400</v>
       </c>
@@ -18029,7 +18028,7 @@
         <v>40.679745770792763</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A76" s="8">
         <v>39407</v>
       </c>
@@ -18065,7 +18064,7 @@
         <v>60.493442596881707</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" s="8">
         <v>39414</v>
       </c>
@@ -18101,7 +18100,7 @@
         <v>68.934714752142</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" s="8">
         <v>39421</v>
       </c>
@@ -18137,7 +18136,7 @@
         <v>60.536316005812211</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" s="8">
         <v>39428</v>
       </c>
@@ -18173,7 +18172,7 @@
         <v>69.021440028975547</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" s="8">
         <v>39435</v>
       </c>
@@ -18209,7 +18208,7 @@
         <v>71.467344717337483</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A81" s="8">
         <v>39442</v>
       </c>
@@ -18245,7 +18244,7 @@
         <v>50.496362770611753</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A82" s="8">
         <v>39449</v>
       </c>
@@ -18281,7 +18280,7 @@
         <v>55.229668567997003</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A83" s="8">
         <v>39456</v>
       </c>
@@ -18317,7 +18316,7 @@
         <v>75.139220764041383</v>
       </c>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A84" s="8">
         <v>39463</v>
       </c>
@@ -18353,7 +18352,7 @@
         <v>58.387484404345059</v>
       </c>
     </row>
-    <row r="85" spans="1:11">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A85" s="8">
         <v>39470</v>
       </c>
@@ -18389,7 +18388,7 @@
         <v>74.040278246155765</v>
       </c>
     </row>
-    <row r="86" spans="1:11">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A86" s="8">
         <v>39477</v>
       </c>
@@ -18425,7 +18424,7 @@
         <v>62.164148383994373</v>
       </c>
     </row>
-    <row r="87" spans="1:11">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A87" s="8">
         <v>39484</v>
       </c>
@@ -18461,7 +18460,7 @@
         <v>70.447213919214661</v>
       </c>
     </row>
-    <row r="88" spans="1:11">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A88" s="8">
         <v>39491</v>
       </c>
@@ -18497,7 +18496,7 @@
         <v>74.676338659280532</v>
       </c>
     </row>
-    <row r="89" spans="1:11">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A89" s="8">
         <v>39498</v>
       </c>
@@ -18533,7 +18532,7 @@
         <v>57.328488167363666</v>
       </c>
     </row>
-    <row r="90" spans="1:11">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A90" s="8">
         <v>39505</v>
       </c>
@@ -18569,7 +18568,7 @@
         <v>82.926777823027351</v>
       </c>
     </row>
-    <row r="91" spans="1:11">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A91" s="8">
         <v>39512</v>
       </c>
@@ -18605,7 +18604,7 @@
         <v>56.330836013124284</v>
       </c>
     </row>
-    <row r="92" spans="1:11">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A92" s="8">
         <v>39519</v>
       </c>
@@ -18641,7 +18640,7 @@
         <v>63.152843166400672</v>
       </c>
     </row>
-    <row r="93" spans="1:11">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A93" s="8">
         <v>39526</v>
       </c>
@@ -18677,7 +18676,7 @@
         <v>44.173359780366653</v>
       </c>
     </row>
-    <row r="94" spans="1:11">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A94" s="8">
         <v>39533</v>
       </c>
@@ -18713,7 +18712,7 @@
         <v>69.09468937538611</v>
       </c>
     </row>
-    <row r="95" spans="1:11">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A95" s="8">
         <v>39540</v>
       </c>
@@ -18749,7 +18748,7 @@
         <v>72.946618726802328</v>
       </c>
     </row>
-    <row r="96" spans="1:11">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A96" s="8">
         <v>39547</v>
       </c>
@@ -18785,7 +18784,7 @@
         <v>69.469947459315094</v>
       </c>
     </row>
-    <row r="97" spans="1:11">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A97" s="8">
         <v>39554</v>
       </c>
@@ -18821,7 +18820,7 @@
         <v>56.323052699867915</v>
       </c>
     </row>
-    <row r="98" spans="1:11">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A98" s="8">
         <v>39561</v>
       </c>
@@ -18857,7 +18856,7 @@
         <v>41.974862158849767</v>
       </c>
     </row>
-    <row r="99" spans="1:11">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A99" s="8">
         <v>39569</v>
       </c>
@@ -18893,7 +18892,7 @@
         <v>44.962229438992097</v>
       </c>
     </row>
-    <row r="100" spans="1:11">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A100" s="8">
         <v>39575</v>
       </c>
@@ -18929,7 +18928,7 @@
         <v>37.798178950335576</v>
       </c>
     </row>
-    <row r="101" spans="1:11">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A101" s="8">
         <v>39582</v>
       </c>
@@ -18965,7 +18964,7 @@
         <v>68.460251596471679</v>
       </c>
     </row>
-    <row r="102" spans="1:11">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A102" s="8">
         <v>39589</v>
       </c>
@@ -19001,7 +19000,7 @@
         <v>65.70356446097523</v>
       </c>
     </row>
-    <row r="103" spans="1:11">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A103" s="8">
         <v>39596</v>
       </c>
@@ -19037,7 +19036,7 @@
         <v>66.213667550072984</v>
       </c>
     </row>
-    <row r="104" spans="1:11">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A104" s="8">
         <v>39603</v>
       </c>
@@ -19073,7 +19072,7 @@
         <v>65.788974489430842</v>
       </c>
     </row>
-    <row r="105" spans="1:11">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A105" s="8">
         <v>39610</v>
       </c>
@@ -19109,7 +19108,7 @@
         <v>78.830161121302538</v>
       </c>
     </row>
-    <row r="106" spans="1:11" s="14" customFormat="1">
+    <row r="106" spans="1:11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="8">
         <v>39617</v>
       </c>
@@ -19145,7 +19144,7 @@
         <v>65.083754207393383</v>
       </c>
     </row>
-    <row r="107" spans="1:11">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A107" s="8">
         <v>39624</v>
       </c>
@@ -19181,7 +19180,7 @@
         <v>55.264758647687017</v>
       </c>
     </row>
-    <row r="108" spans="1:11">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A108" s="8">
         <v>39631</v>
       </c>
@@ -19217,7 +19216,7 @@
         <v>52.723327174933317</v>
       </c>
     </row>
-    <row r="109" spans="1:11" s="14" customFormat="1">
+    <row r="109" spans="1:11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="8">
         <v>39638</v>
       </c>
@@ -19253,7 +19252,7 @@
         <v>75.848904583590468</v>
       </c>
     </row>
-    <row r="110" spans="1:11">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A110" s="8">
         <v>39645</v>
       </c>
@@ -19289,7 +19288,7 @@
         <v>51.278326455349131</v>
       </c>
     </row>
-    <row r="111" spans="1:11">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A111" s="8">
         <v>39652</v>
       </c>
@@ -19325,7 +19324,7 @@
         <v>57.909108469652679</v>
       </c>
     </row>
-    <row r="112" spans="1:11">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A112" s="8">
         <v>39659</v>
       </c>
@@ -19361,7 +19360,7 @@
         <v>61.750517406739192</v>
       </c>
     </row>
-    <row r="113" spans="1:11">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A113" s="8">
         <v>39666</v>
       </c>
@@ -19397,7 +19396,7 @@
         <v>52.661575232504951</v>
       </c>
     </row>
-    <row r="114" spans="1:11">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A114" s="8">
         <v>39673</v>
       </c>
@@ -19433,7 +19432,7 @@
         <v>53.118250871076597</v>
       </c>
     </row>
-    <row r="115" spans="1:11">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A115" s="8">
         <v>39681</v>
       </c>
@@ -19469,7 +19468,7 @@
         <v>50.104043997600584</v>
       </c>
     </row>
-    <row r="116" spans="1:11">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A116" s="8">
         <v>39687</v>
       </c>
@@ -19505,7 +19504,7 @@
         <v>50.177676148596895</v>
       </c>
     </row>
-    <row r="117" spans="1:11">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A117" s="8">
         <v>39694</v>
       </c>
@@ -19541,7 +19540,7 @@
         <v>65.073504542370074</v>
       </c>
     </row>
-    <row r="118" spans="1:11">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A118" s="8">
         <v>39701</v>
       </c>
@@ -19577,7 +19576,7 @@
         <v>44.254182598587626</v>
       </c>
     </row>
-    <row r="119" spans="1:11">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A119" s="8">
         <v>39708</v>
       </c>
@@ -19613,7 +19612,7 @@
         <v>47.422942867393644</v>
       </c>
     </row>
-    <row r="120" spans="1:11">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A120" s="8">
         <v>39715</v>
       </c>
@@ -19649,7 +19648,7 @@
         <v>46.359571574198242</v>
       </c>
     </row>
-    <row r="121" spans="1:11">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A121" s="8">
         <v>39722</v>
       </c>
@@ -19685,7 +19684,7 @@
         <v>33.405873873919091</v>
       </c>
     </row>
-    <row r="122" spans="1:11">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A122" s="8">
         <v>39729</v>
       </c>
@@ -19721,7 +19720,7 @@
         <v>51.281080608690978</v>
       </c>
     </row>
-    <row r="123" spans="1:11">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A123" s="8">
         <v>39736</v>
       </c>
@@ -19757,7 +19756,7 @@
         <v>40.551750201988128</v>
       </c>
     </row>
-    <row r="124" spans="1:11">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A124" s="8">
         <v>39743</v>
       </c>
@@ -19793,7 +19792,7 @@
         <v>44.129844927173707</v>
       </c>
     </row>
-    <row r="125" spans="1:11">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A125" s="8">
         <v>39750</v>
       </c>
@@ -19829,7 +19828,7 @@
         <v>53.882588406027168</v>
       </c>
     </row>
-    <row r="126" spans="1:11">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A126" s="8">
         <v>39757</v>
       </c>
@@ -19865,7 +19864,7 @@
         <v>49.886350075701394</v>
       </c>
     </row>
-    <row r="127" spans="1:11">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A127" s="8">
         <v>39764</v>
       </c>
@@ -19901,7 +19900,7 @@
         <v>44.405800463275128</v>
       </c>
     </row>
-    <row r="128" spans="1:11">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A128" s="8">
         <v>39771</v>
       </c>
@@ -19937,7 +19936,7 @@
         <v>43.976952126529874</v>
       </c>
     </row>
-    <row r="129" spans="1:11">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" s="8">
         <v>39778</v>
       </c>
@@ -19973,7 +19972,7 @@
         <v>57.854397526301433</v>
       </c>
     </row>
-    <row r="130" spans="1:11">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="8">
         <v>39785</v>
       </c>
@@ -20009,7 +20008,7 @@
         <v>45.357327933111691</v>
       </c>
     </row>
-    <row r="131" spans="1:11">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="8">
         <v>39792</v>
       </c>
@@ -20060,7 +20059,7 @@
         <v>49.214072926201013</v>
       </c>
     </row>
-    <row r="132" spans="1:11">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="8">
         <v>39799</v>
       </c>
@@ -20096,7 +20095,7 @@
         <v>53.491406900967732</v>
       </c>
     </row>
-    <row r="133" spans="1:11">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="8">
         <v>39806</v>
       </c>
@@ -20132,7 +20131,7 @@
         <v>55.286482576750558</v>
       </c>
     </row>
-    <row r="134" spans="1:11">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="8">
         <v>39813</v>
       </c>
@@ -20168,7 +20167,7 @@
         <v>55.143723549589758</v>
       </c>
     </row>
-    <row r="135" spans="1:11">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="8">
         <v>39820</v>
       </c>
@@ -20204,7 +20203,7 @@
         <v>51.012811516083978</v>
       </c>
     </row>
-    <row r="136" spans="1:11">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="8">
         <v>39827</v>
       </c>
@@ -20240,7 +20239,7 @@
         <v>64.584992254313974</v>
       </c>
     </row>
-    <row r="137" spans="1:11">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="8">
         <v>39834</v>
       </c>
@@ -20276,7 +20275,7 @@
         <v>51.036330889936345</v>
       </c>
     </row>
-    <row r="138" spans="1:11">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="8">
         <v>39841</v>
       </c>
@@ -20312,7 +20311,7 @@
         <v>49.006860617093729</v>
       </c>
     </row>
-    <row r="139" spans="1:11">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" s="8">
         <v>39848</v>
       </c>
@@ -20348,7 +20347,7 @@
         <v>33.08758938678627</v>
       </c>
     </row>
-    <row r="140" spans="1:11">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A140" s="8">
         <v>39855</v>
       </c>
@@ -20384,7 +20383,7 @@
         <v>42.688334209137516</v>
       </c>
     </row>
-    <row r="141" spans="1:11">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" s="8">
         <v>39862</v>
       </c>
@@ -20420,7 +20419,7 @@
         <v>49.836210913235156</v>
       </c>
     </row>
-    <row r="142" spans="1:11">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" s="8">
         <v>39869</v>
       </c>
@@ -20456,7 +20455,7 @@
         <v>46.376897362766087</v>
       </c>
     </row>
-    <row r="143" spans="1:11">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" s="8">
         <v>39876</v>
       </c>
@@ -20492,7 +20491,7 @@
         <v>48.797982331083887</v>
       </c>
     </row>
-    <row r="144" spans="1:11">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" s="8">
         <v>39883</v>
       </c>
@@ -20528,7 +20527,7 @@
         <v>50.995285896575474</v>
       </c>
     </row>
-    <row r="145" spans="1:11">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" s="8">
         <v>39890</v>
       </c>
@@ -20564,7 +20563,7 @@
         <v>50.632752300623871</v>
       </c>
     </row>
-    <row r="146" spans="1:11">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" s="8">
         <v>39897</v>
       </c>
@@ -20600,7 +20599,7 @@
         <v>49.159815906896966</v>
       </c>
     </row>
-    <row r="147" spans="1:11">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" s="8">
         <v>39904</v>
       </c>
@@ -20636,7 +20635,7 @@
         <v>67.93322071407249</v>
       </c>
     </row>
-    <row r="148" spans="1:11">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" s="8">
         <v>39911</v>
       </c>
@@ -20672,7 +20671,7 @@
         <v>59.144140747470985</v>
       </c>
     </row>
-    <row r="149" spans="1:11">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" s="8">
         <v>39918</v>
       </c>
@@ -20708,7 +20707,7 @@
         <v>48.417328037810883</v>
       </c>
     </row>
-    <row r="150" spans="1:11">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" s="8">
         <v>39925</v>
       </c>
@@ -20744,7 +20743,7 @@
         <v>65.507189828231219</v>
       </c>
     </row>
-    <row r="151" spans="1:11">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" s="8">
         <v>39932</v>
       </c>
@@ -20780,7 +20779,7 @@
         <v>67.77459535800439</v>
       </c>
     </row>
-    <row r="152" spans="1:11">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" s="8">
         <v>39939</v>
       </c>
@@ -20816,7 +20815,7 @@
         <v>67.144419826628891</v>
       </c>
     </row>
-    <row r="153" spans="1:11">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" s="8">
         <v>39946</v>
       </c>
@@ -20852,7 +20851,7 @@
         <v>50.709106035336958</v>
       </c>
     </row>
-    <row r="154" spans="1:11">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" s="8">
         <v>39953</v>
       </c>
@@ -20888,7 +20887,7 @@
         <v>45.673803993182069</v>
       </c>
     </row>
-    <row r="155" spans="1:11">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" s="8">
         <v>39960</v>
       </c>
@@ -20924,7 +20923,7 @@
         <v>56.578290137928242</v>
       </c>
     </row>
-    <row r="156" spans="1:11">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" s="8">
         <v>39967</v>
       </c>
@@ -20960,7 +20959,7 @@
         <v>65.158129608233793</v>
       </c>
     </row>
-    <row r="157" spans="1:11">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" s="8">
         <v>39974</v>
       </c>
@@ -20996,7 +20995,7 @@
         <v>44.471505975736868</v>
       </c>
     </row>
-    <row r="158" spans="1:11">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" s="8">
         <v>39981</v>
       </c>
@@ -21032,7 +21031,7 @@
         <v>52.627079222161107</v>
       </c>
     </row>
-    <row r="159" spans="1:11">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" s="8">
         <v>39988</v>
       </c>
@@ -21068,7 +21067,7 @@
         <v>66.261051954921754</v>
       </c>
     </row>
-    <row r="160" spans="1:11">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="8">
         <v>39995</v>
       </c>
@@ -21104,7 +21103,7 @@
         <v>54.893058424976317</v>
       </c>
     </row>
-    <row r="161" spans="1:11">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="8">
         <v>40002</v>
       </c>
@@ -21140,7 +21139,7 @@
         <v>64.161205849108597</v>
       </c>
     </row>
-    <row r="162" spans="1:11">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="8">
         <v>40009</v>
       </c>
@@ -21176,7 +21175,7 @@
         <v>52.811235830415114</v>
       </c>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="8">
         <v>40016</v>
       </c>
@@ -21212,7 +21211,7 @@
         <v>57.645867319279404</v>
       </c>
     </row>
-    <row r="164" spans="1:11">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="8">
         <v>40023</v>
       </c>
@@ -21248,7 +21247,7 @@
         <v>61.365403956693434</v>
       </c>
     </row>
-    <row r="165" spans="1:11">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="8">
         <v>40030</v>
       </c>
@@ -21284,7 +21283,7 @@
         <v>44.582988427682338</v>
       </c>
     </row>
-    <row r="166" spans="1:11">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="8">
         <v>40037</v>
       </c>
@@ -21320,7 +21319,7 @@
         <v>54.166951121047973</v>
       </c>
     </row>
-    <row r="167" spans="1:11">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="8">
         <v>40044</v>
       </c>
@@ -21356,7 +21355,7 @@
         <v>76.385981144531414</v>
       </c>
     </row>
-    <row r="168" spans="1:11">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="8">
         <v>40051</v>
       </c>
@@ -21392,7 +21391,7 @@
         <v>71.141667275747665</v>
       </c>
     </row>
-    <row r="169" spans="1:11">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="8">
         <v>40058</v>
       </c>
@@ -21428,7 +21427,7 @@
         <v>81.41339889263179</v>
       </c>
     </row>
-    <row r="170" spans="1:11">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="8">
         <v>40065</v>
       </c>
@@ -21464,7 +21463,7 @@
         <v>63.355150657102897</v>
       </c>
     </row>
-    <row r="171" spans="1:11">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="8">
         <v>40072</v>
       </c>
@@ -21500,7 +21499,7 @@
         <v>63.586872250336747</v>
       </c>
     </row>
-    <row r="172" spans="1:11">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="8">
         <v>40079</v>
       </c>
@@ -21536,7 +21535,7 @@
         <v>53.318827599106207</v>
       </c>
     </row>
-    <row r="173" spans="1:11">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="8">
         <v>40086</v>
       </c>
@@ -21572,7 +21571,7 @@
         <v>49.477873007591704</v>
       </c>
     </row>
-    <row r="174" spans="1:11">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="8">
         <v>40093</v>
       </c>
@@ -21608,7 +21607,7 @@
         <v>71.403538470599969</v>
       </c>
     </row>
-    <row r="175" spans="1:11">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="8">
         <v>40100</v>
       </c>
@@ -21644,7 +21643,7 @@
         <v>61.732827908030352</v>
       </c>
     </row>
-    <row r="176" spans="1:11">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="8">
         <v>40107</v>
       </c>
@@ -21680,7 +21679,7 @@
         <v>52.229993511604249</v>
       </c>
     </row>
-    <row r="177" spans="1:11">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="8">
         <v>40114</v>
       </c>
@@ -21716,7 +21715,7 @@
         <v>64.598575021541549</v>
       </c>
     </row>
-    <row r="178" spans="1:11">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="8">
         <v>40121</v>
       </c>
@@ -21752,7 +21751,7 @@
         <v>61.131436014016572</v>
       </c>
     </row>
-    <row r="179" spans="1:11">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="8">
         <v>40128</v>
       </c>
@@ -21788,7 +21787,7 @@
         <v>53.907207534999003</v>
       </c>
     </row>
-    <row r="180" spans="1:11">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="8">
         <v>40135</v>
       </c>
@@ -21824,7 +21823,7 @@
         <v>44.756939056977522</v>
       </c>
     </row>
-    <row r="181" spans="1:11">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="8">
         <v>40142</v>
       </c>
@@ -21860,7 +21859,7 @@
         <v>56.685418081441156</v>
       </c>
     </row>
-    <row r="182" spans="1:11">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>40149</v>
       </c>
@@ -21896,7 +21895,7 @@
         <v>49.326994067650219</v>
       </c>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="8">
         <v>40156</v>
       </c>
@@ -21932,7 +21931,7 @@
         <v>56.94789248873581</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="8">
         <v>40163</v>
       </c>
@@ -21968,7 +21967,7 @@
         <v>53.684534257154517</v>
       </c>
     </row>
-    <row r="185" spans="1:11">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="8">
         <v>40170</v>
       </c>
@@ -22004,7 +22003,7 @@
         <v>65.364947708147739</v>
       </c>
     </row>
-    <row r="186" spans="1:11">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="8">
         <v>40177</v>
       </c>
@@ -22040,7 +22039,7 @@
         <v>53.704634029690361</v>
       </c>
     </row>
-    <row r="187" spans="1:11">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="8">
         <v>40184</v>
       </c>
@@ -22076,7 +22075,7 @@
         <v>54.771375546492628</v>
       </c>
     </row>
-    <row r="188" spans="1:11">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="8">
         <v>40191</v>
       </c>
@@ -22112,7 +22111,7 @@
         <v>57.833752535015343</v>
       </c>
     </row>
-    <row r="189" spans="1:11">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="8">
         <v>40198</v>
       </c>
@@ -22148,7 +22147,7 @@
         <v>79.252584956089748</v>
       </c>
     </row>
-    <row r="190" spans="1:11">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="8">
         <v>40205</v>
       </c>
@@ -22184,7 +22183,7 @@
         <v>66.112908932661171</v>
       </c>
     </row>
-    <row r="191" spans="1:11">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="8">
         <v>40212</v>
       </c>
@@ -22220,7 +22219,7 @@
         <v>68.480905740352668</v>
       </c>
     </row>
-    <row r="192" spans="1:11">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="8">
         <v>40219</v>
       </c>
@@ -22256,7 +22255,7 @@
         <v>68.820680112015253</v>
       </c>
     </row>
-    <row r="193" spans="1:11">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A193" s="8">
         <v>40226</v>
       </c>
@@ -22292,7 +22291,7 @@
         <v>59.032374376182737</v>
       </c>
     </row>
-    <row r="194" spans="1:11">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A194" s="8">
         <v>40233</v>
       </c>
@@ -22328,7 +22327,7 @@
         <v>60.995325657513426</v>
       </c>
     </row>
-    <row r="195" spans="1:11">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A195" s="8">
         <v>40240</v>
       </c>
@@ -22379,7 +22378,7 @@
         <v>61.01651833892263</v>
       </c>
     </row>
-    <row r="196" spans="1:11">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A196" s="8">
         <v>40247</v>
       </c>
@@ -22415,7 +22414,7 @@
         <v>68.948409164893818</v>
       </c>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A197" s="8">
         <v>40254</v>
       </c>
@@ -22451,7 +22450,7 @@
         <v>55.495282272042076</v>
       </c>
     </row>
-    <row r="198" spans="1:11">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A198" s="8">
         <v>40261</v>
       </c>
@@ -22487,7 +22486,7 @@
         <v>57.756350696573961</v>
       </c>
     </row>
-    <row r="199" spans="1:11">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A199" s="8">
         <v>40268</v>
       </c>
@@ -22523,7 +22522,7 @@
         <v>46.374631010759359</v>
       </c>
     </row>
-    <row r="200" spans="1:11">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A200" s="8">
         <v>40275</v>
       </c>
@@ -22559,7 +22558,7 @@
         <v>50.035497779699199</v>
       </c>
     </row>
-    <row r="201" spans="1:11">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A201" s="8">
         <v>40282</v>
       </c>
@@ -22595,7 +22594,7 @@
         <v>45.14920394961522</v>
       </c>
     </row>
-    <row r="202" spans="1:11">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A202" s="8">
         <v>40289</v>
       </c>
@@ -22631,7 +22630,7 @@
         <v>42.330808834030208</v>
       </c>
     </row>
-    <row r="203" spans="1:11">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A203" s="8">
         <v>40296</v>
       </c>
@@ -22667,7 +22666,7 @@
         <v>46.031147244235598</v>
       </c>
     </row>
-    <row r="204" spans="1:11">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A204" s="8">
         <v>40303</v>
       </c>
@@ -22703,7 +22702,7 @@
         <v>73.783147168729855</v>
       </c>
     </row>
-    <row r="205" spans="1:11">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A205" s="8">
         <v>40310</v>
       </c>
@@ -22739,7 +22738,7 @@
         <v>67.420059029224618</v>
       </c>
     </row>
-    <row r="206" spans="1:11">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A206" s="8">
         <v>40317</v>
       </c>
@@ -22775,7 +22774,7 @@
         <v>65.236302377809508</v>
       </c>
     </row>
-    <row r="207" spans="1:11">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A207" s="8">
         <v>40324</v>
       </c>
@@ -22811,7 +22810,7 @@
         <v>45.438603264918548</v>
       </c>
     </row>
-    <row r="208" spans="1:11">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A208" s="8">
         <v>40331</v>
       </c>
@@ -22847,7 +22846,7 @@
         <v>55.842613656597415</v>
       </c>
     </row>
-    <row r="209" spans="1:11">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A209" s="8">
         <v>40338</v>
       </c>
@@ -22883,7 +22882,7 @@
         <v>50.566226976684703</v>
       </c>
     </row>
-    <row r="210" spans="1:11">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A210" s="8">
         <v>40345</v>
       </c>
@@ -22919,7 +22918,7 @@
         <v>60.167993983512531</v>
       </c>
     </row>
-    <row r="211" spans="1:11">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A211" s="8">
         <v>40352</v>
       </c>
@@ -22955,7 +22954,7 @@
         <v>59.384867216709665</v>
       </c>
     </row>
-    <row r="212" spans="1:11">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A212" s="8">
         <v>40359</v>
       </c>
@@ -22991,7 +22990,7 @@
         <v>51.877165703250242</v>
       </c>
     </row>
-    <row r="213" spans="1:11">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A213" s="8">
         <v>40366</v>
       </c>
@@ -23027,7 +23026,7 @@
         <v>60.791159694094574</v>
       </c>
     </row>
-    <row r="214" spans="1:11">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <v>40373</v>
       </c>
@@ -23063,7 +23062,7 @@
         <v>52.381556868806406</v>
       </c>
     </row>
-    <row r="215" spans="1:11">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A215" s="8">
         <v>40380</v>
       </c>
@@ -23099,7 +23098,7 @@
         <v>55.497901708236633</v>
       </c>
     </row>
-    <row r="216" spans="1:11">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A216" s="8">
         <v>40387</v>
       </c>
@@ -23135,7 +23134,7 @@
         <v>63.648541403343927</v>
       </c>
     </row>
-    <row r="217" spans="1:11">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A217" s="8">
         <v>40394</v>
       </c>
@@ -23171,7 +23170,7 @@
         <v>58.51627398414611</v>
       </c>
     </row>
-    <row r="218" spans="1:11">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A218" s="8">
         <v>40401</v>
       </c>
@@ -23207,7 +23206,7 @@
         <v>70.168158657672691</v>
       </c>
     </row>
-    <row r="219" spans="1:11">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A219" s="8">
         <v>40408</v>
       </c>
@@ -23243,7 +23242,7 @@
         <v>53.947041077312385</v>
       </c>
     </row>
-    <row r="220" spans="1:11">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A220" s="8">
         <v>40415</v>
       </c>
@@ -23279,7 +23278,7 @@
         <v>55.908131213647891</v>
       </c>
     </row>
-    <row r="221" spans="1:11">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A221" s="8">
         <v>40422</v>
       </c>
@@ -23315,7 +23314,7 @@
         <v>62.564187638553811</v>
       </c>
     </row>
-    <row r="222" spans="1:11">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A222" s="8">
         <v>40429</v>
       </c>
@@ -23351,7 +23350,7 @@
         <v>72.423309874299363</v>
       </c>
     </row>
-    <row r="223" spans="1:11">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A223" s="8">
         <v>40436</v>
       </c>
@@ -23387,7 +23386,7 @@
         <v>73.388746907379783</v>
       </c>
     </row>
-    <row r="224" spans="1:11">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A224" s="8">
         <v>40443</v>
       </c>
@@ -23423,7 +23422,7 @@
         <v>74.427829003026858</v>
       </c>
     </row>
-    <row r="225" spans="1:11">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A225" s="8">
         <v>40450</v>
       </c>
@@ -23459,7 +23458,7 @@
         <v>65.974731715358232</v>
       </c>
     </row>
-    <row r="226" spans="1:11">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A226" s="8">
         <v>40457</v>
       </c>
@@ -23495,7 +23494,7 @@
         <v>59.692906241492011</v>
       </c>
     </row>
-    <row r="227" spans="1:11">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A227" s="8">
         <v>40464</v>
       </c>
@@ -23531,7 +23530,7 @@
         <v>55.007204521826623</v>
       </c>
     </row>
-    <row r="228" spans="1:11">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A228" s="8">
         <v>40471</v>
       </c>
@@ -23567,7 +23566,7 @@
         <v>54.037281159418455</v>
       </c>
     </row>
-    <row r="229" spans="1:11">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A229" s="8">
         <v>40478</v>
       </c>
@@ -23603,7 +23602,7 @@
         <v>74.053447495288836</v>
       </c>
     </row>
-    <row r="230" spans="1:11">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A230" s="8">
         <v>40485</v>
       </c>
@@ -23639,7 +23638,7 @@
         <v>57.599139747516887</v>
       </c>
     </row>
-    <row r="231" spans="1:11">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A231" s="8">
         <v>40493</v>
       </c>
@@ -23675,7 +23674,7 @@
         <v>73.628931758084974</v>
       </c>
     </row>
-    <row r="232" spans="1:11">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A232" s="8">
         <v>40499</v>
       </c>
@@ -23711,7 +23710,7 @@
         <v>64.712269652083734</v>
       </c>
     </row>
-    <row r="233" spans="1:11">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A233" s="8">
         <v>40506</v>
       </c>
@@ -23747,7 +23746,7 @@
         <v>68.728127833919316</v>
       </c>
     </row>
-    <row r="234" spans="1:11">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A234" s="8">
         <v>40513</v>
       </c>
@@ -23783,7 +23782,7 @@
         <v>71.396578703865657</v>
       </c>
     </row>
-    <row r="235" spans="1:11">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A235" s="8">
         <v>40520</v>
       </c>
@@ -23819,7 +23818,7 @@
         <v>56.848732557127434</v>
       </c>
     </row>
-    <row r="236" spans="1:11">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A236" s="8">
         <v>40527</v>
       </c>
@@ -23855,7 +23854,7 @@
         <v>48.876462768440668</v>
       </c>
     </row>
-    <row r="237" spans="1:11">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A237" s="8">
         <v>40534</v>
       </c>
@@ -23891,7 +23890,7 @@
         <v>30.939366105335772</v>
       </c>
     </row>
-    <row r="238" spans="1:11">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A238" s="8">
         <v>40541</v>
       </c>
@@ -23927,7 +23926,7 @@
         <v>25.867679114547297</v>
       </c>
     </row>
-    <row r="239" spans="1:11">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A239" s="8">
         <v>40548</v>
       </c>
@@ -23963,7 +23962,7 @@
         <v>35.99596195192472</v>
       </c>
     </row>
-    <row r="240" spans="1:11">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A240" s="8">
         <v>40555</v>
       </c>
@@ -23999,7 +23998,7 @@
         <v>34.5248029413723</v>
       </c>
     </row>
-    <row r="241" spans="1:11">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A241" s="8">
         <v>40562</v>
       </c>
@@ -24035,7 +24034,7 @@
         <v>48.204614903131251</v>
       </c>
     </row>
-    <row r="242" spans="1:11">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A242" s="8">
         <v>40569</v>
       </c>
@@ -24071,7 +24070,7 @@
         <v>44.563550516112116</v>
       </c>
     </row>
-    <row r="243" spans="1:11">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A243" s="8">
         <v>40576</v>
       </c>
@@ -24107,7 +24106,7 @@
         <v>37.30092994819298</v>
       </c>
     </row>
-    <row r="244" spans="1:11">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A244" s="8">
         <v>40583</v>
       </c>
@@ -24143,7 +24142,7 @@
         <v>36.241942484664484</v>
       </c>
     </row>
-    <row r="245" spans="1:11">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A245" s="8">
         <v>40590</v>
       </c>
@@ -24179,7 +24178,7 @@
         <v>39.530799594711759</v>
       </c>
     </row>
-    <row r="246" spans="1:11">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A246" s="8">
         <v>40597</v>
       </c>
@@ -24215,7 +24214,7 @@
         <v>53.939404659302646</v>
       </c>
     </row>
-    <row r="247" spans="1:11">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A247" s="8">
         <v>40604</v>
       </c>
@@ -24251,7 +24250,7 @@
         <v>43.942750002449529</v>
       </c>
     </row>
-    <row r="248" spans="1:11">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A248" s="8">
         <v>40611</v>
       </c>
@@ -24287,7 +24286,7 @@
         <v>34.894786457057684</v>
       </c>
     </row>
-    <row r="249" spans="1:11">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A249" s="8">
         <v>40618</v>
       </c>
@@ -24323,7 +24322,7 @@
         <v>64.316923641190016</v>
       </c>
     </row>
-    <row r="250" spans="1:11">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A250" s="8">
         <v>40625</v>
       </c>
@@ -24359,7 +24358,7 @@
         <v>54.669969412425644</v>
       </c>
     </row>
-    <row r="251" spans="1:11">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A251" s="8">
         <v>40632</v>
       </c>
@@ -24395,7 +24394,7 @@
         <v>33.436812839822487</v>
       </c>
     </row>
-    <row r="252" spans="1:11">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A252" s="8">
         <v>40639</v>
       </c>
@@ -24431,7 +24430,7 @@
         <v>39.172313642501635</v>
       </c>
     </row>
-    <row r="253" spans="1:11">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A253" s="8">
         <v>40646</v>
       </c>
@@ -24467,7 +24466,7 @@
         <v>38.729050102374607</v>
       </c>
     </row>
-    <row r="254" spans="1:11">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A254" s="8">
         <v>40653</v>
       </c>
@@ -24503,7 +24502,7 @@
         <v>41.715563146345993</v>
       </c>
     </row>
-    <row r="255" spans="1:11">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A255" s="8">
         <v>40660</v>
       </c>
@@ -24539,7 +24538,7 @@
         <v>43.741742077791095</v>
       </c>
     </row>
-    <row r="256" spans="1:11">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A256" s="8">
         <v>40667</v>
       </c>
@@ -24575,7 +24574,7 @@
         <v>47.873989122981456</v>
       </c>
     </row>
-    <row r="257" spans="1:11">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A257" s="8">
         <v>40674</v>
       </c>
@@ -24611,7 +24610,7 @@
         <v>51.779665709540218</v>
       </c>
     </row>
-    <row r="258" spans="1:11">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A258" s="8">
         <v>40681</v>
       </c>
@@ -24647,7 +24646,7 @@
         <v>57.023035358289334</v>
       </c>
     </row>
-    <row r="259" spans="1:11">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A259" s="8">
         <v>40688</v>
       </c>
@@ -24698,7 +24697,7 @@
         <v>56.87088409797628</v>
       </c>
     </row>
-    <row r="260" spans="1:11">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A260" s="8">
         <v>40695</v>
       </c>
@@ -24734,7 +24733,7 @@
         <v>47.063569688632143</v>
       </c>
     </row>
-    <row r="261" spans="1:11">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A261" s="8">
         <v>40702</v>
       </c>
@@ -24770,7 +24769,7 @@
         <v>58.561562455438484</v>
       </c>
     </row>
-    <row r="262" spans="1:11">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A262" s="8">
         <v>40709</v>
       </c>
@@ -24806,7 +24805,7 @@
         <v>54.876464024706216</v>
       </c>
     </row>
-    <row r="263" spans="1:11">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A263" s="8">
         <v>40716</v>
       </c>
@@ -24842,7 +24841,7 @@
         <v>48.129506282529015</v>
       </c>
     </row>
-    <row r="264" spans="1:11">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A264" s="8">
         <v>40723</v>
       </c>
@@ -24878,7 +24877,7 @@
         <v>53.998865301934728</v>
       </c>
     </row>
-    <row r="265" spans="1:11">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A265" s="8">
         <v>40730</v>
       </c>
@@ -24914,7 +24913,7 @@
         <v>57.89850820929329</v>
       </c>
     </row>
-    <row r="266" spans="1:11">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A266" s="8">
         <v>40737</v>
       </c>
@@ -24950,7 +24949,7 @@
         <v>53.479549570113456</v>
       </c>
     </row>
-    <row r="267" spans="1:11">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A267" s="8">
         <v>40744</v>
       </c>
@@ -24986,7 +24985,7 @@
         <v>49.79143878947302</v>
       </c>
     </row>
-    <row r="268" spans="1:11">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A268" s="8">
         <v>40751</v>
       </c>
@@ -25022,7 +25021,7 @@
         <v>42.651475813694034</v>
       </c>
     </row>
-    <row r="269" spans="1:11">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A269" s="8">
         <v>40758</v>
       </c>
@@ -25058,7 +25057,7 @@
         <v>50.439188817558389</v>
       </c>
     </row>
-    <row r="270" spans="1:11">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A270" s="8">
         <v>40765</v>
       </c>
@@ -25094,7 +25093,7 @@
         <v>42.049324508367285</v>
       </c>
     </row>
-    <row r="271" spans="1:11">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A271" s="8">
         <v>40772</v>
       </c>
@@ -25130,7 +25129,7 @@
         <v>47.516027185636773</v>
       </c>
     </row>
-    <row r="272" spans="1:11">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A272" s="8">
         <v>40779</v>
       </c>
@@ -25166,7 +25165,7 @@
         <v>40.399772058656886</v>
       </c>
     </row>
-    <row r="273" spans="1:11">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A273" s="8">
         <v>40786</v>
       </c>
@@ -25202,7 +25201,7 @@
         <v>44.783201620610939</v>
       </c>
     </row>
-    <row r="274" spans="1:11">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A274" s="8">
         <v>40793</v>
       </c>
@@ -25238,7 +25237,7 @@
         <v>46.854774319627346</v>
       </c>
     </row>
-    <row r="275" spans="1:11">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A275" s="8">
         <v>40800</v>
       </c>
@@ -25274,7 +25273,7 @@
         <v>50.572231681862235</v>
       </c>
     </row>
-    <row r="276" spans="1:11">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A276" s="8">
         <v>40807</v>
       </c>
@@ -25310,7 +25309,7 @@
         <v>51.000097894093308</v>
       </c>
     </row>
-    <row r="277" spans="1:11">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A277" s="8">
         <v>40814</v>
       </c>
@@ -25346,7 +25345,7 @@
         <v>38.969787977354969</v>
       </c>
     </row>
-    <row r="278" spans="1:11">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A278" s="8">
         <v>40821</v>
       </c>
@@ -25382,7 +25381,7 @@
         <v>54.517864058372737</v>
       </c>
     </row>
-    <row r="279" spans="1:11">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A279" s="8">
         <v>40828</v>
       </c>
@@ -25418,7 +25417,7 @@
         <v>58.875398087826127</v>
       </c>
     </row>
-    <row r="280" spans="1:11">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A280" s="8">
         <v>40835</v>
       </c>
@@ -25454,7 +25453,7 @@
         <v>40.918862469344425</v>
       </c>
     </row>
-    <row r="281" spans="1:11">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A281" s="8">
         <v>40842</v>
       </c>
@@ -25490,7 +25489,7 @@
         <v>45.233867381064172</v>
       </c>
     </row>
-    <row r="282" spans="1:11">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A282" s="8">
         <v>40849</v>
       </c>
@@ -25526,7 +25525,7 @@
         <v>55.320831293464849</v>
       </c>
     </row>
-    <row r="283" spans="1:11">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A283" s="8">
         <v>40856</v>
       </c>
@@ -25562,7 +25561,7 @@
         <v>55.690513263814637</v>
       </c>
     </row>
-    <row r="284" spans="1:11">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A284" s="8">
         <v>40863</v>
       </c>
@@ -25598,7 +25597,7 @@
         <v>51.999145292121014</v>
       </c>
     </row>
-    <row r="285" spans="1:11">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A285" s="8">
         <v>40870</v>
       </c>
@@ -25634,7 +25633,7 @@
         <v>45.873095396241652</v>
       </c>
     </row>
-    <row r="286" spans="1:11">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A286" s="8">
         <v>40877</v>
       </c>
@@ -25670,7 +25669,7 @@
         <v>42.216169288999922</v>
       </c>
     </row>
-    <row r="287" spans="1:11">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A287" s="8">
         <v>40884</v>
       </c>
@@ -25706,7 +25705,7 @@
         <v>43.664531422515303</v>
       </c>
     </row>
-    <row r="288" spans="1:11">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A288" s="8">
         <v>40891</v>
       </c>
@@ -25742,7 +25741,7 @@
         <v>48.198670933439651</v>
       </c>
     </row>
-    <row r="289" spans="1:11">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A289" s="8">
         <v>40898</v>
       </c>
@@ -25778,7 +25777,7 @@
         <v>39.516792034075834</v>
       </c>
     </row>
-    <row r="290" spans="1:11">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A290" s="8">
         <v>40905</v>
       </c>
@@ -25814,7 +25813,7 @@
         <v>28.563193765273795</v>
       </c>
     </row>
-    <row r="291" spans="1:11">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A291" s="8">
         <v>40912</v>
       </c>
@@ -25850,7 +25849,7 @@
         <v>41.403003244764143</v>
       </c>
     </row>
-    <row r="292" spans="1:11">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A292" s="8">
         <v>40919</v>
       </c>
@@ -25886,7 +25885,7 @@
         <v>47.072652594140706</v>
       </c>
     </row>
-    <row r="293" spans="1:11">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A293" s="8">
         <v>40926</v>
       </c>
@@ -25922,7 +25921,7 @@
         <v>49.053078858054825</v>
       </c>
     </row>
-    <row r="294" spans="1:11">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A294" s="8">
         <v>40933</v>
       </c>
@@ -25958,7 +25957,7 @@
         <v>53.510954226421923</v>
       </c>
     </row>
-    <row r="295" spans="1:11">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A295" s="8">
         <v>40940</v>
       </c>
@@ -25994,7 +25993,7 @@
         <v>39.384750530886507</v>
       </c>
     </row>
-    <row r="296" spans="1:11">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A296" s="8">
         <v>40947</v>
       </c>
@@ -26030,7 +26029,7 @@
         <v>36.817697808266423</v>
       </c>
     </row>
-    <row r="297" spans="1:11">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A297" s="8">
         <v>40954</v>
       </c>
@@ -26066,7 +26065,7 @@
         <v>36.233572758862671</v>
       </c>
     </row>
-    <row r="298" spans="1:11">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A298" s="8">
         <v>40961</v>
       </c>
@@ -26102,7 +26101,7 @@
         <v>37.171889580703322</v>
       </c>
     </row>
-    <row r="299" spans="1:11">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A299" s="8">
         <v>40968</v>
       </c>
@@ -26138,7 +26137,7 @@
         <v>36.759941210655207</v>
       </c>
     </row>
-    <row r="300" spans="1:11">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A300" s="8">
         <v>40975</v>
       </c>
@@ -26174,7 +26173,7 @@
         <v>56.661237586866619</v>
       </c>
     </row>
-    <row r="301" spans="1:11">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A301" s="8">
         <v>40982</v>
       </c>
@@ -26210,7 +26209,7 @@
         <v>47.798457305394521</v>
       </c>
     </row>
-    <row r="302" spans="1:11">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A302" s="8">
         <v>40989</v>
       </c>
@@ -26246,7 +26245,7 @@
         <v>47.064324329465158</v>
       </c>
     </row>
-    <row r="303" spans="1:11">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A303" s="8">
         <v>40996</v>
       </c>
@@ -26282,7 +26281,7 @@
         <v>40.595204301061202</v>
       </c>
     </row>
-    <row r="304" spans="1:11">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A304" s="8">
         <v>41003</v>
       </c>
@@ -26318,7 +26317,7 @@
         <v>38.549937035348876</v>
       </c>
     </row>
-    <row r="305" spans="1:11">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A305" s="8">
         <v>41010</v>
       </c>
@@ -26354,7 +26353,7 @@
         <v>53.214477468494394</v>
       </c>
     </row>
-    <row r="306" spans="1:11">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A306" s="8">
         <v>41017</v>
       </c>
@@ -26390,7 +26389,7 @@
         <v>56.900572530695925</v>
       </c>
     </row>
-    <row r="307" spans="1:11">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A307" s="8">
         <v>41024</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>56.771006536281874</v>
       </c>
     </row>
-    <row r="308" spans="1:11">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A308" s="8">
         <v>41031</v>
       </c>
@@ -26462,7 +26461,7 @@
         <v>50.543476884317684</v>
       </c>
     </row>
-    <row r="309" spans="1:11">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A309" s="8">
         <v>41038</v>
       </c>
@@ -26498,7 +26497,7 @@
         <v>54.137497957615317</v>
       </c>
     </row>
-    <row r="310" spans="1:11">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A310" s="8">
         <v>41045</v>
       </c>
@@ -26534,7 +26533,7 @@
         <v>41.363917899541384</v>
       </c>
     </row>
-    <row r="311" spans="1:11">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A311" s="8">
         <v>41052</v>
       </c>
@@ -26570,7 +26569,7 @@
         <v>45.49777201728218</v>
       </c>
     </row>
-    <row r="312" spans="1:11">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A312" s="8">
         <v>41059</v>
       </c>
@@ -26606,7 +26605,7 @@
         <v>46.729614872834489</v>
       </c>
     </row>
-    <row r="313" spans="1:11">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A313" s="8">
         <v>41066</v>
       </c>
@@ -26642,7 +26641,7 @@
         <v>34.956741028578463</v>
       </c>
     </row>
-    <row r="314" spans="1:11">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A314" s="8">
         <v>41073</v>
       </c>
@@ -26678,7 +26677,7 @@
         <v>29.532500348198187</v>
       </c>
     </row>
-    <row r="315" spans="1:11">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A315" s="8">
         <v>41080</v>
       </c>
@@ -26714,7 +26713,7 @@
         <v>45.65945115969452</v>
       </c>
     </row>
-    <row r="316" spans="1:11">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A316" s="8">
         <v>41087</v>
       </c>
@@ -26750,7 +26749,7 @@
         <v>48.136271215938542</v>
       </c>
     </row>
-    <row r="317" spans="1:11">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A317" s="8">
         <v>41095</v>
       </c>
@@ -26786,7 +26785,7 @@
         <v>49.207476611003706</v>
       </c>
     </row>
-    <row r="318" spans="1:11">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A318" s="8">
         <v>41101</v>
       </c>
@@ -26822,7 +26821,7 @@
         <v>53.618962087056566</v>
       </c>
     </row>
-    <row r="319" spans="1:11">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A319" s="8">
         <v>41108</v>
       </c>
@@ -26858,7 +26857,7 @@
         <v>52.76407806027715</v>
       </c>
     </row>
-    <row r="320" spans="1:11">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A320" s="8">
         <v>41115</v>
       </c>
@@ -26894,7 +26893,7 @@
         <v>50.011052339523104</v>
       </c>
     </row>
-    <row r="321" spans="1:11">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A321" s="8">
         <v>41122</v>
       </c>
@@ -26930,7 +26929,7 @@
         <v>53.937797639233743</v>
       </c>
     </row>
-    <row r="322" spans="1:11">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A322" s="8">
         <v>41129</v>
       </c>
@@ -26966,7 +26965,7 @@
         <v>39.420666681528402</v>
       </c>
     </row>
-    <row r="323" spans="1:11">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A323" s="8">
         <v>41136</v>
       </c>
@@ -27017,7 +27016,7 @@
         <v>42.597308792434582</v>
       </c>
     </row>
-    <row r="324" spans="1:11">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A324" s="8">
         <v>41143</v>
       </c>
@@ -27053,7 +27052,7 @@
         <v>59.566739758018073</v>
       </c>
     </row>
-    <row r="325" spans="1:11">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A325" s="8">
         <v>41150</v>
       </c>
@@ -27089,7 +27088,7 @@
         <v>40.667483971490398</v>
       </c>
     </row>
-    <row r="326" spans="1:11">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A326" s="8">
         <v>41157</v>
       </c>
@@ -27125,7 +27124,7 @@
         <v>50.154861297471179</v>
       </c>
     </row>
-    <row r="327" spans="1:11">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A327" s="8">
         <v>41164</v>
       </c>
@@ -27161,7 +27160,7 @@
         <v>50.124976846592538</v>
       </c>
     </row>
-    <row r="328" spans="1:11">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A328" s="8">
         <v>41171</v>
       </c>
@@ -27197,7 +27196,7 @@
         <v>52.943578895895669</v>
       </c>
     </row>
-    <row r="329" spans="1:11">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A329" s="8">
         <v>41178</v>
       </c>
@@ -27233,7 +27232,7 @@
         <v>56.021511245433409</v>
       </c>
     </row>
-    <row r="330" spans="1:11">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A330" s="8">
         <v>41185</v>
       </c>
@@ -27269,7 +27268,7 @@
         <v>57.266397751374981</v>
       </c>
     </row>
-    <row r="331" spans="1:11">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A331" s="8">
         <v>41192</v>
       </c>
@@ -27305,7 +27304,7 @@
         <v>66.483484497561491</v>
       </c>
     </row>
-    <row r="332" spans="1:11">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A332" s="8">
         <v>41199</v>
       </c>
@@ -27341,7 +27340,7 @@
         <v>71.777760309165402</v>
       </c>
     </row>
-    <row r="333" spans="1:11">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A333" s="8">
         <v>41206</v>
       </c>
@@ -27377,7 +27376,7 @@
         <v>59.778361750310793</v>
       </c>
     </row>
-    <row r="334" spans="1:11">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A334" s="8">
         <v>41213</v>
       </c>
@@ -27413,7 +27412,7 @@
         <v>59.216704581992914</v>
       </c>
     </row>
-    <row r="335" spans="1:11">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A335" s="8">
         <v>41220</v>
       </c>
@@ -27449,7 +27448,7 @@
         <v>57.538374466714032</v>
       </c>
     </row>
-    <row r="336" spans="1:11">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A336" s="8">
         <v>41227</v>
       </c>
@@ -27485,7 +27484,7 @@
         <v>64.794060427377659</v>
       </c>
     </row>
-    <row r="337" spans="1:11">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A337" s="8">
         <v>41234</v>
       </c>
@@ -27521,7 +27520,7 @@
         <v>42.978585224257763</v>
       </c>
     </row>
-    <row r="338" spans="1:11">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A338" s="8">
         <v>41241</v>
       </c>
@@ -27557,7 +27556,7 @@
         <v>58.262610437726366</v>
       </c>
     </row>
-    <row r="339" spans="1:11">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A339" s="8">
         <v>41248</v>
       </c>
@@ -27593,7 +27592,7 @@
         <v>53.947354080111261</v>
       </c>
     </row>
-    <row r="340" spans="1:11">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A340" s="8">
         <v>41255</v>
       </c>
@@ -27629,7 +27628,7 @@
         <v>40.867278029986856</v>
       </c>
     </row>
-    <row r="341" spans="1:11">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A341" s="8">
         <v>41262</v>
       </c>
@@ -27665,7 +27664,7 @@
         <v>49.812955030683419</v>
       </c>
     </row>
-    <row r="342" spans="1:11">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A342" s="8">
         <v>41269</v>
       </c>
@@ -27701,7 +27700,7 @@
         <v>44.510630134900872</v>
       </c>
     </row>
-    <row r="343" spans="1:11">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A343" s="8">
         <v>41276</v>
       </c>
@@ -27737,7 +27736,7 @@
         <v>53.24693033779436</v>
       </c>
     </row>
-    <row r="344" spans="1:11">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A344" s="8">
         <v>41283</v>
       </c>
@@ -27773,7 +27772,7 @@
         <v>43.585114686349307</v>
       </c>
     </row>
-    <row r="345" spans="1:11">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A345" s="8">
         <v>41290</v>
       </c>
@@ -27809,7 +27808,7 @@
         <v>60.84780147014353</v>
       </c>
     </row>
-    <row r="346" spans="1:11">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A346" s="8">
         <v>41297</v>
       </c>
@@ -27845,7 +27844,7 @@
         <v>53.953140270861297</v>
       </c>
     </row>
-    <row r="347" spans="1:11">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A347" s="8">
         <v>41304</v>
       </c>
@@ -27881,7 +27880,7 @@
         <v>32.239533185206014</v>
       </c>
     </row>
-    <row r="348" spans="1:11">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A348" s="8">
         <v>41311</v>
       </c>
@@ -27917,7 +27916,7 @@
         <v>40.084712867791588</v>
       </c>
     </row>
-    <row r="349" spans="1:11">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A349" s="8">
         <v>41318</v>
       </c>
@@ -27953,7 +27952,7 @@
         <v>38.38710256166938</v>
       </c>
     </row>
-    <row r="350" spans="1:11">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A350" s="8">
         <v>41325</v>
       </c>
@@ -27989,7 +27988,7 @@
         <v>38.080293444545788</v>
       </c>
     </row>
-    <row r="351" spans="1:11">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A351" s="8">
         <v>41332</v>
       </c>
@@ -28025,7 +28024,7 @@
         <v>48.402767285139547</v>
       </c>
     </row>
-    <row r="352" spans="1:11">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A352" s="8">
         <v>41339</v>
       </c>
@@ -28061,7 +28060,7 @@
         <v>40.094000618700669</v>
       </c>
     </row>
-    <row r="353" spans="1:11">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A353" s="8">
         <v>41346</v>
       </c>
@@ -28097,7 +28096,7 @@
         <v>42.821783159517786</v>
       </c>
     </row>
-    <row r="354" spans="1:11">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A354" s="8">
         <v>41353</v>
       </c>
@@ -28133,7 +28132,7 @@
         <v>32.607118719705234</v>
       </c>
     </row>
-    <row r="355" spans="1:11">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A355" s="8">
         <v>41360</v>
       </c>
@@ -28169,7 +28168,7 @@
         <v>40.659143503192773</v>
       </c>
     </row>
-    <row r="356" spans="1:11">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A356" s="8">
         <v>41367</v>
       </c>
@@ -28205,7 +28204,7 @@
         <v>61.567550890600387</v>
       </c>
     </row>
-    <row r="357" spans="1:11">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A357" s="8">
         <v>41374</v>
       </c>
@@ -28241,7 +28240,7 @@
         <v>52.116557963159231</v>
       </c>
     </row>
-    <row r="358" spans="1:11">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A358" s="8">
         <v>41381</v>
       </c>
@@ -28277,7 +28276,7 @@
         <v>53.354057268656028</v>
       </c>
     </row>
-    <row r="359" spans="1:11">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A359" s="8">
         <v>41388</v>
       </c>
@@ -28313,7 +28312,7 @@
         <v>58.802213497238505</v>
       </c>
     </row>
-    <row r="360" spans="1:11">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A360" s="8">
         <v>41395</v>
       </c>
@@ -28349,7 +28348,7 @@
         <v>37.937705662389739</v>
       </c>
     </row>
-    <row r="361" spans="1:11">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A361" s="8">
         <v>41402</v>
       </c>
@@ -28385,7 +28384,7 @@
         <v>54.929642662956802</v>
       </c>
     </row>
-    <row r="362" spans="1:11">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A362" s="8">
         <v>41409</v>
       </c>
@@ -28421,7 +28420,7 @@
         <v>35.515606966366008</v>
       </c>
     </row>
-    <row r="363" spans="1:11">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A363" s="8">
         <v>41416</v>
       </c>
@@ -28457,7 +28456,7 @@
         <v>47.22321621646487</v>
       </c>
     </row>
-    <row r="364" spans="1:11">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A364" s="8">
         <v>41423</v>
       </c>
@@ -28493,7 +28492,7 @@
         <v>58.20055953610327</v>
       </c>
     </row>
-    <row r="365" spans="1:11">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A365" s="8">
         <v>41430</v>
       </c>
@@ -28529,7 +28528,7 @@
         <v>58.972667790307163</v>
       </c>
     </row>
-    <row r="366" spans="1:11">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A366" s="8">
         <v>41437</v>
       </c>
@@ -28565,7 +28564,7 @@
         <v>54.209657868522129</v>
       </c>
     </row>
-    <row r="367" spans="1:11">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A367" s="8">
         <v>41444</v>
       </c>
@@ -28601,7 +28600,7 @@
         <v>49.424558707629132</v>
       </c>
     </row>
-    <row r="368" spans="1:11">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A368" s="8">
         <v>41451</v>
       </c>
@@ -28637,7 +28636,7 @@
         <v>49.303982121743722</v>
       </c>
     </row>
-    <row r="369" spans="1:11">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A369" s="8">
         <v>41458</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>35.218787549159295</v>
       </c>
     </row>
-    <row r="370" spans="1:11">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A370" s="8">
         <v>41465</v>
       </c>
@@ -28709,7 +28708,7 @@
         <v>55.882367115793201</v>
       </c>
     </row>
-    <row r="371" spans="1:11">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A371" s="8">
         <v>41472</v>
       </c>
@@ -28745,7 +28744,7 @@
         <v>53.110925423170286</v>
       </c>
     </row>
-    <row r="372" spans="1:11">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="8">
         <v>41479</v>
       </c>
@@ -28781,7 +28780,7 @@
         <v>33.44447705914984</v>
       </c>
     </row>
-    <row r="373" spans="1:11">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A373" s="8">
         <v>41486</v>
       </c>
@@ -28817,7 +28816,7 @@
         <v>54.484641664282961</v>
       </c>
     </row>
-    <row r="374" spans="1:11">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A374" s="8">
         <v>41493</v>
       </c>
@@ -28853,7 +28852,7 @@
         <v>30.238330855873073</v>
       </c>
     </row>
-    <row r="375" spans="1:11">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A375" s="8">
         <v>41500</v>
       </c>
@@ -28889,7 +28888,7 @@
         <v>42.699029269899285</v>
       </c>
     </row>
-    <row r="376" spans="1:11">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A376" s="8">
         <v>41507</v>
       </c>
@@ -28925,7 +28924,7 @@
         <v>56.528524201883307</v>
       </c>
     </row>
-    <row r="377" spans="1:11">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A377" s="8">
         <v>41514</v>
       </c>
@@ -28961,7 +28960,7 @@
         <v>45.736639980287038</v>
       </c>
     </row>
-    <row r="378" spans="1:11">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A378" s="8">
         <v>41521</v>
       </c>
@@ -28997,7 +28996,7 @@
         <v>44.32004194458554</v>
       </c>
     </row>
-    <row r="379" spans="1:11">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A379" s="8">
         <v>41528</v>
       </c>
@@ -29033,7 +29032,7 @@
         <v>31.097341411399512</v>
       </c>
     </row>
-    <row r="380" spans="1:11">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A380" s="8">
         <v>41535</v>
       </c>
@@ -29069,7 +29068,7 @@
         <v>32.054779929422871</v>
       </c>
     </row>
-    <row r="381" spans="1:11">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A381" s="8">
         <v>41542</v>
       </c>
@@ -29105,7 +29104,7 @@
         <v>48.279990820009985</v>
       </c>
     </row>
-    <row r="382" spans="1:11">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A382" s="8">
         <v>41549</v>
       </c>
@@ -29141,7 +29140,7 @@
         <v>55.268275006754301</v>
       </c>
     </row>
-    <row r="383" spans="1:11">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A383" s="8">
         <v>41556</v>
       </c>
@@ -29177,7 +29176,7 @@
         <v>64.648358122534788</v>
       </c>
     </row>
-    <row r="384" spans="1:11">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A384" s="8">
         <v>41563</v>
       </c>
@@ -29213,7 +29212,7 @@
         <v>30.40107245824677</v>
       </c>
     </row>
-    <row r="385" spans="1:11">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A385" s="8">
         <v>41570</v>
       </c>
@@ -29249,7 +29248,7 @@
         <v>46.050815851660722</v>
       </c>
     </row>
-    <row r="386" spans="1:11">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A386" s="8">
         <v>41577</v>
       </c>
@@ -29285,7 +29284,7 @@
         <v>29.663869105622428</v>
       </c>
     </row>
-    <row r="387" spans="1:11">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A387" s="8">
         <v>41584</v>
       </c>
@@ -29336,7 +29335,7 @@
         <v>29.763192589775961</v>
       </c>
     </row>
-    <row r="388" spans="1:11">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A388" s="8">
         <v>41591</v>
       </c>
@@ -29372,7 +29371,7 @@
         <v>53.718056830358535</v>
       </c>
     </row>
-    <row r="389" spans="1:11">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A389" s="8">
         <v>41598</v>
       </c>
@@ -29408,7 +29407,7 @@
         <v>47.320660371123139</v>
       </c>
     </row>
-    <row r="390" spans="1:11">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A390" s="8">
         <v>41605</v>
       </c>
@@ -29444,7 +29443,7 @@
         <v>26.84883647436958</v>
       </c>
     </row>
-    <row r="391" spans="1:11">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A391" s="8">
         <v>41612</v>
       </c>
@@ -29480,7 +29479,7 @@
         <v>30.228012575603316</v>
       </c>
     </row>
-    <row r="392" spans="1:11">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A392" s="8">
         <v>41619</v>
       </c>
@@ -29516,7 +29515,7 @@
         <v>35.628299402813028</v>
       </c>
     </row>
-    <row r="393" spans="1:11">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A393" s="8">
         <v>41626</v>
       </c>
@@ -29552,7 +29551,7 @@
         <v>29.564716897124189</v>
       </c>
     </row>
-    <row r="394" spans="1:11">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A394" s="8">
         <v>41634</v>
       </c>
@@ -29588,7 +29587,7 @@
         <v>25.48504766173663</v>
       </c>
     </row>
-    <row r="395" spans="1:11">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A395" s="8">
         <v>41641</v>
       </c>
@@ -29624,7 +29623,7 @@
         <v>29.440463564644233</v>
       </c>
     </row>
-    <row r="396" spans="1:11">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A396" s="8">
         <v>41647</v>
       </c>
@@ -29660,7 +29659,7 @@
         <v>36.868005424758209</v>
       </c>
     </row>
-    <row r="397" spans="1:11">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A397" s="8">
         <v>41654</v>
       </c>
@@ -29696,7 +29695,7 @@
         <v>33.543405654015224</v>
       </c>
     </row>
-    <row r="398" spans="1:11">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A398" s="8">
         <v>41661</v>
       </c>
@@ -29732,7 +29731,7 @@
         <v>33.281205492789098</v>
       </c>
     </row>
-    <row r="399" spans="1:11">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A399" s="8">
         <v>41668</v>
       </c>
@@ -29768,7 +29767,7 @@
         <v>48.6755678567065</v>
       </c>
     </row>
-    <row r="400" spans="1:11">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A400" s="8">
         <v>41675</v>
       </c>
@@ -29804,7 +29803,7 @@
         <v>48.899855436252473</v>
       </c>
     </row>
-    <row r="401" spans="1:11">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A401" s="8">
         <v>41682</v>
       </c>
@@ -29840,7 +29839,7 @@
         <v>50.456539714887306</v>
       </c>
     </row>
-    <row r="402" spans="1:11">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A402" s="8">
         <v>41689</v>
       </c>
@@ -29876,7 +29875,7 @@
         <v>53.893528968558918</v>
       </c>
     </row>
-    <row r="403" spans="1:11">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A403" s="8">
         <v>41696</v>
       </c>
@@ -29912,7 +29911,7 @@
         <v>32.173253175865931</v>
       </c>
     </row>
-    <row r="404" spans="1:11">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A404" s="8">
         <v>41703</v>
       </c>
@@ -29948,7 +29947,7 @@
         <v>28.177917475995674</v>
       </c>
     </row>
-    <row r="405" spans="1:11">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A405" s="8">
         <v>41710</v>
       </c>
@@ -29984,7 +29983,7 @@
         <v>38.591960706244812</v>
       </c>
     </row>
-    <row r="406" spans="1:11">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A406" s="8">
         <v>41716</v>
       </c>
@@ -30020,7 +30019,7 @@
         <v>62.434033436115925</v>
       </c>
     </row>
-    <row r="407" spans="1:11">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A407" s="8">
         <v>41717</v>
       </c>
@@ -30056,7 +30055,7 @@
         <v>38.474239554033893</v>
       </c>
     </row>
-    <row r="408" spans="1:11">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A408" s="8">
         <v>41724</v>
       </c>
@@ -30092,7 +30091,7 @@
         <v>30.022064656219442</v>
       </c>
     </row>
-    <row r="409" spans="1:11">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A409" s="8">
         <v>41731</v>
       </c>
@@ -30128,7 +30127,7 @@
         <v>44.188138476313277</v>
       </c>
     </row>
-    <row r="410" spans="1:11">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A410" s="8">
         <v>41738</v>
       </c>
@@ -30164,7 +30163,7 @@
         <v>31.323363729632899</v>
       </c>
     </row>
-    <row r="411" spans="1:11">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A411" s="8">
         <v>41745</v>
       </c>
@@ -30200,7 +30199,7 @@
         <v>35.606324792337006</v>
       </c>
     </row>
-    <row r="412" spans="1:11">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A412" s="8">
         <v>41752</v>
       </c>
@@ -30236,7 +30235,7 @@
         <v>35.382781553838939</v>
       </c>
     </row>
-    <row r="413" spans="1:11">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A413" s="8">
         <v>41759</v>
       </c>
@@ -30272,7 +30271,7 @@
         <v>45.803062444786249</v>
       </c>
     </row>
-    <row r="414" spans="1:11">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A414" s="8">
         <v>41766</v>
       </c>
@@ -30308,7 +30307,7 @@
         <v>37.395218193640751</v>
       </c>
     </row>
-    <row r="415" spans="1:11">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A415" s="8">
         <v>41773</v>
       </c>
@@ -30344,7 +30343,7 @@
         <v>30.364171137854051</v>
       </c>
     </row>
-    <row r="416" spans="1:11">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A416" s="8">
         <v>41780</v>
       </c>
@@ -30380,7 +30379,7 @@
         <v>46.926276851752007</v>
       </c>
     </row>
-    <row r="417" spans="1:11">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A417" s="8">
         <v>41787</v>
       </c>
@@ -30416,7 +30415,7 @@
         <v>56.381294114615542</v>
       </c>
     </row>
-    <row r="418" spans="1:11">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A418" s="8">
         <v>41794</v>
       </c>
@@ -30452,7 +30451,7 @@
         <v>42.349237020811792</v>
       </c>
     </row>
-    <row r="419" spans="1:11">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A419" s="8">
         <v>41801</v>
       </c>
@@ -30488,7 +30487,7 @@
         <v>38.373204647880215</v>
       </c>
     </row>
-    <row r="420" spans="1:11">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A420" s="8">
         <v>41808</v>
       </c>
@@ -30524,7 +30523,7 @@
         <v>44.314119769408713</v>
       </c>
     </row>
-    <row r="421" spans="1:11">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A421" s="8">
         <v>41815</v>
       </c>
@@ -30560,7 +30559,7 @@
         <v>60.45119572753616</v>
       </c>
     </row>
-    <row r="422" spans="1:11">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A422" s="8">
         <v>41822</v>
       </c>
@@ -30596,7 +30595,7 @@
         <v>47.49836466704955</v>
       </c>
     </row>
-    <row r="423" spans="1:11">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A423" s="8">
         <v>41829</v>
       </c>
@@ -30632,7 +30631,7 @@
         <v>35.064608489041966</v>
       </c>
     </row>
-    <row r="424" spans="1:11">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A424" s="8">
         <v>41836</v>
       </c>
@@ -30668,7 +30667,7 @@
         <v>44.721213423875326</v>
       </c>
     </row>
-    <row r="425" spans="1:11">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A425" s="8">
         <v>41843</v>
       </c>
@@ -30704,7 +30703,7 @@
         <v>39.312318980389804</v>
       </c>
     </row>
-    <row r="426" spans="1:11">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A426" s="8">
         <v>41850</v>
       </c>
@@ -30740,7 +30739,7 @@
         <v>34.47072790576</v>
       </c>
     </row>
-    <row r="427" spans="1:11">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A427" s="8">
         <v>41857</v>
       </c>
@@ -30776,7 +30775,7 @@
         <v>51.803015068152312</v>
       </c>
     </row>
-    <row r="428" spans="1:11">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A428" s="8">
         <v>41864</v>
       </c>
@@ -30812,7 +30811,7 @@
         <v>45.922649241726944</v>
       </c>
     </row>
-    <row r="429" spans="1:11">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A429" s="8">
         <v>41871</v>
       </c>
@@ -30848,7 +30847,7 @@
         <v>62.557833587887913</v>
       </c>
     </row>
-    <row r="430" spans="1:11">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A430" s="8">
         <v>41878</v>
       </c>
@@ -30884,7 +30883,7 @@
         <v>47.65914443041865</v>
       </c>
     </row>
-    <row r="431" spans="1:11">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A431" s="8">
         <v>41885</v>
       </c>
@@ -30920,7 +30919,7 @@
         <v>59.213557190072954</v>
       </c>
     </row>
-    <row r="432" spans="1:11">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A432" s="8">
         <v>41892</v>
       </c>
@@ -30956,7 +30955,7 @@
         <v>57.333019762644675</v>
       </c>
     </row>
-    <row r="433" spans="1:11">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A433" s="8">
         <v>41899</v>
       </c>
@@ -30992,7 +30991,7 @@
         <v>49.133395431991111</v>
       </c>
     </row>
-    <row r="434" spans="1:11">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A434" s="8">
         <v>41906</v>
       </c>
@@ -31028,7 +31027,7 @@
         <v>55.537677707137746</v>
       </c>
     </row>
-    <row r="435" spans="1:11">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A435" s="8">
         <v>41913</v>
       </c>
@@ -31064,7 +31063,7 @@
         <v>66.806525599248758</v>
       </c>
     </row>
-    <row r="436" spans="1:11">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A436" s="8">
         <v>41920</v>
       </c>
@@ -31100,7 +31099,7 @@
         <v>66.570355280429666</v>
       </c>
     </row>
-    <row r="437" spans="1:11">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A437" s="8">
         <v>41927</v>
       </c>
@@ -31136,7 +31135,7 @@
         <v>67.686973863523022</v>
       </c>
     </row>
-    <row r="438" spans="1:11">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A438" s="8">
         <v>41934</v>
       </c>
@@ -31172,7 +31171,7 @@
         <v>62.311923006128566</v>
       </c>
     </row>
-    <row r="439" spans="1:11">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A439" s="8">
         <v>41941</v>
       </c>
@@ -31208,7 +31207,7 @@
         <v>65.532799765784759</v>
       </c>
     </row>
-    <row r="440" spans="1:11">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A440" s="8">
         <v>41948</v>
       </c>
@@ -31244,7 +31243,7 @@
         <v>62.905619401035253</v>
       </c>
     </row>
-    <row r="441" spans="1:11">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A441" s="8">
         <v>41955</v>
       </c>
@@ -31280,7 +31279,7 @@
         <v>59.753766943925129</v>
       </c>
     </row>
-    <row r="442" spans="1:11">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A442" s="8">
         <v>41962</v>
       </c>
@@ -31316,7 +31315,7 @@
         <v>54.685208883890532</v>
       </c>
     </row>
-    <row r="443" spans="1:11">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A443" s="8">
         <v>41968</v>
       </c>
@@ -31352,7 +31351,7 @@
         <v>64.443637389582548</v>
       </c>
     </row>
-    <row r="444" spans="1:11">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A444" s="8">
         <v>41976</v>
       </c>
@@ -31388,7 +31387,7 @@
         <v>53.372403786390393</v>
       </c>
     </row>
-    <row r="445" spans="1:11">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A445" s="8">
         <v>41983</v>
       </c>
@@ -31424,7 +31423,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="446" spans="1:11">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A446" s="8">
         <v>41990</v>
       </c>
@@ -31460,7 +31459,7 @@
         <v>61.82397380318033</v>
       </c>
     </row>
-    <row r="447" spans="1:11">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A447" s="8">
         <v>41997</v>
       </c>
@@ -31496,7 +31495,7 @@
         <v>32.707053916439136</v>
       </c>
     </row>
-    <row r="448" spans="1:11">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A448" s="8">
         <v>42004</v>
       </c>
@@ -31532,7 +31531,7 @@
         <v>43.310807829305034</v>
       </c>
     </row>
-    <row r="449" spans="1:11">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A449" s="8">
         <v>42011</v>
       </c>
@@ -31568,7 +31567,7 @@
         <v>73.520753699141281</v>
       </c>
     </row>
-    <row r="450" spans="1:11">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A450" s="8">
         <v>42018</v>
       </c>
@@ -31604,7 +31603,7 @@
         <v>53.380532408043727</v>
       </c>
     </row>
-    <row r="451" spans="1:11">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A451" s="8">
         <v>42025</v>
       </c>
@@ -31655,7 +31654,7 @@
         <v>52.550400098141971</v>
       </c>
     </row>
-    <row r="452" spans="1:11">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A452" s="8">
         <v>42032</v>
       </c>
@@ -31691,7 +31690,7 @@
         <v>39.19736690032088</v>
       </c>
     </row>
-    <row r="453" spans="1:11">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A453" s="8">
         <v>42039</v>
       </c>
@@ -31727,7 +31726,7 @@
         <v>44.064003122982612</v>
       </c>
     </row>
-    <row r="454" spans="1:11">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A454" s="8">
         <v>42046</v>
       </c>
@@ -31763,7 +31762,7 @@
         <v>37.007673607771878</v>
       </c>
     </row>
-    <row r="455" spans="1:11">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A455" s="8">
         <v>42053</v>
       </c>
@@ -31799,7 +31798,7 @@
         <v>42.561466476456637</v>
       </c>
     </row>
-    <row r="456" spans="1:11">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A456" s="8">
         <v>42060</v>
       </c>
@@ -31835,7 +31834,7 @@
         <v>45.402755221031484</v>
       </c>
     </row>
-    <row r="457" spans="1:11">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A457" s="8">
         <v>42067</v>
       </c>
@@ -31871,7 +31870,7 @@
         <v>48.211272729748821</v>
       </c>
     </row>
-    <row r="458" spans="1:11">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A458" s="8">
         <v>42074</v>
       </c>
@@ -31907,7 +31906,7 @@
         <v>67.383421717313624</v>
       </c>
     </row>
-    <row r="459" spans="1:11">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A459" s="8">
         <v>42088</v>
       </c>
@@ -31943,7 +31942,7 @@
         <v>30.956834906605707</v>
       </c>
     </row>
-    <row r="460" spans="1:11">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A460" s="8">
         <v>42095</v>
       </c>
@@ -31979,7 +31978,7 @@
         <v>54.500081021599833</v>
       </c>
     </row>
-    <row r="461" spans="1:11">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A461" s="8">
         <v>42102</v>
       </c>
@@ -32015,7 +32014,7 @@
         <v>28.291363992271719</v>
       </c>
     </row>
-    <row r="462" spans="1:11">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A462" s="8">
         <v>42109</v>
       </c>
@@ -32051,7 +32050,7 @@
         <v>40.543750857694739</v>
       </c>
     </row>
-    <row r="463" spans="1:11">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A463" s="8">
         <v>42116</v>
       </c>
@@ -32087,7 +32086,7 @@
         <v>59.571201699918042</v>
       </c>
     </row>
-    <row r="464" spans="1:11">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A464" s="8">
         <v>42123</v>
       </c>
@@ -32123,7 +32122,7 @@
         <v>34.27313982014654</v>
       </c>
     </row>
-    <row r="465" spans="1:11">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A465" s="8">
         <v>42130</v>
       </c>
@@ -32159,7 +32158,7 @@
         <v>56.955691995283715</v>
       </c>
     </row>
-    <row r="466" spans="1:11">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A466" s="8">
         <v>42137</v>
       </c>
@@ -32195,7 +32194,7 @@
         <v>54.764046582566408</v>
       </c>
     </row>
-    <row r="467" spans="1:11">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A467" s="8">
         <v>42144</v>
       </c>
@@ -32231,7 +32230,7 @@
         <v>55.757136500127764</v>
       </c>
     </row>
-    <row r="468" spans="1:11">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A468" s="8">
         <v>42151</v>
       </c>
@@ -32267,7 +32266,7 @@
         <v>59.139689894729841</v>
       </c>
     </row>
-    <row r="469" spans="1:11">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A469" s="8">
         <v>42158</v>
       </c>
@@ -32303,7 +32302,7 @@
         <v>58.565690013670491</v>
       </c>
     </row>
-    <row r="470" spans="1:11">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A470" s="8">
         <v>42165</v>
       </c>
@@ -32339,7 +32338,7 @@
         <v>58.285726582262178</v>
       </c>
     </row>
-    <row r="471" spans="1:11">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A471" s="8">
         <v>42172</v>
       </c>
@@ -32375,7 +32374,7 @@
         <v>51.057335391353512</v>
       </c>
     </row>
-    <row r="472" spans="1:11">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A472" s="8">
         <v>42179</v>
       </c>
@@ -32411,7 +32410,7 @@
         <v>58.045476963818579</v>
       </c>
     </row>
-    <row r="473" spans="1:11">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A473" s="8">
         <v>42186</v>
       </c>
@@ -32447,7 +32446,7 @@
         <v>60.134571875867529</v>
       </c>
     </row>
-    <row r="474" spans="1:11">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A474" s="8">
         <v>42193</v>
       </c>
@@ -32483,7 +32482,7 @@
         <v>64.152197101026005</v>
       </c>
     </row>
-    <row r="475" spans="1:11">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A475" s="8">
         <v>42200</v>
       </c>
@@ -32519,7 +32518,7 @@
         <v>62.876249643492336</v>
       </c>
     </row>
-    <row r="476" spans="1:11">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A476" s="8">
         <v>42207</v>
       </c>
@@ -32555,7 +32554,7 @@
         <v>69.115289526281927</v>
       </c>
     </row>
-    <row r="477" spans="1:11">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A477" s="8">
         <v>42214</v>
       </c>
@@ -32591,7 +32590,7 @@
         <v>65.005582381367375</v>
       </c>
     </row>
-    <row r="478" spans="1:11">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A478" s="8">
         <v>42221</v>
       </c>
@@ -32627,7 +32626,7 @@
         <v>63.076909141434115</v>
       </c>
     </row>
-    <row r="479" spans="1:11">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A479" s="8">
         <v>42228</v>
       </c>
@@ -32663,7 +32662,7 @@
         <v>62.189535700762221</v>
       </c>
     </row>
-    <row r="480" spans="1:11">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A480" s="8">
         <v>42235</v>
       </c>
@@ -32699,7 +32698,7 @@
         <v>56.905421187389813</v>
       </c>
     </row>
-    <row r="481" spans="1:11">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A481" s="8">
         <v>42242</v>
       </c>
@@ -32735,7 +32734,7 @@
         <v>54.437212556646394</v>
       </c>
     </row>
-    <row r="482" spans="1:11">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A482" s="8">
         <v>42249</v>
       </c>
@@ -32771,7 +32770,7 @@
         <v>45.740626444393065</v>
       </c>
     </row>
-    <row r="483" spans="1:11">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A483" s="8">
         <v>42256</v>
       </c>
@@ -32807,7 +32806,7 @@
         <v>39.805313843808364</v>
       </c>
     </row>
-    <row r="484" spans="1:11">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A484" s="8">
         <v>42263</v>
       </c>
@@ -32843,7 +32842,7 @@
         <v>43.806543446148218</v>
       </c>
     </row>
-    <row r="485" spans="1:11">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A485" s="8">
         <v>42270</v>
       </c>
@@ -32879,7 +32878,7 @@
         <v>51.716685867776327</v>
       </c>
     </row>
-    <row r="486" spans="1:11">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A486" s="8">
         <v>42277</v>
       </c>
@@ -32915,7 +32914,7 @@
         <v>58.081158609585614</v>
       </c>
     </row>
-    <row r="487" spans="1:11">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A487" s="8">
         <v>42284</v>
       </c>
@@ -32951,7 +32950,7 @@
         <v>56.825158228391729</v>
       </c>
     </row>
-    <row r="488" spans="1:11">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A488" s="8">
         <v>42291</v>
       </c>
@@ -32987,7 +32986,7 @@
         <v>67.174925319764782</v>
       </c>
     </row>
-    <row r="489" spans="1:11">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A489" s="8">
         <v>42298</v>
       </c>
@@ -33023,7 +33022,7 @@
         <v>45.345586579315764</v>
       </c>
     </row>
-    <row r="490" spans="1:11">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A490" s="8">
         <v>42305</v>
       </c>
@@ -33059,7 +33058,7 @@
         <v>57.374167645036572</v>
       </c>
     </row>
-    <row r="491" spans="1:11">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A491" s="8">
         <v>42312</v>
       </c>
@@ -33095,7 +33094,7 @@
         <v>51.179056631292994</v>
       </c>
     </row>
-    <row r="492" spans="1:11">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A492" s="8">
         <v>42319</v>
       </c>
@@ -33131,7 +33130,7 @@
         <v>53.107945174576969</v>
       </c>
     </row>
-    <row r="493" spans="1:11">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A493" s="8">
         <v>42326</v>
       </c>
@@ -33167,7 +33166,7 @@
         <v>58.422447069085209</v>
       </c>
     </row>
-    <row r="494" spans="1:11">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A494" s="8">
         <v>42333</v>
       </c>
@@ -33203,7 +33202,7 @@
         <v>34.740224585926597</v>
       </c>
     </row>
-    <row r="495" spans="1:11">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A495" s="8">
         <v>42340</v>
       </c>
@@ -33239,7 +33238,7 @@
         <v>53.475606892716783</v>
       </c>
     </row>
-    <row r="496" spans="1:11">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A496" s="8">
         <v>42347</v>
       </c>
@@ -33275,7 +33274,7 @@
         <v>49.782638326185712</v>
       </c>
     </row>
-    <row r="497" spans="1:11">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A497" s="8">
         <v>42354</v>
       </c>
@@ -33311,7 +33310,7 @@
         <v>64.682794789944978</v>
       </c>
     </row>
-    <row r="498" spans="1:11">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A498" s="8">
         <v>42361</v>
       </c>
@@ -33347,7 +33346,7 @@
         <v>58.632036840912747</v>
       </c>
     </row>
-    <row r="499" spans="1:11">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A499" s="8">
         <v>42368</v>
       </c>
@@ -33383,7 +33382,7 @@
         <v>60.952600023373698</v>
       </c>
     </row>
-    <row r="500" spans="1:11">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A500" s="8">
         <v>42375</v>
       </c>
@@ -33419,7 +33418,7 @@
         <v>66.58828791661989</v>
       </c>
     </row>
-    <row r="501" spans="1:11">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A501" s="8">
         <v>42382</v>
       </c>
@@ -33455,7 +33454,7 @@
         <v>64.934642249421515</v>
       </c>
     </row>
-    <row r="502" spans="1:11">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A502" s="8">
         <v>42396</v>
       </c>
@@ -33491,7 +33490,7 @@
         <v>41.40576650661113</v>
       </c>
     </row>
-    <row r="503" spans="1:11">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A503" s="8">
         <v>42403</v>
       </c>
@@ -33527,7 +33526,7 @@
         <v>31.776137400465753</v>
       </c>
     </row>
-    <row r="504" spans="1:11">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A504" s="8">
         <v>42410</v>
       </c>
@@ -33563,7 +33562,7 @@
         <v>53.128851841152972</v>
       </c>
     </row>
-    <row r="505" spans="1:11">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A505" s="8">
         <v>42417</v>
       </c>
@@ -33599,7 +33598,7 @@
         <v>38.552772794324362</v>
       </c>
     </row>
-    <row r="506" spans="1:11">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A506" s="8">
         <v>42424</v>
       </c>
@@ -33635,7 +33634,7 @@
         <v>57.386093846065783</v>
       </c>
     </row>
-    <row r="507" spans="1:11">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A507" s="8">
         <v>42431</v>
       </c>
@@ -33671,7 +33670,7 @@
         <v>56.216108002049303</v>
       </c>
     </row>
-    <row r="508" spans="1:11">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A508" s="8">
         <v>42438</v>
       </c>
@@ -33707,7 +33706,7 @@
         <v>49.345050684492676</v>
       </c>
     </row>
-    <row r="509" spans="1:11">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A509" s="8">
         <v>42445</v>
       </c>
@@ -33743,7 +33742,7 @@
         <v>47.469934929618582</v>
       </c>
     </row>
-    <row r="510" spans="1:11">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A510" s="8">
         <v>42452</v>
       </c>
@@ -33779,7 +33778,7 @@
         <v>55.942502690409157</v>
       </c>
     </row>
-    <row r="511" spans="1:11">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A511" s="8">
         <v>42459</v>
       </c>
@@ -33815,7 +33814,7 @@
         <v>51.171281684204004</v>
       </c>
     </row>
-    <row r="512" spans="1:11">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A512" s="8">
         <v>42466</v>
       </c>
@@ -33851,7 +33850,7 @@
         <v>44.987298684587493</v>
       </c>
     </row>
-    <row r="513" spans="1:11">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A513" s="8">
         <v>42473</v>
       </c>
@@ -33887,7 +33886,7 @@
         <v>52.267754767722032</v>
       </c>
     </row>
-    <row r="514" spans="1:11">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A514" s="8">
         <v>42480</v>
       </c>
@@ -33923,7 +33922,7 @@
         <v>59.274689783916969</v>
       </c>
     </row>
-    <row r="515" spans="1:11">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A515" s="8">
         <v>42487</v>
       </c>
@@ -33974,7 +33973,7 @@
         <v>56.059043268503345</v>
       </c>
     </row>
-    <row r="516" spans="1:11">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A516" s="8">
         <v>42494</v>
       </c>
@@ -34010,7 +34009,7 @@
         <v>63.557616832598796</v>
       </c>
     </row>
-    <row r="517" spans="1:11">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A517" s="8">
         <v>42501</v>
       </c>
@@ -34046,7 +34045,7 @@
         <v>60.325228184861054</v>
       </c>
     </row>
-    <row r="518" spans="1:11">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A518" s="8">
         <v>42508</v>
       </c>
@@ -34082,7 +34081,7 @@
         <v>66.025148795269672</v>
       </c>
     </row>
-    <row r="519" spans="1:11">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A519" s="8">
         <v>42515</v>
       </c>
@@ -34118,7 +34117,7 @@
         <v>65.838860527469308</v>
       </c>
     </row>
-    <row r="520" spans="1:11">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A520" s="8">
         <v>42522</v>
       </c>
@@ -34154,7 +34153,7 @@
         <v>58.204477883361697</v>
       </c>
     </row>
-    <row r="521" spans="1:11">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A521" s="8">
         <v>42529</v>
       </c>
@@ -34190,7 +34189,7 @@
         <v>67.614110056909553</v>
       </c>
     </row>
-    <row r="522" spans="1:11">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522" s="8">
         <v>42536</v>
       </c>
@@ -34226,7 +34225,7 @@
         <v>74.11356391861203</v>
       </c>
     </row>
-    <row r="523" spans="1:11">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523" s="8">
         <v>42543</v>
       </c>
@@ -34262,7 +34261,7 @@
         <v>73.151472857827756</v>
       </c>
     </row>
-    <row r="524" spans="1:11">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A524" s="8">
         <v>42550</v>
       </c>
@@ -34298,7 +34297,7 @@
         <v>61.145192933839347</v>
       </c>
     </row>
-    <row r="525" spans="1:11">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A525" s="8">
         <v>42557</v>
       </c>
@@ -34334,7 +34333,7 @@
         <v>59.461294600399974</v>
       </c>
     </row>
-    <row r="526" spans="1:11">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A526" s="8">
         <v>42564</v>
       </c>
@@ -34370,7 +34369,7 @@
         <v>55.474316952158986</v>
       </c>
     </row>
-    <row r="527" spans="1:11">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A527" s="8">
         <v>42571</v>
       </c>
@@ -34406,7 +34405,7 @@
         <v>47.642829505911699</v>
       </c>
     </row>
-    <row r="528" spans="1:11">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A528" s="8">
         <v>42578</v>
       </c>
@@ -34442,7 +34441,7 @@
         <v>38.757015074458316</v>
       </c>
     </row>
-    <row r="529" spans="1:11">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A529" s="8">
         <v>42585</v>
       </c>
@@ -34478,7 +34477,7 @@
         <v>40.898792194128127</v>
       </c>
     </row>
-    <row r="530" spans="1:11">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A530" s="8">
         <v>42592</v>
       </c>
@@ -34514,7 +34513,7 @@
         <v>44.684911157119551</v>
       </c>
     </row>
-    <row r="531" spans="1:11">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A531" s="8">
         <v>42599</v>
       </c>
@@ -34550,7 +34549,7 @@
         <v>38.351540526685874</v>
       </c>
     </row>
-    <row r="532" spans="1:11">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A532" s="8">
         <v>42606</v>
       </c>
@@ -34586,7 +34585,7 @@
         <v>52.845347659285657</v>
       </c>
     </row>
-    <row r="533" spans="1:11">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A533" s="8">
         <v>42613</v>
       </c>
@@ -34622,7 +34621,7 @@
         <v>50.592178955136646</v>
       </c>
     </row>
-    <row r="534" spans="1:11">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A534" s="8">
         <v>42620</v>
       </c>
@@ -34658,7 +34657,7 @@
         <v>45.8727017663767</v>
       </c>
     </row>
-    <row r="535" spans="1:11">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A535" s="8">
         <v>42627</v>
       </c>
@@ -34694,7 +34693,7 @@
         <v>74.814030546861105</v>
       </c>
     </row>
-    <row r="536" spans="1:11">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A536" s="8">
         <v>42634</v>
       </c>
@@ -34730,7 +34729,7 @@
         <v>53.632347230101267</v>
       </c>
     </row>
-    <row r="537" spans="1:11">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A537" s="8">
         <v>42641</v>
       </c>
@@ -34766,7 +34765,7 @@
         <v>48.896571681685643</v>
       </c>
     </row>
-    <row r="538" spans="1:11">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A538" s="8">
         <v>42648</v>
       </c>
@@ -34802,7 +34801,7 @@
         <v>61.205113840328835</v>
       </c>
     </row>
-    <row r="539" spans="1:11">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A539" s="8">
         <v>42655</v>
       </c>
@@ -34838,7 +34837,7 @@
         <v>57.785327901705259</v>
       </c>
     </row>
-    <row r="540" spans="1:11">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A540" s="8">
         <v>42662</v>
       </c>
@@ -34874,7 +34873,7 @@
         <v>79.940100561197539</v>
       </c>
     </row>
-    <row r="541" spans="1:11">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A541" s="8">
         <v>42669</v>
       </c>
@@ -34910,7 +34909,7 @@
         <v>73.199803298495794</v>
       </c>
     </row>
-    <row r="542" spans="1:11">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A542" s="8">
         <v>42676</v>
       </c>
@@ -34946,7 +34945,7 @@
         <v>81.972971493996454</v>
       </c>
     </row>
-    <row r="543" spans="1:11">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A543" s="8">
         <v>42683</v>
       </c>
@@ -34982,7 +34981,7 @@
         <v>70.252181451028676</v>
       </c>
     </row>
-    <row r="544" spans="1:11">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A544" s="8">
         <v>42689</v>
       </c>
@@ -35018,7 +35017,7 @@
         <v>45.034554333138182</v>
       </c>
     </row>
-    <row r="545" spans="1:11">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A545" s="8">
         <v>42697</v>
       </c>
@@ -35054,7 +35053,7 @@
         <v>31.902622834964525</v>
       </c>
     </row>
-    <row r="546" spans="1:11">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A546" s="8">
         <v>42704</v>
       </c>
@@ -35090,7 +35089,7 @@
         <v>33.812107442362681</v>
       </c>
     </row>
-    <row r="547" spans="1:11">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A547" s="8">
         <v>42711</v>
       </c>
@@ -35126,7 +35125,7 @@
         <v>44.571790079241985</v>
       </c>
     </row>
-    <row r="548" spans="1:11">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A548" s="8">
         <v>42718</v>
       </c>
@@ -35162,7 +35161,7 @@
         <v>51.225600837105361</v>
       </c>
     </row>
-    <row r="549" spans="1:11">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A549" s="8">
         <v>42725</v>
       </c>
@@ -35198,7 +35197,7 @@
         <v>31.324298121335335</v>
       </c>
     </row>
-    <row r="550" spans="1:11">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A550" s="8">
         <v>42732</v>
       </c>
@@ -35234,7 +35233,7 @@
         <v>40.560500686953205</v>
       </c>
     </row>
-    <row r="551" spans="1:11">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A551" s="8">
         <v>42739</v>
       </c>
@@ -35270,7 +35269,7 @@
         <v>41.368869961849803</v>
       </c>
     </row>
-    <row r="552" spans="1:11">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A552" s="8">
         <v>42746</v>
       </c>
@@ -35306,7 +35305,7 @@
         <v>36.188090354038536</v>
       </c>
     </row>
-    <row r="553" spans="1:11">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A553" s="8">
         <v>42753</v>
       </c>
@@ -35342,7 +35341,7 @@
         <v>37.743249902447104</v>
       </c>
     </row>
-    <row r="554" spans="1:11">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A554" s="8">
         <v>42760</v>
       </c>
@@ -35378,7 +35377,7 @@
         <v>38.125600177425255</v>
       </c>
     </row>
-    <row r="555" spans="1:11">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A555" s="8">
         <v>42767</v>
       </c>
@@ -35414,7 +35413,7 @@
         <v>35.21374453775752</v>
       </c>
     </row>
-    <row r="556" spans="1:11">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A556" s="8">
         <v>42774</v>
       </c>
@@ -35450,7 +35449,7 @@
         <v>37.200813418944776</v>
       </c>
     </row>
-    <row r="557" spans="1:11">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A557" s="8">
         <v>42781</v>
       </c>
@@ -35486,7 +35485,7 @@
         <v>46.401461865606194</v>
       </c>
     </row>
-    <row r="558" spans="1:11">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A558" s="8">
         <v>42788</v>
       </c>
@@ -35522,7 +35521,7 @@
         <v>47.306097125086168</v>
       </c>
     </row>
-    <row r="559" spans="1:11">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A559" s="8">
         <v>42795</v>
       </c>
@@ -35558,7 +35557,7 @@
         <v>40.981014136054526</v>
       </c>
     </row>
-    <row r="560" spans="1:11">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A560" s="8">
         <v>42802</v>
       </c>
@@ -35594,7 +35593,7 @@
         <v>33.994932520079296</v>
       </c>
     </row>
-    <row r="561" spans="1:11">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A561" s="8">
         <v>42809</v>
       </c>
@@ -35630,7 +35629,7 @@
         <v>44.968363852363964</v>
       </c>
     </row>
-    <row r="562" spans="1:11">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A562" s="8">
         <v>42816</v>
       </c>
@@ -35666,7 +35665,7 @@
         <v>49.659201917259722</v>
       </c>
     </row>
-    <row r="563" spans="1:11">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A563" s="8">
         <v>42823</v>
       </c>
@@ -35702,7 +35701,7 @@
         <v>64.362780454268531</v>
       </c>
     </row>
-    <row r="564" spans="1:11">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A564" s="8">
         <v>42830</v>
       </c>
@@ -35738,7 +35737,7 @@
         <v>64.776799001384475</v>
       </c>
     </row>
-    <row r="565" spans="1:11">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A565" s="8">
         <v>42837</v>
       </c>
@@ -35774,7 +35773,7 @@
         <v>65.166932244503599</v>
       </c>
     </row>
-    <row r="566" spans="1:11">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A566" s="8">
         <v>42844</v>
       </c>
@@ -35810,7 +35809,7 @@
         <v>59.958870200350503</v>
       </c>
     </row>
-    <row r="567" spans="1:11">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A567" s="8">
         <v>42851</v>
       </c>
@@ -35846,7 +35845,7 @@
         <v>59.381621852968017</v>
       </c>
     </row>
-    <row r="568" spans="1:11">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A568" s="8">
         <v>42858</v>
       </c>
@@ -35882,7 +35881,7 @@
         <v>43.61543763393874</v>
       </c>
     </row>
-    <row r="569" spans="1:11">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A569" s="8">
         <v>42865</v>
       </c>
@@ -35918,7 +35917,7 @@
         <v>45.396879132363082</v>
       </c>
     </row>
-    <row r="570" spans="1:11">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A570" s="8">
         <v>42872</v>
       </c>
@@ -35954,7 +35953,7 @@
         <v>57.001842496633159</v>
       </c>
     </row>
-    <row r="571" spans="1:11">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A571" s="8">
         <v>42879</v>
       </c>
@@ -35990,7 +35989,7 @@
         <v>43.069217656771137</v>
       </c>
     </row>
-    <row r="572" spans="1:11">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A572" s="8">
         <v>42886</v>
       </c>
@@ -36026,7 +36025,7 @@
         <v>48.392374712148168</v>
       </c>
     </row>
-    <row r="573" spans="1:11">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A573" s="8">
         <v>42893</v>
       </c>
@@ -36062,7 +36061,7 @@
         <v>40.948483493075209</v>
       </c>
     </row>
-    <row r="574" spans="1:11">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A574" s="8">
         <v>42900</v>
       </c>
@@ -36098,7 +36097,7 @@
         <v>37.402091766235387</v>
       </c>
     </row>
-    <row r="575" spans="1:11">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A575" s="8">
         <v>42907</v>
       </c>
@@ -36134,7 +36133,7 @@
         <v>46.287563991280784</v>
       </c>
     </row>
-    <row r="576" spans="1:11">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A576" s="8">
         <v>42914</v>
       </c>
@@ -36170,7 +36169,7 @@
         <v>51.63023920146022</v>
       </c>
     </row>
-    <row r="577" spans="1:11">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A577" s="8">
         <v>42921</v>
       </c>
@@ -36206,7 +36205,7 @@
         <v>38.938715947404972</v>
       </c>
     </row>
-    <row r="578" spans="1:11">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A578" s="8">
         <v>42928</v>
       </c>
@@ -36242,7 +36241,7 @@
         <v>32.992166958557021</v>
       </c>
     </row>
-    <row r="579" spans="1:11">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A579" s="8">
         <v>42935</v>
       </c>
@@ -36293,7 +36292,7 @@
         <v>41.819650581896475</v>
       </c>
     </row>
-    <row r="580" spans="1:11">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A580" s="8">
         <v>42942</v>
       </c>
@@ -36329,7 +36328,7 @@
         <v>50.264603848036046</v>
       </c>
     </row>
-    <row r="581" spans="1:11">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A581" s="8">
         <v>42949</v>
       </c>
@@ -36365,7 +36364,7 @@
         <v>42.982310991380189</v>
       </c>
     </row>
-    <row r="582" spans="1:11">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A582" s="8">
         <v>42956</v>
       </c>
@@ -36401,7 +36400,7 @@
         <v>42.602862162618685</v>
       </c>
     </row>
-    <row r="583" spans="1:11">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A583" s="8">
         <v>42963</v>
       </c>
@@ -36437,7 +36436,7 @@
         <v>35.515471002867969</v>
       </c>
     </row>
-    <row r="584" spans="1:11">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A584" s="8">
         <v>42970</v>
       </c>
@@ -36473,7 +36472,7 @@
         <v>41.20422836194178</v>
       </c>
     </row>
-    <row r="585" spans="1:11">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A585" s="8">
         <v>42977</v>
       </c>
@@ -36509,7 +36508,7 @@
         <v>46.305875728509086</v>
       </c>
     </row>
-    <row r="586" spans="1:11">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A586" s="8">
         <v>42984</v>
       </c>
@@ -36545,7 +36544,7 @@
         <v>52.28157999497369</v>
       </c>
     </row>
-    <row r="587" spans="1:11">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A587" s="8">
         <v>42991</v>
       </c>
@@ -36581,7 +36580,7 @@
         <v>45.246656707228858</v>
       </c>
     </row>
-    <row r="588" spans="1:11">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A588" s="8">
         <v>42998</v>
       </c>
@@ -36617,7 +36616,7 @@
         <v>42.836271786367632</v>
       </c>
     </row>
-    <row r="589" spans="1:11">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A589" s="8">
         <v>43005</v>
       </c>
@@ -36653,7 +36652,7 @@
         <v>25.850229689501795</v>
       </c>
     </row>
-    <row r="590" spans="1:11">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A590" s="8">
         <v>43012</v>
       </c>
@@ -36689,7 +36688,7 @@
         <v>29.219171788399478</v>
       </c>
     </row>
-    <row r="591" spans="1:11">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A591" s="8">
         <v>43019</v>
       </c>
@@ -36725,7 +36724,7 @@
         <v>47.697764295090394</v>
       </c>
     </row>
-    <row r="592" spans="1:11">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A592" s="8">
         <v>43026</v>
       </c>
@@ -36761,7 +36760,7 @@
         <v>38.422382980352594</v>
       </c>
     </row>
-    <row r="593" spans="1:11">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A593" s="8">
         <v>43033</v>
       </c>
@@ -36797,7 +36796,7 @@
         <v>64.258296622360419</v>
       </c>
     </row>
-    <row r="594" spans="1:11">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A594" s="8">
         <v>43040</v>
       </c>
@@ -36833,7 +36832,7 @@
         <v>57.905260906954553</v>
       </c>
     </row>
-    <row r="595" spans="1:11">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A595" s="8">
         <v>43047</v>
       </c>
@@ -36869,7 +36868,7 @@
         <v>34.736286502733705</v>
       </c>
     </row>
-    <row r="596" spans="1:11">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A596" s="8">
         <v>43054</v>
       </c>
@@ -36905,7 +36904,7 @@
         <v>68.592291112048443</v>
       </c>
     </row>
-    <row r="597" spans="1:11">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A597" s="8">
         <v>43061</v>
       </c>
@@ -36941,7 +36940,7 @@
         <v>27.3096898737011</v>
       </c>
     </row>
-    <row r="598" spans="1:11">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A598" s="8">
         <v>43068</v>
       </c>
@@ -36977,7 +36976,7 @@
         <v>47.380261477684584</v>
       </c>
     </row>
-    <row r="599" spans="1:11">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A599" s="8">
         <v>43075</v>
       </c>
@@ -37013,7 +37012,7 @@
         <v>48.440037392978304</v>
       </c>
     </row>
-    <row r="600" spans="1:11">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A600" s="8">
         <v>43082</v>
       </c>
@@ -37049,7 +37048,7 @@
         <v>44.562343622567724</v>
       </c>
     </row>
-    <row r="601" spans="1:11">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A601" s="8">
         <v>43089</v>
       </c>
@@ -37085,7 +37084,7 @@
         <v>36.623281382599032</v>
       </c>
     </row>
-    <row r="602" spans="1:11">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A602" s="8">
         <v>43096</v>
       </c>
@@ -37121,7 +37120,7 @@
         <v>34.643577434597006</v>
       </c>
     </row>
-    <row r="603" spans="1:11">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A603" s="8">
         <v>43103</v>
       </c>
@@ -37157,7 +37156,7 @@
         <v>25.360655270394762</v>
       </c>
     </row>
-    <row r="604" spans="1:11">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A604" s="8">
         <v>43110</v>
       </c>
@@ -37193,7 +37192,7 @@
         <v>25.396638870684793</v>
       </c>
     </row>
-    <row r="605" spans="1:11">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A605" s="8">
         <v>43117</v>
       </c>
@@ -37229,7 +37228,7 @@
         <v>27.71</v>
       </c>
     </row>
-    <row r="606" spans="1:11">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A606" s="8">
         <v>43124</v>
       </c>
@@ -37265,7 +37264,7 @@
         <v>29.33</v>
       </c>
     </row>
-    <row r="607" spans="1:11">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A607" s="8">
         <v>43131</v>
       </c>
@@ -37301,7 +37300,7 @@
         <v>53.07</v>
       </c>
     </row>
-    <row r="608" spans="1:11">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A608" s="8">
         <v>43138</v>
       </c>
@@ -37337,7 +37336,7 @@
         <v>44.02</v>
       </c>
     </row>
-    <row r="609" spans="1:11">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A609" s="8">
         <v>43145</v>
       </c>
@@ -37373,7 +37372,7 @@
         <v>55.52</v>
       </c>
     </row>
-    <row r="610" spans="1:11">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A610" s="8">
         <v>43152</v>
       </c>
@@ -37409,7 +37408,7 @@
         <v>50.17</v>
       </c>
     </row>
-    <row r="611" spans="1:11">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A611" s="8">
         <v>43159</v>
       </c>
@@ -37445,7 +37444,7 @@
         <v>34.54</v>
       </c>
     </row>
-    <row r="612" spans="1:11">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A612" s="8">
         <v>43166</v>
       </c>
@@ -37481,7 +37480,7 @@
         <v>53.35</v>
       </c>
     </row>
-    <row r="613" spans="1:11">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A613" s="8">
         <v>43173</v>
       </c>
@@ -37517,7 +37516,7 @@
         <v>34.69</v>
       </c>
     </row>
-    <row r="614" spans="1:11">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A614" s="8">
         <v>43180</v>
       </c>
@@ -37553,7 +37552,7 @@
         <v>50.12</v>
       </c>
     </row>
-    <row r="615" spans="1:11">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A615" s="8">
         <v>43187</v>
       </c>
@@ -37589,7 +37588,7 @@
         <v>66.569999999999993</v>
       </c>
     </row>
-    <row r="616" spans="1:11">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A616" s="8">
         <v>43194</v>
       </c>
@@ -37625,7 +37624,7 @@
         <v>58.83</v>
       </c>
     </row>
-    <row r="617" spans="1:11">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A617" s="8">
         <v>43201</v>
       </c>
@@ -37661,7 +37660,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="618" spans="1:11">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A618" s="8">
         <v>43208</v>
       </c>
@@ -37697,7 +37696,7 @@
         <v>38.979999999999997</v>
       </c>
     </row>
-    <row r="619" spans="1:11">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A619" s="8">
         <v>43215</v>
       </c>
@@ -37733,7 +37732,7 @@
         <v>63.14</v>
       </c>
     </row>
-    <row r="620" spans="1:11">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A620" s="8">
         <v>43222</v>
       </c>
@@ -37769,7 +37768,7 @@
         <v>68.150000000000006</v>
       </c>
     </row>
-    <row r="621" spans="1:11">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A621" s="8">
         <v>43229</v>
       </c>
@@ -37805,7 +37804,7 @@
         <v>39.549999999999997</v>
       </c>
     </row>
-    <row r="622" spans="1:11">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A622" s="8">
         <v>43236</v>
       </c>
@@ -37841,7 +37840,7 @@
         <v>54.33</v>
       </c>
     </row>
-    <row r="623" spans="1:11">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A623" s="8">
         <v>43243</v>
       </c>
@@ -37877,7 +37876,7 @@
         <v>53.99</v>
       </c>
     </row>
-    <row r="624" spans="1:11">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A624" s="8">
         <v>43250</v>
       </c>
@@ -37913,7 +37912,7 @@
         <v>39.76</v>
       </c>
     </row>
-    <row r="625" spans="1:11">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A625" s="8">
         <v>43257</v>
       </c>
@@ -37949,7 +37948,7 @@
         <v>34.51</v>
       </c>
     </row>
-    <row r="626" spans="1:11">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A626" s="8">
         <v>43264</v>
       </c>
@@ -37985,7 +37984,7 @@
         <v>41.63</v>
       </c>
     </row>
-    <row r="627" spans="1:11">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A627" s="8">
         <v>43271</v>
       </c>
@@ -38021,7 +38020,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="628" spans="1:11">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A628" s="8">
         <v>43278</v>
       </c>
@@ -38057,7 +38056,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="629" spans="1:11">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A629" s="8">
         <v>43285</v>
       </c>
@@ -38093,7 +38092,7 @@
         <v>46.74</v>
       </c>
     </row>
-    <row r="630" spans="1:11">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A630" s="8">
         <v>43292</v>
       </c>
@@ -38129,7 +38128,7 @@
         <v>38.47</v>
       </c>
     </row>
-    <row r="631" spans="1:11">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A631" s="8">
         <v>43299</v>
       </c>
@@ -38165,7 +38164,7 @@
         <v>38.82</v>
       </c>
     </row>
-    <row r="632" spans="1:11">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A632" s="8">
         <v>43306</v>
       </c>
@@ -38201,7 +38200,7 @@
         <v>39.159999999999997</v>
       </c>
     </row>
-    <row r="633" spans="1:11">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A633" s="8">
         <v>43313</v>
       </c>
@@ -38237,7 +38236,7 @@
         <v>40.450000000000003</v>
       </c>
     </row>
-    <row r="634" spans="1:11">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A634" s="8">
         <v>43320</v>
       </c>
@@ -38273,7 +38272,7 @@
         <v>32.78</v>
       </c>
     </row>
-    <row r="635" spans="1:11">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A635" s="8">
         <v>43327</v>
       </c>
@@ -38309,7 +38308,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="636" spans="1:11">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A636" s="8">
         <v>43334</v>
       </c>
@@ -38345,7 +38344,7 @@
         <v>31.73</v>
       </c>
     </row>
-    <row r="637" spans="1:11">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A637" s="8">
         <v>43341</v>
       </c>
@@ -38381,7 +38380,7 @@
         <v>38.53</v>
       </c>
     </row>
-    <row r="638" spans="1:11">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A638" s="8">
         <v>43348</v>
       </c>
@@ -38417,7 +38416,7 @@
         <v>43.57</v>
       </c>
     </row>
-    <row r="639" spans="1:11">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A639" s="8">
         <v>43355</v>
       </c>
@@ -38453,7 +38452,7 @@
         <v>37.619999999999997</v>
       </c>
     </row>
-    <row r="640" spans="1:11">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A640" s="8">
         <v>43362</v>
       </c>
@@ -38489,7 +38488,7 @@
         <v>38.020000000000003</v>
       </c>
     </row>
-    <row r="641" spans="1:11">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A641" s="8">
         <v>43369</v>
       </c>
@@ -38525,7 +38524,7 @@
         <v>44.58</v>
       </c>
     </row>
-    <row r="642" spans="1:11">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A642" s="8">
         <v>43376</v>
       </c>
@@ -38561,7 +38560,7 @@
         <v>43.37</v>
       </c>
     </row>
-    <row r="643" spans="1:11">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A643" s="8">
         <v>43383</v>
       </c>
@@ -38612,7 +38611,7 @@
         <v>64.94</v>
       </c>
     </row>
-    <row r="644" spans="1:11">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A644" s="8">
         <v>43391</v>
       </c>
@@ -38648,7 +38647,7 @@
         <v>45.19</v>
       </c>
     </row>
-    <row r="645" spans="1:11">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A645" s="8">
         <v>43397</v>
       </c>
@@ -38684,7 +38683,7 @@
         <v>72.86</v>
       </c>
     </row>
-    <row r="646" spans="1:11">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A646" s="8">
         <v>43404</v>
       </c>
@@ -38720,7 +38719,7 @@
         <v>38.96</v>
       </c>
     </row>
-    <row r="647" spans="1:11">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A647" s="8">
         <v>43411</v>
       </c>
@@ -38756,7 +38755,7 @@
         <v>33.590000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:11">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A648" s="8">
         <v>43418</v>
       </c>
@@ -38792,7 +38791,7 @@
         <v>48.37</v>
       </c>
     </row>
-    <row r="649" spans="1:11">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A649" s="8">
         <v>43425</v>
       </c>
@@ -38828,7 +38827,7 @@
         <v>73.89</v>
       </c>
     </row>
-    <row r="650" spans="1:11">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A650" s="8">
         <v>43432</v>
       </c>
@@ -38864,7 +38863,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="651" spans="1:11">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A651" s="8">
         <v>43439</v>
       </c>
@@ -38900,7 +38899,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="652" spans="1:11">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A652" s="8">
         <v>43446</v>
       </c>
@@ -38936,7 +38935,7 @@
         <v>50.14</v>
       </c>
     </row>
-    <row r="653" spans="1:11">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A653" s="8">
         <v>43453</v>
       </c>
@@ -38972,7 +38971,7 @@
         <v>63.86</v>
       </c>
     </row>
-    <row r="654" spans="1:11">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A654" s="8">
         <v>43460</v>
       </c>
@@ -39008,7 +39007,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="655" spans="1:11">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A655" s="8">
         <v>43467</v>
       </c>
@@ -39044,7 +39043,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="656" spans="1:11">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A656" s="8">
         <v>43474</v>
       </c>
@@ -39080,7 +39079,7 @@
         <v>60.63</v>
       </c>
     </row>
-    <row r="657" spans="1:11">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A657" s="8">
         <v>43481</v>
       </c>
@@ -39116,7 +39115,7 @@
         <v>51.01</v>
       </c>
     </row>
-    <row r="658" spans="1:11">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A658" s="8">
         <v>43488</v>
       </c>
@@ -39152,7 +39151,7 @@
         <v>45.67</v>
       </c>
     </row>
-    <row r="659" spans="1:11">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A659" s="8">
         <v>43495</v>
       </c>
@@ -39188,7 +39187,7 @@
         <v>46.03</v>
       </c>
     </row>
-    <row r="660" spans="1:11">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A660" s="8">
         <v>43502</v>
       </c>
@@ -39224,7 +39223,7 @@
         <v>42.17</v>
       </c>
     </row>
-    <row r="661" spans="1:11">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A661" s="8">
         <v>43509</v>
       </c>
@@ -39260,7 +39259,7 @@
         <v>40.51</v>
       </c>
     </row>
-    <row r="662" spans="1:11">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A662" s="8">
         <v>43516</v>
       </c>
@@ -39296,7 +39295,7 @@
         <v>46.58</v>
       </c>
     </row>
-    <row r="663" spans="1:11">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A663" s="8">
         <v>43523</v>
       </c>
@@ -39332,7 +39331,7 @@
         <v>48.78</v>
       </c>
     </row>
-    <row r="664" spans="1:11">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A664" s="8">
         <v>43530</v>
       </c>
@@ -39368,7 +39367,7 @@
         <v>51.87</v>
       </c>
     </row>
-    <row r="665" spans="1:11">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A665" s="8">
         <v>43537</v>
       </c>
@@ -39404,7 +39403,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="666" spans="1:11">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A666" s="8">
         <v>43544</v>
       </c>
@@ -39440,7 +39439,7 @@
         <v>57.44</v>
       </c>
     </row>
-    <row r="667" spans="1:11">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A667" s="8">
         <v>43551</v>
       </c>
@@ -39476,7 +39475,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="668" spans="1:11">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A668" s="8">
         <v>43558</v>
       </c>
@@ -39512,7 +39511,7 @@
         <v>37.44</v>
       </c>
     </row>
-    <row r="669" spans="1:11">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A669" s="8">
         <v>43565</v>
       </c>
@@ -39548,7 +39547,7 @@
         <v>44.35</v>
       </c>
     </row>
-    <row r="670" spans="1:11">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A670" s="8">
         <v>43572</v>
       </c>
@@ -39584,7 +39583,7 @@
         <v>29.9</v>
       </c>
     </row>
-    <row r="671" spans="1:11">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A671" s="8">
         <v>43579</v>
       </c>
@@ -39620,7 +39619,7 @@
         <v>38.32</v>
       </c>
     </row>
-    <row r="672" spans="1:11">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A672" s="8">
         <v>43586</v>
       </c>
@@ -39656,7 +39655,7 @@
         <v>43.11</v>
       </c>
     </row>
-    <row r="673" spans="1:11">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A673" s="8">
         <v>43593</v>
       </c>
@@ -39692,7 +39691,7 @@
         <v>63.69</v>
       </c>
     </row>
-    <row r="674" spans="1:11">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A674" s="8">
         <v>43600</v>
       </c>
@@ -39728,7 +39727,7 @@
         <v>54.45</v>
       </c>
     </row>
-    <row r="675" spans="1:11">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A675" s="8">
         <v>43607</v>
       </c>
@@ -39764,7 +39763,7 @@
         <v>38.76</v>
       </c>
     </row>
-    <row r="676" spans="1:11">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A676" s="8">
         <v>43614</v>
       </c>
@@ -39800,7 +39799,7 @@
         <v>76.66</v>
       </c>
     </row>
-    <row r="677" spans="1:11">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A677" s="8">
         <v>43621</v>
       </c>
@@ -39836,7 +39835,7 @@
         <v>57.55</v>
       </c>
     </row>
-    <row r="678" spans="1:11">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A678" s="8">
         <v>43628</v>
       </c>
@@ -39872,7 +39871,7 @@
         <v>36.67</v>
       </c>
     </row>
-    <row r="679" spans="1:11">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A679" s="8">
         <v>43635</v>
       </c>
@@ -39908,7 +39907,7 @@
         <v>25.39</v>
       </c>
     </row>
-    <row r="680" spans="1:11">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A680" s="8">
         <v>43642</v>
       </c>
@@ -39944,7 +39943,7 @@
         <v>56.56</v>
       </c>
     </row>
-    <row r="681" spans="1:11">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A681" s="8">
         <v>43649</v>
       </c>
@@ -39980,7 +39979,7 @@
         <v>37.46</v>
       </c>
     </row>
-    <row r="682" spans="1:11">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A682" s="8">
         <v>43656</v>
       </c>
@@ -40016,7 +40015,7 @@
         <v>35.630000000000003</v>
       </c>
     </row>
-    <row r="683" spans="1:11">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A683" s="8">
         <v>43663</v>
       </c>
@@ -40052,7 +40051,7 @@
         <v>53.98</v>
       </c>
     </row>
-    <row r="684" spans="1:11">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A684" s="8">
         <v>43670</v>
       </c>
@@ -40088,7 +40087,7 @@
         <v>37.93</v>
       </c>
     </row>
-    <row r="685" spans="1:11">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A685" s="8">
         <v>43677</v>
       </c>
@@ -40124,7 +40123,7 @@
         <v>41.31</v>
       </c>
     </row>
-    <row r="686" spans="1:11">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A686" s="8">
         <v>43684</v>
       </c>
@@ -40160,7 +40159,7 @@
         <v>61.58</v>
       </c>
     </row>
-    <row r="687" spans="1:11">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A687" s="8">
         <v>43691</v>
       </c>
@@ -40196,7 +40195,7 @@
         <v>49.29</v>
       </c>
     </row>
-    <row r="688" spans="1:11">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A688" s="8">
         <v>43698</v>
       </c>
@@ -40232,7 +40231,7 @@
         <v>60.34</v>
       </c>
     </row>
-    <row r="689" spans="1:11">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A689" s="8">
         <v>43705</v>
       </c>
@@ -40268,7 +40267,7 @@
         <v>66.010000000000005</v>
       </c>
     </row>
-    <row r="690" spans="1:11">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A690" s="8">
         <v>43712</v>
       </c>
@@ -40304,7 +40303,7 @@
         <v>53.29</v>
       </c>
     </row>
-    <row r="691" spans="1:11">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A691" s="8">
         <v>43719</v>
       </c>
@@ -40340,7 +40339,7 @@
         <v>58.2</v>
       </c>
     </row>
-    <row r="692" spans="1:11">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A692" s="8">
         <v>43726</v>
       </c>
@@ -40376,7 +40375,7 @@
         <v>62.04</v>
       </c>
     </row>
-    <row r="693" spans="1:11">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A693" s="8">
         <v>43733</v>
       </c>
@@ -40412,7 +40411,7 @@
         <v>53.22</v>
       </c>
     </row>
-    <row r="694" spans="1:11">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A694" s="8">
         <v>43740</v>
       </c>
@@ -40448,7 +40447,7 @@
         <v>78.3</v>
       </c>
     </row>
-    <row r="695" spans="1:11">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A695" s="8">
         <v>43747</v>
       </c>
@@ -40484,7 +40483,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="696" spans="1:11">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A696" s="8">
         <v>43754</v>
       </c>
@@ -40520,7 +40519,7 @@
         <v>67.400000000000006</v>
       </c>
     </row>
-    <row r="697" spans="1:11">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A697" s="8">
         <v>43761</v>
       </c>
@@ -40556,7 +40555,7 @@
         <v>38.35</v>
       </c>
     </row>
-    <row r="698" spans="1:11">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A698" s="8">
         <v>43768</v>
       </c>
@@ -40592,7 +40591,7 @@
         <v>39.58</v>
       </c>
     </row>
-    <row r="699" spans="1:11">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A699" s="8">
         <v>43775</v>
       </c>
@@ -40628,7 +40627,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="700" spans="1:11">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A700" s="8">
         <v>43782</v>
       </c>
@@ -40664,7 +40663,7 @@
         <v>49.68</v>
       </c>
     </row>
-    <row r="701" spans="1:11">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A701" s="8">
         <v>43789</v>
       </c>
@@ -40700,7 +40699,7 @@
         <v>52.05</v>
       </c>
     </row>
-    <row r="702" spans="1:11">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A702" s="8">
         <v>43796</v>
       </c>
@@ -40736,7 +40735,7 @@
         <v>41.28</v>
       </c>
     </row>
-    <row r="703" spans="1:11">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A703" s="8">
         <v>43803</v>
       </c>
@@ -40772,7 +40771,7 @@
         <v>56.13</v>
       </c>
     </row>
-    <row r="704" spans="1:11">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A704" s="8">
         <v>43810</v>
       </c>
@@ -40808,7 +40807,7 @@
         <v>50.69</v>
       </c>
     </row>
-    <row r="705" spans="1:11">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A705" s="8">
         <v>43817</v>
       </c>
@@ -40844,7 +40843,7 @@
         <v>35.82</v>
       </c>
     </row>
-    <row r="706" spans="1:11">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A706" s="8">
         <v>43824</v>
       </c>
@@ -40880,7 +40879,7 @@
         <v>29.16</v>
       </c>
     </row>
-    <row r="707" spans="1:11">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A707" s="8">
         <v>43831</v>
       </c>
@@ -40931,7 +40930,7 @@
         <v>32.42</v>
       </c>
     </row>
-    <row r="708" spans="1:11">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A708" s="8">
         <v>43838</v>
       </c>
@@ -40967,7 +40966,7 @@
         <v>40.659999999999997</v>
       </c>
     </row>
-    <row r="709" spans="1:11">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A709" s="8">
         <v>43845</v>
       </c>
@@ -41003,7 +41002,7 @@
         <v>37.35</v>
       </c>
     </row>
-    <row r="710" spans="1:11">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A710" s="8">
         <v>43852</v>
       </c>
@@ -41039,7 +41038,7 @@
         <v>21.13</v>
       </c>
     </row>
-    <row r="711" spans="1:11">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A711" s="8">
         <v>43859</v>
       </c>
@@ -41075,7 +41074,7 @@
         <v>57.93</v>
       </c>
     </row>
-    <row r="712" spans="1:11">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A712" s="8">
         <v>43866</v>
       </c>
@@ -41111,7 +41110,7 @@
         <v>57.84</v>
       </c>
     </row>
-    <row r="713" spans="1:11">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A713" s="8">
         <v>43873</v>
       </c>
@@ -41147,7 +41146,7 @@
         <v>37.590000000000003</v>
       </c>
     </row>
-    <row r="714" spans="1:11">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A714" s="8">
         <v>43880</v>
       </c>
@@ -41183,7 +41182,7 @@
         <v>35.15</v>
       </c>
     </row>
-    <row r="715" spans="1:11">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A715" s="8">
         <v>43887</v>
       </c>
@@ -41219,7 +41218,7 @@
         <v>69.72</v>
       </c>
     </row>
-    <row r="716" spans="1:11">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A716" s="8">
         <v>43894</v>
       </c>
@@ -41255,7 +41254,7 @@
         <v>72.709999999999994</v>
       </c>
     </row>
-    <row r="717" spans="1:11">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A717" s="8">
         <v>43901</v>
       </c>
@@ -41291,7 +41290,7 @@
         <v>58.88</v>
       </c>
     </row>
-    <row r="718" spans="1:11">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A718" s="8">
         <v>43908</v>
       </c>
@@ -41327,7 +41326,7 @@
         <v>42.67</v>
       </c>
     </row>
-    <row r="719" spans="1:11">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A719" s="8">
         <v>43915</v>
       </c>
@@ -41363,7 +41362,7 @@
         <v>34.049999999999997</v>
       </c>
     </row>
-    <row r="720" spans="1:11">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A720" s="8">
         <v>43922</v>
       </c>
@@ -41399,7 +41398,7 @@
         <v>40.64</v>
       </c>
     </row>
-    <row r="721" spans="1:11">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A721" s="8">
         <v>43929</v>
       </c>
@@ -41435,7 +41434,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="722" spans="1:11">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A722" s="8">
         <v>43936</v>
       </c>
@@ -41471,7 +41470,7 @@
         <v>56.57</v>
       </c>
     </row>
-    <row r="723" spans="1:11">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A723" s="8">
         <v>43943</v>
       </c>
@@ -41507,7 +41506,7 @@
         <v>57.95</v>
       </c>
     </row>
-    <row r="724" spans="1:11">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A724" s="8">
         <v>43950</v>
       </c>
@@ -41543,7 +41542,7 @@
         <v>41.89</v>
       </c>
     </row>
-    <row r="725" spans="1:11">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A725" s="8">
         <v>43957</v>
       </c>
@@ -41579,7 +41578,7 @@
         <v>41.07</v>
       </c>
     </row>
-    <row r="726" spans="1:11">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A726" s="8">
         <v>43964</v>
       </c>
@@ -41615,7 +41614,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="727" spans="1:11">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A727" s="8">
         <v>43971</v>
       </c>
@@ -41651,7 +41650,7 @@
         <v>51.08</v>
       </c>
     </row>
-    <row r="728" spans="1:11">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A728" s="8">
         <v>43978</v>
       </c>
@@ -41687,7 +41686,7 @@
         <v>43.17</v>
       </c>
     </row>
-    <row r="729" spans="1:11">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A729" s="8">
         <v>43985</v>
       </c>
@@ -41723,7 +41722,7 @@
         <v>36.69</v>
       </c>
     </row>
-    <row r="730" spans="1:11">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A730" s="8">
         <v>43992</v>
       </c>
@@ -41759,7 +41758,7 @@
         <v>54.73</v>
       </c>
     </row>
-    <row r="731" spans="1:11">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A731" s="8">
         <v>43999</v>
       </c>
@@ -41795,7 +41794,7 @@
         <v>37.33</v>
       </c>
     </row>
-    <row r="732" spans="1:11">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A732" s="8">
         <v>44006</v>
       </c>
@@ -41831,7 +41830,7 @@
         <v>43.91</v>
       </c>
     </row>
-    <row r="733" spans="1:11">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A733" s="8">
         <v>44013</v>
       </c>
@@ -41867,7 +41866,7 @@
         <v>52.64</v>
       </c>
     </row>
-    <row r="734" spans="1:11">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A734" s="8">
         <v>44020</v>
       </c>
@@ -41903,7 +41902,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="735" spans="1:11">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A735" s="8">
         <v>44027</v>
       </c>
@@ -41939,7 +41938,7 @@
         <v>49.38</v>
       </c>
     </row>
-    <row r="736" spans="1:11">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A736" s="8">
         <v>44034</v>
       </c>
@@ -41975,7 +41974,7 @@
         <v>33.909999999999997</v>
       </c>
     </row>
-    <row r="737" spans="1:11">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A737" s="8">
         <v>44041</v>
       </c>
@@ -42011,7 +42010,7 @@
         <v>36.130000000000003</v>
       </c>
     </row>
-    <row r="738" spans="1:11">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A738" s="8">
         <v>44048</v>
       </c>
@@ -42047,7 +42046,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="739" spans="1:11">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A739" s="8">
         <v>44055</v>
       </c>
@@ -42083,7 +42082,7 @@
         <v>29.1</v>
       </c>
     </row>
-    <row r="740" spans="1:11">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A740" s="8">
         <v>44062</v>
       </c>
@@ -42119,7 +42118,7 @@
         <v>42.31</v>
       </c>
     </row>
-    <row r="741" spans="1:11">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A741" s="8">
         <v>44069</v>
       </c>
@@ -42155,7 +42154,7 @@
         <v>38.44</v>
       </c>
     </row>
-    <row r="742" spans="1:11">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A742" s="8">
         <v>44076</v>
       </c>
@@ -42191,7 +42190,7 @@
         <v>35.47</v>
       </c>
     </row>
-    <row r="743" spans="1:11">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A743" s="8">
         <v>44083</v>
       </c>
@@ -42227,7 +42226,7 @@
         <v>60.47</v>
       </c>
     </row>
-    <row r="744" spans="1:11">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A744" s="8">
         <v>44090</v>
       </c>
@@ -42263,7 +42262,7 @@
         <v>71.73</v>
       </c>
     </row>
-    <row r="745" spans="1:11">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A745" s="8">
         <v>44097</v>
       </c>
@@ -42299,7 +42298,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="746" spans="1:11">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A746" s="8">
         <v>44104</v>
       </c>
@@ -42335,7 +42334,7 @@
         <v>62.62</v>
       </c>
     </row>
-    <row r="747" spans="1:11">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A747" s="8">
         <v>44111</v>
       </c>
@@ -42371,7 +42370,7 @@
         <v>63.41</v>
       </c>
     </row>
-    <row r="748" spans="1:11">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A748" s="8">
         <v>44118</v>
       </c>
@@ -42407,7 +42406,7 @@
         <v>41.56</v>
       </c>
     </row>
-    <row r="749" spans="1:11">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A749" s="8">
         <v>44125</v>
       </c>
@@ -42443,7 +42442,7 @@
         <v>42.48</v>
       </c>
     </row>
-    <row r="750" spans="1:11">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A750" s="8">
         <v>44132</v>
       </c>
@@ -42479,7 +42478,7 @@
         <v>49.64</v>
       </c>
     </row>
-    <row r="751" spans="1:11">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A751" s="8">
         <v>44139</v>
       </c>
@@ -42515,7 +42514,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="752" spans="1:11">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A752" s="8">
         <v>44146</v>
       </c>
@@ -42551,7 +42550,7 @@
         <v>50.26</v>
       </c>
     </row>
-    <row r="753" spans="1:11">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A753" s="8">
         <v>44153</v>
       </c>
@@ -42587,7 +42586,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="754" spans="1:11">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A754" s="8">
         <v>44160</v>
       </c>
@@ -42623,7 +42622,7 @@
         <v>44.54</v>
       </c>
     </row>
-    <row r="755" spans="1:11">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A755" s="8">
         <v>44167</v>
       </c>
@@ -42659,7 +42658,7 @@
         <v>38.9</v>
       </c>
     </row>
-    <row r="756" spans="1:11">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A756" s="8">
         <v>44174</v>
       </c>
@@ -42695,7 +42694,7 @@
         <v>40.98</v>
       </c>
     </row>
-    <row r="757" spans="1:11">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A757" s="8">
         <v>44181</v>
       </c>
@@ -42731,7 +42730,7 @@
         <v>42.33</v>
       </c>
     </row>
-    <row r="758" spans="1:11">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A758" s="8">
         <v>44188</v>
       </c>
@@ -42767,7 +42766,7 @@
         <v>44.19</v>
       </c>
     </row>
-    <row r="759" spans="1:11">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A759" s="8">
         <v>44195</v>
       </c>
@@ -42803,7 +42802,7 @@
         <v>47.07</v>
       </c>
     </row>
-    <row r="760" spans="1:11">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A760" s="8">
         <v>44202</v>
       </c>
@@ -42839,7 +42838,7 @@
         <v>39.11</v>
       </c>
     </row>
-    <row r="761" spans="1:11">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A761" s="8">
         <v>44209</v>
       </c>
@@ -42875,7 +42874,7 @@
         <v>39.85</v>
       </c>
     </row>
-    <row r="762" spans="1:11">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A762" s="8">
         <v>44216</v>
       </c>
@@ -42911,7 +42910,7 @@
         <v>36.46</v>
       </c>
     </row>
-    <row r="763" spans="1:11">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A763" s="8">
         <v>44223</v>
       </c>
@@ -42947,7 +42946,7 @@
         <v>53.82</v>
       </c>
     </row>
-    <row r="764" spans="1:11">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A764" s="8">
         <v>44230</v>
       </c>
@@ -42983,7 +42982,7 @@
         <v>50.88</v>
       </c>
     </row>
-    <row r="765" spans="1:11">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A765" s="8">
         <v>44237</v>
       </c>
@@ -43019,7 +43018,7 @@
         <v>29.44</v>
       </c>
     </row>
-    <row r="766" spans="1:11">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A766" s="8">
         <v>44244</v>
       </c>
@@ -43055,7 +43054,7 @@
         <v>44.76</v>
       </c>
     </row>
-    <row r="767" spans="1:11">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A767" s="8">
         <v>44251</v>
       </c>
@@ -43091,7 +43090,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="768" spans="1:11">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A768" s="8">
         <v>44258</v>
       </c>
@@ -43127,7 +43126,7 @@
         <v>62.65</v>
       </c>
     </row>
-    <row r="769" spans="1:11">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A769" s="8">
         <v>44265</v>
       </c>
@@ -43163,7 +43162,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="770" spans="1:11">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A770" s="8">
         <v>44272</v>
       </c>
@@ -43199,7 +43198,7 @@
         <v>33.979999999999997</v>
       </c>
     </row>
-    <row r="771" spans="1:11">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A771" s="8">
         <v>44279</v>
       </c>
@@ -43250,7 +43249,7 @@
         <v>42.24</v>
       </c>
     </row>
-    <row r="772" spans="1:11">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A772" s="8">
         <v>44286</v>
       </c>
@@ -43286,7 +43285,7 @@
         <v>47.49</v>
       </c>
     </row>
-    <row r="773" spans="1:11">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A773" s="8">
         <v>44293</v>
       </c>
@@ -43322,7 +43321,7 @@
         <v>35.159999999999997</v>
       </c>
     </row>
-    <row r="774" spans="1:11">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A774" s="8">
         <v>44300</v>
       </c>
@@ -43358,7 +43357,7 @@
         <v>39.590000000000003</v>
       </c>
     </row>
-    <row r="775" spans="1:11">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A775" s="8">
         <v>44307</v>
       </c>
@@ -43394,7 +43393,7 @@
         <v>39.06</v>
       </c>
     </row>
-    <row r="776" spans="1:11">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A776" s="8">
         <v>44314</v>
       </c>
@@ -43430,7 +43429,7 @@
         <v>43.65</v>
       </c>
     </row>
-    <row r="777" spans="1:11">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A777" s="8">
         <v>44321</v>
       </c>
@@ -43466,7 +43465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:11">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A778" s="8">
         <v>44328</v>
       </c>
@@ -43502,7 +43501,7 @@
         <v>44.2</v>
       </c>
     </row>
-    <row r="779" spans="1:11">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A779" s="8">
         <v>44335</v>
       </c>
@@ -43538,7 +43537,7 @@
         <v>35.25</v>
       </c>
     </row>
-    <row r="780" spans="1:11">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A780" s="8">
         <v>44342</v>
       </c>
@@ -43574,7 +43573,7 @@
         <v>35.119999999999997</v>
       </c>
     </row>
-    <row r="781" spans="1:11">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A781" s="8">
         <v>44349</v>
       </c>
@@ -43610,7 +43609,7 @@
         <v>35.83</v>
       </c>
     </row>
-    <row r="782" spans="1:11">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A782" s="8">
         <v>44356</v>
       </c>
@@ -43646,7 +43645,7 @@
         <v>38.92</v>
       </c>
     </row>
-    <row r="783" spans="1:11">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A783" s="8">
         <v>44363</v>
       </c>
@@ -43682,7 +43681,7 @@
         <v>34.159999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:11">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A784" s="8">
         <v>44370</v>
       </c>
@@ -43718,7 +43717,7 @@
         <v>42.79</v>
       </c>
     </row>
-    <row r="785" spans="1:11">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A785" s="8">
         <v>44377</v>
       </c>
@@ -43754,7 +43753,7 @@
         <v>38.18</v>
       </c>
     </row>
-    <row r="786" spans="1:11">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A786" s="8">
         <v>44384</v>
       </c>
@@ -43790,7 +43789,7 @@
         <v>42.66</v>
       </c>
     </row>
-    <row r="787" spans="1:11">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A787" s="8">
         <v>44391</v>
       </c>
@@ -43826,7 +43825,7 @@
         <v>37.85</v>
       </c>
     </row>
-    <row r="788" spans="1:11">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A788" s="8">
         <v>44398</v>
       </c>
@@ -43862,7 +43861,7 @@
         <v>48.75</v>
       </c>
     </row>
-    <row r="789" spans="1:11">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A789" s="8">
         <v>44405</v>
       </c>
@@ -43898,7 +43897,7 @@
         <v>43.07</v>
       </c>
     </row>
-    <row r="790" spans="1:11">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A790" s="8">
         <v>44412</v>
       </c>
@@ -43934,7 +43933,7 @@
         <v>41.16</v>
       </c>
     </row>
-    <row r="791" spans="1:11">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A791" s="8">
         <v>44419</v>
       </c>
@@ -43970,7 +43969,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="792" spans="1:11">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A792" s="8">
         <v>44426</v>
       </c>
@@ -44006,7 +44005,7 @@
         <v>58.22</v>
       </c>
     </row>
-    <row r="793" spans="1:11">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A793" s="8">
         <v>44433</v>
       </c>
@@ -44042,7 +44041,7 @@
         <v>37.950000000000003</v>
       </c>
     </row>
-    <row r="794" spans="1:11">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A794" s="8">
         <v>44440</v>
       </c>
@@ -44078,7 +44077,7 @@
         <v>39.24</v>
       </c>
     </row>
-    <row r="795" spans="1:11">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A795" s="8">
         <v>44447</v>
       </c>
@@ -44114,7 +44113,7 @@
         <v>43.85</v>
       </c>
     </row>
-    <row r="796" spans="1:11">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A796" s="8">
         <v>44454</v>
       </c>
@@ -44150,7 +44149,7 @@
         <v>47.86</v>
       </c>
     </row>
-    <row r="797" spans="1:11">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A797" s="8">
         <v>44461</v>
       </c>
@@ -44186,7 +44185,7 @@
         <v>47.37</v>
       </c>
     </row>
-    <row r="798" spans="1:11">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A798" s="8">
         <v>44468</v>
       </c>
@@ -44222,7 +44221,7 @@
         <v>72.13</v>
       </c>
     </row>
-    <row r="799" spans="1:11">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A799" s="8">
         <v>44475</v>
       </c>
@@ -44258,7 +44257,7 @@
         <v>51.09</v>
       </c>
     </row>
-    <row r="800" spans="1:11">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A800" s="8">
         <v>44482</v>
       </c>
@@ -44294,7 +44293,7 @@
         <v>52.37</v>
       </c>
     </row>
-    <row r="801" spans="1:11">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A801" s="8">
         <v>44489</v>
       </c>
@@ -44330,7 +44329,7 @@
         <v>33.46</v>
       </c>
     </row>
-    <row r="802" spans="1:11">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A802" s="8">
         <v>44496</v>
       </c>
@@ -44366,7 +44365,7 @@
         <v>33.03</v>
       </c>
     </row>
-    <row r="803" spans="1:11">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A803" s="8">
         <v>44503</v>
       </c>
@@ -44402,7 +44401,7 @@
         <v>37.31</v>
       </c>
     </row>
-    <row r="804" spans="1:11">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A804" s="8">
         <v>44510</v>
       </c>
@@ -44438,7 +44437,7 @@
         <v>43.41</v>
       </c>
     </row>
-    <row r="805" spans="1:11">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A805" s="8">
         <v>44517</v>
       </c>
@@ -44474,7 +44473,7 @@
         <v>47.38</v>
       </c>
     </row>
-    <row r="806" spans="1:11">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A806" s="8">
         <v>44524</v>
       </c>
@@ -44510,7 +44509,7 @@
         <v>46.63</v>
       </c>
     </row>
-    <row r="807" spans="1:11">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A807" s="8">
         <v>44531</v>
       </c>
@@ -44546,7 +44545,7 @@
         <v>59.91</v>
       </c>
     </row>
-    <row r="808" spans="1:11">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A808" s="8">
         <v>44538</v>
       </c>
@@ -44582,7 +44581,7 @@
         <v>78.33</v>
       </c>
     </row>
-    <row r="809" spans="1:11">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A809" s="8">
         <v>44545</v>
       </c>
@@ -44618,7 +44617,7 @@
         <v>61.89</v>
       </c>
     </row>
-    <row r="810" spans="1:11">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A810" s="8">
         <v>44552</v>
       </c>
@@ -44654,7 +44653,7 @@
         <v>51.45</v>
       </c>
     </row>
-    <row r="811" spans="1:11">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A811" s="8">
         <v>44559</v>
       </c>
@@ -44690,7 +44689,7 @@
         <v>38.94</v>
       </c>
     </row>
-    <row r="812" spans="1:11">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A812" s="8">
         <v>44566</v>
       </c>
@@ -44726,7 +44725,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="813" spans="1:11">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A813" s="8">
         <v>44573</v>
       </c>
@@ -44762,7 +44761,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="814" spans="1:11">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A814" s="8">
         <v>44580</v>
       </c>
@@ -44798,7 +44797,7 @@
         <v>76.22</v>
       </c>
     </row>
-    <row r="815" spans="1:11">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A815" s="8">
         <v>44587</v>
       </c>
@@ -44834,7 +44833,7 @@
         <v>66.22</v>
       </c>
     </row>
-    <row r="816" spans="1:11">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A816" s="8">
         <v>44594</v>
       </c>
@@ -44870,7 +44869,7 @@
         <v>49.17</v>
       </c>
     </row>
-    <row r="817" spans="1:11">
+    <row r="817" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A817" s="8">
         <v>44601</v>
       </c>
@@ -44906,7 +44905,7 @@
         <v>40.53</v>
       </c>
     </row>
-    <row r="818" spans="1:11">
+    <row r="818" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A818" s="8">
         <v>44608</v>
       </c>
@@ -44942,7 +44941,7 @@
         <v>72.38</v>
       </c>
     </row>
-    <row r="819" spans="1:11">
+    <row r="819" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A819" s="8">
         <v>44615</v>
       </c>
@@ -44978,7 +44977,7 @@
         <v>71.64</v>
       </c>
     </row>
-    <row r="820" spans="1:11">
+    <row r="820" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A820" s="8">
         <v>44622</v>
       </c>
@@ -45014,7 +45013,7 @@
         <v>72.260000000000005</v>
       </c>
     </row>
-    <row r="821" spans="1:11">
+    <row r="821" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A821" s="8">
         <v>44629</v>
       </c>
@@ -45050,7 +45049,7 @@
         <v>70.959999999999994</v>
       </c>
     </row>
-    <row r="822" spans="1:11">
+    <row r="822" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A822" s="8">
         <v>44636</v>
       </c>
@@ -45086,7 +45085,7 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="823" spans="1:11">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A823" s="8">
         <v>44643</v>
       </c>
@@ -45122,7 +45121,7 @@
         <v>65.23</v>
       </c>
     </row>
-    <row r="824" spans="1:11">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A824" s="8">
         <v>44650</v>
       </c>
@@ -45158,7 +45157,7 @@
         <v>21.67</v>
       </c>
     </row>
-    <row r="825" spans="1:11">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A825" s="8">
         <v>44657</v>
       </c>
@@ -45194,7 +45193,7 @@
         <v>40.35</v>
       </c>
     </row>
-    <row r="826" spans="1:11">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A826" s="8">
         <v>44664</v>
       </c>
@@ -45230,7 +45229,7 @@
         <v>31.86</v>
       </c>
     </row>
-    <row r="827" spans="1:11">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A827" s="8">
         <v>44671</v>
       </c>
@@ -45266,7 +45265,7 @@
         <v>28.88</v>
       </c>
     </row>
-    <row r="828" spans="1:11">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A828" s="8">
         <v>44678</v>
       </c>
@@ -45302,7 +45301,7 @@
         <v>69.22</v>
       </c>
     </row>
-    <row r="829" spans="1:11">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A829" s="8">
         <v>44685</v>
       </c>
@@ -45338,7 +45337,7 @@
         <v>45.33</v>
       </c>
     </row>
-    <row r="830" spans="1:11">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A830" s="8">
         <v>44692</v>
       </c>
@@ -45374,7 +45373,7 @@
         <v>58.81</v>
       </c>
     </row>
-    <row r="831" spans="1:11">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A831" s="8">
         <v>44699</v>
       </c>
@@ -45410,7 +45409,7 @@
         <v>44.74</v>
       </c>
     </row>
-    <row r="832" spans="1:11">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A832" s="8">
         <v>44706</v>
       </c>
@@ -45446,7 +45445,7 @@
         <v>35.08</v>
       </c>
     </row>
-    <row r="833" spans="1:11">
+    <row r="833" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A833" s="8">
         <v>44713</v>
       </c>
@@ -45482,7 +45481,7 @@
         <v>74.08</v>
       </c>
     </row>
-    <row r="834" spans="1:11">
+    <row r="834" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A834" s="8">
         <v>44720</v>
       </c>
@@ -45518,7 +45517,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="835" spans="1:11">
+    <row r="835" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A835" s="8">
         <v>44727</v>
       </c>
@@ -45569,7 +45568,7 @@
         <v>50.59</v>
       </c>
     </row>
-    <row r="836" spans="1:11">
+    <row r="836" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A836" s="8">
         <v>44734</v>
       </c>
@@ -45605,7 +45604,7 @@
         <v>59.84</v>
       </c>
     </row>
-    <row r="837" spans="1:11">
+    <row r="837" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A837" s="8">
         <v>44741</v>
       </c>
@@ -45641,7 +45640,7 @@
         <v>51.78</v>
       </c>
     </row>
-    <row r="838" spans="1:11">
+    <row r="838" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A838" s="8">
         <v>44748</v>
       </c>
@@ -45677,7 +45676,7 @@
         <v>62.05</v>
       </c>
     </row>
-    <row r="839" spans="1:11">
+    <row r="839" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A839" s="8">
         <v>44755</v>
       </c>
@@ -45713,7 +45712,7 @@
         <v>58.93</v>
       </c>
     </row>
-    <row r="840" spans="1:11">
+    <row r="840" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A840" s="8">
         <v>44762</v>
       </c>
@@ -45749,7 +45748,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="841" spans="1:11">
+    <row r="841" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A841" s="8">
         <v>44769</v>
       </c>
@@ -45785,7 +45784,7 @@
         <v>50.16</v>
       </c>
     </row>
-    <row r="842" spans="1:11">
+    <row r="842" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A842" s="8">
         <v>44776</v>
       </c>
@@ -45821,7 +45820,7 @@
         <v>53.21</v>
       </c>
     </row>
-    <row r="843" spans="1:11">
+    <row r="843" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A843" s="8">
         <v>44783</v>
       </c>
@@ -45857,7 +45856,7 @@
         <v>54.24</v>
       </c>
     </row>
-    <row r="844" spans="1:11">
+    <row r="844" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A844" s="8">
         <v>44790</v>
       </c>
@@ -45893,7 +45892,7 @@
         <v>54.27</v>
       </c>
     </row>
-    <row r="845" spans="1:11">
+    <row r="845" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A845" s="8">
         <v>44797</v>
       </c>
@@ -45929,7 +45928,7 @@
         <v>59.7</v>
       </c>
     </row>
-    <row r="846" spans="1:11">
+    <row r="846" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A846" s="8">
         <v>44804</v>
       </c>
@@ -45965,7 +45964,7 @@
         <v>60.43</v>
       </c>
     </row>
-    <row r="847" spans="1:11">
+    <row r="847" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A847" s="8">
         <v>44811</v>
       </c>
@@ -46001,7 +46000,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="848" spans="1:11">
+    <row r="848" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A848" s="8">
         <v>44818</v>
       </c>
@@ -46037,7 +46036,7 @@
         <v>70.459999999999994</v>
       </c>
     </row>
-    <row r="849" spans="1:11">
+    <row r="849" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A849" s="8">
         <v>44825</v>
       </c>
@@ -46073,7 +46072,7 @@
         <v>60.97</v>
       </c>
     </row>
-    <row r="850" spans="1:11">
+    <row r="850" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A850" s="8">
         <v>44832</v>
       </c>
@@ -46109,7 +46108,7 @@
         <v>66.88</v>
       </c>
     </row>
-    <row r="851" spans="1:11">
+    <row r="851" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A851" s="8">
         <v>44839</v>
       </c>
@@ -46145,7 +46144,7 @@
         <v>58.96</v>
       </c>
     </row>
-    <row r="852" spans="1:11">
+    <row r="852" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A852" s="8">
         <v>44846</v>
       </c>
@@ -46181,7 +46180,7 @@
         <v>59.65</v>
       </c>
     </row>
-    <row r="853" spans="1:11">
+    <row r="853" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A853" s="8">
         <v>44853</v>
       </c>
@@ -46217,7 +46216,7 @@
         <v>55.43</v>
       </c>
     </row>
-    <row r="854" spans="1:11">
+    <row r="854" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A854" s="8">
         <v>44860</v>
       </c>
@@ -46253,7 +46252,7 @@
         <v>54.08</v>
       </c>
     </row>
-    <row r="855" spans="1:11">
+    <row r="855" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A855" s="8">
         <v>44867</v>
       </c>
@@ -46289,7 +46288,7 @@
         <v>59.48</v>
       </c>
     </row>
-    <row r="856" spans="1:11">
+    <row r="856" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A856" s="8">
         <v>44874</v>
       </c>
@@ -46325,7 +46324,7 @@
         <v>54.63</v>
       </c>
     </row>
-    <row r="857" spans="1:11">
+    <row r="857" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A857" s="8">
         <v>44881</v>
       </c>
@@ -46361,7 +46360,7 @@
         <v>60.66</v>
       </c>
     </row>
-    <row r="858" spans="1:11">
+    <row r="858" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A858" s="8">
         <v>44888</v>
       </c>
@@ -46397,7 +46396,7 @@
         <v>56.55</v>
       </c>
     </row>
-    <row r="859" spans="1:11">
+    <row r="859" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A859" s="8">
         <v>44895</v>
       </c>
@@ -46433,7 +46432,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="860" spans="1:11">
+    <row r="860" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A860" s="8">
         <v>44902</v>
       </c>
@@ -46469,7 +46468,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="861" spans="1:11">
+    <row r="861" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A861" s="8">
         <v>44909</v>
       </c>
@@ -46505,7 +46504,7 @@
         <v>48.94</v>
       </c>
     </row>
-    <row r="862" spans="1:11">
+    <row r="862" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A862" s="8">
         <v>44916</v>
       </c>
@@ -46541,7 +46540,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="863" spans="1:11">
+    <row r="863" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A863" s="8">
         <v>44923</v>
       </c>
@@ -46577,7 +46576,7 @@
         <v>46.68</v>
       </c>
     </row>
-    <row r="864" spans="1:11">
+    <row r="864" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A864" s="8">
         <v>44930</v>
       </c>
@@ -46613,7 +46612,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="865" spans="1:11">
+    <row r="865" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A865" s="8">
         <v>44937</v>
       </c>
@@ -46649,7 +46648,7 @@
         <v>39.74</v>
       </c>
     </row>
-    <row r="866" spans="1:11">
+    <row r="866" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A866" s="8">
         <v>44944</v>
       </c>
@@ -46685,7 +46684,7 @@
         <v>58.85</v>
       </c>
     </row>
-    <row r="867" spans="1:11">
+    <row r="867" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A867" s="8">
         <v>44951</v>
       </c>
@@ -46721,7 +46720,7 @@
         <v>45.01</v>
       </c>
     </row>
-    <row r="868" spans="1:11">
+    <row r="868" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A868" s="8">
         <v>44958</v>
       </c>
@@ -46757,7 +46756,7 @@
         <v>44.29</v>
       </c>
     </row>
-    <row r="869" spans="1:11">
+    <row r="869" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A869" s="8">
         <v>44965</v>
       </c>
@@ -46793,7 +46792,7 @@
         <v>44.25</v>
       </c>
     </row>
-    <row r="870" spans="1:11">
+    <row r="870" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A870" s="8">
         <v>44972</v>
       </c>
@@ -46829,7 +46828,7 @@
         <v>47.28</v>
       </c>
     </row>
-    <row r="871" spans="1:11">
+    <row r="871" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A871" s="8">
         <v>44979</v>
       </c>
@@ -46865,7 +46864,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="872" spans="1:11">
+    <row r="872" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A872" s="8">
         <v>44986</v>
       </c>
@@ -46901,7 +46900,7 @@
         <v>69.319999999999993</v>
       </c>
     </row>
-    <row r="873" spans="1:11">
+    <row r="873" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A873" s="8">
         <v>44993</v>
       </c>
@@ -46937,7 +46936,7 @@
         <v>63.44</v>
       </c>
     </row>
-    <row r="874" spans="1:11">
+    <row r="874" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A874" s="8">
         <v>45000</v>
       </c>
@@ -46973,7 +46972,7 @@
         <v>66.69</v>
       </c>
     </row>
-    <row r="875" spans="1:11">
+    <row r="875" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A875" s="8">
         <v>45007</v>
       </c>
@@ -47009,7 +47008,7 @@
         <v>57.12</v>
       </c>
     </row>
-    <row r="876" spans="1:11">
+    <row r="876" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A876" s="8">
         <v>45014</v>
       </c>
@@ -47045,7 +47044,7 @@
         <v>49.69</v>
       </c>
     </row>
-    <row r="877" spans="1:11">
+    <row r="877" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A877" s="8">
         <v>45021</v>
       </c>
@@ -47081,7 +47080,7 @@
         <v>45.38</v>
       </c>
     </row>
-    <row r="878" spans="1:11">
+    <row r="878" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A878" s="8">
         <v>45028</v>
       </c>
@@ -47117,7 +47116,7 @@
         <v>64.83</v>
       </c>
     </row>
-    <row r="879" spans="1:11">
+    <row r="879" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A879" s="8">
         <v>45035</v>
       </c>
@@ -47153,7 +47152,7 @@
         <v>39.61</v>
       </c>
     </row>
-    <row r="880" spans="1:11">
+    <row r="880" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A880" s="8">
         <v>45042</v>
       </c>
@@ -47189,7 +47188,7 @@
         <v>56.93</v>
       </c>
     </row>
-    <row r="881" spans="1:11">
+    <row r="881" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A881" s="8">
         <v>45049</v>
       </c>
@@ -47225,7 +47224,7 @@
         <v>43.05</v>
       </c>
     </row>
-    <row r="882" spans="1:11">
+    <row r="882" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A882" s="8">
         <v>45056</v>
       </c>
@@ -47261,7 +47260,7 @@
         <v>50.84</v>
       </c>
     </row>
-    <row r="883" spans="1:11">
+    <row r="883" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A883" s="8">
         <v>45063</v>
       </c>
@@ -47297,7 +47296,7 @@
         <v>48.49</v>
       </c>
     </row>
-    <row r="884" spans="1:11">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A884" s="8">
         <v>45070</v>
       </c>
@@ -47333,7 +47332,7 @@
         <v>52.21</v>
       </c>
     </row>
-    <row r="885" spans="1:11">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A885" s="8">
         <v>45077</v>
       </c>
@@ -47369,7 +47368,7 @@
         <v>59.12</v>
       </c>
     </row>
-    <row r="886" spans="1:11">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A886" s="8">
         <v>45084</v>
       </c>
@@ -47405,7 +47404,7 @@
         <v>40.46</v>
       </c>
     </row>
-    <row r="887" spans="1:11">
+    <row r="887" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A887" s="8">
         <v>45091</v>
       </c>
@@ -47441,7 +47440,7 @@
         <v>56.21</v>
       </c>
     </row>
-    <row r="888" spans="1:11">
+    <row r="888" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A888" s="8">
         <v>45098</v>
       </c>
@@ -47477,7 +47476,7 @@
         <v>45.51</v>
       </c>
     </row>
-    <row r="889" spans="1:11">
+    <row r="889" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A889" s="8">
         <v>45105</v>
       </c>
@@ -47513,7 +47512,7 @@
         <v>54.14</v>
       </c>
     </row>
-    <row r="890" spans="1:11">
+    <row r="890" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A890" s="8">
         <v>45112</v>
       </c>
@@ -47549,7 +47548,7 @@
         <v>50.49</v>
       </c>
     </row>
-    <row r="891" spans="1:11">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A891" s="8">
         <v>45119</v>
       </c>
@@ -47585,7 +47584,7 @@
         <v>44.26</v>
       </c>
     </row>
-    <row r="892" spans="1:11">
+    <row r="892" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A892" s="8">
         <v>45126</v>
       </c>
@@ -47621,7 +47620,7 @@
         <v>44.69</v>
       </c>
     </row>
-    <row r="893" spans="1:11">
+    <row r="893" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A893" s="8">
         <v>45133</v>
       </c>
@@ -47657,7 +47656,7 @@
         <v>36.340000000000003</v>
       </c>
     </row>
-    <row r="894" spans="1:11">
+    <row r="894" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A894" s="8">
         <v>45140</v>
       </c>
@@ -47693,7 +47692,7 @@
         <v>72.739999999999995</v>
       </c>
     </row>
-    <row r="895" spans="1:11">
+    <row r="895" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A895" s="8">
         <v>45147</v>
       </c>
@@ -47729,7 +47728,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="896" spans="1:11">
+    <row r="896" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A896" s="8">
         <v>45154</v>
       </c>
@@ -47765,7 +47764,7 @@
         <v>67.22</v>
       </c>
     </row>
-    <row r="897" spans="1:11">
+    <row r="897" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A897" s="8">
         <v>45161</v>
       </c>
@@ -47801,7 +47800,7 @@
         <v>79.38</v>
       </c>
     </row>
-    <row r="898" spans="1:11">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A898" s="8">
         <v>45168</v>
       </c>
@@ -47837,7 +47836,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="899" spans="1:11">
+    <row r="899" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A899" s="8">
         <v>45175</v>
       </c>
@@ -47888,7 +47887,7 @@
         <v>70.89</v>
       </c>
     </row>
-    <row r="900" spans="1:11">
+    <row r="900" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A900" s="8">
         <v>45182</v>
       </c>
@@ -47924,7 +47923,7 @@
         <v>64.010000000000005</v>
       </c>
     </row>
-    <row r="901" spans="1:11">
+    <row r="901" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A901" s="8">
         <v>45189</v>
       </c>
@@ -47960,7 +47959,7 @@
         <v>53.81</v>
       </c>
     </row>
-    <row r="902" spans="1:11">
+    <row r="902" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A902" s="8">
         <v>45196</v>
       </c>
@@ -47996,7 +47995,7 @@
         <v>60.53</v>
       </c>
     </row>
-    <row r="903" spans="1:11">
+    <row r="903" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A903" s="8">
         <v>45203</v>
       </c>
@@ -48032,7 +48031,7 @@
         <v>74.3</v>
       </c>
     </row>
-    <row r="904" spans="1:11">
+    <row r="904" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A904" s="8">
         <v>45210</v>
       </c>
@@ -48068,7 +48067,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="905" spans="1:11">
+    <row r="905" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A905" s="8">
         <v>45217</v>
       </c>
@@ -48104,7 +48103,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="906" spans="1:11">
+    <row r="906" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A906" s="8">
         <v>45224</v>
       </c>
@@ -48140,7 +48139,7 @@
         <v>73.540000000000006</v>
       </c>
     </row>
-    <row r="907" spans="1:11">
+    <row r="907" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A907" s="8">
         <v>45231</v>
       </c>
@@ -48176,7 +48175,7 @@
         <v>71.180000000000007</v>
       </c>
     </row>
-    <row r="908" spans="1:11">
+    <row r="908" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A908" s="8">
         <v>45238</v>
       </c>
@@ -48212,7 +48211,7 @@
         <v>52.63</v>
       </c>
     </row>
-    <row r="909" spans="1:11">
+    <row r="909" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A909" s="8">
         <v>45245</v>
       </c>
@@ -48248,7 +48247,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="910" spans="1:11">
+    <row r="910" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A910" s="8">
         <v>45252</v>
       </c>
@@ -48284,7 +48283,7 @@
         <v>68.56</v>
       </c>
     </row>
-    <row r="911" spans="1:11">
+    <row r="911" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A911" s="8">
         <v>45259</v>
       </c>
@@ -48298,29 +48297,29 @@
         <f t="shared" si="14"/>
         <v>UTC-5</v>
       </c>
-      <c r="E911" s="15">
+      <c r="E911" s="14">
         <v>81.38</v>
       </c>
-      <c r="F911" s="16">
+      <c r="F911" s="15">
         <v>-200</v>
       </c>
-      <c r="G911" s="15">
+      <c r="G911" s="14">
         <v>80</v>
       </c>
-      <c r="H911" s="17">
+      <c r="H911" s="16">
         <v>95</v>
       </c>
-      <c r="I911" s="17">
-        <v>100</v>
-      </c>
-      <c r="J911" s="17">
-        <v>200</v>
-      </c>
-      <c r="K911" s="15">
+      <c r="I911" s="16">
+        <v>100</v>
+      </c>
+      <c r="J911" s="16">
+        <v>200</v>
+      </c>
+      <c r="K911" s="14">
         <v>64.95</v>
       </c>
     </row>
-    <row r="912" spans="1:11">
+    <row r="912" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A912" s="8">
         <v>45266</v>
       </c>
@@ -48356,7 +48355,7 @@
         <v>71.14</v>
       </c>
     </row>
-    <row r="913" spans="1:11">
+    <row r="913" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A913" s="8">
         <v>45273</v>
       </c>
@@ -48392,7 +48391,7 @@
         <v>69.78</v>
       </c>
     </row>
-    <row r="914" spans="1:11">
+    <row r="914" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A914" s="8">
         <v>45280</v>
       </c>
@@ -48406,29 +48405,29 @@
         <f t="shared" si="14"/>
         <v>UTC-5</v>
       </c>
-      <c r="E914" s="15">
+      <c r="E914" s="14">
         <v>97.32</v>
       </c>
-      <c r="F914" s="16">
+      <c r="F914" s="15">
         <v>1</v>
       </c>
-      <c r="G914" s="15">
+      <c r="G914" s="14">
         <v>81.5</v>
       </c>
-      <c r="H914" s="17">
-        <v>100</v>
-      </c>
-      <c r="I914" s="17">
-        <v>100</v>
-      </c>
-      <c r="J914" s="17">
-        <v>200</v>
-      </c>
-      <c r="K914" s="15">
+      <c r="H914" s="16">
+        <v>100</v>
+      </c>
+      <c r="I914" s="16">
+        <v>100</v>
+      </c>
+      <c r="J914" s="16">
+        <v>200</v>
+      </c>
+      <c r="K914" s="14">
         <v>49.87</v>
       </c>
     </row>
-    <row r="915" spans="1:11">
+    <row r="915" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A915" s="8">
         <v>45287</v>
       </c>
@@ -48464,7 +48463,7 @@
         <v>48.43</v>
       </c>
     </row>
-    <row r="916" spans="1:11">
+    <row r="916" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A916" s="8">
         <v>45294</v>
       </c>
@@ -48500,7 +48499,7 @@
         <v>68.19</v>
       </c>
     </row>
-    <row r="917" spans="1:11">
+    <row r="917" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A917" s="8">
         <v>45301</v>
       </c>
@@ -48536,7 +48535,7 @@
         <v>43.94</v>
       </c>
     </row>
-    <row r="918" spans="1:11">
+    <row r="918" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A918" s="8">
         <v>45308</v>
       </c>
@@ -48572,7 +48571,7 @@
         <v>71.66</v>
       </c>
     </row>
-    <row r="919" spans="1:11">
+    <row r="919" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A919" s="8">
         <v>45315</v>
       </c>
@@ -48608,7 +48607,7 @@
         <v>70.540000000000006</v>
       </c>
     </row>
-    <row r="920" spans="1:11">
+    <row r="920" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A920" s="8">
         <v>45322</v>
       </c>
@@ -48644,7 +48643,7 @@
         <v>67.72</v>
       </c>
     </row>
-    <row r="921" spans="1:11">
+    <row r="921" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A921" s="8">
         <v>45329</v>
       </c>
@@ -48680,7 +48679,7 @@
         <v>40.520000000000003</v>
       </c>
     </row>
-    <row r="922" spans="1:11">
+    <row r="922" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A922" s="8">
         <v>45336</v>
       </c>
@@ -48716,7 +48715,7 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="923" spans="1:11">
+    <row r="923" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A923" s="8">
         <v>45343</v>
       </c>
@@ -48752,7 +48751,7 @@
         <v>87.34</v>
       </c>
     </row>
-    <row r="924" spans="1:11">
+    <row r="924" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A924" s="8">
         <v>45350</v>
       </c>
@@ -48788,7 +48787,7 @@
         <v>63.8</v>
       </c>
     </row>
-    <row r="925" spans="1:11">
+    <row r="925" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A925" s="8">
         <v>45357</v>
       </c>
@@ -48824,7 +48823,7 @@
         <v>43.54</v>
       </c>
     </row>
-    <row r="926" spans="1:11">
+    <row r="926" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A926" s="8">
         <v>45364</v>
       </c>
@@ -48860,7 +48859,7 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="927" spans="1:11">
+    <row r="927" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A927" s="8">
         <v>45371</v>
       </c>
@@ -48896,7 +48895,7 @@
         <v>71.209999999999994</v>
       </c>
     </row>
-    <row r="928" spans="1:11">
+    <row r="928" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A928" s="8">
         <v>45378</v>
       </c>
@@ -48932,7 +48931,7 @@
         <v>31.21</v>
       </c>
     </row>
-    <row r="929" spans="1:11">
+    <row r="929" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A929" s="8">
         <v>45385</v>
       </c>
@@ -48968,7 +48967,7 @@
         <v>68.209999999999994</v>
       </c>
     </row>
-    <row r="930" spans="1:11">
+    <row r="930" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A930" s="8">
         <v>45392</v>
       </c>
@@ -49004,7 +49003,7 @@
         <v>65.73</v>
       </c>
     </row>
-    <row r="931" spans="1:11">
+    <row r="931" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A931" s="8">
         <v>45399</v>
       </c>
@@ -49040,7 +49039,7 @@
         <v>71.42</v>
       </c>
     </row>
-    <row r="932" spans="1:11">
+    <row r="932" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A932" s="8">
         <v>45406</v>
       </c>
@@ -49076,7 +49075,7 @@
         <v>70.790000000000006</v>
       </c>
     </row>
-    <row r="933" spans="1:11">
+    <row r="933" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A933" s="8">
         <v>45413</v>
       </c>
@@ -49112,7 +49111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="934" spans="1:11">
+    <row r="934" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A934" s="8">
         <v>45420</v>
       </c>
@@ -49148,7 +49147,7 @@
         <v>59.39</v>
       </c>
     </row>
-    <row r="935" spans="1:11">
+    <row r="935" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A935" s="8">
         <v>45427</v>
       </c>
@@ -49184,7 +49183,7 @@
         <v>71.739999999999995</v>
       </c>
     </row>
-    <row r="936" spans="1:11">
+    <row r="936" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A936" s="8">
         <v>45434</v>
       </c>
@@ -49220,7 +49219,7 @@
         <v>72.540000000000006</v>
       </c>
     </row>
-    <row r="937" spans="1:11">
+    <row r="937" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A937" s="8">
         <v>45441</v>
       </c>
@@ -49256,7 +49255,7 @@
         <v>78.959999999999994</v>
       </c>
     </row>
-    <row r="938" spans="1:11">
+    <row r="938" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A938" s="8">
         <v>45448</v>
       </c>
@@ -49292,7 +49291,7 @@
         <v>90.94</v>
       </c>
     </row>
-    <row r="939" spans="1:11">
+    <row r="939" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A939" s="8">
         <v>45455</v>
       </c>
@@ -49328,7 +49327,7 @@
         <v>56.33</v>
       </c>
     </row>
-    <row r="940" spans="1:11">
+    <row r="940" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A940" s="8">
         <v>45462</v>
       </c>
@@ -49364,7 +49363,7 @@
         <v>74.87</v>
       </c>
     </row>
-    <row r="941" spans="1:11">
+    <row r="941" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A941" s="8">
         <v>45469</v>
       </c>
@@ -49400,7 +49399,7 @@
         <v>58.35</v>
       </c>
     </row>
-    <row r="942" spans="1:11">
+    <row r="942" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A942" s="8">
         <v>45476</v>
       </c>
@@ -49436,7 +49435,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="943" spans="1:11">
+    <row r="943" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A943" s="8">
         <v>45483</v>
       </c>
@@ -49472,7 +49471,7 @@
         <v>71.989999999999995</v>
       </c>
     </row>
-    <row r="944" spans="1:11">
+    <row r="944" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A944" s="8">
         <v>45490</v>
       </c>
@@ -49508,7 +49507,7 @@
         <v>71.55</v>
       </c>
     </row>
-    <row r="945" spans="1:11">
+    <row r="945" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A945" s="8">
         <v>45497</v>
       </c>
@@ -49544,7 +49543,7 @@
         <v>54.03</v>
       </c>
     </row>
-    <row r="946" spans="1:11">
+    <row r="946" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A946" s="8">
         <v>45504</v>
       </c>
@@ -49580,7 +49579,7 @@
         <v>62.38</v>
       </c>
     </row>
-    <row r="947" spans="1:11">
+    <row r="947" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A947" s="8">
         <v>45511</v>
       </c>
@@ -49616,7 +49615,7 @@
         <v>60.29</v>
       </c>
     </row>
-    <row r="948" spans="1:11">
+    <row r="948" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A948" s="8">
         <v>45518</v>
       </c>
@@ -49652,7 +49651,7 @@
         <v>89.06</v>
       </c>
     </row>
-    <row r="949" spans="1:11">
+    <row r="949" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A949" s="8">
         <v>45525</v>
       </c>
@@ -49688,7 +49687,7 @@
         <v>67.78</v>
       </c>
     </row>
-    <row r="950" spans="1:11">
+    <row r="950" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A950" s="8">
         <v>45532</v>
       </c>
@@ -49724,7 +49723,7 @@
         <v>76.260000000000005</v>
       </c>
     </row>
-    <row r="951" spans="1:11">
+    <row r="951" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A951" s="8">
         <v>45539</v>
       </c>
@@ -49760,7 +49759,7 @@
         <v>70.38</v>
       </c>
     </row>
-    <row r="952" spans="1:11">
+    <row r="952" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A952" s="8">
         <v>45546</v>
       </c>
@@ -49796,7 +49795,7 @@
         <v>70.66</v>
       </c>
     </row>
-    <row r="953" spans="1:11">
+    <row r="953" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A953" s="8">
         <v>45553</v>
       </c>
@@ -49832,7 +49831,7 @@
         <v>69.36</v>
       </c>
     </row>
-    <row r="954" spans="1:11">
+    <row r="954" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A954" s="8">
         <v>45560</v>
       </c>
@@ -49868,7 +49867,7 @@
         <v>75.61</v>
       </c>
     </row>
-    <row r="955" spans="1:11">
+    <row r="955" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A955" s="8">
         <v>45567</v>
       </c>
@@ -49904,7 +49903,7 @@
         <v>56.15</v>
       </c>
     </row>
-    <row r="956" spans="1:11">
+    <row r="956" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A956" s="8">
         <v>45574</v>
       </c>
@@ -49940,7 +49939,7 @@
         <v>54.22</v>
       </c>
     </row>
-    <row r="957" spans="1:11">
+    <row r="957" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A957" s="8">
         <v>45581</v>
       </c>
@@ -49976,7 +49975,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="958" spans="1:11">
+    <row r="958" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A958" s="8">
         <v>45588</v>
       </c>
@@ -50012,7 +50011,7 @@
         <v>75.64</v>
       </c>
     </row>
-    <row r="959" spans="1:11">
+    <row r="959" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A959" s="8">
         <v>45595</v>
       </c>
@@ -50048,7 +50047,7 @@
         <v>60.95</v>
       </c>
     </row>
-    <row r="960" spans="1:11">
+    <row r="960" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A960" s="8">
         <v>45602</v>
       </c>
@@ -50084,7 +50083,7 @@
         <v>56.27</v>
       </c>
     </row>
-    <row r="961" spans="1:11">
+    <row r="961" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A961" s="8">
         <v>45609</v>
       </c>
@@ -50120,7 +50119,7 @@
         <v>66.66</v>
       </c>
     </row>
-    <row r="962" spans="1:11">
+    <row r="962" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A962" s="8">
         <v>45616</v>
       </c>
@@ -50156,7 +50155,7 @@
         <v>55.21</v>
       </c>
     </row>
-    <row r="963" spans="1:11">
+    <row r="963" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A963" s="8">
         <v>45623</v>
       </c>
@@ -50207,7 +50206,7 @@
         <v>44.97</v>
       </c>
     </row>
-    <row r="964" spans="1:11">
+    <row r="964" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A964" s="8">
         <v>45630</v>
       </c>
@@ -50243,7 +50242,7 @@
         <v>65.58</v>
       </c>
     </row>
-    <row r="965" spans="1:11">
+    <row r="965" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A965" s="8">
         <v>45637</v>
       </c>
@@ -50279,7 +50278,7 @@
         <v>50.55</v>
       </c>
     </row>
-    <row r="966" spans="1:11">
+    <row r="966" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A966" s="8">
         <v>45644</v>
       </c>
@@ -50315,7 +50314,7 @@
         <v>55.02</v>
       </c>
     </row>
-    <row r="967" spans="1:11">
+    <row r="967" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A967" s="8">
         <v>45651</v>
       </c>
@@ -50351,7 +50350,7 @@
         <v>72.16</v>
       </c>
     </row>
-    <row r="968" spans="1:11">
+    <row r="968" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A968" s="8">
         <v>45658</v>
       </c>
@@ -50387,7 +50386,7 @@
         <v>90.01</v>
       </c>
     </row>
-    <row r="969" spans="1:11">
+    <row r="969" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A969" s="8">
         <v>45665</v>
       </c>
@@ -50423,7 +50422,7 @@
         <v>55.05</v>
       </c>
     </row>
-    <row r="970" spans="1:11">
+    <row r="970" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A970" s="8">
         <v>45672</v>
       </c>
@@ -50459,7 +50458,7 @@
         <v>58.09</v>
       </c>
     </row>
-    <row r="971" spans="1:11">
+    <row r="971" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A971" s="8">
         <v>45679</v>
       </c>
@@ -50495,7 +50494,7 @@
         <v>45.88</v>
       </c>
     </row>
-    <row r="972" spans="1:11">
+    <row r="972" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A972" s="8">
         <v>45686</v>
       </c>
@@ -50531,7 +50530,7 @@
         <v>65.86</v>
       </c>
     </row>
-    <row r="973" spans="1:11">
+    <row r="973" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A973" s="8">
         <v>45693</v>
       </c>
@@ -50567,7 +50566,7 @@
         <v>54.2</v>
       </c>
     </row>
-    <row r="974" spans="1:11">
+    <row r="974" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A974" s="8">
         <v>45700</v>
       </c>
@@ -50603,7 +50602,7 @@
         <v>52.44</v>
       </c>
     </row>
-    <row r="975" spans="1:11">
+    <row r="975" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A975" s="8">
         <v>45707</v>
       </c>
@@ -50639,7 +50638,7 @@
         <v>49.61</v>
       </c>
     </row>
-    <row r="976" spans="1:11">
+    <row r="976" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A976" s="8">
         <v>45714</v>
       </c>
@@ -50675,7 +50674,7 @@
         <v>51.43</v>
       </c>
     </row>
-    <row r="977" spans="1:11">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A977" s="8">
         <v>45721</v>
       </c>
@@ -50711,7 +50710,7 @@
         <v>69.739999999999995</v>
       </c>
     </row>
-    <row r="978" spans="1:11">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A978" s="8">
         <v>45728</v>
       </c>
@@ -50747,7 +50746,7 @@
         <v>70.47</v>
       </c>
     </row>
-    <row r="979" spans="1:11">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A979" s="8">
         <v>45735</v>
       </c>
@@ -50783,7 +50782,7 @@
         <v>53.55</v>
       </c>
     </row>
-    <row r="980" spans="1:11">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A980" s="8">
         <v>45742</v>
       </c>
@@ -50819,7 +50818,7 @@
         <v>54.17</v>
       </c>
     </row>
-    <row r="981" spans="1:11">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A981" s="8">
         <v>45749</v>
       </c>
@@ -50855,7 +50854,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="982" spans="1:11">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A982" s="8">
         <v>45756</v>
       </c>
@@ -50891,7 +50890,7 @@
         <v>60.04</v>
       </c>
     </row>
-    <row r="983" spans="1:11">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A983" s="8">
         <v>45763</v>
       </c>
@@ -50927,7 +50926,7 @@
         <v>65.53</v>
       </c>
     </row>
-    <row r="984" spans="1:11">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A984" s="8">
         <v>45770</v>
       </c>
@@ -50963,7 +50962,7 @@
         <v>50.87</v>
       </c>
     </row>
-    <row r="985" spans="1:11">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A985" s="8">
         <v>45777</v>
       </c>
@@ -50999,7 +50998,7 @@
         <v>77.239999999999995</v>
       </c>
     </row>
-    <row r="986" spans="1:11">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A986" s="8">
         <v>45784</v>
       </c>
@@ -51035,7 +51034,7 @@
         <v>51.46</v>
       </c>
     </row>
-    <row r="987" spans="1:11">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A987" s="8">
         <v>45791</v>
       </c>
@@ -51071,7 +51070,7 @@
         <v>65.03</v>
       </c>
     </row>
-    <row r="988" spans="1:11">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A988" s="8">
         <v>45798</v>
       </c>
@@ -51107,7 +51106,7 @@
         <v>60.35</v>
       </c>
     </row>
-    <row r="989" spans="1:11">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A989" s="8">
         <v>45805</v>
       </c>
@@ -51143,7 +51142,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="990" spans="1:11">
+    <row r="990" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A990" s="8">
         <v>45812</v>
       </c>
@@ -51179,7 +51178,7 @@
         <v>67.680000000000007</v>
       </c>
     </row>
-    <row r="991" spans="1:11">
+    <row r="991" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A991" s="8">
         <v>45819</v>
       </c>
@@ -51215,7 +51214,7 @@
         <v>73.680000000000007</v>
       </c>
     </row>
-    <row r="992" spans="1:11">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A992" s="8">
         <v>45826</v>
       </c>
@@ -51251,7 +51250,7 @@
         <v>52.15</v>
       </c>
     </row>
-    <row r="993" spans="1:11">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A993" s="8">
         <v>45833</v>
       </c>
@@ -51287,7 +51286,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="994" spans="1:11">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A994" s="8">
         <v>45840</v>
       </c>
@@ -51323,7 +51322,7 @@
         <v>54.77</v>
       </c>
     </row>
-    <row r="995" spans="1:11">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A995" s="8">
         <v>45847</v>
       </c>
@@ -51359,7 +51358,7 @@
         <v>69.709999999999994</v>
       </c>
     </row>
-    <row r="996" spans="1:11">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A996" s="8">
         <v>45854</v>
       </c>
@@ -51395,7 +51394,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="997" spans="1:11">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A997" s="8">
         <v>45861</v>
       </c>
@@ -51431,7 +51430,7 @@
         <v>64.98</v>
       </c>
     </row>
-    <row r="998" spans="1:11">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A998" s="8">
         <v>45868</v>
       </c>
@@ -51467,7 +51466,7 @@
         <v>64.89</v>
       </c>
     </row>
-    <row r="999" spans="1:11">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A999" s="8">
         <v>45875</v>
       </c>
@@ -51503,7 +51502,7 @@
         <v>35.96</v>
       </c>
     </row>
-    <row r="1000" spans="1:11">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1000" s="8">
         <v>45882</v>
       </c>
@@ -51539,7 +51538,7 @@
         <v>69.55</v>
       </c>
     </row>
-    <row r="1001" spans="1:11">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1001" s="8">
         <v>45889</v>
       </c>
@@ -51575,7 +51574,7 @@
         <v>44.79</v>
       </c>
     </row>
-    <row r="1002" spans="1:11">
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1002" s="8">
         <v>45896</v>
       </c>
@@ -51611,7 +51610,7 @@
         <v>44.7</v>
       </c>
     </row>
-    <row r="1003" spans="1:11">
+    <row r="1003" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1003" s="8">
         <v>45903</v>
       </c>
@@ -51647,7 +51646,7 @@
         <v>63.56</v>
       </c>
     </row>
-    <row r="1004" spans="1:11">
+    <row r="1004" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1004" s="8">
         <v>45910</v>
       </c>
@@ -51683,7 +51682,7 @@
         <v>71.06</v>
       </c>
     </row>
-    <row r="1005" spans="1:11">
+    <row r="1005" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1005" s="8">
         <v>45917</v>
       </c>
@@ -51719,7 +51718,7 @@
         <v>71.959999999999994</v>
       </c>
     </row>
-    <row r="1006" spans="1:11">
+    <row r="1006" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1006" s="8">
         <v>45924</v>
       </c>
@@ -51755,7 +51754,7 @@
         <v>66.77</v>
       </c>
     </row>
-    <row r="1007" spans="1:11">
+    <row r="1007" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1007" s="8">
         <v>45931</v>
       </c>
@@ -51791,7 +51790,7 @@
         <v>71.13</v>
       </c>
     </row>
-    <row r="1008" spans="1:11">
+    <row r="1008" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1008" s="8">
         <v>45938</v>
       </c>
@@ -51827,7 +51826,7 @@
         <v>69.27</v>
       </c>
     </row>
-    <row r="1009" spans="1:11">
+    <row r="1009" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1009" s="8">
         <v>45945</v>
       </c>
@@ -51863,7 +51862,7 @@
         <v>50.98</v>
       </c>
     </row>
-    <row r="1010" spans="1:11">
+    <row r="1010" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1010" s="8">
         <v>45952</v>
       </c>
@@ -51899,7 +51898,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="1011" spans="1:11">
+    <row r="1011" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1011" s="8">
         <v>45959</v>
       </c>
@@ -51935,7 +51934,7 @@
         <v>55.36</v>
       </c>
     </row>
-    <row r="1012" spans="1:11">
+    <row r="1012" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1012" s="8">
         <v>45966</v>
       </c>
@@ -51971,7 +51970,7 @@
         <v>40.86</v>
       </c>
     </row>
-    <row r="1013" spans="1:11">
+    <row r="1013" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1013" s="8">
         <v>45973</v>
       </c>
@@ -52007,7 +52006,7 @@
         <v>39.42</v>
       </c>
     </row>
-    <row r="1014" spans="1:11">
+    <row r="1014" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1014" s="8">
         <v>45980</v>
       </c>
@@ -52043,7 +52042,7 @@
         <v>51.59</v>
       </c>
     </row>
-    <row r="1015" spans="1:11">
+    <row r="1015" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1015" s="8">
         <v>45987</v>
       </c>
@@ -52079,7 +52078,7 @@
         <v>50.29</v>
       </c>
     </row>
-    <row r="1016" spans="1:11">
+    <row r="1016" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1016" s="8">
         <v>45994</v>
       </c>
@@ -52115,7 +52114,7 @@
         <v>47.59</v>
       </c>
     </row>
-    <row r="1017" spans="1:11">
+    <row r="1017" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1017" s="8">
         <v>46001</v>
       </c>
@@ -52151,7 +52150,7 @@
         <v>45.89</v>
       </c>
     </row>
-    <row r="1018" spans="1:11">
+    <row r="1018" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1018" s="8">
         <v>46008</v>
       </c>
@@ -52187,7 +52186,7 @@
         <v>46.38</v>
       </c>
     </row>
-    <row r="1019" spans="1:11">
+    <row r="1019" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1019" s="8">
         <v>46015</v>
       </c>
@@ -52223,7 +52222,7 @@
         <v>49.27</v>
       </c>
     </row>
-    <row r="1020" spans="1:11">
+    <row r="1020" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1020" s="8">
         <v>46022</v>
       </c>
@@ -52259,7 +52258,7 @@
         <v>48.97</v>
       </c>
     </row>
-    <row r="1021" spans="1:11">
+    <row r="1021" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1021" s="8">
         <v>46029</v>
       </c>
@@ -52295,7 +52294,7 @@
         <v>50.86</v>
       </c>
     </row>
-    <row r="1022" spans="1:11">
+    <row r="1022" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1022" s="8">
         <v>46036</v>
       </c>
@@ -52331,7 +52330,7 @@
         <v>50.37</v>
       </c>
     </row>
-    <row r="1023" spans="1:11">
+    <row r="1023" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1023" s="8">
         <v>46043</v>
       </c>
@@ -52367,7 +52366,7 @@
         <v>60.31</v>
       </c>
     </row>
-    <row r="1024" spans="1:11">
+    <row r="1024" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1024" s="8">
         <v>46050</v>
       </c>
@@ -52403,7 +52402,7 @@
         <v>46.41</v>
       </c>
     </row>
-    <row r="1025" spans="1:11">
+    <row r="1025" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1025" s="8">
         <v>46057</v>
       </c>
@@ -52439,7 +52438,7 @@
         <v>64.569999999999993</v>
       </c>
     </row>
-    <row r="1026" spans="1:11">
+    <row r="1026" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1026" s="8">
         <v>46064</v>
       </c>
@@ -52475,7 +52474,7 @@
         <v>63.52</v>
       </c>
     </row>
-    <row r="1027" spans="1:11">
+    <row r="1027" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1027" s="8">
         <v>46071</v>
       </c>
@@ -52526,7 +52525,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1028" spans="1:11">
+    <row r="1028" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1028" s="8">
         <v>46078</v>
       </c>
@@ -52562,7 +52561,7 @@
         <v>64.84</v>
       </c>
     </row>
-    <row r="1029" spans="1:11">
+    <row r="1029" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1029" s="8">
         <v>46085</v>
       </c>
@@ -52598,7 +52597,7 @@
         <v>49.98</v>
       </c>
     </row>
-    <row r="1030" spans="1:11">
+    <row r="1030" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1030" s="8">
         <v>46092</v>
       </c>
@@ -52634,7 +52633,7 @@
         <v>62.78</v>
       </c>
     </row>
-    <row r="1031" spans="1:11">
+    <row r="1031" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1031" s="8">
         <v>46099</v>
       </c>
@@ -52670,7 +52669,7 @@
         <v>68.13</v>
       </c>
     </row>
-    <row r="1032" spans="1:11">
+    <row r="1032" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1032" s="8">
         <v>46106</v>
       </c>
@@ -52721,7 +52720,7 @@
         <v>47.03</v>
       </c>
     </row>
-    <row r="1033" spans="1:11">
+    <row r="1033" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1033" s="8">
         <v>46113</v>
       </c>
@@ -52757,7 +52756,7 @@
         <v>55.64</v>
       </c>
     </row>
-    <row r="1034" spans="1:11">
+    <row r="1034" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1034" s="8">
         <v>46120</v>
       </c>
@@ -52808,7 +52807,7 @@
         <v>51.31</v>
       </c>
     </row>
-    <row r="1035" spans="1:11">
+    <row r="1035" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1035" s="8">
         <v>46127</v>
       </c>
@@ -52844,7 +52843,7 @@
         <v>68.87</v>
       </c>
     </row>
-    <row r="1036" spans="1:11">
+    <row r="1036" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1036" s="8">
         <v>46134</v>
       </c>
@@ -52880,7 +52879,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="1037" spans="1:11">
+    <row r="1037" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1037" s="8">
         <v>46141</v>
       </c>
@@ -52931,7 +52930,7 @@
         <v>48.61</v>
       </c>
     </row>
-    <row r="1038" spans="1:11">
+    <row r="1038" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1038" s="8">
         <v>46148</v>
       </c>
@@ -52967,7 +52966,7 @@
         <v>43.28</v>
       </c>
     </row>
-    <row r="1039" spans="1:11">
+    <row r="1039" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1039" s="8">
         <v>46155</v>
       </c>
@@ -53003,7 +53002,7 @@
         <v>68.17</v>
       </c>
     </row>
-    <row r="1040" spans="1:11">
+    <row r="1040" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1040" s="8">
         <v>46162</v>
       </c>
@@ -53054,7 +53053,7 @@
         <v>55.01</v>
       </c>
     </row>
-    <row r="1041" spans="1:11">
+    <row r="1041" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1041" s="8">
         <v>46169</v>
       </c>
@@ -53090,7 +53089,7 @@
         <v>47.62</v>
       </c>
     </row>
-    <row r="1042" spans="1:11">
+    <row r="1042" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1042" s="8">
         <v>46176</v>
       </c>
@@ -53141,7 +53140,7 @@
         <v>72.069999999999993</v>
       </c>
     </row>
-    <row r="1043" spans="1:11">
+    <row r="1043" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1043" s="8">
         <v>46183</v>
       </c>
@@ -53187,7 +53186,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{115169E1-C49D-409D-8D5D-92B2FD26EE0D}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -53198,9 +53197,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>7</v>
       </c>
@@ -53208,7 +53207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>8</v>
       </c>

--- a/data/sentiment/NAAIM Exposure Index.xlsx
+++ b/data/sentiment/NAAIM Exposure Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\sentiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3320ADA0-203B-4C62-8984-CB6EBDED5E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{546A0B91-BA5F-4A3D-B073-8D1348017934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAAIM" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>median</t>
   </si>
@@ -87,6 +87,48 @@
   <si>
     <t>estimated skewness</t>
   </si>
+  <si>
+    <t>original</t>
+  </si>
+  <si>
+    <t>1Q</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>3Q</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>std</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_1st_quartile</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_3rd_quartile</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_2nd_quartile</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_number</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_deviation</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_bearish</t>
+  </si>
+  <si>
+    <t>https://ycharts.com/indicators/naaim_survey_of_managers_bullish</t>
+  </si>
 </sst>
 </file>
 
@@ -99,7 +141,7 @@
     <numFmt numFmtId="166" formatCode="0.00_ "/>
     <numFmt numFmtId="167" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,6 +287,14 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -595,7 +645,7 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="43"/>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -637,6 +687,13 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="20" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3889,6 +3946,9 @@
                 <c:pt idx="1042">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="1043">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -7026,6 +7086,9 @@
                 </c:pt>
                 <c:pt idx="1042">
                   <c:v>92.83</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>98.59</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10439,6 +10502,9 @@
                 <c:pt idx="1042">
                   <c:v>46191</c:v>
                 </c:pt>
+                <c:pt idx="1043">
+                  <c:v>46198</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -13576,6 +13642,9 @@
                 </c:pt>
                 <c:pt idx="1042">
                   <c:v>49.11</c:v>
+                </c:pt>
+                <c:pt idx="1043">
+                  <c:v>43.91</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -15282,7 +15351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1044"/>
+  <dimension ref="A1:L1045"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -15295,7 +15364,8 @@
     <col min="8" max="8" width="8.88671875" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="18.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" style="19" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="8.77734375" style="13"/>
   </cols>
   <sheetData>
@@ -15333,7 +15403,7 @@
       <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -15387,7 +15457,7 @@
       <c r="K2" s="10">
         <v>55.55</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="19">
         <f>IF(OR(K2=0,I2=G2,J2=F2),"",0.4*((3*(E2-H2)/K2)/(1+ABS(3*(E2-H2)/K2)))+0.45*((I2+G2-2*H2)/(I2-G2))+0.15*((J2+F2-2*H2)/(J2-F2)))</f>
         <v>4.8257906692294295E-2</v>
       </c>
@@ -15442,7 +15512,7 @@
       <c r="K3" s="10">
         <v>47.84</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="19">
         <f t="shared" ref="L3:L66" si="1">IF(OR(K3=0,I3=G3,J3=F3),"",0.4*((3*(E3-H3)/K3)/(1+ABS(3*(E3-H3)/K3)))+0.45*((I3+G3-2*H3)/(I3-G3))+0.15*((J3+F3-2*H3)/(J3-F3)))</f>
         <v>0.1494807344972908</v>
       </c>
@@ -15482,7 +15552,7 @@
       <c r="K4" s="10">
         <v>55.549999722194443</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="19">
         <f t="shared" si="1"/>
         <v>4.8348383281615753E-2</v>
       </c>
@@ -15522,7 +15592,7 @@
       <c r="K5" s="10">
         <v>47.838896308338889</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="19">
         <f t="shared" si="1"/>
         <v>0.14948259473594222</v>
       </c>
@@ -15562,7 +15632,7 @@
       <c r="K6" s="10">
         <v>38.170438823780898</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="19">
         <f t="shared" si="1"/>
         <v>-0.16912141398125274</v>
       </c>
@@ -15602,7 +15672,7 @@
       <c r="K7" s="10">
         <v>33.778460222455372</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="19">
         <f t="shared" si="1"/>
         <v>0.26967625683744467</v>
       </c>
@@ -15642,7 +15712,7 @@
       <c r="K8" s="10">
         <v>43.692625871599382</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="19">
         <f t="shared" si="1"/>
         <v>-0.44294351787418168</v>
       </c>
@@ -15682,7 +15752,7 @@
       <c r="K9" s="10">
         <v>47.483927790753583</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="19">
         <f t="shared" si="1"/>
         <v>-0.28938716218497396</v>
       </c>
@@ -15722,7 +15792,7 @@
       <c r="K10" s="10">
         <v>56.524684873071166</v>
       </c>
-      <c r="L10" s="10">
+      <c r="L10" s="19">
         <f t="shared" si="1"/>
         <v>-0.33078586405826682</v>
       </c>
@@ -15762,7 +15832,7 @@
       <c r="K11" s="10">
         <v>45.170475778833321</v>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="19">
         <f t="shared" si="1"/>
         <v>-0.34395410291196005</v>
       </c>
@@ -15802,7 +15872,7 @@
       <c r="K12" s="10">
         <v>45.170475778833321</v>
       </c>
-      <c r="L12" s="10">
+      <c r="L12" s="19">
         <f t="shared" si="1"/>
         <v>-0.34395410291196005</v>
       </c>
@@ -15842,7 +15912,7 @@
       <c r="K13" s="10">
         <v>50.374290674884271</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="19">
         <f t="shared" si="1"/>
         <v>-9.3750992304363068E-3</v>
       </c>
@@ -15882,7 +15952,7 @@
       <c r="K14" s="10">
         <v>56.228640389040173</v>
       </c>
-      <c r="L14" s="10">
+      <c r="L14" s="19">
         <f t="shared" si="1"/>
         <v>-0.10322533136659981</v>
       </c>
@@ -15922,7 +15992,7 @@
       <c r="K15" s="10">
         <v>31.264996401726965</v>
       </c>
-      <c r="L15" s="10">
+      <c r="L15" s="19">
         <f t="shared" si="1"/>
         <v>-0.24986073536635631</v>
       </c>
@@ -15962,7 +16032,7 @@
       <c r="K16" s="10">
         <v>55.807410979021469</v>
       </c>
-      <c r="L16" s="10">
+      <c r="L16" s="19">
         <f t="shared" si="1"/>
         <v>0.28626902342992477</v>
       </c>
@@ -16002,7 +16072,7 @@
       <c r="K17" s="10">
         <v>59.404629449227272</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="19">
         <f t="shared" si="1"/>
         <v>-0.48120911205270922</v>
       </c>
@@ -16042,7 +16112,7 @@
       <c r="K18" s="10">
         <v>59.825434763385545</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="19">
         <f t="shared" si="1"/>
         <v>-0.45073323474809168</v>
       </c>
@@ -16082,7 +16152,7 @@
       <c r="K19" s="10">
         <v>33.215082952435786</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L19" s="19">
         <f t="shared" si="1"/>
         <v>-0.49850232655485421</v>
       </c>
@@ -16122,7 +16192,7 @@
       <c r="K20" s="10">
         <v>53.121506002748077</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="19">
         <f t="shared" si="1"/>
         <v>-0.33288219771318478</v>
       </c>
@@ -16162,7 +16232,7 @@
       <c r="K21" s="10">
         <v>53.864396997357062</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="19">
         <f t="shared" si="1"/>
         <v>-0.33596815388505824</v>
       </c>
@@ -16202,7 +16272,7 @@
       <c r="K22" s="10">
         <v>46.653652879834993</v>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="19">
         <f t="shared" si="1"/>
         <v>-0.52162673497442213</v>
       </c>
@@ -16242,7 +16312,7 @@
       <c r="K23" s="10">
         <v>61.297793607386772</v>
       </c>
-      <c r="L23" s="10">
+      <c r="L23" s="19">
         <f t="shared" si="1"/>
         <v>-0.51628444215216274</v>
       </c>
@@ -16282,7 +16352,7 @@
       <c r="K24" s="10">
         <v>20.824828195876073</v>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="19">
         <f t="shared" si="1"/>
         <v>-0.65867935678391776</v>
       </c>
@@ -16322,7 +16392,7 @@
       <c r="K25" s="10">
         <v>38.414042173363363</v>
       </c>
-      <c r="L25" s="10">
+      <c r="L25" s="19">
         <f t="shared" si="1"/>
         <v>-0.71831919747340311</v>
       </c>
@@ -16362,7 +16432,7 @@
       <c r="K26" s="10">
         <v>58.029540018794734</v>
       </c>
-      <c r="L26" s="10">
+      <c r="L26" s="19">
         <f t="shared" si="1"/>
         <v>-0.79929409868423662</v>
       </c>
@@ -16402,7 +16472,7 @@
       <c r="K27" s="10">
         <v>19.415261547359616</v>
       </c>
-      <c r="L27" s="10">
+      <c r="L27" s="19">
         <f t="shared" si="1"/>
         <v>-0.70784227735744509</v>
       </c>
@@ -16442,7 +16512,7 @@
       <c r="K28" s="10">
         <v>22.354395725773102</v>
       </c>
-      <c r="L28" s="10">
+      <c r="L28" s="19">
         <f t="shared" si="1"/>
         <v>-0.64504130284693306</v>
       </c>
@@ -16482,7 +16552,7 @@
       <c r="K29" s="10">
         <v>35.213204259954928</v>
       </c>
-      <c r="L29" s="10">
+      <c r="L29" s="19">
         <f t="shared" si="1"/>
         <v>-0.73991898507881304</v>
       </c>
@@ -16522,7 +16592,7 @@
       <c r="K30" s="10">
         <v>32.236442245024186</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L30" s="19">
         <f t="shared" si="1"/>
         <v>-8.5191725766915943E-2</v>
       </c>
@@ -16562,7 +16632,7 @@
       <c r="K31" s="10">
         <v>65.212862654704111</v>
       </c>
-      <c r="L31" s="10">
+      <c r="L31" s="19">
         <f t="shared" si="1"/>
         <v>-0.42350353459248807</v>
       </c>
@@ -16602,7 +16672,7 @@
       <c r="K32" s="10">
         <v>27.899999503569333</v>
       </c>
-      <c r="L32" s="10">
+      <c r="L32" s="19">
         <f t="shared" si="1"/>
         <v>-0.81543100694682868</v>
       </c>
@@ -16642,7 +16712,7 @@
       <c r="K33" s="10">
         <v>42.723911860082509</v>
       </c>
-      <c r="L33" s="10">
+      <c r="L33" s="19">
         <f t="shared" si="1"/>
         <v>-0.43346805713904746</v>
       </c>
@@ -16682,7 +16752,7 @@
       <c r="K34" s="10">
         <v>49.378006237595294</v>
       </c>
-      <c r="L34" s="10">
+      <c r="L34" s="19">
         <f t="shared" si="1"/>
         <v>-0.28133249948820804</v>
       </c>
@@ -16722,7 +16792,7 @@
       <c r="K35" s="10">
         <v>45.927163507298019</v>
       </c>
-      <c r="L35" s="10">
+      <c r="L35" s="19">
         <f t="shared" si="1"/>
         <v>-0.36528570584731479</v>
       </c>
@@ -16762,7 +16832,7 @@
       <c r="K36" s="10">
         <v>55.649805268718424</v>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="19">
         <f t="shared" si="1"/>
         <v>-0.45263622262212144</v>
       </c>
@@ -16802,7 +16872,7 @@
       <c r="K37" s="10">
         <v>52.764818137257436</v>
       </c>
-      <c r="L37" s="10">
+      <c r="L37" s="19">
         <f t="shared" si="1"/>
         <v>-0.52739874745364201</v>
       </c>
@@ -16842,7 +16912,7 @@
       <c r="K38" s="10">
         <v>53.726231363347424</v>
       </c>
-      <c r="L38" s="10">
+      <c r="L38" s="19">
         <f t="shared" si="1"/>
         <v>-0.64931252425815489</v>
       </c>
@@ -16882,7 +16952,7 @@
       <c r="K39" s="10">
         <v>48.602880573068916</v>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="19">
         <f t="shared" si="1"/>
         <v>0.18494357227483196</v>
       </c>
@@ -16922,7 +16992,7 @@
       <c r="K40" s="10">
         <v>68.635171039352031</v>
       </c>
-      <c r="L40" s="10">
+      <c r="L40" s="19">
         <f t="shared" si="1"/>
         <v>-1.3536366354628501E-2</v>
       </c>
@@ -16962,7 +17032,7 @@
       <c r="K41" s="10">
         <v>54.906588487696794</v>
       </c>
-      <c r="L41" s="10">
+      <c r="L41" s="19">
         <f t="shared" si="1"/>
         <v>0.31619972313269584</v>
       </c>
@@ -17002,7 +17072,7 @@
       <c r="K42" s="10">
         <v>61.630606010506028</v>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="19">
         <f t="shared" si="1"/>
         <v>-3.369764562932831E-2</v>
       </c>
@@ -17042,7 +17112,7 @@
       <c r="K43" s="10">
         <v>64.537968733792852</v>
       </c>
-      <c r="L43" s="10">
+      <c r="L43" s="19">
         <f t="shared" si="1"/>
         <v>-0.20449178142674376</v>
       </c>
@@ -17082,7 +17152,7 @@
       <c r="K44" s="10">
         <v>57.825060311252592</v>
       </c>
-      <c r="L44" s="10">
+      <c r="L44" s="19">
         <f t="shared" si="1"/>
         <v>-3.9255021545701971E-2</v>
       </c>
@@ -17122,7 +17192,7 @@
       <c r="K45" s="10">
         <v>69.279479346364909</v>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="19">
         <f t="shared" si="1"/>
         <v>-0.49020120589498062</v>
       </c>
@@ -17162,7 +17232,7 @@
       <c r="K46" s="10">
         <v>59.001416591157486</v>
       </c>
-      <c r="L46" s="10">
+      <c r="L46" s="19">
         <f t="shared" si="1"/>
         <v>-0.21873249641261724</v>
       </c>
@@ -17202,7 +17272,7 @@
       <c r="K47" s="10">
         <v>59.063995424924954</v>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="19">
         <f t="shared" si="1"/>
         <v>-0.43032800913674135</v>
       </c>
@@ -17242,7 +17312,7 @@
       <c r="K48" s="10">
         <v>55.064860745205635</v>
       </c>
-      <c r="L48" s="10">
+      <c r="L48" s="19">
         <f t="shared" si="1"/>
         <v>-0.73187653511106066</v>
       </c>
@@ -17282,7 +17352,7 @@
       <c r="K49" s="10">
         <v>51.819247148139851</v>
       </c>
-      <c r="L49" s="10">
+      <c r="L49" s="19">
         <f t="shared" si="1"/>
         <v>-0.67659946151431505</v>
       </c>
@@ -17322,7 +17392,7 @@
       <c r="K50" s="10">
         <v>53.983793864455286</v>
       </c>
-      <c r="L50" s="10">
+      <c r="L50" s="19">
         <f t="shared" si="1"/>
         <v>-0.16043732296481714</v>
       </c>
@@ -17362,7 +17432,7 @@
       <c r="K51" s="10">
         <v>48.786852991286374</v>
       </c>
-      <c r="L51" s="10">
+      <c r="L51" s="19">
         <f t="shared" si="1"/>
         <v>-0.3579133007677035</v>
       </c>
@@ -17402,7 +17472,7 @@
       <c r="K52" s="10">
         <v>62.811083593759328</v>
       </c>
-      <c r="L52" s="10">
+      <c r="L52" s="19">
         <f t="shared" si="1"/>
         <v>-0.47242936301055077</v>
       </c>
@@ -17442,7 +17512,7 @@
       <c r="K53" s="10">
         <v>65.542340513594723</v>
       </c>
-      <c r="L53" s="10">
+      <c r="L53" s="19">
         <f t="shared" si="1"/>
         <v>-0.49369567219641824</v>
       </c>
@@ -17482,7 +17552,7 @@
       <c r="K54" s="10">
         <v>67.954431672633518</v>
       </c>
-      <c r="L54" s="10">
+      <c r="L54" s="19">
         <f t="shared" si="1"/>
         <v>-0.47264136688512071</v>
       </c>
@@ -17522,7 +17592,7 @@
       <c r="K55" s="10">
         <v>55.826175891531534</v>
       </c>
-      <c r="L55" s="10">
+      <c r="L55" s="19">
         <f t="shared" si="1"/>
         <v>-0.12793187085730767</v>
       </c>
@@ -17562,7 +17632,7 @@
       <c r="K56" s="10">
         <v>60.176790324426577</v>
       </c>
-      <c r="L56" s="10">
+      <c r="L56" s="19">
         <f t="shared" si="1"/>
         <v>-0.45785307308202794</v>
       </c>
@@ -17602,7 +17672,7 @@
       <c r="K57" s="10">
         <v>51.354938031690303</v>
       </c>
-      <c r="L57" s="10">
+      <c r="L57" s="19">
         <f t="shared" si="1"/>
         <v>-0.30713937958815768</v>
       </c>
@@ -17642,7 +17712,7 @@
       <c r="K58" s="10">
         <v>45.888802797874582</v>
       </c>
-      <c r="L58" s="10">
+      <c r="L58" s="19">
         <f t="shared" si="1"/>
         <v>-0.23762726767206502</v>
       </c>
@@ -17682,7 +17752,7 @@
       <c r="K59" s="10">
         <v>63.76609180512709</v>
       </c>
-      <c r="L59" s="10">
+      <c r="L59" s="19">
         <f t="shared" si="1"/>
         <v>-0.21377912528898257</v>
       </c>
@@ -17722,7 +17792,7 @@
       <c r="K60" s="10">
         <v>59.657354953098618</v>
       </c>
-      <c r="L60" s="10">
+      <c r="L60" s="19">
         <f t="shared" si="1"/>
         <v>-0.11332394680966355</v>
       </c>
@@ -17762,7 +17832,7 @@
       <c r="K61" s="10">
         <v>65.099669293697346</v>
       </c>
-      <c r="L61" s="10">
+      <c r="L61" s="19">
         <f t="shared" si="1"/>
         <v>0.25276736552028362</v>
       </c>
@@ -17802,7 +17872,7 @@
       <c r="K62" s="10">
         <v>57.034529015325447</v>
       </c>
-      <c r="L62" s="10">
+      <c r="L62" s="19">
         <f t="shared" si="1"/>
         <v>0.54600364090582942</v>
       </c>
@@ -17842,7 +17912,7 @@
       <c r="K63" s="10">
         <v>52.701658833000693</v>
       </c>
-      <c r="L63" s="10">
+      <c r="L63" s="19">
         <f t="shared" si="1"/>
         <v>0.33136943914315881</v>
       </c>
@@ -17882,7 +17952,7 @@
       <c r="K64" s="10">
         <v>72.566359583555496</v>
       </c>
-      <c r="L64" s="10">
+      <c r="L64" s="19">
         <f t="shared" si="1"/>
         <v>0.12912288349136314</v>
       </c>
@@ -17922,7 +17992,7 @@
       <c r="K65" s="10">
         <v>45.022968675258781</v>
       </c>
-      <c r="L65" s="10">
+      <c r="L65" s="19">
         <f t="shared" si="1"/>
         <v>-7.6083846326287993E-3</v>
       </c>
@@ -17962,7 +18032,7 @@
       <c r="K66" s="10">
         <v>69.603104472428257</v>
       </c>
-      <c r="L66" s="10">
+      <c r="L66" s="19">
         <f t="shared" si="1"/>
         <v>0.11224513591459057</v>
       </c>
@@ -18017,7 +18087,7 @@
       <c r="K67" s="10">
         <v>42.408304442812678</v>
       </c>
-      <c r="L67" s="10">
+      <c r="L67" s="19">
         <f t="shared" ref="L67:L130" si="3">IF(OR(K67=0,I67=G67,J67=F67),"",0.4*((3*(E67-H67)/K67)/(1+ABS(3*(E67-H67)/K67)))+0.45*((I67+G67-2*H67)/(I67-G67))+0.15*((J67+F67-2*H67)/(J67-F67)))</f>
         <v>0.45293891063754477</v>
       </c>
@@ -18057,7 +18127,7 @@
       <c r="K68" s="10">
         <v>38.186796212286225</v>
       </c>
-      <c r="L68" s="10">
+      <c r="L68" s="19">
         <f t="shared" si="3"/>
         <v>0.15014371432629706</v>
       </c>
@@ -18097,7 +18167,7 @@
       <c r="K69" s="10">
         <v>61.369548273391054</v>
       </c>
-      <c r="L69" s="10">
+      <c r="L69" s="19">
         <f t="shared" si="3"/>
         <v>-0.40727359718253719</v>
       </c>
@@ -18137,7 +18207,7 @@
       <c r="K70" s="10">
         <v>56.227919122877815</v>
       </c>
-      <c r="L70" s="10">
+      <c r="L70" s="19">
         <f t="shared" si="3"/>
         <v>-0.58627111336585169</v>
       </c>
@@ -18177,7 +18247,7 @@
       <c r="K71" s="10">
         <v>49.208363214031834</v>
       </c>
-      <c r="L71" s="10">
+      <c r="L71" s="19">
         <f t="shared" si="3"/>
         <v>-0.30859567246213765</v>
       </c>
@@ -18217,7 +18287,7 @@
       <c r="K72" s="10">
         <v>65.850867379966061</v>
       </c>
-      <c r="L72" s="10">
+      <c r="L72" s="19">
         <f t="shared" si="3"/>
         <v>-0.53239272671191196</v>
       </c>
@@ -18257,7 +18327,7 @@
       <c r="K73" s="10">
         <v>75.074716234904798</v>
       </c>
-      <c r="L73" s="10">
+      <c r="L73" s="19">
         <f t="shared" si="3"/>
         <v>-0.56765356044168258</v>
       </c>
@@ -18297,7 +18367,7 @@
       <c r="K74" s="10">
         <v>52.534527153195896</v>
       </c>
-      <c r="L74" s="10">
+      <c r="L74" s="19">
         <f t="shared" si="3"/>
         <v>4.606555987215261E-3</v>
       </c>
@@ -18337,7 +18407,7 @@
       <c r="K75" s="10">
         <v>40.679745770792763</v>
       </c>
-      <c r="L75" s="10">
+      <c r="L75" s="19">
         <f t="shared" si="3"/>
         <v>0.23328337924245268</v>
       </c>
@@ -18377,7 +18447,7 @@
       <c r="K76" s="10">
         <v>60.493442596881707</v>
       </c>
-      <c r="L76" s="10">
+      <c r="L76" s="19">
         <f t="shared" si="3"/>
         <v>3.4802258995979204E-2</v>
       </c>
@@ -18417,7 +18487,7 @@
       <c r="K77" s="10">
         <v>68.934714752142</v>
       </c>
-      <c r="L77" s="10">
+      <c r="L77" s="19">
         <f t="shared" si="3"/>
         <v>-0.11390163641424941</v>
       </c>
@@ -18457,7 +18527,7 @@
       <c r="K78" s="10">
         <v>60.536316005812211</v>
       </c>
-      <c r="L78" s="10">
+      <c r="L78" s="19">
         <f t="shared" si="3"/>
         <v>-0.20587365769864382</v>
       </c>
@@ -18497,7 +18567,7 @@
       <c r="K79" s="10">
         <v>69.021440028975547</v>
       </c>
-      <c r="L79" s="10">
+      <c r="L79" s="19">
         <f t="shared" si="3"/>
         <v>-0.44146621433908068</v>
       </c>
@@ -18537,7 +18607,7 @@
       <c r="K80" s="10">
         <v>71.467344717337483</v>
       </c>
-      <c r="L80" s="10">
+      <c r="L80" s="19">
         <f t="shared" si="3"/>
         <v>0.10526800694555072</v>
       </c>
@@ -18577,7 +18647,7 @@
       <c r="K81" s="10">
         <v>50.496362770611753</v>
       </c>
-      <c r="L81" s="10">
+      <c r="L81" s="19">
         <f t="shared" si="3"/>
         <v>-0.20774849152029889</v>
       </c>
@@ -18617,7 +18687,7 @@
       <c r="K82" s="10">
         <v>55.229668567997003</v>
       </c>
-      <c r="L82" s="10">
+      <c r="L82" s="19">
         <f t="shared" si="3"/>
         <v>0.30459999932216231</v>
       </c>
@@ -18657,7 +18727,7 @@
       <c r="K83" s="10">
         <v>75.139220764041383</v>
       </c>
-      <c r="L83" s="10">
+      <c r="L83" s="19">
         <f t="shared" si="3"/>
         <v>-0.21872366755063258</v>
       </c>
@@ -18697,7 +18767,7 @@
       <c r="K84" s="10">
         <v>58.387484404345059</v>
       </c>
-      <c r="L84" s="10">
+      <c r="L84" s="19">
         <f t="shared" si="3"/>
         <v>-8.6703956973141066E-2</v>
       </c>
@@ -18737,7 +18807,7 @@
       <c r="K85" s="10">
         <v>74.040278246155765</v>
       </c>
-      <c r="L85" s="10">
+      <c r="L85" s="19">
         <f t="shared" si="3"/>
         <v>0.10536302394960867</v>
       </c>
@@ -18777,7 +18847,7 @@
       <c r="K86" s="10">
         <v>62.164148383994373</v>
       </c>
-      <c r="L86" s="10">
+      <c r="L86" s="19">
         <f t="shared" si="3"/>
         <v>0.46668260186807159</v>
       </c>
@@ -18817,7 +18887,7 @@
       <c r="K87" s="10">
         <v>70.447213919214661</v>
       </c>
-      <c r="L87" s="10">
+      <c r="L87" s="19">
         <f t="shared" si="3"/>
         <v>0.17844626387040172</v>
       </c>
@@ -18857,7 +18927,7 @@
       <c r="K88" s="10">
         <v>74.676338659280532</v>
       </c>
-      <c r="L88" s="10">
+      <c r="L88" s="19">
         <f t="shared" si="3"/>
         <v>5.880551567970374E-2</v>
       </c>
@@ -18897,7 +18967,7 @@
       <c r="K89" s="10">
         <v>57.328488167363666</v>
       </c>
-      <c r="L89" s="10">
+      <c r="L89" s="19">
         <f t="shared" si="3"/>
         <v>0.32617091515143604</v>
       </c>
@@ -18937,7 +19007,7 @@
       <c r="K90" s="10">
         <v>82.926777823027351</v>
       </c>
-      <c r="L90" s="10">
+      <c r="L90" s="19">
         <f t="shared" si="3"/>
         <v>0.13127591525402371</v>
       </c>
@@ -18977,7 +19047,7 @@
       <c r="K91" s="10">
         <v>56.330836013124284</v>
       </c>
-      <c r="L91" s="10">
+      <c r="L91" s="19">
         <f t="shared" si="3"/>
         <v>-7.4536258712445277E-2</v>
       </c>
@@ -19017,7 +19087,7 @@
       <c r="K92" s="10">
         <v>63.152843166400672</v>
       </c>
-      <c r="L92" s="10">
+      <c r="L92" s="19">
         <f t="shared" si="3"/>
         <v>0.39303845057149678</v>
       </c>
@@ -19057,7 +19127,7 @@
       <c r="K93" s="10">
         <v>44.173359780366653</v>
       </c>
-      <c r="L93" s="10">
+      <c r="L93" s="19">
         <f t="shared" si="3"/>
         <v>0.22625021087162875</v>
       </c>
@@ -19097,7 +19167,7 @@
       <c r="K94" s="10">
         <v>69.09468937538611</v>
       </c>
-      <c r="L94" s="10">
+      <c r="L94" s="19">
         <f t="shared" si="3"/>
         <v>-0.28387290890182271</v>
       </c>
@@ -19137,7 +19207,7 @@
       <c r="K95" s="10">
         <v>72.946618726802328</v>
       </c>
-      <c r="L95" s="10">
+      <c r="L95" s="19">
         <f t="shared" si="3"/>
         <v>0.20459297879550334</v>
       </c>
@@ -19177,7 +19247,7 @@
       <c r="K96" s="10">
         <v>69.469947459315094</v>
       </c>
-      <c r="L96" s="10">
+      <c r="L96" s="19">
         <f t="shared" si="3"/>
         <v>3.1504322514844467E-2</v>
       </c>
@@ -19217,7 +19287,7 @@
       <c r="K97" s="10">
         <v>56.323052699867915</v>
       </c>
-      <c r="L97" s="10">
+      <c r="L97" s="19">
         <f t="shared" si="3"/>
         <v>4.7170121933921838E-4</v>
       </c>
@@ -19257,7 +19327,7 @@
       <c r="K98" s="10">
         <v>41.974862158849767</v>
       </c>
-      <c r="L98" s="10">
+      <c r="L98" s="19">
         <f t="shared" si="3"/>
         <v>0.33555903246767138</v>
       </c>
@@ -19297,7 +19367,7 @@
       <c r="K99" s="10">
         <v>44.962229438992097</v>
       </c>
-      <c r="L99" s="10">
+      <c r="L99" s="19">
         <f t="shared" si="3"/>
         <v>0.31988738230487651</v>
       </c>
@@ -19337,7 +19407,7 @@
       <c r="K100" s="10">
         <v>37.798178950335576</v>
       </c>
-      <c r="L100" s="10">
+      <c r="L100" s="19">
         <f t="shared" si="3"/>
         <v>-0.38225941672837199</v>
       </c>
@@ -19377,7 +19447,7 @@
       <c r="K101" s="10">
         <v>68.460251596471679</v>
       </c>
-      <c r="L101" s="10">
+      <c r="L101" s="19">
         <f t="shared" si="3"/>
         <v>-0.29179753354587762</v>
       </c>
@@ -19417,7 +19487,7 @@
       <c r="K102" s="10">
         <v>65.70356446097523</v>
       </c>
-      <c r="L102" s="10">
+      <c r="L102" s="19">
         <f t="shared" si="3"/>
         <v>-0.22755336346636462</v>
       </c>
@@ -19457,7 +19527,7 @@
       <c r="K103" s="10">
         <v>66.213667550072984</v>
       </c>
-      <c r="L103" s="10">
+      <c r="L103" s="19">
         <f t="shared" si="3"/>
         <v>-3.9123226497980584E-2</v>
       </c>
@@ -19497,7 +19567,7 @@
       <c r="K104" s="10">
         <v>65.788974489430842</v>
       </c>
-      <c r="L104" s="10">
+      <c r="L104" s="19">
         <f t="shared" si="3"/>
         <v>0.28971226113350662</v>
       </c>
@@ -19537,7 +19607,7 @@
       <c r="K105" s="10">
         <v>78.830161121302538</v>
       </c>
-      <c r="L105" s="10">
+      <c r="L105" s="19">
         <f t="shared" si="3"/>
         <v>0.18878040910176783</v>
       </c>
@@ -19577,7 +19647,7 @@
       <c r="K106" s="10">
         <v>65.083754207393383</v>
       </c>
-      <c r="L106" s="10">
+      <c r="L106" s="19">
         <f t="shared" si="3"/>
         <v>0.12707053991223585</v>
       </c>
@@ -19617,7 +19687,7 @@
       <c r="K107" s="10">
         <v>55.264758647687017</v>
       </c>
-      <c r="L107" s="10">
+      <c r="L107" s="19">
         <f t="shared" si="3"/>
         <v>0.26581190699681445</v>
       </c>
@@ -19657,7 +19727,7 @@
       <c r="K108" s="10">
         <v>52.723327174933317</v>
       </c>
-      <c r="L108" s="10">
+      <c r="L108" s="19">
         <f t="shared" si="3"/>
         <v>0.15747026766765782</v>
       </c>
@@ -19697,7 +19767,7 @@
       <c r="K109" s="10">
         <v>75.848904583590468</v>
       </c>
-      <c r="L109" s="10">
+      <c r="L109" s="19">
         <f t="shared" si="3"/>
         <v>5.6180688164710807E-2</v>
       </c>
@@ -19737,7 +19807,7 @@
       <c r="K110" s="10">
         <v>51.278326455349131</v>
       </c>
-      <c r="L110" s="10">
+      <c r="L110" s="19">
         <f t="shared" si="3"/>
         <v>0.39852670503534476</v>
       </c>
@@ -19777,7 +19847,7 @@
       <c r="K111" s="10">
         <v>57.909108469652679</v>
       </c>
-      <c r="L111" s="10">
+      <c r="L111" s="19">
         <f t="shared" si="3"/>
         <v>-7.7094858452553247E-2</v>
       </c>
@@ -19817,7 +19887,7 @@
       <c r="K112" s="10">
         <v>61.750517406739192</v>
       </c>
-      <c r="L112" s="10">
+      <c r="L112" s="19">
         <f t="shared" si="3"/>
         <v>-8.6196563021084971E-2</v>
       </c>
@@ -19857,7 +19927,7 @@
       <c r="K113" s="10">
         <v>52.661575232504951</v>
       </c>
-      <c r="L113" s="10">
+      <c r="L113" s="19">
         <f t="shared" si="3"/>
         <v>-1.5260191145371214E-2</v>
       </c>
@@ -19897,7 +19967,7 @@
       <c r="K114" s="10">
         <v>53.118250871076597</v>
       </c>
-      <c r="L114" s="10">
+      <c r="L114" s="19">
         <f t="shared" si="3"/>
         <v>0.32736000338447518</v>
       </c>
@@ -19937,7 +20007,7 @@
       <c r="K115" s="10">
         <v>50.104043997600584</v>
       </c>
-      <c r="L115" s="10">
+      <c r="L115" s="19">
         <f t="shared" si="3"/>
         <v>0.22263456608639615</v>
       </c>
@@ -19977,7 +20047,7 @@
       <c r="K116" s="10">
         <v>50.177676148596895</v>
       </c>
-      <c r="L116" s="10">
+      <c r="L116" s="19">
         <f t="shared" si="3"/>
         <v>0.30593492860402854</v>
       </c>
@@ -20017,7 +20087,7 @@
       <c r="K117" s="10">
         <v>65.073504542370074</v>
       </c>
-      <c r="L117" s="10">
+      <c r="L117" s="19">
         <f t="shared" si="3"/>
         <v>-0.11398962250258773</v>
       </c>
@@ -20057,7 +20127,7 @@
       <c r="K118" s="10">
         <v>44.254182598587626</v>
       </c>
-      <c r="L118" s="10">
+      <c r="L118" s="19">
         <f t="shared" si="3"/>
         <v>0.32269429290876611</v>
       </c>
@@ -20097,7 +20167,7 @@
       <c r="K119" s="10">
         <v>47.422942867393644</v>
       </c>
-      <c r="L119" s="10">
+      <c r="L119" s="19">
         <f t="shared" si="3"/>
         <v>0.28657291640915211</v>
       </c>
@@ -20137,7 +20207,7 @@
       <c r="K120" s="10">
         <v>46.359571574198242</v>
       </c>
-      <c r="L120" s="10">
+      <c r="L120" s="19">
         <f t="shared" si="3"/>
         <v>0.25805810309453803</v>
       </c>
@@ -20177,7 +20247,7 @@
       <c r="K121" s="10">
         <v>33.405873873919091</v>
       </c>
-      <c r="L121" s="10">
+      <c r="L121" s="19">
         <f t="shared" si="3"/>
         <v>0.6874622633042955</v>
       </c>
@@ -20217,7 +20287,7 @@
       <c r="K122" s="10">
         <v>51.281080608690978</v>
       </c>
-      <c r="L122" s="10">
+      <c r="L122" s="19">
         <f t="shared" si="3"/>
         <v>0.30075082826020128</v>
       </c>
@@ -20257,7 +20327,7 @@
       <c r="K123" s="10">
         <v>40.551750201988128</v>
       </c>
-      <c r="L123" s="10">
+      <c r="L123" s="19">
         <f t="shared" si="3"/>
         <v>0.57069897861937646</v>
       </c>
@@ -20297,7 +20367,7 @@
       <c r="K124" s="10">
         <v>44.129844927173707</v>
       </c>
-      <c r="L124" s="10">
+      <c r="L124" s="19">
         <f t="shared" si="3"/>
         <v>0.44180225821123742</v>
       </c>
@@ -20337,7 +20407,7 @@
       <c r="K125" s="10">
         <v>53.882588406027168</v>
       </c>
-      <c r="L125" s="10">
+      <c r="L125" s="19">
         <f t="shared" si="3"/>
         <v>0.47465482322818098</v>
       </c>
@@ -20377,7 +20447,7 @@
       <c r="K126" s="10">
         <v>49.886350075701394</v>
       </c>
-      <c r="L126" s="10">
+      <c r="L126" s="19">
         <f t="shared" si="3"/>
         <v>0.45932966474306947</v>
       </c>
@@ -20417,7 +20487,7 @@
       <c r="K127" s="10">
         <v>44.405800463275128</v>
       </c>
-      <c r="L127" s="10">
+      <c r="L127" s="19">
         <f t="shared" si="3"/>
         <v>0.52078824052690198</v>
       </c>
@@ -20457,7 +20527,7 @@
       <c r="K128" s="10">
         <v>43.976952126529874</v>
       </c>
-      <c r="L128" s="10">
+      <c r="L128" s="19">
         <f t="shared" si="3"/>
         <v>0.67759820478527222</v>
       </c>
@@ -20497,7 +20567,7 @@
       <c r="K129" s="10">
         <v>57.854397526301433</v>
       </c>
-      <c r="L129" s="10">
+      <c r="L129" s="19">
         <f t="shared" si="3"/>
         <v>0.58355685296748805</v>
       </c>
@@ -20537,7 +20607,7 @@
       <c r="K130" s="10">
         <v>45.357327933111691</v>
       </c>
-      <c r="L130" s="10">
+      <c r="L130" s="19">
         <f t="shared" si="3"/>
         <v>0.6700959917757523</v>
       </c>
@@ -20592,7 +20662,7 @@
       <c r="K131" s="10">
         <v>49.214072926201013</v>
       </c>
-      <c r="L131" s="10">
+      <c r="L131" s="19">
         <f t="shared" ref="L131:L194" si="5">IF(OR(K131=0,I131=G131,J131=F131),"",0.4*((3*(E131-H131)/K131)/(1+ABS(3*(E131-H131)/K131)))+0.45*((I131+G131-2*H131)/(I131-G131))+0.15*((J131+F131-2*H131)/(J131-F131)))</f>
         <v>0.47324766758802955</v>
       </c>
@@ -20632,7 +20702,7 @@
       <c r="K132" s="10">
         <v>53.491406900967732</v>
       </c>
-      <c r="L132" s="10">
+      <c r="L132" s="19">
         <f t="shared" si="5"/>
         <v>0.31428831447709799</v>
       </c>
@@ -20672,7 +20742,7 @@
       <c r="K133" s="10">
         <v>55.286482576750558</v>
       </c>
-      <c r="L133" s="10">
+      <c r="L133" s="19">
         <f t="shared" si="5"/>
         <v>0.42526572011998676</v>
       </c>
@@ -20712,7 +20782,7 @@
       <c r="K134" s="10">
         <v>55.143723549589758</v>
       </c>
-      <c r="L134" s="10">
+      <c r="L134" s="19">
         <f t="shared" si="5"/>
         <v>0.23561109941937339</v>
       </c>
@@ -20752,7 +20822,7 @@
       <c r="K135" s="10">
         <v>51.012811516083978</v>
       </c>
-      <c r="L135" s="10">
+      <c r="L135" s="19">
         <f t="shared" si="5"/>
         <v>-0.49637321111333166</v>
       </c>
@@ -20792,7 +20862,7 @@
       <c r="K136" s="10">
         <v>64.584992254313974</v>
       </c>
-      <c r="L136" s="10">
+      <c r="L136" s="19">
         <f t="shared" si="5"/>
         <v>-0.26135660896508051</v>
       </c>
@@ -20832,7 +20902,7 @@
       <c r="K137" s="10">
         <v>51.036330889936345</v>
       </c>
-      <c r="L137" s="10">
+      <c r="L137" s="19">
         <f t="shared" si="5"/>
         <v>-0.37611241280038199</v>
       </c>
@@ -20872,7 +20942,7 @@
       <c r="K138" s="10">
         <v>49.006860617093729</v>
       </c>
-      <c r="L138" s="10">
+      <c r="L138" s="19">
         <f t="shared" si="5"/>
         <v>-0.16549734836509639</v>
       </c>
@@ -20912,7 +20982,7 @@
       <c r="K139" s="10">
         <v>33.08758938678627</v>
       </c>
-      <c r="L139" s="10">
+      <c r="L139" s="19">
         <f t="shared" si="5"/>
         <v>-0.10805799675817862</v>
       </c>
@@ -20952,7 +21022,7 @@
       <c r="K140" s="10">
         <v>42.688334209137516</v>
       </c>
-      <c r="L140" s="10">
+      <c r="L140" s="19">
         <f t="shared" si="5"/>
         <v>0.52958743513001483</v>
       </c>
@@ -20992,7 +21062,7 @@
       <c r="K141" s="10">
         <v>49.836210913235156</v>
       </c>
-      <c r="L141" s="10">
+      <c r="L141" s="19">
         <f t="shared" si="5"/>
         <v>0.39036481976131682</v>
       </c>
@@ -21032,7 +21102,7 @@
       <c r="K142" s="10">
         <v>46.376897362766087</v>
       </c>
-      <c r="L142" s="10">
+      <c r="L142" s="19">
         <f t="shared" si="5"/>
         <v>-1.5930230002458197E-2</v>
       </c>
@@ -21072,7 +21142,7 @@
       <c r="K143" s="10">
         <v>48.797982331083887</v>
       </c>
-      <c r="L143" s="10">
+      <c r="L143" s="19">
         <f t="shared" si="5"/>
         <v>0.44664210397348236</v>
       </c>
@@ -21112,7 +21182,7 @@
       <c r="K144" s="10">
         <v>50.995285896575474</v>
       </c>
-      <c r="L144" s="10">
+      <c r="L144" s="19">
         <f t="shared" si="5"/>
         <v>0.12049226338537306</v>
       </c>
@@ -21152,7 +21222,7 @@
       <c r="K145" s="10">
         <v>50.632752300623871</v>
       </c>
-      <c r="L145" s="10">
+      <c r="L145" s="19">
         <f t="shared" si="5"/>
         <v>-7.9245859822572817E-2</v>
       </c>
@@ -21192,7 +21262,7 @@
       <c r="K146" s="10">
         <v>49.159815906896966</v>
       </c>
-      <c r="L146" s="10">
+      <c r="L146" s="19">
         <f t="shared" si="5"/>
         <v>-0.26490222619398596</v>
       </c>
@@ -21232,7 +21302,7 @@
       <c r="K147" s="10">
         <v>67.93322071407249</v>
       </c>
-      <c r="L147" s="10">
+      <c r="L147" s="19">
         <f t="shared" si="5"/>
         <v>-0.14307269615380569</v>
       </c>
@@ -21272,7 +21342,7 @@
       <c r="K148" s="10">
         <v>59.144140747470985</v>
       </c>
-      <c r="L148" s="10">
+      <c r="L148" s="19">
         <f t="shared" si="5"/>
         <v>-0.28663506711370368</v>
       </c>
@@ -21312,7 +21382,7 @@
       <c r="K149" s="10">
         <v>48.417328037810883</v>
       </c>
-      <c r="L149" s="10">
+      <c r="L149" s="19">
         <f t="shared" si="5"/>
         <v>-0.30324281718316309</v>
       </c>
@@ -21352,7 +21422,7 @@
       <c r="K150" s="10">
         <v>65.507189828231219</v>
       </c>
-      <c r="L150" s="10">
+      <c r="L150" s="19">
         <f t="shared" si="5"/>
         <v>-0.2266206762829614</v>
       </c>
@@ -21392,7 +21462,7 @@
       <c r="K151" s="10">
         <v>67.77459535800439</v>
       </c>
-      <c r="L151" s="10">
+      <c r="L151" s="19">
         <f t="shared" si="5"/>
         <v>-0.28216291426848084</v>
       </c>
@@ -21432,7 +21502,7 @@
       <c r="K152" s="10">
         <v>67.144419826628891</v>
       </c>
-      <c r="L152" s="10">
+      <c r="L152" s="19">
         <f t="shared" si="5"/>
         <v>-0.27336549624012574</v>
       </c>
@@ -21472,7 +21542,7 @@
       <c r="K153" s="10">
         <v>50.709106035336958</v>
       </c>
-      <c r="L153" s="10">
+      <c r="L153" s="19">
         <f t="shared" si="5"/>
         <v>0.12403403170772412</v>
       </c>
@@ -21512,7 +21582,7 @@
       <c r="K154" s="10">
         <v>45.673803993182069</v>
       </c>
-      <c r="L154" s="10">
+      <c r="L154" s="19">
         <f t="shared" si="5"/>
         <v>5.9895876529999018E-3</v>
       </c>
@@ -21552,7 +21622,7 @@
       <c r="K155" s="10">
         <v>56.578290137928242</v>
       </c>
-      <c r="L155" s="10">
+      <c r="L155" s="19">
         <f t="shared" si="5"/>
         <v>-0.25502187711413227</v>
       </c>
@@ -21592,7 +21662,7 @@
       <c r="K156" s="10">
         <v>65.158129608233793</v>
       </c>
-      <c r="L156" s="10">
+      <c r="L156" s="19">
         <f t="shared" si="5"/>
         <v>7.4271281127367764E-3</v>
       </c>
@@ -21632,7 +21702,7 @@
       <c r="K157" s="10">
         <v>44.471505975736868</v>
       </c>
-      <c r="L157" s="10">
+      <c r="L157" s="19">
         <f t="shared" si="5"/>
         <v>-1.3859860775056125E-2</v>
       </c>
@@ -21672,7 +21742,7 @@
       <c r="K158" s="10">
         <v>52.627079222161107</v>
       </c>
-      <c r="L158" s="10">
+      <c r="L158" s="19">
         <f t="shared" si="5"/>
         <v>-0.17403991641595026</v>
       </c>
@@ -21712,7 +21782,7 @@
       <c r="K159" s="10">
         <v>66.261051954921754</v>
       </c>
-      <c r="L159" s="10">
+      <c r="L159" s="19">
         <f t="shared" si="5"/>
         <v>-0.24106851260952444</v>
       </c>
@@ -21752,7 +21822,7 @@
       <c r="K160" s="10">
         <v>54.893058424976317</v>
       </c>
-      <c r="L160" s="10">
+      <c r="L160" s="19">
         <f t="shared" si="5"/>
         <v>0.16465486148018726</v>
       </c>
@@ -21792,7 +21862,7 @@
       <c r="K161" s="10">
         <v>64.161205849108597</v>
       </c>
-      <c r="L161" s="10">
+      <c r="L161" s="19">
         <f t="shared" si="5"/>
         <v>0.16362769376236913</v>
       </c>
@@ -21832,7 +21902,7 @@
       <c r="K162" s="10">
         <v>52.811235830415114</v>
       </c>
-      <c r="L162" s="10">
+      <c r="L162" s="19">
         <f t="shared" si="5"/>
         <v>0.26288423163491698</v>
       </c>
@@ -21872,7 +21942,7 @@
       <c r="K163" s="10">
         <v>57.645867319279404</v>
       </c>
-      <c r="L163" s="10">
+      <c r="L163" s="19">
         <f t="shared" si="5"/>
         <v>-0.28457008156585545</v>
       </c>
@@ -21912,7 +21982,7 @@
       <c r="K164" s="10">
         <v>61.365403956693434</v>
       </c>
-      <c r="L164" s="10">
+      <c r="L164" s="19">
         <f t="shared" si="5"/>
         <v>-0.25195202439372982</v>
       </c>
@@ -21952,7 +22022,7 @@
       <c r="K165" s="10">
         <v>44.582988427682338</v>
       </c>
-      <c r="L165" s="10">
+      <c r="L165" s="19">
         <f t="shared" si="5"/>
         <v>0.1123456605953624</v>
       </c>
@@ -21992,7 +22062,7 @@
       <c r="K166" s="10">
         <v>54.166951121047973</v>
       </c>
-      <c r="L166" s="10">
+      <c r="L166" s="19">
         <f t="shared" si="5"/>
         <v>-7.8600567570467558E-3</v>
       </c>
@@ -22032,7 +22102,7 @@
       <c r="K167" s="10">
         <v>76.385981144531414</v>
       </c>
-      <c r="L167" s="10">
+      <c r="L167" s="19">
         <f t="shared" si="5"/>
         <v>-0.19688269908637526</v>
       </c>
@@ -22072,7 +22142,7 @@
       <c r="K168" s="10">
         <v>71.141667275747665</v>
       </c>
-      <c r="L168" s="10">
+      <c r="L168" s="19">
         <f t="shared" si="5"/>
         <v>0.18457521752688821</v>
       </c>
@@ -22112,7 +22182,7 @@
       <c r="K169" s="10">
         <v>81.41339889263179</v>
       </c>
-      <c r="L169" s="10">
+      <c r="L169" s="19">
         <f t="shared" si="5"/>
         <v>0.15022433932698262</v>
       </c>
@@ -22152,7 +22222,7 @@
       <c r="K170" s="10">
         <v>63.355150657102897</v>
       </c>
-      <c r="L170" s="10">
+      <c r="L170" s="19">
         <f t="shared" si="5"/>
         <v>-0.15143005875367724</v>
       </c>
@@ -22192,7 +22262,7 @@
       <c r="K171" s="10">
         <v>63.586872250336747</v>
       </c>
-      <c r="L171" s="10">
+      <c r="L171" s="19">
         <f t="shared" si="5"/>
         <v>-0.17924040044122375</v>
       </c>
@@ -22232,7 +22302,7 @@
       <c r="K172" s="10">
         <v>53.318827599106207</v>
       </c>
-      <c r="L172" s="10">
+      <c r="L172" s="19">
         <f t="shared" si="5"/>
         <v>1.2040439798075762E-2</v>
       </c>
@@ -22272,7 +22342,7 @@
       <c r="K173" s="10">
         <v>49.477873007591704</v>
       </c>
-      <c r="L173" s="10">
+      <c r="L173" s="19">
         <f t="shared" si="5"/>
         <v>0.13676552944341455</v>
       </c>
@@ -22312,7 +22382,7 @@
       <c r="K174" s="10">
         <v>71.403538470599969</v>
       </c>
-      <c r="L174" s="10">
+      <c r="L174" s="19">
         <f t="shared" si="5"/>
         <v>-0.1485825838520565</v>
       </c>
@@ -22352,7 +22422,7 @@
       <c r="K175" s="10">
         <v>61.732827908030352</v>
       </c>
-      <c r="L175" s="10">
+      <c r="L175" s="19">
         <f t="shared" si="5"/>
         <v>-0.23578113504672399</v>
       </c>
@@ -22392,7 +22462,7 @@
       <c r="K176" s="10">
         <v>52.229993511604249</v>
       </c>
-      <c r="L176" s="10">
+      <c r="L176" s="19">
         <f t="shared" si="5"/>
         <v>-0.32342752571685818</v>
       </c>
@@ -22432,7 +22502,7 @@
       <c r="K177" s="10">
         <v>64.598575021541549</v>
       </c>
-      <c r="L177" s="10">
+      <c r="L177" s="19">
         <f t="shared" si="5"/>
         <v>-0.23529832984745655</v>
       </c>
@@ -22472,7 +22542,7 @@
       <c r="K178" s="10">
         <v>61.131436014016572</v>
       </c>
-      <c r="L178" s="10">
+      <c r="L178" s="19">
         <f t="shared" si="5"/>
         <v>-0.20676857957398112</v>
       </c>
@@ -22512,7 +22582,7 @@
       <c r="K179" s="10">
         <v>53.907207534999003</v>
       </c>
-      <c r="L179" s="10">
+      <c r="L179" s="19">
         <f t="shared" si="5"/>
         <v>0.24086726576623108</v>
       </c>
@@ -22552,7 +22622,7 @@
       <c r="K180" s="10">
         <v>44.756939056977522</v>
       </c>
-      <c r="L180" s="10">
+      <c r="L180" s="19">
         <f t="shared" si="5"/>
         <v>-0.40475640291179715</v>
       </c>
@@ -22592,7 +22662,7 @@
       <c r="K181" s="10">
         <v>56.685418081441156</v>
       </c>
-      <c r="L181" s="10">
+      <c r="L181" s="19">
         <f t="shared" si="5"/>
         <v>-4.3707023641593457E-2</v>
       </c>
@@ -22632,7 +22702,7 @@
       <c r="K182" s="10">
         <v>49.326994067650219</v>
       </c>
-      <c r="L182" s="10">
+      <c r="L182" s="19">
         <f t="shared" si="5"/>
         <v>8.7158154618809117E-2</v>
       </c>
@@ -22672,7 +22742,7 @@
       <c r="K183" s="10">
         <v>56.94789248873581</v>
       </c>
-      <c r="L183" s="10">
+      <c r="L183" s="19">
         <f t="shared" si="5"/>
         <v>0.12007772986091401</v>
       </c>
@@ -22712,7 +22782,7 @@
       <c r="K184" s="10">
         <v>53.684534257154517</v>
       </c>
-      <c r="L184" s="10">
+      <c r="L184" s="19">
         <f t="shared" si="5"/>
         <v>-0.29416493840333169</v>
       </c>
@@ -22752,7 +22822,7 @@
       <c r="K185" s="10">
         <v>65.364947708147739</v>
       </c>
-      <c r="L185" s="10">
+      <c r="L185" s="19">
         <f t="shared" si="5"/>
         <v>-0.28384366328965066</v>
       </c>
@@ -22792,7 +22862,7 @@
       <c r="K186" s="10">
         <v>53.704634029690361</v>
       </c>
-      <c r="L186" s="10">
+      <c r="L186" s="19">
         <f t="shared" si="5"/>
         <v>-9.3767083490706241E-2</v>
       </c>
@@ -22832,7 +22902,7 @@
       <c r="K187" s="10">
         <v>54.771375546492628</v>
       </c>
-      <c r="L187" s="10">
+      <c r="L187" s="19">
         <f t="shared" si="5"/>
         <v>-0.26471599008312879</v>
       </c>
@@ -22872,7 +22942,7 @@
       <c r="K188" s="10">
         <v>57.833752535015343</v>
       </c>
-      <c r="L188" s="10">
+      <c r="L188" s="19">
         <f t="shared" si="5"/>
         <v>-0.40205645146440933</v>
       </c>
@@ -22912,7 +22982,7 @@
       <c r="K189" s="10">
         <v>79.252584956089748</v>
       </c>
-      <c r="L189" s="10">
+      <c r="L189" s="19">
         <f t="shared" si="5"/>
         <v>-0.23415252580020307</v>
       </c>
@@ -22952,7 +23022,7 @@
       <c r="K190" s="10">
         <v>66.112908932661171</v>
       </c>
-      <c r="L190" s="10">
+      <c r="L190" s="19">
         <f t="shared" si="5"/>
         <v>-0.28745430193981458</v>
       </c>
@@ -22992,7 +23062,7 @@
       <c r="K191" s="10">
         <v>68.480905740352668</v>
       </c>
-      <c r="L191" s="10">
+      <c r="L191" s="19">
         <f t="shared" si="5"/>
         <v>-0.25388429027105947</v>
       </c>
@@ -23032,7 +23102,7 @@
       <c r="K192" s="10">
         <v>68.820680112015253</v>
       </c>
-      <c r="L192" s="10">
+      <c r="L192" s="19">
         <f t="shared" si="5"/>
         <v>-0.15691934530650653</v>
       </c>
@@ -23072,7 +23142,7 @@
       <c r="K193" s="10">
         <v>59.032374376182737</v>
       </c>
-      <c r="L193" s="10">
+      <c r="L193" s="19">
         <f t="shared" si="5"/>
         <v>-0.30429978404224434</v>
       </c>
@@ -23112,7 +23182,7 @@
       <c r="K194" s="10">
         <v>60.995325657513426</v>
       </c>
-      <c r="L194" s="10">
+      <c r="L194" s="19">
         <f t="shared" si="5"/>
         <v>-0.11066604830544244</v>
       </c>
@@ -23167,7 +23237,7 @@
       <c r="K195" s="10">
         <v>61.01651833892263</v>
       </c>
-      <c r="L195" s="10">
+      <c r="L195" s="19">
         <f t="shared" ref="L195:L258" si="7">IF(OR(K195=0,I195=G195,J195=F195),"",0.4*((3*(E195-H195)/K195)/(1+ABS(3*(E195-H195)/K195)))+0.45*((I195+G195-2*H195)/(I195-G195))+0.15*((J195+F195-2*H195)/(J195-F195)))</f>
         <v>0.17307992738376682</v>
       </c>
@@ -23207,7 +23277,7 @@
       <c r="K196" s="10">
         <v>68.948409164893818</v>
       </c>
-      <c r="L196" s="10">
+      <c r="L196" s="19">
         <f t="shared" si="7"/>
         <v>-0.29607922048625773</v>
       </c>
@@ -23247,7 +23317,7 @@
       <c r="K197" s="10">
         <v>55.495282272042076</v>
       </c>
-      <c r="L197" s="10">
+      <c r="L197" s="19">
         <f t="shared" si="7"/>
         <v>-0.60057149366608453</v>
       </c>
@@ -23287,7 +23357,7 @@
       <c r="K198" s="10">
         <v>57.756350696573961</v>
       </c>
-      <c r="L198" s="10">
+      <c r="L198" s="19">
         <f t="shared" si="7"/>
         <v>-0.19148179837387846</v>
       </c>
@@ -23327,7 +23397,7 @@
       <c r="K199" s="10">
         <v>46.374631010759359</v>
       </c>
-      <c r="L199" s="10">
+      <c r="L199" s="19">
         <f t="shared" si="7"/>
         <v>-0.52420998637465732</v>
       </c>
@@ -23367,7 +23437,7 @@
       <c r="K200" s="10">
         <v>50.035497779699199</v>
       </c>
-      <c r="L200" s="10">
+      <c r="L200" s="19">
         <f t="shared" si="7"/>
         <v>-0.41596973737349352</v>
       </c>
@@ -23407,7 +23477,7 @@
       <c r="K201" s="10">
         <v>45.14920394961522</v>
       </c>
-      <c r="L201" s="10">
+      <c r="L201" s="19">
         <f t="shared" si="7"/>
         <v>-0.52318947108151814</v>
       </c>
@@ -23447,7 +23517,7 @@
       <c r="K202" s="10">
         <v>42.330808834030208</v>
       </c>
-      <c r="L202" s="10">
+      <c r="L202" s="19">
         <f t="shared" si="7"/>
         <v>-1.8375201091164008E-2</v>
       </c>
@@ -23487,7 +23557,7 @@
       <c r="K203" s="10">
         <v>46.031147244235598</v>
       </c>
-      <c r="L203" s="10">
+      <c r="L203" s="19">
         <f t="shared" si="7"/>
         <v>2.8543153292795942E-2</v>
       </c>
@@ -23527,7 +23597,7 @@
       <c r="K204" s="10">
         <v>73.783147168729855</v>
       </c>
-      <c r="L204" s="10">
+      <c r="L204" s="19">
         <f t="shared" si="7"/>
         <v>-9.0789095374690099E-2</v>
       </c>
@@ -23567,7 +23637,7 @@
       <c r="K205" s="10">
         <v>67.420059029224618</v>
       </c>
-      <c r="L205" s="10">
+      <c r="L205" s="19">
         <f t="shared" si="7"/>
         <v>-0.17930699153329599</v>
       </c>
@@ -23607,7 +23677,7 @@
       <c r="K206" s="10">
         <v>65.236302377809508</v>
       </c>
-      <c r="L206" s="10">
+      <c r="L206" s="19">
         <f t="shared" si="7"/>
         <v>0.13921617684970947</v>
       </c>
@@ -23647,7 +23717,7 @@
       <c r="K207" s="10">
         <v>45.438603264918548</v>
       </c>
-      <c r="L207" s="10">
+      <c r="L207" s="19">
         <f t="shared" si="7"/>
         <v>0.40269413487252531</v>
       </c>
@@ -23687,7 +23757,7 @@
       <c r="K208" s="10">
         <v>55.842613656597415</v>
       </c>
-      <c r="L208" s="10">
+      <c r="L208" s="19">
         <f t="shared" si="7"/>
         <v>2.9017620657423498E-2</v>
       </c>
@@ -23727,7 +23797,7 @@
       <c r="K209" s="10">
         <v>50.566226976684703</v>
       </c>
-      <c r="L209" s="10">
+      <c r="L209" s="19">
         <f t="shared" si="7"/>
         <v>0.17821122596209799</v>
       </c>
@@ -23767,7 +23837,7 @@
       <c r="K210" s="10">
         <v>60.167993983512531</v>
       </c>
-      <c r="L210" s="10">
+      <c r="L210" s="19">
         <f t="shared" si="7"/>
         <v>-0.14002015561935127</v>
       </c>
@@ -23807,7 +23877,7 @@
       <c r="K211" s="10">
         <v>59.384867216709665</v>
       </c>
-      <c r="L211" s="10">
+      <c r="L211" s="19">
         <f t="shared" si="7"/>
         <v>0.13406987723758013</v>
       </c>
@@ -23847,7 +23917,7 @@
       <c r="K212" s="10">
         <v>51.877165703250242</v>
       </c>
-      <c r="L212" s="10">
+      <c r="L212" s="19">
         <f t="shared" si="7"/>
         <v>-0.30162511947508736</v>
       </c>
@@ -23887,7 +23957,7 @@
       <c r="K213" s="10">
         <v>60.791159694094574</v>
       </c>
-      <c r="L213" s="10">
+      <c r="L213" s="19">
         <f t="shared" si="7"/>
         <v>-0.22003054860053523</v>
       </c>
@@ -23927,7 +23997,7 @@
       <c r="K214" s="10">
         <v>52.381556868806406</v>
       </c>
-      <c r="L214" s="10">
+      <c r="L214" s="19">
         <f t="shared" si="7"/>
         <v>-3.4070546216720832E-3</v>
       </c>
@@ -23967,7 +24037,7 @@
       <c r="K215" s="10">
         <v>55.497901708236633</v>
       </c>
-      <c r="L215" s="10">
+      <c r="L215" s="19">
         <f t="shared" si="7"/>
         <v>0.10595542412076808</v>
       </c>
@@ -24007,7 +24077,7 @@
       <c r="K216" s="10">
         <v>63.648541403343927</v>
       </c>
-      <c r="L216" s="10">
+      <c r="L216" s="19">
         <f t="shared" si="7"/>
         <v>0.35874695611573826</v>
       </c>
@@ -24047,7 +24117,7 @@
       <c r="K217" s="10">
         <v>58.51627398414611</v>
       </c>
-      <c r="L217" s="10">
+      <c r="L217" s="19">
         <f t="shared" si="7"/>
         <v>1.7059873526245266E-2</v>
       </c>
@@ -24087,7 +24157,7 @@
       <c r="K218" s="10">
         <v>70.168158657672691</v>
       </c>
-      <c r="L218" s="10">
+      <c r="L218" s="19">
         <f t="shared" si="7"/>
         <v>-9.4940408559007594E-2</v>
       </c>
@@ -24127,7 +24197,7 @@
       <c r="K219" s="10">
         <v>53.947041077312385</v>
       </c>
-      <c r="L219" s="10">
+      <c r="L219" s="19">
         <f t="shared" si="7"/>
         <v>0.33230769488259038</v>
       </c>
@@ -24167,7 +24237,7 @@
       <c r="K220" s="10">
         <v>55.908131213647891</v>
       </c>
-      <c r="L220" s="10">
+      <c r="L220" s="19">
         <f t="shared" si="7"/>
         <v>-0.20880590214343267</v>
       </c>
@@ -24207,7 +24277,7 @@
       <c r="K221" s="10">
         <v>62.564187638553811</v>
       </c>
-      <c r="L221" s="10">
+      <c r="L221" s="19">
         <f t="shared" si="7"/>
         <v>3.5567442021209157E-2</v>
       </c>
@@ -24247,7 +24317,7 @@
       <c r="K222" s="10">
         <v>72.423309874299363</v>
       </c>
-      <c r="L222" s="10">
+      <c r="L222" s="19">
         <f t="shared" si="7"/>
         <v>-5.1590035431447738E-2</v>
       </c>
@@ -24287,7 +24357,7 @@
       <c r="K223" s="10">
         <v>73.388746907379783</v>
       </c>
-      <c r="L223" s="10">
+      <c r="L223" s="19">
         <f t="shared" si="7"/>
         <v>-0.10700140091731264</v>
       </c>
@@ -24327,7 +24397,7 @@
       <c r="K224" s="10">
         <v>74.427829003026858</v>
       </c>
-      <c r="L224" s="10">
+      <c r="L224" s="19">
         <f t="shared" si="7"/>
         <v>9.8089861461242919E-2</v>
       </c>
@@ -24367,7 +24437,7 @@
       <c r="K225" s="10">
         <v>65.974731715358232</v>
       </c>
-      <c r="L225" s="10">
+      <c r="L225" s="19">
         <f t="shared" si="7"/>
         <v>5.8181461810242668E-2</v>
       </c>
@@ -24407,7 +24477,7 @@
       <c r="K226" s="10">
         <v>59.692906241492011</v>
       </c>
-      <c r="L226" s="10">
+      <c r="L226" s="19">
         <f t="shared" si="7"/>
         <v>-0.10257671492022161</v>
       </c>
@@ -24447,7 +24517,7 @@
       <c r="K227" s="10">
         <v>55.007204521826623</v>
       </c>
-      <c r="L227" s="10">
+      <c r="L227" s="19">
         <f t="shared" si="7"/>
         <v>-0.31340557101239197</v>
       </c>
@@ -24487,7 +24557,7 @@
       <c r="K228" s="10">
         <v>54.037281159418455</v>
       </c>
-      <c r="L228" s="10">
+      <c r="L228" s="19">
         <f t="shared" si="7"/>
         <v>-0.26618063369899786</v>
       </c>
@@ -24527,7 +24597,7 @@
       <c r="K229" s="10">
         <v>74.053447495288836</v>
       </c>
-      <c r="L229" s="10">
+      <c r="L229" s="19">
         <f t="shared" si="7"/>
         <v>-0.271554099079027</v>
       </c>
@@ -24567,7 +24637,7 @@
       <c r="K230" s="10">
         <v>57.599139747516887</v>
       </c>
-      <c r="L230" s="10">
+      <c r="L230" s="19">
         <f t="shared" si="7"/>
         <v>-0.25270244751413989</v>
       </c>
@@ -24607,7 +24677,7 @@
       <c r="K231" s="10">
         <v>73.628931758084974</v>
       </c>
-      <c r="L231" s="10">
+      <c r="L231" s="19">
         <f t="shared" si="7"/>
         <v>-0.64959980825736607</v>
       </c>
@@ -24647,7 +24717,7 @@
       <c r="K232" s="10">
         <v>64.712269652083734</v>
       </c>
-      <c r="L232" s="10">
+      <c r="L232" s="19">
         <f t="shared" si="7"/>
         <v>-0.28257402918983521</v>
       </c>
@@ -24687,7 +24757,7 @@
       <c r="K233" s="10">
         <v>68.728127833919316</v>
       </c>
-      <c r="L233" s="10">
+      <c r="L233" s="19">
         <f t="shared" si="7"/>
         <v>-0.42155920462589291</v>
       </c>
@@ -24727,7 +24797,7 @@
       <c r="K234" s="10">
         <v>71.396578703865657</v>
       </c>
-      <c r="L234" s="10">
+      <c r="L234" s="19">
         <f t="shared" si="7"/>
         <v>-0.35584409220114005</v>
       </c>
@@ -24767,7 +24837,7 @@
       <c r="K235" s="10">
         <v>56.848732557127434</v>
       </c>
-      <c r="L235" s="10">
+      <c r="L235" s="19">
         <f t="shared" si="7"/>
         <v>-0.41787746080007254</v>
       </c>
@@ -24807,7 +24877,7 @@
       <c r="K236" s="10">
         <v>48.876462768440668</v>
       </c>
-      <c r="L236" s="10">
+      <c r="L236" s="19">
         <f t="shared" si="7"/>
         <v>-0.40070669794150765</v>
       </c>
@@ -24847,7 +24917,7 @@
       <c r="K237" s="10">
         <v>30.939366105335772</v>
       </c>
-      <c r="L237" s="10">
+      <c r="L237" s="19">
         <f t="shared" si="7"/>
         <v>-0.5122719366993026</v>
       </c>
@@ -24887,7 +24957,7 @@
       <c r="K238" s="10">
         <v>25.867679114547297</v>
       </c>
-      <c r="L238" s="10">
+      <c r="L238" s="19">
         <f t="shared" si="7"/>
         <v>-0.29281050662064834</v>
       </c>
@@ -24927,7 +24997,7 @@
       <c r="K239" s="10">
         <v>35.99596195192472</v>
       </c>
-      <c r="L239" s="10">
+      <c r="L239" s="19">
         <f t="shared" si="7"/>
         <v>-0.51669100131207624</v>
       </c>
@@ -24967,7 +25037,7 @@
       <c r="K240" s="10">
         <v>34.5248029413723</v>
       </c>
-      <c r="L240" s="10">
+      <c r="L240" s="19">
         <f t="shared" si="7"/>
         <v>-0.3812905572365885</v>
       </c>
@@ -25007,7 +25077,7 @@
       <c r="K241" s="10">
         <v>48.204614903131251</v>
       </c>
-      <c r="L241" s="10">
+      <c r="L241" s="19">
         <f t="shared" si="7"/>
         <v>-0.4394550305391311</v>
       </c>
@@ -25047,7 +25117,7 @@
       <c r="K242" s="10">
         <v>44.563550516112116</v>
       </c>
-      <c r="L242" s="10">
+      <c r="L242" s="19">
         <f t="shared" si="7"/>
         <v>-0.63821318271069161</v>
       </c>
@@ -25087,7 +25157,7 @@
       <c r="K243" s="10">
         <v>37.30092994819298</v>
       </c>
-      <c r="L243" s="10">
+      <c r="L243" s="19">
         <f t="shared" si="7"/>
         <v>-0.43951267340843647</v>
       </c>
@@ -25127,7 +25197,7 @@
       <c r="K244" s="10">
         <v>36.241942484664484</v>
       </c>
-      <c r="L244" s="10">
+      <c r="L244" s="19">
         <f t="shared" si="7"/>
         <v>-0.55378919883110023</v>
       </c>
@@ -25167,7 +25237,7 @@
       <c r="K245" s="10">
         <v>39.530799594711759</v>
       </c>
-      <c r="L245" s="10">
+      <c r="L245" s="19">
         <f t="shared" si="7"/>
         <v>-0.6206909336687092</v>
       </c>
@@ -25207,7 +25277,7 @@
       <c r="K246" s="10">
         <v>53.939404659302646</v>
       </c>
-      <c r="L246" s="10">
+      <c r="L246" s="19">
         <f t="shared" si="7"/>
         <v>-0.28851277937640823</v>
       </c>
@@ -25247,7 +25317,7 @@
       <c r="K247" s="10">
         <v>43.942750002449529</v>
       </c>
-      <c r="L247" s="10">
+      <c r="L247" s="19">
         <f t="shared" si="7"/>
         <v>-0.13912293811133336</v>
       </c>
@@ -25287,7 +25357,7 @@
       <c r="K248" s="10">
         <v>34.894786457057684</v>
       </c>
-      <c r="L248" s="10">
+      <c r="L248" s="19">
         <f t="shared" si="7"/>
         <v>-8.1088495458931625E-2</v>
       </c>
@@ -25327,7 +25397,7 @@
       <c r="K249" s="10">
         <v>64.316923641190016</v>
       </c>
-      <c r="L249" s="10">
+      <c r="L249" s="19">
         <f t="shared" si="7"/>
         <v>-0.16702828968083541</v>
       </c>
@@ -25367,7 +25437,7 @@
       <c r="K250" s="10">
         <v>54.669969412425644</v>
       </c>
-      <c r="L250" s="10">
+      <c r="L250" s="19">
         <f t="shared" si="7"/>
         <v>1.1722470035889082E-2</v>
       </c>
@@ -25407,7 +25477,7 @@
       <c r="K251" s="10">
         <v>33.436812839822487</v>
       </c>
-      <c r="L251" s="10">
+      <c r="L251" s="19">
         <f t="shared" si="7"/>
         <v>-1.0367920222352847E-2</v>
       </c>
@@ -25447,7 +25517,7 @@
       <c r="K252" s="10">
         <v>39.172313642501635</v>
       </c>
-      <c r="L252" s="10">
+      <c r="L252" s="19">
         <f t="shared" si="7"/>
         <v>4.1786709278734284E-2</v>
       </c>
@@ -25487,7 +25557,7 @@
       <c r="K253" s="10">
         <v>38.729050102374607</v>
       </c>
-      <c r="L253" s="10">
+      <c r="L253" s="19">
         <f t="shared" si="7"/>
         <v>0.1457862892425156</v>
       </c>
@@ -25527,7 +25597,7 @@
       <c r="K254" s="10">
         <v>41.715563146345993</v>
       </c>
-      <c r="L254" s="10">
+      <c r="L254" s="19">
         <f t="shared" si="7"/>
         <v>6.0718176772379708E-3</v>
       </c>
@@ -25567,7 +25637,7 @@
       <c r="K255" s="10">
         <v>43.741742077791095</v>
       </c>
-      <c r="L255" s="10">
+      <c r="L255" s="19">
         <f t="shared" si="7"/>
         <v>-0.12455967189990541</v>
       </c>
@@ -25607,7 +25677,7 @@
       <c r="K256" s="10">
         <v>47.873989122981456</v>
       </c>
-      <c r="L256" s="10">
+      <c r="L256" s="19">
         <f t="shared" si="7"/>
         <v>5.9763493482400343E-2</v>
       </c>
@@ -25647,7 +25717,7 @@
       <c r="K257" s="10">
         <v>51.779665709540218</v>
       </c>
-      <c r="L257" s="10">
+      <c r="L257" s="19">
         <f t="shared" si="7"/>
         <v>-0.37371007036060022</v>
       </c>
@@ -25687,7 +25757,7 @@
       <c r="K258" s="10">
         <v>57.023035358289334</v>
       </c>
-      <c r="L258" s="10">
+      <c r="L258" s="19">
         <f t="shared" si="7"/>
         <v>-0.30423995341838228</v>
       </c>
@@ -25742,7 +25812,7 @@
       <c r="K259" s="10">
         <v>56.87088409797628</v>
       </c>
-      <c r="L259" s="10">
+      <c r="L259" s="19">
         <f t="shared" ref="L259:L322" si="9">IF(OR(K259=0,I259=G259,J259=F259),"",0.4*((3*(E259-H259)/K259)/(1+ABS(3*(E259-H259)/K259)))+0.45*((I259+G259-2*H259)/(I259-G259))+0.15*((J259+F259-2*H259)/(J259-F259)))</f>
         <v>7.0363975839309256E-2</v>
       </c>
@@ -25782,7 +25852,7 @@
       <c r="K260" s="10">
         <v>47.063569688632143</v>
       </c>
-      <c r="L260" s="10">
+      <c r="L260" s="19">
         <f t="shared" si="9"/>
         <v>-0.182922479514597</v>
       </c>
@@ -25822,7 +25892,7 @@
       <c r="K261" s="10">
         <v>58.561562455438484</v>
       </c>
-      <c r="L261" s="10">
+      <c r="L261" s="19">
         <f t="shared" si="9"/>
         <v>-0.14015414422992065</v>
       </c>
@@ -25862,7 +25932,7 @@
       <c r="K262" s="10">
         <v>54.876464024706216</v>
       </c>
-      <c r="L262" s="10">
+      <c r="L262" s="19">
         <f t="shared" si="9"/>
         <v>9.0810675397727508E-3</v>
       </c>
@@ -25902,7 +25972,7 @@
       <c r="K263" s="10">
         <v>48.129506282529015</v>
       </c>
-      <c r="L263" s="10">
+      <c r="L263" s="19">
         <f t="shared" si="9"/>
         <v>-4.0349960140220673E-2</v>
       </c>
@@ -25942,7 +26012,7 @@
       <c r="K264" s="10">
         <v>53.998865301934728</v>
       </c>
-      <c r="L264" s="10">
+      <c r="L264" s="19">
         <f t="shared" si="9"/>
         <v>-0.16357612119165157</v>
       </c>
@@ -25982,7 +26052,7 @@
       <c r="K265" s="10">
         <v>57.89850820929329</v>
       </c>
-      <c r="L265" s="10">
+      <c r="L265" s="19">
         <f t="shared" si="9"/>
         <v>-8.6177770555903518E-2</v>
       </c>
@@ -26022,7 +26092,7 @@
       <c r="K266" s="10">
         <v>53.479549570113456</v>
       </c>
-      <c r="L266" s="10">
+      <c r="L266" s="19">
         <f t="shared" si="9"/>
         <v>0.13559871705084281</v>
       </c>
@@ -26062,7 +26132,7 @@
       <c r="K267" s="10">
         <v>49.79143878947302</v>
       </c>
-      <c r="L267" s="10">
+      <c r="L267" s="19">
         <f t="shared" si="9"/>
         <v>8.4097881390843413E-2</v>
       </c>
@@ -26102,7 +26172,7 @@
       <c r="K268" s="10">
         <v>42.651475813694034</v>
       </c>
-      <c r="L268" s="10">
+      <c r="L268" s="19">
         <f t="shared" si="9"/>
         <v>0.48334136168725095</v>
       </c>
@@ -26142,7 +26212,7 @@
       <c r="K269" s="10">
         <v>50.439188817558389</v>
       </c>
-      <c r="L269" s="10">
+      <c r="L269" s="19">
         <f t="shared" si="9"/>
         <v>-0.35293369051884532</v>
       </c>
@@ -26182,7 +26252,7 @@
       <c r="K270" s="10">
         <v>42.049324508367285</v>
       </c>
-      <c r="L270" s="10">
+      <c r="L270" s="19">
         <f t="shared" si="9"/>
         <v>0.28501462210858869</v>
       </c>
@@ -26222,7 +26292,7 @@
       <c r="K271" s="10">
         <v>47.516027185636773</v>
       </c>
-      <c r="L271" s="10">
+      <c r="L271" s="19">
         <f t="shared" si="9"/>
         <v>0.24878654140416692</v>
       </c>
@@ -26262,7 +26332,7 @@
       <c r="K272" s="10">
         <v>40.399772058656886</v>
       </c>
-      <c r="L272" s="10">
+      <c r="L272" s="19">
         <f t="shared" si="9"/>
         <v>0.22430918272059153</v>
       </c>
@@ -26302,7 +26372,7 @@
       <c r="K273" s="10">
         <v>44.783201620610939</v>
       </c>
-      <c r="L273" s="10">
+      <c r="L273" s="19">
         <f t="shared" si="9"/>
         <v>0.26628721674884098</v>
       </c>
@@ -26342,7 +26412,7 @@
       <c r="K274" s="10">
         <v>46.854774319627346</v>
       </c>
-      <c r="L274" s="10">
+      <c r="L274" s="19">
         <f t="shared" si="9"/>
         <v>0.31763601706270544</v>
       </c>
@@ -26382,7 +26452,7 @@
       <c r="K275" s="10">
         <v>50.572231681862235</v>
       </c>
-      <c r="L275" s="10">
+      <c r="L275" s="19">
         <f t="shared" si="9"/>
         <v>0.49491110661729831</v>
       </c>
@@ -26422,7 +26492,7 @@
       <c r="K276" s="10">
         <v>51.000097894093308</v>
       </c>
-      <c r="L276" s="10">
+      <c r="L276" s="19">
         <f t="shared" si="9"/>
         <v>0.47190878355424132</v>
       </c>
@@ -26462,7 +26532,7 @@
       <c r="K277" s="10">
         <v>38.969787977354969</v>
       </c>
-      <c r="L277" s="10">
+      <c r="L277" s="19">
         <f t="shared" si="9"/>
         <v>0.52287279505715656</v>
       </c>
@@ -26502,7 +26572,7 @@
       <c r="K278" s="10">
         <v>54.517864058372737</v>
       </c>
-      <c r="L278" s="10">
+      <c r="L278" s="19">
         <f t="shared" si="9"/>
         <v>0.35264318477672391</v>
       </c>
@@ -26542,7 +26612,7 @@
       <c r="K279" s="10">
         <v>58.875398087826127</v>
       </c>
-      <c r="L279" s="10">
+      <c r="L279" s="19">
         <f t="shared" si="9"/>
         <v>-0.17662091261573959</v>
       </c>
@@ -26582,7 +26652,7 @@
       <c r="K280" s="10">
         <v>40.918862469344425</v>
       </c>
-      <c r="L280" s="10">
+      <c r="L280" s="19">
         <f t="shared" si="9"/>
         <v>-9.609299252653658E-2</v>
       </c>
@@ -26622,7 +26692,7 @@
       <c r="K281" s="10">
         <v>45.233867381064172</v>
       </c>
-      <c r="L281" s="10">
+      <c r="L281" s="19">
         <f t="shared" si="9"/>
         <v>-0.35180737734455297</v>
       </c>
@@ -26662,7 +26732,7 @@
       <c r="K282" s="10">
         <v>55.320831293464849</v>
       </c>
-      <c r="L282" s="10">
+      <c r="L282" s="19">
         <f t="shared" si="9"/>
         <v>-9.4949796327762168E-2</v>
       </c>
@@ -26702,7 +26772,7 @@
       <c r="K283" s="10">
         <v>55.690513263814637</v>
       </c>
-      <c r="L283" s="10">
+      <c r="L283" s="19">
         <f t="shared" si="9"/>
         <v>-0.27816063025567672</v>
       </c>
@@ -26742,7 +26812,7 @@
       <c r="K284" s="10">
         <v>51.999145292121014</v>
       </c>
-      <c r="L284" s="10">
+      <c r="L284" s="19">
         <f t="shared" si="9"/>
         <v>-0.19558567149704198</v>
       </c>
@@ -26782,7 +26852,7 @@
       <c r="K285" s="10">
         <v>45.873095396241652</v>
       </c>
-      <c r="L285" s="10">
+      <c r="L285" s="19">
         <f t="shared" si="9"/>
         <v>-0.13216628746765646</v>
       </c>
@@ -26822,7 +26892,7 @@
       <c r="K286" s="10">
         <v>42.216169288999922</v>
       </c>
-      <c r="L286" s="10">
+      <c r="L286" s="19">
         <f t="shared" si="9"/>
         <v>-0.28721799169647483</v>
       </c>
@@ -26862,7 +26932,7 @@
       <c r="K287" s="10">
         <v>43.664531422515303</v>
       </c>
-      <c r="L287" s="10">
+      <c r="L287" s="19">
         <f t="shared" si="9"/>
         <v>-0.27002747463407034</v>
       </c>
@@ -26902,7 +26972,7 @@
       <c r="K288" s="10">
         <v>48.198670933439651</v>
       </c>
-      <c r="L288" s="10">
+      <c r="L288" s="19">
         <f t="shared" si="9"/>
         <v>-0.18362036431459461</v>
       </c>
@@ -26942,7 +27012,7 @@
       <c r="K289" s="10">
         <v>39.516792034075834</v>
       </c>
-      <c r="L289" s="10">
+      <c r="L289" s="19">
         <f t="shared" si="9"/>
         <v>-0.38098100112984434</v>
       </c>
@@ -26982,7 +27052,7 @@
       <c r="K290" s="10">
         <v>28.563193765273795</v>
       </c>
-      <c r="L290" s="10">
+      <c r="L290" s="19">
         <f t="shared" si="9"/>
         <v>-0.20501871195734483</v>
       </c>
@@ -27022,7 +27092,7 @@
       <c r="K291" s="10">
         <v>41.403003244764143</v>
       </c>
-      <c r="L291" s="10">
+      <c r="L291" s="19">
         <f t="shared" si="9"/>
         <v>-0.22286988194994917</v>
       </c>
@@ -27062,7 +27132,7 @@
       <c r="K292" s="10">
         <v>47.072652594140706</v>
       </c>
-      <c r="L292" s="10">
+      <c r="L292" s="19">
         <f t="shared" si="9"/>
         <v>7.5044905017588773E-2</v>
       </c>
@@ -27102,7 +27172,7 @@
       <c r="K293" s="10">
         <v>49.053078858054825</v>
       </c>
-      <c r="L293" s="10">
+      <c r="L293" s="19">
         <f t="shared" si="9"/>
         <v>-0.17969985845999503</v>
       </c>
@@ -27142,7 +27212,7 @@
       <c r="K294" s="10">
         <v>53.510954226421923</v>
       </c>
-      <c r="L294" s="10">
+      <c r="L294" s="19">
         <f t="shared" si="9"/>
         <v>-0.13379958731703942</v>
       </c>
@@ -27182,7 +27252,7 @@
       <c r="K295" s="10">
         <v>39.384750530886507</v>
       </c>
-      <c r="L295" s="10">
+      <c r="L295" s="19">
         <f t="shared" si="9"/>
         <v>-0.22015084644099925</v>
       </c>
@@ -27222,7 +27292,7 @@
       <c r="K296" s="10">
         <v>36.817697808266423</v>
       </c>
-      <c r="L296" s="10">
+      <c r="L296" s="19">
         <f t="shared" si="9"/>
         <v>4.7544792316376427E-2</v>
       </c>
@@ -27262,7 +27332,7 @@
       <c r="K297" s="10">
         <v>36.233572758862671</v>
       </c>
-      <c r="L297" s="10">
+      <c r="L297" s="19">
         <f t="shared" si="9"/>
         <v>-6.3969685734960161E-2</v>
       </c>
@@ -27302,7 +27372,7 @@
       <c r="K298" s="10">
         <v>37.171889580703322</v>
       </c>
-      <c r="L298" s="10">
+      <c r="L298" s="19">
         <f t="shared" si="9"/>
         <v>-0.4758426043987074</v>
       </c>
@@ -27342,7 +27412,7 @@
       <c r="K299" s="10">
         <v>36.759941210655207</v>
       </c>
-      <c r="L299" s="10">
+      <c r="L299" s="19">
         <f t="shared" si="9"/>
         <v>-5.158376037498532E-2</v>
       </c>
@@ -27382,7 +27452,7 @@
       <c r="K300" s="10">
         <v>56.661237586866619</v>
       </c>
-      <c r="L300" s="10">
+      <c r="L300" s="19">
         <f t="shared" si="9"/>
         <v>0.23374975408896476</v>
       </c>
@@ -27422,7 +27492,7 @@
       <c r="K301" s="10">
         <v>47.798457305394521</v>
       </c>
-      <c r="L301" s="10">
+      <c r="L301" s="19">
         <f t="shared" si="9"/>
         <v>-0.28102963754655763</v>
       </c>
@@ -27462,7 +27532,7 @@
       <c r="K302" s="10">
         <v>47.064324329465158</v>
       </c>
-      <c r="L302" s="10">
+      <c r="L302" s="19">
         <f t="shared" si="9"/>
         <v>-0.13874743251609872</v>
       </c>
@@ -27502,7 +27572,7 @@
       <c r="K303" s="10">
         <v>40.595204301061202</v>
       </c>
-      <c r="L303" s="10">
+      <c r="L303" s="19">
         <f t="shared" si="9"/>
         <v>-9.7454222622657044E-2</v>
       </c>
@@ -27542,7 +27612,7 @@
       <c r="K304" s="10">
         <v>38.549937035348876</v>
       </c>
-      <c r="L304" s="10">
+      <c r="L304" s="19">
         <f t="shared" si="9"/>
         <v>5.4346851385662309E-2</v>
       </c>
@@ -27582,7 +27652,7 @@
       <c r="K305" s="10">
         <v>53.214477468494394</v>
       </c>
-      <c r="L305" s="10">
+      <c r="L305" s="19">
         <f t="shared" si="9"/>
         <v>0.17167661894245309</v>
       </c>
@@ -27622,7 +27692,7 @@
       <c r="K306" s="10">
         <v>56.900572530695925</v>
       </c>
-      <c r="L306" s="10">
+      <c r="L306" s="19">
         <f t="shared" si="9"/>
         <v>2.3058487247817585E-2</v>
       </c>
@@ -27662,7 +27732,7 @@
       <c r="K307" s="10">
         <v>56.771006536281874</v>
       </c>
-      <c r="L307" s="10">
+      <c r="L307" s="19">
         <f t="shared" si="9"/>
         <v>-1.5064667497649203E-2</v>
       </c>
@@ -27702,7 +27772,7 @@
       <c r="K308" s="10">
         <v>50.543476884317684</v>
       </c>
-      <c r="L308" s="10">
+      <c r="L308" s="19">
         <f t="shared" si="9"/>
         <v>-8.3451911369959747E-2</v>
       </c>
@@ -27742,7 +27812,7 @@
       <c r="K309" s="10">
         <v>54.137497957615317</v>
       </c>
-      <c r="L309" s="10">
+      <c r="L309" s="19">
         <f t="shared" si="9"/>
         <v>0.45028503979556378</v>
       </c>
@@ -27782,7 +27852,7 @@
       <c r="K310" s="10">
         <v>41.363917899541384</v>
       </c>
-      <c r="L310" s="10">
+      <c r="L310" s="19">
         <f t="shared" si="9"/>
         <v>0.43930791549293036</v>
       </c>
@@ -27822,7 +27892,7 @@
       <c r="K311" s="10">
         <v>45.49777201728218</v>
       </c>
-      <c r="L311" s="10">
+      <c r="L311" s="19">
         <f t="shared" si="9"/>
         <v>-0.38773876736039603</v>
       </c>
@@ -27862,7 +27932,7 @@
       <c r="K312" s="10">
         <v>46.729614872834489</v>
       </c>
-      <c r="L312" s="10">
+      <c r="L312" s="19">
         <f t="shared" si="9"/>
         <v>-0.31549777541443041</v>
       </c>
@@ -27902,7 +27972,7 @@
       <c r="K313" s="10">
         <v>34.956741028578463</v>
       </c>
-      <c r="L313" s="10">
+      <c r="L313" s="19">
         <f t="shared" si="9"/>
         <v>-0.1720289535171983</v>
       </c>
@@ -27942,7 +28012,7 @@
       <c r="K314" s="10">
         <v>29.532500348198187</v>
       </c>
-      <c r="L314" s="10">
+      <c r="L314" s="19">
         <f t="shared" si="9"/>
         <v>0.19951269286738824</v>
       </c>
@@ -27982,7 +28052,7 @@
       <c r="K315" s="10">
         <v>45.65945115969452</v>
       </c>
-      <c r="L315" s="10">
+      <c r="L315" s="19">
         <f t="shared" si="9"/>
         <v>-7.3128217362375417E-2</v>
       </c>
@@ -28022,7 +28092,7 @@
       <c r="K316" s="10">
         <v>48.136271215938542</v>
       </c>
-      <c r="L316" s="10">
+      <c r="L316" s="19">
         <f t="shared" si="9"/>
         <v>-0.18055239816996282</v>
       </c>
@@ -28062,7 +28132,7 @@
       <c r="K317" s="10">
         <v>49.207476611003706</v>
       </c>
-      <c r="L317" s="10">
+      <c r="L317" s="19">
         <f t="shared" si="9"/>
         <v>0.14870193826008388</v>
       </c>
@@ -28102,7 +28172,7 @@
       <c r="K318" s="10">
         <v>53.618962087056566</v>
       </c>
-      <c r="L318" s="10">
+      <c r="L318" s="19">
         <f t="shared" si="9"/>
         <v>7.5255218392824313E-2</v>
       </c>
@@ -28142,7 +28212,7 @@
       <c r="K319" s="10">
         <v>52.76407806027715</v>
       </c>
-      <c r="L319" s="10">
+      <c r="L319" s="19">
         <f t="shared" si="9"/>
         <v>-7.5632810595166994E-2</v>
       </c>
@@ -28182,7 +28252,7 @@
       <c r="K320" s="10">
         <v>50.011052339523104</v>
       </c>
-      <c r="L320" s="10">
+      <c r="L320" s="19">
         <f t="shared" si="9"/>
         <v>0.2167643452050822</v>
       </c>
@@ -28222,7 +28292,7 @@
       <c r="K321" s="10">
         <v>53.937797639233743</v>
       </c>
-      <c r="L321" s="10">
+      <c r="L321" s="19">
         <f t="shared" si="9"/>
         <v>-0.11443226928779199</v>
       </c>
@@ -28262,7 +28332,7 @@
       <c r="K322" s="10">
         <v>39.420666681528402</v>
       </c>
-      <c r="L322" s="10">
+      <c r="L322" s="19">
         <f t="shared" si="9"/>
         <v>-0.34196943797421303</v>
       </c>
@@ -28317,7 +28387,7 @@
       <c r="K323" s="10">
         <v>42.597308792434582</v>
       </c>
-      <c r="L323" s="10">
+      <c r="L323" s="19">
         <f t="shared" ref="L323:L386" si="11">IF(OR(K323=0,I323=G323,J323=F323),"",0.4*((3*(E323-H323)/K323)/(1+ABS(3*(E323-H323)/K323)))+0.45*((I323+G323-2*H323)/(I323-G323))+0.15*((J323+F323-2*H323)/(J323-F323)))</f>
         <v>-0.35251762302307538</v>
       </c>
@@ -28357,7 +28427,7 @@
       <c r="K324" s="10">
         <v>59.566739758018073</v>
       </c>
-      <c r="L324" s="10">
+      <c r="L324" s="19">
         <f t="shared" si="11"/>
         <v>-0.33010517444599696</v>
       </c>
@@ -28397,7 +28467,7 @@
       <c r="K325" s="10">
         <v>40.667483971490398</v>
       </c>
-      <c r="L325" s="10">
+      <c r="L325" s="19">
         <f t="shared" si="11"/>
         <v>9.180012793777971E-2</v>
       </c>
@@ -28437,7 +28507,7 @@
       <c r="K326" s="10">
         <v>50.154861297471179</v>
       </c>
-      <c r="L326" s="10">
+      <c r="L326" s="19">
         <f t="shared" si="11"/>
         <v>-0.14260569695295292</v>
       </c>
@@ -28477,7 +28547,7 @@
       <c r="K327" s="10">
         <v>50.124976846592538</v>
       </c>
-      <c r="L327" s="10">
+      <c r="L327" s="19">
         <f t="shared" si="11"/>
         <v>-2.5406326010816341E-2</v>
       </c>
@@ -28517,7 +28587,7 @@
       <c r="K328" s="10">
         <v>52.943578895895669</v>
       </c>
-      <c r="L328" s="10">
+      <c r="L328" s="19">
         <f t="shared" si="11"/>
         <v>-0.48793529707614092</v>
       </c>
@@ -28557,7 +28627,7 @@
       <c r="K329" s="10">
         <v>56.021511245433409</v>
       </c>
-      <c r="L329" s="10">
+      <c r="L329" s="19">
         <f t="shared" si="11"/>
         <v>-0.30059774746781409</v>
       </c>
@@ -28597,7 +28667,7 @@
       <c r="K330" s="10">
         <v>57.266397751374981</v>
       </c>
-      <c r="L330" s="10">
+      <c r="L330" s="19">
         <f t="shared" si="11"/>
         <v>-0.61108517228084569</v>
       </c>
@@ -28637,7 +28707,7 @@
       <c r="K331" s="10">
         <v>66.483484497561491</v>
       </c>
-      <c r="L331" s="10">
+      <c r="L331" s="19">
         <f t="shared" si="11"/>
         <v>-0.41189559411251714</v>
       </c>
@@ -28677,7 +28747,7 @@
       <c r="K332" s="10">
         <v>71.777760309165402</v>
       </c>
-      <c r="L332" s="10">
+      <c r="L332" s="19">
         <f t="shared" si="11"/>
         <v>-0.45129073330575414</v>
       </c>
@@ -28717,7 +28787,7 @@
       <c r="K333" s="10">
         <v>59.778361750310793</v>
       </c>
-      <c r="L333" s="10">
+      <c r="L333" s="19">
         <f t="shared" si="11"/>
         <v>-8.6239966534986168E-2</v>
       </c>
@@ -28757,7 +28827,7 @@
       <c r="K334" s="10">
         <v>59.216704581992914</v>
       </c>
-      <c r="L334" s="10">
+      <c r="L334" s="19">
         <f t="shared" si="11"/>
         <v>-0.35733616506137533</v>
       </c>
@@ -28797,7 +28867,7 @@
       <c r="K335" s="10">
         <v>57.538374466714032</v>
       </c>
-      <c r="L335" s="10">
+      <c r="L335" s="19">
         <f t="shared" si="11"/>
         <v>-0.15069924898317011</v>
       </c>
@@ -28837,7 +28907,7 @@
       <c r="K336" s="10">
         <v>64.794060427377659</v>
       </c>
-      <c r="L336" s="10">
+      <c r="L336" s="19">
         <f t="shared" si="11"/>
         <v>-0.37227568170685005</v>
       </c>
@@ -28877,7 +28947,7 @@
       <c r="K337" s="10">
         <v>42.978585224257763</v>
       </c>
-      <c r="L337" s="10">
+      <c r="L337" s="19">
         <f t="shared" si="11"/>
         <v>0.53373061835460645</v>
       </c>
@@ -28917,7 +28987,7 @@
       <c r="K338" s="10">
         <v>58.262610437726366</v>
       </c>
-      <c r="L338" s="10">
+      <c r="L338" s="19">
         <f t="shared" si="11"/>
         <v>-0.34829281198065232</v>
       </c>
@@ -28957,7 +29027,7 @@
       <c r="K339" s="10">
         <v>53.947354080111261</v>
       </c>
-      <c r="L339" s="10">
+      <c r="L339" s="19">
         <f t="shared" si="11"/>
         <v>-0.35457684546648066</v>
       </c>
@@ -28997,7 +29067,7 @@
       <c r="K340" s="10">
         <v>40.867278029986856</v>
       </c>
-      <c r="L340" s="10">
+      <c r="L340" s="19">
         <f t="shared" si="11"/>
         <v>2.1452481321865405E-2</v>
       </c>
@@ -29037,7 +29107,7 @@
       <c r="K341" s="10">
         <v>49.812955030683419</v>
       </c>
-      <c r="L341" s="10">
+      <c r="L341" s="19">
         <f t="shared" si="11"/>
         <v>-6.6819318335157252E-2</v>
       </c>
@@ -29077,7 +29147,7 @@
       <c r="K342" s="10">
         <v>44.510630134900872</v>
       </c>
-      <c r="L342" s="10">
+      <c r="L342" s="19">
         <f t="shared" si="11"/>
         <v>5.0785826753217918E-2</v>
       </c>
@@ -29117,7 +29187,7 @@
       <c r="K343" s="10">
         <v>53.24693033779436</v>
       </c>
-      <c r="L343" s="10">
+      <c r="L343" s="19">
         <f t="shared" si="11"/>
         <v>-2.1526999251922023E-2</v>
       </c>
@@ -29157,7 +29227,7 @@
       <c r="K344" s="10">
         <v>43.585114686349307</v>
       </c>
-      <c r="L344" s="10">
+      <c r="L344" s="19">
         <f t="shared" si="11"/>
         <v>-0.3975324657711457</v>
       </c>
@@ -29197,7 +29267,7 @@
       <c r="K345" s="10">
         <v>60.84780147014353</v>
       </c>
-      <c r="L345" s="10">
+      <c r="L345" s="19">
         <f t="shared" si="11"/>
         <v>-0.60832537533303033</v>
       </c>
@@ -29237,7 +29307,7 @@
       <c r="K346" s="10">
         <v>53.953140270861297</v>
       </c>
-      <c r="L346" s="10">
+      <c r="L346" s="19">
         <f t="shared" si="11"/>
         <v>-0.50673354295736683</v>
       </c>
@@ -29277,7 +29347,7 @@
       <c r="K347" s="10">
         <v>32.239533185206014</v>
       </c>
-      <c r="L347" s="10">
+      <c r="L347" s="19">
         <f t="shared" si="11"/>
         <v>0.21511193458385877</v>
       </c>
@@ -29317,7 +29387,7 @@
       <c r="K348" s="10">
         <v>40.084712867791588</v>
       </c>
-      <c r="L348" s="10">
+      <c r="L348" s="19">
         <f t="shared" si="11"/>
         <v>-0.58246509361149024</v>
       </c>
@@ -29357,7 +29427,7 @@
       <c r="K349" s="10">
         <v>38.38710256166938</v>
       </c>
-      <c r="L349" s="10">
+      <c r="L349" s="19">
         <f t="shared" si="11"/>
         <v>-0.60649021371656808</v>
       </c>
@@ -29397,7 +29467,7 @@
       <c r="K350" s="10">
         <v>38.080293444545788</v>
       </c>
-      <c r="L350" s="10">
+      <c r="L350" s="19">
         <f t="shared" si="11"/>
         <v>-0.55479316227919551</v>
       </c>
@@ -29437,7 +29507,7 @@
       <c r="K351" s="10">
         <v>48.402767285139547</v>
       </c>
-      <c r="L351" s="10">
+      <c r="L351" s="19">
         <f t="shared" si="11"/>
         <v>-0.30217091755523096</v>
       </c>
@@ -29477,7 +29547,7 @@
       <c r="K352" s="10">
         <v>40.094000618700669</v>
       </c>
-      <c r="L352" s="10">
+      <c r="L352" s="19">
         <f t="shared" si="11"/>
         <v>-0.54294585783732563</v>
       </c>
@@ -29517,7 +29587,7 @@
       <c r="K353" s="10">
         <v>42.821783159517786</v>
       </c>
-      <c r="L353" s="10">
+      <c r="L353" s="19">
         <f t="shared" si="11"/>
         <v>-0.48545953180417906</v>
       </c>
@@ -29557,7 +29627,7 @@
       <c r="K354" s="10">
         <v>32.607118719705234</v>
       </c>
-      <c r="L354" s="10">
+      <c r="L354" s="19">
         <f t="shared" si="11"/>
         <v>9.4162321475558072E-2</v>
       </c>
@@ -29597,7 +29667,7 @@
       <c r="K355" s="10">
         <v>40.659143503192773</v>
       </c>
-      <c r="L355" s="10">
+      <c r="L355" s="19">
         <f t="shared" si="11"/>
         <v>-0.32894303545540016</v>
       </c>
@@ -29637,7 +29707,7 @@
       <c r="K356" s="10">
         <v>61.567550890600387</v>
       </c>
-      <c r="L356" s="10">
+      <c r="L356" s="19">
         <f t="shared" si="11"/>
         <v>-0.42650466619502048</v>
       </c>
@@ -29677,7 +29747,7 @@
       <c r="K357" s="10">
         <v>52.116557963159231</v>
       </c>
-      <c r="L357" s="10">
+      <c r="L357" s="19">
         <f t="shared" si="11"/>
         <v>-0.31196354740960602</v>
       </c>
@@ -29717,7 +29787,7 @@
       <c r="K358" s="10">
         <v>53.354057268656028</v>
       </c>
-      <c r="L358" s="10">
+      <c r="L358" s="19">
         <f t="shared" si="11"/>
         <v>-0.29580351596939675</v>
       </c>
@@ -29757,7 +29827,7 @@
       <c r="K359" s="10">
         <v>58.802213497238505</v>
       </c>
-      <c r="L359" s="10">
+      <c r="L359" s="19">
         <f t="shared" si="11"/>
         <v>5.8034793563352852E-2</v>
       </c>
@@ -29797,7 +29867,7 @@
       <c r="K360" s="10">
         <v>37.937705662389739</v>
       </c>
-      <c r="L360" s="10">
+      <c r="L360" s="19">
         <f t="shared" si="11"/>
         <v>0.18659957379138606</v>
       </c>
@@ -29837,7 +29907,7 @@
       <c r="K361" s="10">
         <v>54.929642662956802</v>
       </c>
-      <c r="L361" s="10">
+      <c r="L361" s="19">
         <f t="shared" si="11"/>
         <v>-0.55556430686998248</v>
       </c>
@@ -29877,7 +29947,7 @@
       <c r="K362" s="10">
         <v>35.515606966366008</v>
       </c>
-      <c r="L362" s="10">
+      <c r="L362" s="19">
         <f t="shared" si="11"/>
         <v>-0.53517242699235756</v>
       </c>
@@ -29917,7 +29987,7 @@
       <c r="K363" s="10">
         <v>47.22321621646487</v>
       </c>
-      <c r="L363" s="10">
+      <c r="L363" s="19">
         <f t="shared" si="11"/>
         <v>-0.45135576225865165</v>
       </c>
@@ -29957,7 +30027,7 @@
       <c r="K364" s="10">
         <v>58.20055953610327</v>
       </c>
-      <c r="L364" s="10">
+      <c r="L364" s="19">
         <f t="shared" si="11"/>
         <v>-0.60715270493550422</v>
       </c>
@@ -29997,7 +30067,7 @@
       <c r="K365" s="10">
         <v>58.972667790307163</v>
       </c>
-      <c r="L365" s="10">
+      <c r="L365" s="19">
         <f t="shared" si="11"/>
         <v>0.168287613241904</v>
       </c>
@@ -30037,7 +30107,7 @@
       <c r="K366" s="10">
         <v>54.209657868522129</v>
       </c>
-      <c r="L366" s="10">
+      <c r="L366" s="19">
         <f t="shared" si="11"/>
         <v>0.17082787746659125</v>
       </c>
@@ -30077,7 +30147,7 @@
       <c r="K367" s="10">
         <v>49.424558707629132</v>
       </c>
-      <c r="L367" s="10">
+      <c r="L367" s="19">
         <f t="shared" si="11"/>
         <v>0.12801407691180602</v>
       </c>
@@ -30117,7 +30187,7 @@
       <c r="K368" s="10">
         <v>49.303982121743722</v>
       </c>
-      <c r="L368" s="10">
+      <c r="L368" s="19">
         <f t="shared" si="11"/>
         <v>-0.13545727007256222</v>
       </c>
@@ -30157,7 +30227,7 @@
       <c r="K369" s="10">
         <v>35.218787549159295</v>
       </c>
-      <c r="L369" s="10">
+      <c r="L369" s="19">
         <f t="shared" si="11"/>
         <v>-4.457010478437929E-2</v>
       </c>
@@ -30197,7 +30267,7 @@
       <c r="K370" s="10">
         <v>55.882367115793201</v>
       </c>
-      <c r="L370" s="10">
+      <c r="L370" s="19">
         <f t="shared" si="11"/>
         <v>0.1092563096314976</v>
       </c>
@@ -30237,7 +30307,7 @@
       <c r="K371" s="10">
         <v>53.110925423170286</v>
       </c>
-      <c r="L371" s="10">
+      <c r="L371" s="19">
         <f t="shared" si="11"/>
         <v>-0.37016905603296635</v>
       </c>
@@ -30277,7 +30347,7 @@
       <c r="K372" s="10">
         <v>33.44447705914984</v>
       </c>
-      <c r="L372" s="10">
+      <c r="L372" s="19">
         <f t="shared" si="11"/>
         <v>-0.41064454547196616</v>
       </c>
@@ -30317,7 +30387,7 @@
       <c r="K373" s="10">
         <v>54.484641664282961</v>
       </c>
-      <c r="L373" s="10">
+      <c r="L373" s="19">
         <f t="shared" si="11"/>
         <v>-0.62748591292242106</v>
       </c>
@@ -30357,7 +30427,7 @@
       <c r="K374" s="10">
         <v>30.238330855873073</v>
       </c>
-      <c r="L374" s="10">
+      <c r="L374" s="19">
         <f t="shared" si="11"/>
         <v>2.54965459739563E-2</v>
       </c>
@@ -30397,7 +30467,7 @@
       <c r="K375" s="10">
         <v>42.699029269899285</v>
       </c>
-      <c r="L375" s="10">
+      <c r="L375" s="19">
         <f t="shared" si="11"/>
         <v>-4.9808558292461086E-2</v>
       </c>
@@ -30437,7 +30507,7 @@
       <c r="K376" s="10">
         <v>56.528524201883307</v>
       </c>
-      <c r="L376" s="10">
+      <c r="L376" s="19">
         <f t="shared" si="11"/>
         <v>-0.36848296197378166</v>
       </c>
@@ -30477,7 +30547,7 @@
       <c r="K377" s="10">
         <v>45.736639980287038</v>
       </c>
-      <c r="L377" s="10">
+      <c r="L377" s="19">
         <f t="shared" si="11"/>
         <v>9.1216590787700086E-2</v>
       </c>
@@ -30517,7 +30587,7 @@
       <c r="K378" s="10">
         <v>44.32004194458554</v>
       </c>
-      <c r="L378" s="10">
+      <c r="L378" s="19">
         <f t="shared" si="11"/>
         <v>-0.2182232606407476</v>
       </c>
@@ -30557,7 +30627,7 @@
       <c r="K379" s="10">
         <v>31.097341411399512</v>
       </c>
-      <c r="L379" s="10">
+      <c r="L379" s="19">
         <f t="shared" si="11"/>
         <v>3.86848463408156E-3</v>
       </c>
@@ -30597,7 +30667,7 @@
       <c r="K380" s="10">
         <v>32.054779929422871</v>
       </c>
-      <c r="L380" s="10">
+      <c r="L380" s="19">
         <f t="shared" si="11"/>
         <v>-0.24663946314162366</v>
       </c>
@@ -30637,7 +30707,7 @@
       <c r="K381" s="10">
         <v>48.279990820009985</v>
       </c>
-      <c r="L381" s="10">
+      <c r="L381" s="19">
         <f t="shared" si="11"/>
         <v>-0.75931703115541704</v>
       </c>
@@ -30677,7 +30747,7 @@
       <c r="K382" s="10">
         <v>55.268275006754301</v>
       </c>
-      <c r="L382" s="10">
+      <c r="L382" s="19">
         <f t="shared" si="11"/>
         <v>-0.60539035840038868</v>
       </c>
@@ -30717,7 +30787,7 @@
       <c r="K383" s="10">
         <v>64.648358122534788</v>
       </c>
-      <c r="L383" s="10">
+      <c r="L383" s="19">
         <f t="shared" si="11"/>
         <v>0.38941019738928728</v>
       </c>
@@ -30757,7 +30827,7 @@
       <c r="K384" s="10">
         <v>30.40107245824677</v>
       </c>
-      <c r="L384" s="10">
+      <c r="L384" s="19">
         <f t="shared" si="11"/>
         <v>-0.78368775881011887</v>
       </c>
@@ -30797,7 +30867,7 @@
       <c r="K385" s="10">
         <v>46.050815851660722</v>
       </c>
-      <c r="L385" s="10">
+      <c r="L385" s="19">
         <f t="shared" si="11"/>
         <v>-0.61080347686614178</v>
       </c>
@@ -30837,7 +30907,7 @@
       <c r="K386" s="10">
         <v>29.663869105622428</v>
       </c>
-      <c r="L386" s="10">
+      <c r="L386" s="19">
         <f t="shared" si="11"/>
         <v>-0.64463878587771828</v>
       </c>
@@ -30892,7 +30962,7 @@
       <c r="K387" s="10">
         <v>29.763192589775961</v>
       </c>
-      <c r="L387" s="10">
+      <c r="L387" s="19">
         <f t="shared" ref="L387:L450" si="13">IF(OR(K387=0,I387=G387,J387=F387),"",0.4*((3*(E387-H387)/K387)/(1+ABS(3*(E387-H387)/K387)))+0.45*((I387+G387-2*H387)/(I387-G387))+0.15*((J387+F387-2*H387)/(J387-F387)))</f>
         <v>-0.74197957581351837</v>
       </c>
@@ -30932,7 +31002,7 @@
       <c r="K388" s="10">
         <v>53.718056830358535</v>
       </c>
-      <c r="L388" s="10">
+      <c r="L388" s="19">
         <f t="shared" si="13"/>
         <v>-0.66889519270396902</v>
       </c>
@@ -30972,7 +31042,7 @@
       <c r="K389" s="10">
         <v>47.320660371123139</v>
       </c>
-      <c r="L389" s="10">
+      <c r="L389" s="19">
         <f t="shared" si="13"/>
         <v>-0.71740605457151974</v>
       </c>
@@ -31012,7 +31082,7 @@
       <c r="K390" s="10">
         <v>26.84883647436958</v>
       </c>
-      <c r="L390" s="10">
+      <c r="L390" s="19">
         <f t="shared" si="13"/>
         <v>0.13353710346059189</v>
       </c>
@@ -31052,7 +31122,7 @@
       <c r="K391" s="10">
         <v>30.228012575603316</v>
       </c>
-      <c r="L391" s="10">
+      <c r="L391" s="19">
         <f t="shared" si="13"/>
         <v>-0.62109254322860463</v>
       </c>
@@ -31092,7 +31162,7 @@
       <c r="K392" s="10">
         <v>35.628299402813028</v>
       </c>
-      <c r="L392" s="10">
+      <c r="L392" s="19">
         <f t="shared" si="13"/>
         <v>6.6116334851422931E-2</v>
       </c>
@@ -31132,7 +31202,7 @@
       <c r="K393" s="10">
         <v>29.564716897124189</v>
       </c>
-      <c r="L393" s="10">
+      <c r="L393" s="19">
         <f t="shared" si="13"/>
         <v>-0.62764155256474197</v>
       </c>
@@ -31172,7 +31242,7 @@
       <c r="K394" s="10">
         <v>25.48504766173663</v>
       </c>
-      <c r="L394" s="10">
+      <c r="L394" s="19">
         <f t="shared" si="13"/>
         <v>-0.47464388828901388</v>
       </c>
@@ -31212,7 +31282,7 @@
       <c r="K395" s="10">
         <v>29.440463564644233</v>
       </c>
-      <c r="L395" s="10">
+      <c r="L395" s="19">
         <f t="shared" si="13"/>
         <v>-0.59514807792072177</v>
       </c>
@@ -31252,7 +31322,7 @@
       <c r="K396" s="10">
         <v>36.868005424758209</v>
       </c>
-      <c r="L396" s="10">
+      <c r="L396" s="19">
         <f t="shared" si="13"/>
         <v>-0.63087219970664266</v>
       </c>
@@ -31292,7 +31362,7 @@
       <c r="K397" s="10">
         <v>33.543405654015224</v>
       </c>
-      <c r="L397" s="10">
+      <c r="L397" s="19">
         <f t="shared" si="13"/>
         <v>-0.55277960752889477</v>
       </c>
@@ -31332,7 +31402,7 @@
       <c r="K398" s="10">
         <v>33.281205492789098</v>
       </c>
-      <c r="L398" s="10">
+      <c r="L398" s="19">
         <f t="shared" si="13"/>
         <v>-0.59070959114697486</v>
       </c>
@@ -31372,7 +31442,7 @@
       <c r="K399" s="10">
         <v>48.6755678567065</v>
       </c>
-      <c r="L399" s="10">
+      <c r="L399" s="19">
         <f t="shared" si="13"/>
         <v>-0.25274180365639709</v>
       </c>
@@ -31412,7 +31482,7 @@
       <c r="K400" s="10">
         <v>48.899855436252473</v>
       </c>
-      <c r="L400" s="10">
+      <c r="L400" s="19">
         <f t="shared" si="13"/>
         <v>-0.12541538155515383</v>
       </c>
@@ -31452,7 +31522,7 @@
       <c r="K401" s="10">
         <v>50.456539714887306</v>
       </c>
-      <c r="L401" s="10">
+      <c r="L401" s="19">
         <f t="shared" si="13"/>
         <v>-0.18807320551667345</v>
       </c>
@@ -31492,7 +31562,7 @@
       <c r="K402" s="10">
         <v>53.893528968558918</v>
       </c>
-      <c r="L402" s="10">
+      <c r="L402" s="19">
         <f t="shared" si="13"/>
         <v>-0.11284927345236145</v>
       </c>
@@ -31532,7 +31602,7 @@
       <c r="K403" s="10">
         <v>32.173253175865931</v>
       </c>
-      <c r="L403" s="10">
+      <c r="L403" s="19">
         <f t="shared" si="13"/>
         <v>5.8751405877161558E-2</v>
       </c>
@@ -31572,7 +31642,7 @@
       <c r="K404" s="10">
         <v>28.177917475995674</v>
       </c>
-      <c r="L404" s="10">
+      <c r="L404" s="19">
         <f t="shared" si="13"/>
         <v>-0.57814264863435327</v>
       </c>
@@ -31612,7 +31682,7 @@
       <c r="K405" s="10">
         <v>38.591960706244812</v>
       </c>
-      <c r="L405" s="10">
+      <c r="L405" s="19">
         <f t="shared" si="13"/>
         <v>-0.51245858248428067</v>
       </c>
@@ -31652,7 +31722,7 @@
       <c r="K406" s="10">
         <v>62.434033436115925</v>
       </c>
-      <c r="L406" s="10">
+      <c r="L406" s="19">
         <f t="shared" si="13"/>
         <v>-0.23452316016358943</v>
       </c>
@@ -31692,7 +31762,7 @@
       <c r="K407" s="10">
         <v>38.474239554033893</v>
       </c>
-      <c r="L407" s="10">
+      <c r="L407" s="19">
         <f t="shared" si="13"/>
         <v>-0.49881758468774823</v>
       </c>
@@ -31732,7 +31802,7 @@
       <c r="K408" s="10">
         <v>30.022064656219442</v>
       </c>
-      <c r="L408" s="10">
+      <c r="L408" s="19">
         <f t="shared" si="13"/>
         <v>-0.41636969798873091</v>
       </c>
@@ -31772,7 +31842,7 @@
       <c r="K409" s="10">
         <v>44.188138476313277</v>
       </c>
-      <c r="L409" s="10">
+      <c r="L409" s="19">
         <f t="shared" si="13"/>
         <v>4.5299842845765534E-2</v>
       </c>
@@ -31812,7 +31882,7 @@
       <c r="K410" s="10">
         <v>31.323363729632899</v>
       </c>
-      <c r="L410" s="10">
+      <c r="L410" s="19">
         <f t="shared" si="13"/>
         <v>-0.34111401946813835</v>
       </c>
@@ -31852,7 +31922,7 @@
       <c r="K411" s="10">
         <v>35.606324792337006</v>
       </c>
-      <c r="L411" s="10">
+      <c r="L411" s="19">
         <f t="shared" si="13"/>
         <v>9.4044695765439154E-2</v>
       </c>
@@ -31892,7 +31962,7 @@
       <c r="K412" s="10">
         <v>35.382781553838939</v>
       </c>
-      <c r="L412" s="10">
+      <c r="L412" s="19">
         <f t="shared" si="13"/>
         <v>-0.11972558561681648</v>
       </c>
@@ -31932,7 +32002,7 @@
       <c r="K413" s="10">
         <v>45.803062444786249</v>
       </c>
-      <c r="L413" s="10">
+      <c r="L413" s="19">
         <f t="shared" si="13"/>
         <v>-0.17830575725738232</v>
       </c>
@@ -31972,7 +32042,7 @@
       <c r="K414" s="10">
         <v>37.395218193640751</v>
       </c>
-      <c r="L414" s="10">
+      <c r="L414" s="19">
         <f t="shared" si="13"/>
         <v>-7.9114557904803928E-2</v>
       </c>
@@ -32012,7 +32082,7 @@
       <c r="K415" s="10">
         <v>30.364171137854051</v>
       </c>
-      <c r="L415" s="10">
+      <c r="L415" s="19">
         <f t="shared" si="13"/>
         <v>-0.13329853252265472</v>
       </c>
@@ -32052,7 +32122,7 @@
       <c r="K416" s="10">
         <v>46.926276851752007</v>
       </c>
-      <c r="L416" s="10">
+      <c r="L416" s="19">
         <f t="shared" si="13"/>
         <v>-0.18143357817068589</v>
       </c>
@@ -32092,7 +32162,7 @@
       <c r="K417" s="10">
         <v>56.381294114615542</v>
       </c>
-      <c r="L417" s="10">
+      <c r="L417" s="19">
         <f t="shared" si="13"/>
         <v>-0.43547095462295571</v>
       </c>
@@ -32132,7 +32202,7 @@
       <c r="K418" s="10">
         <v>42.349237020811792</v>
       </c>
-      <c r="L418" s="10">
+      <c r="L418" s="19">
         <f t="shared" si="13"/>
         <v>-0.13499241963143899</v>
       </c>
@@ -32172,7 +32242,7 @@
       <c r="K419" s="10">
         <v>38.373204647880215</v>
       </c>
-      <c r="L419" s="10">
+      <c r="L419" s="19">
         <f t="shared" si="13"/>
         <v>-0.44280222370526706</v>
       </c>
@@ -32212,7 +32282,7 @@
       <c r="K420" s="10">
         <v>44.314119769408713</v>
       </c>
-      <c r="L420" s="10">
+      <c r="L420" s="19">
         <f t="shared" si="13"/>
         <v>-0.55545851356835818</v>
       </c>
@@ -32252,7 +32322,7 @@
       <c r="K421" s="10">
         <v>60.45119572753616</v>
       </c>
-      <c r="L421" s="10">
+      <c r="L421" s="19">
         <f t="shared" si="13"/>
         <v>-0.43197699562057468</v>
       </c>
@@ -32292,7 +32362,7 @@
       <c r="K422" s="10">
         <v>47.49836466704955</v>
       </c>
-      <c r="L422" s="10">
+      <c r="L422" s="19">
         <f t="shared" si="13"/>
         <v>-0.48786804288718572</v>
       </c>
@@ -32332,7 +32402,7 @@
       <c r="K423" s="10">
         <v>35.064608489041966</v>
       </c>
-      <c r="L423" s="10">
+      <c r="L423" s="19">
         <f t="shared" si="13"/>
         <v>-0.73999676955247007</v>
       </c>
@@ -32372,7 +32442,7 @@
       <c r="K424" s="10">
         <v>44.721213423875326</v>
       </c>
-      <c r="L424" s="10">
+      <c r="L424" s="19">
         <f t="shared" si="13"/>
         <v>-0.65593480781602365</v>
       </c>
@@ -32412,7 +32482,7 @@
       <c r="K425" s="10">
         <v>39.312318980389804</v>
       </c>
-      <c r="L425" s="10">
+      <c r="L425" s="19">
         <f t="shared" si="13"/>
         <v>-0.39814946943862795</v>
       </c>
@@ -32452,7 +32522,7 @@
       <c r="K426" s="10">
         <v>34.47072790576</v>
       </c>
-      <c r="L426" s="10">
+      <c r="L426" s="19">
         <f t="shared" si="13"/>
         <v>-0.33493678022905127</v>
       </c>
@@ -32492,7 +32562,7 @@
       <c r="K427" s="10">
         <v>51.803015068152312</v>
       </c>
-      <c r="L427" s="10">
+      <c r="L427" s="19">
         <f t="shared" si="13"/>
         <v>0.15760505158001492</v>
       </c>
@@ -32532,7 +32602,7 @@
       <c r="K428" s="10">
         <v>45.922649241726944</v>
       </c>
-      <c r="L428" s="10">
+      <c r="L428" s="19">
         <f t="shared" si="13"/>
         <v>-0.40166716528711699</v>
       </c>
@@ -32572,7 +32642,7 @@
       <c r="K429" s="10">
         <v>62.557833587887913</v>
       </c>
-      <c r="L429" s="10">
+      <c r="L429" s="19">
         <f t="shared" si="13"/>
         <v>-0.34159420693659598</v>
       </c>
@@ -32612,7 +32682,7 @@
       <c r="K430" s="10">
         <v>47.65914443041865</v>
       </c>
-      <c r="L430" s="10">
+      <c r="L430" s="19">
         <f t="shared" si="13"/>
         <v>-0.2803459233598396</v>
       </c>
@@ -32652,7 +32722,7 @@
       <c r="K431" s="10">
         <v>59.213557190072954</v>
       </c>
-      <c r="L431" s="10">
+      <c r="L431" s="19">
         <f t="shared" si="13"/>
         <v>-2.9363753651123349E-2</v>
       </c>
@@ -32692,7 +32762,7 @@
       <c r="K432" s="10">
         <v>57.333019762644675</v>
       </c>
-      <c r="L432" s="10">
+      <c r="L432" s="19">
         <f t="shared" si="13"/>
         <v>-0.26459954593095841</v>
       </c>
@@ -32732,7 +32802,7 @@
       <c r="K433" s="10">
         <v>49.133395431991111</v>
       </c>
-      <c r="L433" s="10">
+      <c r="L433" s="19">
         <f t="shared" si="13"/>
         <v>-0.21502155736098122</v>
       </c>
@@ -32772,7 +32842,7 @@
       <c r="K434" s="10">
         <v>55.537677707137746</v>
       </c>
-      <c r="L434" s="10">
+      <c r="L434" s="19">
         <f t="shared" si="13"/>
         <v>-2.223256788600193E-2</v>
       </c>
@@ -32812,7 +32882,7 @@
       <c r="K435" s="10">
         <v>66.806525599248758</v>
       </c>
-      <c r="L435" s="10">
+      <c r="L435" s="19">
         <f t="shared" si="13"/>
         <v>-0.14089098871664446</v>
       </c>
@@ -32852,7 +32922,7 @@
       <c r="K436" s="10">
         <v>66.570355280429666</v>
       </c>
-      <c r="L436" s="10">
+      <c r="L436" s="19">
         <f t="shared" si="13"/>
         <v>-0.37511310887257948</v>
       </c>
@@ -32892,7 +32962,7 @@
       <c r="K437" s="10">
         <v>67.686973863523022</v>
       </c>
-      <c r="L437" s="10">
+      <c r="L437" s="19">
         <f t="shared" si="13"/>
         <v>-0.37019340834920977</v>
       </c>
@@ -32932,7 +33002,7 @@
       <c r="K438" s="10">
         <v>62.311923006128566</v>
       </c>
-      <c r="L438" s="10">
+      <c r="L438" s="19">
         <f t="shared" si="13"/>
         <v>-0.23865982118624204</v>
       </c>
@@ -32972,7 +33042,7 @@
       <c r="K439" s="10">
         <v>65.532799765784759</v>
       </c>
-      <c r="L439" s="10">
+      <c r="L439" s="19">
         <f t="shared" si="13"/>
         <v>-0.25329184603406596</v>
       </c>
@@ -33012,7 +33082,7 @@
       <c r="K440" s="10">
         <v>62.905619401035253</v>
       </c>
-      <c r="L440" s="10">
+      <c r="L440" s="19">
         <f t="shared" si="13"/>
         <v>-7.9057795215073307E-2</v>
       </c>
@@ -33052,7 +33122,7 @@
       <c r="K441" s="10">
         <v>59.753766943925129</v>
       </c>
-      <c r="L441" s="10">
+      <c r="L441" s="19">
         <f t="shared" si="13"/>
         <v>-0.16341145537630086</v>
       </c>
@@ -33092,7 +33162,7 @@
       <c r="K442" s="10">
         <v>54.685208883890532</v>
       </c>
-      <c r="L442" s="10">
+      <c r="L442" s="19">
         <f t="shared" si="13"/>
         <v>-0.16223934358611539</v>
       </c>
@@ -33132,7 +33202,7 @@
       <c r="K443" s="10">
         <v>64.443637389582548</v>
       </c>
-      <c r="L443" s="10">
+      <c r="L443" s="19">
         <f t="shared" si="13"/>
         <v>-0.42347418701018774</v>
       </c>
@@ -33172,7 +33242,7 @@
       <c r="K444" s="10">
         <v>53.372403786390393</v>
       </c>
-      <c r="L444" s="10">
+      <c r="L444" s="19">
         <f t="shared" si="13"/>
         <v>-0.2624672658523306</v>
       </c>
@@ -33212,7 +33282,7 @@
       <c r="K445" s="10">
         <v>52.550400098141971</v>
       </c>
-      <c r="L445" s="10">
+      <c r="L445" s="19">
         <f t="shared" si="13"/>
         <v>-0.61425564756617401</v>
       </c>
@@ -33252,7 +33322,7 @@
       <c r="K446" s="10">
         <v>61.82397380318033</v>
       </c>
-      <c r="L446" s="10">
+      <c r="L446" s="19">
         <f t="shared" si="13"/>
         <v>-0.30242646044819749</v>
       </c>
@@ -33292,7 +33362,7 @@
       <c r="K447" s="10">
         <v>32.707053916439136</v>
       </c>
-      <c r="L447" s="10">
+      <c r="L447" s="19">
         <f t="shared" si="13"/>
         <v>-0.39348794619159055</v>
       </c>
@@ -33332,7 +33402,7 @@
       <c r="K448" s="10">
         <v>43.310807829305034</v>
       </c>
-      <c r="L448" s="10">
+      <c r="L448" s="19">
         <f t="shared" si="13"/>
         <v>-0.44363964370138725</v>
       </c>
@@ -33372,7 +33442,7 @@
       <c r="K449" s="10">
         <v>73.520753699141281</v>
       </c>
-      <c r="L449" s="10">
+      <c r="L449" s="19">
         <f t="shared" si="13"/>
         <v>-0.29842061511853957</v>
       </c>
@@ -33412,7 +33482,7 @@
       <c r="K450" s="10">
         <v>53.380532408043727</v>
       </c>
-      <c r="L450" s="10">
+      <c r="L450" s="19">
         <f t="shared" si="13"/>
         <v>2.563519491358348E-2</v>
       </c>
@@ -33467,7 +33537,7 @@
       <c r="K451" s="10">
         <v>52.550400098141971</v>
       </c>
-      <c r="L451" s="10">
+      <c r="L451" s="19">
         <f t="shared" ref="L451:L514" si="15">IF(OR(K451=0,I451=G451,J451=F451),"",0.4*((3*(E451-H451)/K451)/(1+ABS(3*(E451-H451)/K451)))+0.45*((I451+G451-2*H451)/(I451-G451))+0.15*((J451+F451-2*H451)/(J451-F451)))</f>
         <v>-0.61425564756617401</v>
       </c>
@@ -33507,7 +33577,7 @@
       <c r="K452" s="10">
         <v>39.19736690032088</v>
       </c>
-      <c r="L452" s="10">
+      <c r="L452" s="19">
         <f t="shared" si="15"/>
         <v>-0.34044847878807127</v>
       </c>
@@ -33547,7 +33617,7 @@
       <c r="K453" s="10">
         <v>44.064003122982612</v>
       </c>
-      <c r="L453" s="10">
+      <c r="L453" s="19">
         <f t="shared" si="15"/>
         <v>-0.41124063712499587</v>
       </c>
@@ -33587,7 +33657,7 @@
       <c r="K454" s="10">
         <v>37.007673607771878</v>
       </c>
-      <c r="L454" s="10">
+      <c r="L454" s="19">
         <f t="shared" si="15"/>
         <v>-0.43089879465269409</v>
       </c>
@@ -33627,7 +33697,7 @@
       <c r="K455" s="10">
         <v>42.561466476456637</v>
       </c>
-      <c r="L455" s="10">
+      <c r="L455" s="19">
         <f t="shared" si="15"/>
         <v>-0.25489113186267476</v>
       </c>
@@ -33667,7 +33737,7 @@
       <c r="K456" s="10">
         <v>45.402755221031484</v>
       </c>
-      <c r="L456" s="10">
+      <c r="L456" s="19">
         <f t="shared" si="15"/>
         <v>-0.2387026772439185</v>
       </c>
@@ -33707,7 +33777,7 @@
       <c r="K457" s="10">
         <v>48.211272729748821</v>
       </c>
-      <c r="L457" s="10">
+      <c r="L457" s="19">
         <f t="shared" si="15"/>
         <v>-0.53463040328193345</v>
       </c>
@@ -33747,7 +33817,7 @@
       <c r="K458" s="10">
         <v>67.383421717313624</v>
       </c>
-      <c r="L458" s="10">
+      <c r="L458" s="19">
         <f t="shared" si="15"/>
         <v>-0.24559086972539587</v>
       </c>
@@ -33787,7 +33857,7 @@
       <c r="K459" s="10">
         <v>30.956834906605707</v>
       </c>
-      <c r="L459" s="10">
+      <c r="L459" s="19">
         <f t="shared" si="15"/>
         <v>-0.268998459222269</v>
       </c>
@@ -33827,7 +33897,7 @@
       <c r="K460" s="10">
         <v>54.500081021599833</v>
       </c>
-      <c r="L460" s="10">
+      <c r="L460" s="19">
         <f t="shared" si="15"/>
         <v>-0.14928388152710767</v>
       </c>
@@ -33867,7 +33937,7 @@
       <c r="K461" s="10">
         <v>28.291363992271719</v>
       </c>
-      <c r="L461" s="10">
+      <c r="L461" s="19">
         <f t="shared" si="15"/>
         <v>-0.45194135207933656</v>
       </c>
@@ -33907,7 +33977,7 @@
       <c r="K462" s="10">
         <v>40.543750857694739</v>
       </c>
-      <c r="L462" s="10">
+      <c r="L462" s="19">
         <f t="shared" si="15"/>
         <v>-0.34168813253822328</v>
       </c>
@@ -33947,7 +34017,7 @@
       <c r="K463" s="10">
         <v>59.571201699918042</v>
       </c>
-      <c r="L463" s="10">
+      <c r="L463" s="19">
         <f t="shared" si="15"/>
         <v>-0.40703288905825291</v>
       </c>
@@ -33987,7 +34057,7 @@
       <c r="K464" s="10">
         <v>34.27313982014654</v>
       </c>
-      <c r="L464" s="10">
+      <c r="L464" s="19">
         <f t="shared" si="15"/>
         <v>-0.63059271721107857</v>
       </c>
@@ -34027,7 +34097,7 @@
       <c r="K465" s="10">
         <v>56.955691995283715</v>
       </c>
-      <c r="L465" s="10">
+      <c r="L465" s="19">
         <f t="shared" si="15"/>
         <v>-0.25247384602016115</v>
       </c>
@@ -34067,7 +34137,7 @@
       <c r="K466" s="10">
         <v>54.764046582566408</v>
       </c>
-      <c r="L466" s="10">
+      <c r="L466" s="19">
         <f t="shared" si="15"/>
         <v>-0.53238601638498917</v>
       </c>
@@ -34107,7 +34177,7 @@
       <c r="K467" s="10">
         <v>55.757136500127764</v>
       </c>
-      <c r="L467" s="10">
+      <c r="L467" s="19">
         <f t="shared" si="15"/>
         <v>-0.29717680640962907</v>
       </c>
@@ -34147,7 +34217,7 @@
       <c r="K468" s="10">
         <v>59.139689894729841</v>
       </c>
-      <c r="L468" s="10">
+      <c r="L468" s="19">
         <f t="shared" si="15"/>
         <v>-0.3066413806622163</v>
       </c>
@@ -34187,7 +34257,7 @@
       <c r="K469" s="10">
         <v>58.565690013670491</v>
       </c>
-      <c r="L469" s="10">
+      <c r="L469" s="19">
         <f t="shared" si="15"/>
         <v>-0.16244038317478265</v>
       </c>
@@ -34227,7 +34297,7 @@
       <c r="K470" s="10">
         <v>58.285726582262178</v>
       </c>
-      <c r="L470" s="10">
+      <c r="L470" s="19">
         <f t="shared" si="15"/>
         <v>-0.43867374703933137</v>
       </c>
@@ -34267,7 +34337,7 @@
       <c r="K471" s="10">
         <v>51.057335391353512</v>
       </c>
-      <c r="L471" s="10">
+      <c r="L471" s="19">
         <f t="shared" si="15"/>
         <v>-0.46780806875300912</v>
       </c>
@@ -34307,7 +34377,7 @@
       <c r="K472" s="10">
         <v>58.045476963818579</v>
       </c>
-      <c r="L472" s="10">
+      <c r="L472" s="19">
         <f t="shared" si="15"/>
         <v>-0.45925668120854574</v>
       </c>
@@ -34347,7 +34417,7 @@
       <c r="K473" s="10">
         <v>60.134571875867529</v>
       </c>
-      <c r="L473" s="10">
+      <c r="L473" s="19">
         <f t="shared" si="15"/>
         <v>-0.18000809005359794</v>
       </c>
@@ -34387,7 +34457,7 @@
       <c r="K474" s="10">
         <v>64.152197101026005</v>
       </c>
-      <c r="L474" s="10">
+      <c r="L474" s="19">
         <f t="shared" si="15"/>
         <v>-0.25506752885521011</v>
       </c>
@@ -34427,7 +34497,7 @@
       <c r="K475" s="10">
         <v>62.876249643492336</v>
       </c>
-      <c r="L475" s="10">
+      <c r="L475" s="19">
         <f t="shared" si="15"/>
         <v>-0.31300125541918389</v>
       </c>
@@ -34467,7 +34537,7 @@
       <c r="K476" s="10">
         <v>69.115289526281927</v>
       </c>
-      <c r="L476" s="10">
+      <c r="L476" s="19">
         <f t="shared" si="15"/>
         <v>-0.39459253747351297</v>
       </c>
@@ -34507,7 +34577,7 @@
       <c r="K477" s="10">
         <v>65.005582381367375</v>
       </c>
-      <c r="L477" s="10">
+      <c r="L477" s="19">
         <f t="shared" si="15"/>
         <v>-0.42965490318204097</v>
       </c>
@@ -34547,7 +34617,7 @@
       <c r="K478" s="10">
         <v>63.076909141434115</v>
       </c>
-      <c r="L478" s="10">
+      <c r="L478" s="19">
         <f t="shared" si="15"/>
         <v>-0.22385139711682031</v>
       </c>
@@ -34587,7 +34657,7 @@
       <c r="K479" s="10">
         <v>62.189535700762221</v>
       </c>
-      <c r="L479" s="10">
+      <c r="L479" s="19">
         <f t="shared" si="15"/>
         <v>-0.14758775380430583</v>
       </c>
@@ -34627,7 +34697,7 @@
       <c r="K480" s="10">
         <v>56.905421187389813</v>
       </c>
-      <c r="L480" s="10">
+      <c r="L480" s="19">
         <f t="shared" si="15"/>
         <v>-0.26794521458194076</v>
       </c>
@@ -34667,7 +34737,7 @@
       <c r="K481" s="10">
         <v>54.437212556646394</v>
       </c>
-      <c r="L481" s="10">
+      <c r="L481" s="19">
         <f t="shared" si="15"/>
         <v>1.593289145044012E-2</v>
       </c>
@@ -34707,7 +34777,7 @@
       <c r="K482" s="10">
         <v>45.740626444393065</v>
       </c>
-      <c r="L482" s="10">
+      <c r="L482" s="19">
         <f t="shared" si="15"/>
         <v>0.20149649843183942</v>
       </c>
@@ -34747,7 +34817,7 @@
       <c r="K483" s="10">
         <v>39.805313843808364</v>
       </c>
-      <c r="L483" s="10">
+      <c r="L483" s="19">
         <f t="shared" si="15"/>
         <v>0.31726693902862885</v>
       </c>
@@ -34787,7 +34857,7 @@
       <c r="K484" s="10">
         <v>43.806543446148218</v>
       </c>
-      <c r="L484" s="10">
+      <c r="L484" s="19">
         <f t="shared" si="15"/>
         <v>0.16508046126928461</v>
       </c>
@@ -34827,7 +34897,7 @@
       <c r="K485" s="10">
         <v>51.716685867776327</v>
       </c>
-      <c r="L485" s="10">
+      <c r="L485" s="19">
         <f t="shared" si="15"/>
         <v>0.15307407070595128</v>
       </c>
@@ -34867,7 +34937,7 @@
       <c r="K486" s="10">
         <v>58.081158609585614</v>
       </c>
-      <c r="L486" s="10">
+      <c r="L486" s="19">
         <f t="shared" si="15"/>
         <v>-0.25753303825342649</v>
       </c>
@@ -34907,7 +34977,7 @@
       <c r="K487" s="10">
         <v>56.825158228391729</v>
       </c>
-      <c r="L487" s="10">
+      <c r="L487" s="19">
         <f t="shared" si="15"/>
         <v>0.4157395586373</v>
       </c>
@@ -34947,7 +35017,7 @@
       <c r="K488" s="10">
         <v>67.174925319764782</v>
       </c>
-      <c r="L488" s="10">
+      <c r="L488" s="19">
         <f t="shared" si="15"/>
         <v>0.3482631802180513</v>
       </c>
@@ -34987,7 +35057,7 @@
       <c r="K489" s="10">
         <v>45.345586579315764</v>
       </c>
-      <c r="L489" s="10">
+      <c r="L489" s="19">
         <f t="shared" si="15"/>
         <v>4.0486218264600853E-2</v>
       </c>
@@ -35027,7 +35097,7 @@
       <c r="K490" s="10">
         <v>57.374167645036572</v>
       </c>
-      <c r="L490" s="10">
+      <c r="L490" s="19">
         <f t="shared" si="15"/>
         <v>0.23248632778661743</v>
       </c>
@@ -35067,7 +35137,7 @@
       <c r="K491" s="10">
         <v>51.179056631292994</v>
       </c>
-      <c r="L491" s="10">
+      <c r="L491" s="19">
         <f t="shared" si="15"/>
         <v>-0.12921266168992826</v>
       </c>
@@ -35107,7 +35177,7 @@
       <c r="K492" s="10">
         <v>53.107945174576969</v>
       </c>
-      <c r="L492" s="10">
+      <c r="L492" s="19">
         <f t="shared" si="15"/>
         <v>-0.12615100102774618</v>
       </c>
@@ -35147,7 +35217,7 @@
       <c r="K493" s="10">
         <v>58.422447069085209</v>
       </c>
-      <c r="L493" s="10">
+      <c r="L493" s="19">
         <f t="shared" si="15"/>
         <v>7.8154363094919715E-2</v>
       </c>
@@ -35187,7 +35257,7 @@
       <c r="K494" s="10">
         <v>34.740224585926597</v>
       </c>
-      <c r="L494" s="10">
+      <c r="L494" s="19">
         <f t="shared" si="15"/>
         <v>-0.11304615180297306</v>
       </c>
@@ -35227,7 +35297,7 @@
       <c r="K495" s="10">
         <v>53.475606892716783</v>
       </c>
-      <c r="L495" s="10">
+      <c r="L495" s="19">
         <f t="shared" si="15"/>
         <v>-0.18487841166326244</v>
       </c>
@@ -35267,7 +35337,7 @@
       <c r="K496" s="10">
         <v>49.782638326185712</v>
       </c>
-      <c r="L496" s="10">
+      <c r="L496" s="19">
         <f t="shared" si="15"/>
         <v>-0.35885916813929786</v>
       </c>
@@ -35307,7 +35377,7 @@
       <c r="K497" s="10">
         <v>64.682794789944978</v>
       </c>
-      <c r="L497" s="10">
+      <c r="L497" s="19">
         <f t="shared" si="15"/>
         <v>-0.28939428579576199</v>
       </c>
@@ -35347,7 +35417,7 @@
       <c r="K498" s="10">
         <v>58.632036840912747</v>
       </c>
-      <c r="L498" s="10">
+      <c r="L498" s="19">
         <f t="shared" si="15"/>
         <v>-7.0763615165079702E-2</v>
       </c>
@@ -35387,7 +35457,7 @@
       <c r="K499" s="10">
         <v>60.952600023373698</v>
       </c>
-      <c r="L499" s="10">
+      <c r="L499" s="19">
         <f t="shared" si="15"/>
         <v>-0.33719528893783213</v>
       </c>
@@ -35427,7 +35497,7 @@
       <c r="K500" s="10">
         <v>66.58828791661989</v>
       </c>
-      <c r="L500" s="10">
+      <c r="L500" s="19">
         <f t="shared" si="15"/>
         <v>-0.27143178129120216</v>
       </c>
@@ -35467,7 +35537,7 @@
       <c r="K501" s="10">
         <v>64.934642249421515</v>
       </c>
-      <c r="L501" s="10">
+      <c r="L501" s="19">
         <f t="shared" si="15"/>
         <v>-0.36920691469724082</v>
       </c>
@@ -35507,7 +35577,7 @@
       <c r="K502" s="10">
         <v>41.40576650661113</v>
       </c>
-      <c r="L502" s="10">
+      <c r="L502" s="19">
         <f t="shared" si="15"/>
         <v>7.3152876577749645E-2</v>
       </c>
@@ -35547,7 +35617,7 @@
       <c r="K503" s="10">
         <v>31.776137400465753</v>
       </c>
-      <c r="L503" s="10">
+      <c r="L503" s="19">
         <f t="shared" si="15"/>
         <v>0.64777301410724086</v>
       </c>
@@ -35587,7 +35657,7 @@
       <c r="K504" s="10">
         <v>53.128851841152972</v>
       </c>
-      <c r="L504" s="10">
+      <c r="L504" s="19">
         <f t="shared" si="15"/>
         <v>7.0588131376970079E-2</v>
       </c>
@@ -35627,7 +35697,7 @@
       <c r="K505" s="10">
         <v>38.552772794324362</v>
       </c>
-      <c r="L505" s="10">
+      <c r="L505" s="19">
         <f t="shared" si="15"/>
         <v>-0.2189747596808363</v>
       </c>
@@ -35667,7 +35737,7 @@
       <c r="K506" s="10">
         <v>57.386093846065783</v>
       </c>
-      <c r="L506" s="10">
+      <c r="L506" s="19">
         <f t="shared" si="15"/>
         <v>-0.10934561561073808</v>
       </c>
@@ -35707,7 +35777,7 @@
       <c r="K507" s="10">
         <v>56.216108002049303</v>
       </c>
-      <c r="L507" s="10">
+      <c r="L507" s="19">
         <f t="shared" si="15"/>
         <v>0.1804174754246865</v>
       </c>
@@ -35747,7 +35817,7 @@
       <c r="K508" s="10">
         <v>49.345050684492676</v>
       </c>
-      <c r="L508" s="10">
+      <c r="L508" s="19">
         <f t="shared" si="15"/>
         <v>1.6047484914216814E-2</v>
       </c>
@@ -35787,7 +35857,7 @@
       <c r="K509" s="10">
         <v>47.469934929618582</v>
       </c>
-      <c r="L509" s="10">
+      <c r="L509" s="19">
         <f t="shared" si="15"/>
         <v>6.2590666076186199E-2</v>
       </c>
@@ -35827,7 +35897,7 @@
       <c r="K510" s="10">
         <v>55.942502690409157</v>
       </c>
-      <c r="L510" s="10">
+      <c r="L510" s="19">
         <f t="shared" si="15"/>
         <v>-2.3186898599818061E-2</v>
       </c>
@@ -35867,7 +35937,7 @@
       <c r="K511" s="10">
         <v>51.171281684204004</v>
       </c>
-      <c r="L511" s="10">
+      <c r="L511" s="19">
         <f t="shared" si="15"/>
         <v>8.6771076891831236E-2</v>
       </c>
@@ -35907,7 +35977,7 @@
       <c r="K512" s="10">
         <v>44.987298684587493</v>
       </c>
-      <c r="L512" s="10">
+      <c r="L512" s="19">
         <f t="shared" si="15"/>
         <v>0.11819402831942208</v>
       </c>
@@ -35947,7 +36017,7 @@
       <c r="K513" s="10">
         <v>52.267754767722032</v>
       </c>
-      <c r="L513" s="10">
+      <c r="L513" s="19">
         <f t="shared" si="15"/>
         <v>6.7790523859577109E-2</v>
       </c>
@@ -35987,7 +36057,7 @@
       <c r="K514" s="10">
         <v>59.274689783916969</v>
       </c>
-      <c r="L514" s="10">
+      <c r="L514" s="19">
         <f t="shared" si="15"/>
         <v>-0.54413855029629998</v>
       </c>
@@ -36042,7 +36112,7 @@
       <c r="K515" s="10">
         <v>56.059043268503345</v>
       </c>
-      <c r="L515" s="10">
+      <c r="L515" s="19">
         <f t="shared" ref="L515:L578" si="17">IF(OR(K515=0,I515=G515,J515=F515),"",0.4*((3*(E515-H515)/K515)/(1+ABS(3*(E515-H515)/K515)))+0.45*((I515+G515-2*H515)/(I515-G515))+0.15*((J515+F515-2*H515)/(J515-F515)))</f>
         <v>-0.42384229878060409</v>
       </c>
@@ -36082,7 +36152,7 @@
       <c r="K516" s="10">
         <v>63.557616832598796</v>
       </c>
-      <c r="L516" s="10">
+      <c r="L516" s="19">
         <f t="shared" si="17"/>
         <v>-0.41220352717462805</v>
       </c>
@@ -36122,7 +36192,7 @@
       <c r="K517" s="10">
         <v>60.325228184861054</v>
       </c>
-      <c r="L517" s="10">
+      <c r="L517" s="19">
         <f t="shared" si="17"/>
         <v>-0.24870694077705288</v>
       </c>
@@ -36162,7 +36232,7 @@
       <c r="K518" s="10">
         <v>66.025148795269672</v>
       </c>
-      <c r="L518" s="10">
+      <c r="L518" s="19">
         <f t="shared" si="17"/>
         <v>-0.3443452631296296</v>
       </c>
@@ -36202,7 +36272,7 @@
       <c r="K519" s="10">
         <v>65.838860527469308</v>
       </c>
-      <c r="L519" s="10">
+      <c r="L519" s="19">
         <f t="shared" si="17"/>
         <v>-0.36986874204754489</v>
       </c>
@@ -36242,7 +36312,7 @@
       <c r="K520" s="10">
         <v>58.204477883361697</v>
       </c>
-      <c r="L520" s="10">
+      <c r="L520" s="19">
         <f t="shared" si="17"/>
         <v>-0.45588844834134962</v>
       </c>
@@ -36282,7 +36352,7 @@
       <c r="K521" s="10">
         <v>67.614110056909553</v>
       </c>
-      <c r="L521" s="10">
+      <c r="L521" s="19">
         <f t="shared" si="17"/>
         <v>-0.58655875483783149</v>
       </c>
@@ -36322,7 +36392,7 @@
       <c r="K522" s="10">
         <v>74.11356391861203</v>
       </c>
-      <c r="L522" s="10">
+      <c r="L522" s="19">
         <f t="shared" si="17"/>
         <v>-0.68846193356277419</v>
       </c>
@@ -36362,7 +36432,7 @@
       <c r="K523" s="10">
         <v>73.151472857827756</v>
       </c>
-      <c r="L523" s="10">
+      <c r="L523" s="19">
         <f t="shared" si="17"/>
         <v>-0.64019235487876625</v>
       </c>
@@ -36402,7 +36472,7 @@
       <c r="K524" s="10">
         <v>61.145192933839347</v>
       </c>
-      <c r="L524" s="10">
+      <c r="L524" s="19">
         <f t="shared" si="17"/>
         <v>-8.1960387697874532E-2</v>
       </c>
@@ -36442,7 +36512,7 @@
       <c r="K525" s="10">
         <v>59.461294600399974</v>
       </c>
-      <c r="L525" s="10">
+      <c r="L525" s="19">
         <f t="shared" si="17"/>
         <v>-9.7896538079194587E-2</v>
       </c>
@@ -36482,7 +36552,7 @@
       <c r="K526" s="10">
         <v>55.474316952158986</v>
       </c>
-      <c r="L526" s="10">
+      <c r="L526" s="19">
         <f t="shared" si="17"/>
         <v>-0.56330229907392726</v>
       </c>
@@ -36522,7 +36592,7 @@
       <c r="K527" s="10">
         <v>47.642829505911699</v>
       </c>
-      <c r="L527" s="10">
+      <c r="L527" s="19">
         <f t="shared" si="17"/>
         <v>-0.5185419923789788</v>
       </c>
@@ -36562,7 +36632,7 @@
       <c r="K528" s="10">
         <v>38.757015074458316</v>
       </c>
-      <c r="L528" s="10">
+      <c r="L528" s="19">
         <f t="shared" si="17"/>
         <v>-0.42078968461197541</v>
       </c>
@@ -36602,7 +36672,7 @@
       <c r="K529" s="10">
         <v>40.898792194128127</v>
       </c>
-      <c r="L529" s="10">
+      <c r="L529" s="19">
         <f t="shared" si="17"/>
         <v>-0.34248670449593954</v>
       </c>
@@ -36642,7 +36712,7 @@
       <c r="K530" s="10">
         <v>44.684911157119551</v>
       </c>
-      <c r="L530" s="10">
+      <c r="L530" s="19">
         <f t="shared" si="17"/>
         <v>-0.31268995648925307</v>
       </c>
@@ -36682,7 +36752,7 @@
       <c r="K531" s="10">
         <v>38.351540526685874</v>
       </c>
-      <c r="L531" s="10">
+      <c r="L531" s="19">
         <f t="shared" si="17"/>
         <v>-0.45071255319162962</v>
       </c>
@@ -36722,7 +36792,7 @@
       <c r="K532" s="10">
         <v>52.845347659285657</v>
       </c>
-      <c r="L532" s="10">
+      <c r="L532" s="19">
         <f t="shared" si="17"/>
         <v>-0.49441054016760566</v>
       </c>
@@ -36762,7 +36832,7 @@
       <c r="K533" s="10">
         <v>50.592178955136646</v>
       </c>
-      <c r="L533" s="10">
+      <c r="L533" s="19">
         <f t="shared" si="17"/>
         <v>-0.64548429038307387</v>
       </c>
@@ -36802,7 +36872,7 @@
       <c r="K534" s="10">
         <v>45.8727017663767</v>
       </c>
-      <c r="L534" s="10">
+      <c r="L534" s="19">
         <f t="shared" si="17"/>
         <v>-0.61334145712303245</v>
       </c>
@@ -36842,7 +36912,7 @@
       <c r="K535" s="10">
         <v>74.814030546861105</v>
       </c>
-      <c r="L535" s="10">
+      <c r="L535" s="19">
         <f t="shared" si="17"/>
         <v>-0.66241387972676347</v>
       </c>
@@ -36882,7 +36952,7 @@
       <c r="K536" s="10">
         <v>53.632347230101267</v>
       </c>
-      <c r="L536" s="10">
+      <c r="L536" s="19">
         <f t="shared" si="17"/>
         <v>-0.47145024278706799</v>
       </c>
@@ -36922,7 +36992,7 @@
       <c r="K537" s="10">
         <v>48.896571681685643</v>
       </c>
-      <c r="L537" s="10">
+      <c r="L537" s="19">
         <f t="shared" si="17"/>
         <v>-0.4543657387617257</v>
       </c>
@@ -36962,7 +37032,7 @@
       <c r="K538" s="10">
         <v>61.205113840328835</v>
       </c>
-      <c r="L538" s="10">
+      <c r="L538" s="19">
         <f t="shared" si="17"/>
         <v>-0.52437019289779496</v>
       </c>
@@ -37002,7 +37072,7 @@
       <c r="K539" s="10">
         <v>57.785327901705259</v>
       </c>
-      <c r="L539" s="10">
+      <c r="L539" s="19">
         <f t="shared" si="17"/>
         <v>-0.24594148365976176</v>
       </c>
@@ -37042,7 +37112,7 @@
       <c r="K540" s="10">
         <v>79.940100561197539</v>
       </c>
-      <c r="L540" s="10">
+      <c r="L540" s="19">
         <f t="shared" si="17"/>
         <v>-0.54075642013616698</v>
       </c>
@@ -37082,7 +37152,7 @@
       <c r="K541" s="10">
         <v>73.199803298495794</v>
       </c>
-      <c r="L541" s="10">
+      <c r="L541" s="19">
         <f t="shared" si="17"/>
         <v>-0.52208554757920866</v>
       </c>
@@ -37122,7 +37192,7 @@
       <c r="K542" s="10">
         <v>81.972971493996454</v>
       </c>
-      <c r="L542" s="10">
+      <c r="L542" s="19">
         <f t="shared" si="17"/>
         <v>-0.37595266225372997</v>
       </c>
@@ -37162,7 +37232,7 @@
       <c r="K543" s="10">
         <v>70.252181451028676</v>
       </c>
-      <c r="L543" s="10">
+      <c r="L543" s="19">
         <f t="shared" si="17"/>
         <v>-0.62210823303714968</v>
       </c>
@@ -37202,7 +37272,7 @@
       <c r="K544" s="10">
         <v>45.034554333138182</v>
       </c>
-      <c r="L544" s="10">
+      <c r="L544" s="19">
         <f t="shared" si="17"/>
         <v>-0.63710426148559118</v>
       </c>
@@ -37242,7 +37312,7 @@
       <c r="K545" s="10">
         <v>31.902622834964525</v>
       </c>
-      <c r="L545" s="10">
+      <c r="L545" s="19">
         <f t="shared" si="17"/>
         <v>-0.37111555806891244</v>
       </c>
@@ -37282,7 +37352,7 @@
       <c r="K546" s="10">
         <v>33.812107442362681</v>
       </c>
-      <c r="L546" s="10">
+      <c r="L546" s="19">
         <f t="shared" si="17"/>
         <v>-0.50597927402539467</v>
       </c>
@@ -37322,7 +37392,7 @@
       <c r="K547" s="10">
         <v>44.571790079241985</v>
       </c>
-      <c r="L547" s="10">
+      <c r="L547" s="19">
         <f t="shared" si="17"/>
         <v>-0.41103574835991097</v>
       </c>
@@ -37362,7 +37432,7 @@
       <c r="K548" s="10">
         <v>51.225600837105361</v>
       </c>
-      <c r="L548" s="10">
+      <c r="L548" s="19">
         <f t="shared" si="17"/>
         <v>-0.52509828434487749</v>
       </c>
@@ -37402,7 +37472,7 @@
       <c r="K549" s="10">
         <v>31.324298121335335</v>
       </c>
-      <c r="L549" s="10">
+      <c r="L549" s="19">
         <f t="shared" si="17"/>
         <v>-0.37840802257851414</v>
       </c>
@@ -37442,7 +37512,7 @@
       <c r="K550" s="10">
         <v>40.560500686953205</v>
       </c>
-      <c r="L550" s="10">
+      <c r="L550" s="19">
         <f t="shared" si="17"/>
         <v>-0.33662057290293174</v>
       </c>
@@ -37482,7 +37552,7 @@
       <c r="K551" s="10">
         <v>41.368869961849803</v>
       </c>
-      <c r="L551" s="10">
+      <c r="L551" s="19">
         <f t="shared" si="17"/>
         <v>-0.35348680502100455</v>
       </c>
@@ -37522,7 +37592,7 @@
       <c r="K552" s="10">
         <v>36.188090354038536</v>
       </c>
-      <c r="L552" s="10">
+      <c r="L552" s="19">
         <f t="shared" si="17"/>
         <v>-0.35496998956097708</v>
       </c>
@@ -37562,7 +37632,7 @@
       <c r="K553" s="10">
         <v>37.743249902447104</v>
       </c>
-      <c r="L553" s="10">
+      <c r="L553" s="19">
         <f t="shared" si="17"/>
         <v>-0.57790121921733639</v>
       </c>
@@ -37602,7 +37672,7 @@
       <c r="K554" s="10">
         <v>38.125600177425255</v>
       </c>
-      <c r="L554" s="10">
+      <c r="L554" s="19">
         <f t="shared" si="17"/>
         <v>-0.39477659360081063</v>
       </c>
@@ -37642,7 +37712,7 @@
       <c r="K555" s="10">
         <v>35.21374453775752</v>
       </c>
-      <c r="L555" s="10">
+      <c r="L555" s="19">
         <f t="shared" si="17"/>
         <v>-0.58506248254347315</v>
       </c>
@@ -37682,7 +37752,7 @@
       <c r="K556" s="10">
         <v>37.200813418944776</v>
       </c>
-      <c r="L556" s="10">
+      <c r="L556" s="19">
         <f t="shared" si="17"/>
         <v>-0.54259778775852263</v>
       </c>
@@ -37722,7 +37792,7 @@
       <c r="K557" s="10">
         <v>46.401461865606194</v>
       </c>
-      <c r="L557" s="10">
+      <c r="L557" s="19">
         <f t="shared" si="17"/>
         <v>-0.53392930579355702</v>
       </c>
@@ -37762,7 +37832,7 @@
       <c r="K558" s="10">
         <v>47.306097125086168</v>
       </c>
-      <c r="L558" s="10">
+      <c r="L558" s="19">
         <f t="shared" si="17"/>
         <v>-0.43005370010215344</v>
       </c>
@@ -37802,7 +37872,7 @@
       <c r="K559" s="10">
         <v>40.981014136054526</v>
       </c>
-      <c r="L559" s="10">
+      <c r="L559" s="19">
         <f t="shared" si="17"/>
         <v>-0.39738570569235493</v>
       </c>
@@ -37842,7 +37912,7 @@
       <c r="K560" s="10">
         <v>33.994932520079296</v>
       </c>
-      <c r="L560" s="10">
+      <c r="L560" s="19">
         <f t="shared" si="17"/>
         <v>-0.6470700436205471</v>
       </c>
@@ -37882,7 +37952,7 @@
       <c r="K561" s="10">
         <v>44.968363852363964</v>
       </c>
-      <c r="L561" s="10">
+      <c r="L561" s="19">
         <f t="shared" si="17"/>
         <v>-0.32794460020089505</v>
       </c>
@@ -37922,7 +37992,7 @@
       <c r="K562" s="10">
         <v>49.659201917259722</v>
       </c>
-      <c r="L562" s="10">
+      <c r="L562" s="19">
         <f t="shared" si="17"/>
         <v>-0.37273465690567598</v>
       </c>
@@ -37962,7 +38032,7 @@
       <c r="K563" s="10">
         <v>64.362780454268531</v>
       </c>
-      <c r="L563" s="10">
+      <c r="L563" s="19">
         <f t="shared" si="17"/>
         <v>-0.39240133151649076</v>
       </c>
@@ -38002,7 +38072,7 @@
       <c r="K564" s="10">
         <v>64.776799001384475</v>
       </c>
-      <c r="L564" s="10">
+      <c r="L564" s="19">
         <f t="shared" si="17"/>
         <v>-0.37439053557559565</v>
       </c>
@@ -38042,7 +38112,7 @@
       <c r="K565" s="10">
         <v>65.166932244503599</v>
       </c>
-      <c r="L565" s="10">
+      <c r="L565" s="19">
         <f t="shared" si="17"/>
         <v>-0.69019647949319618</v>
       </c>
@@ -38082,7 +38152,7 @@
       <c r="K566" s="10">
         <v>59.958870200350503</v>
       </c>
-      <c r="L566" s="10">
+      <c r="L566" s="19">
         <f t="shared" si="17"/>
         <v>-0.6511325382082126</v>
       </c>
@@ -38122,7 +38192,7 @@
       <c r="K567" s="10">
         <v>59.381621852968017</v>
       </c>
-      <c r="L567" s="10">
+      <c r="L567" s="19">
         <f t="shared" si="17"/>
         <v>-0.6645381333243372</v>
       </c>
@@ -38162,7 +38232,7 @@
       <c r="K568" s="10">
         <v>43.61543763393874</v>
       </c>
-      <c r="L568" s="10">
+      <c r="L568" s="19">
         <f t="shared" si="17"/>
         <v>-0.49398848797371364</v>
       </c>
@@ -38202,7 +38272,7 @@
       <c r="K569" s="10">
         <v>45.396879132363082</v>
       </c>
-      <c r="L569" s="10">
+      <c r="L569" s="19">
         <f t="shared" si="17"/>
         <v>-0.23278119896539043</v>
       </c>
@@ -38242,7 +38312,7 @@
       <c r="K570" s="10">
         <v>57.001842496633159</v>
       </c>
-      <c r="L570" s="10">
+      <c r="L570" s="19">
         <f t="shared" si="17"/>
         <v>-0.588262113780741</v>
       </c>
@@ -38282,7 +38352,7 @@
       <c r="K571" s="10">
         <v>43.069217656771137</v>
       </c>
-      <c r="L571" s="10">
+      <c r="L571" s="19">
         <f t="shared" si="17"/>
         <v>-0.5095049823132185</v>
       </c>
@@ -38322,7 +38392,7 @@
       <c r="K572" s="10">
         <v>48.392374712148168</v>
       </c>
-      <c r="L572" s="10">
+      <c r="L572" s="19">
         <f t="shared" si="17"/>
         <v>-0.24911193832400008</v>
       </c>
@@ -38362,7 +38432,7 @@
       <c r="K573" s="10">
         <v>40.948483493075209</v>
       </c>
-      <c r="L573" s="10">
+      <c r="L573" s="19">
         <f t="shared" si="17"/>
         <v>0.10637968178854849</v>
       </c>
@@ -38402,7 +38472,7 @@
       <c r="K574" s="10">
         <v>37.402091766235387</v>
       </c>
-      <c r="L574" s="10">
+      <c r="L574" s="19">
         <f t="shared" si="17"/>
         <v>-0.18873247480868943</v>
       </c>
@@ -38442,7 +38512,7 @@
       <c r="K575" s="10">
         <v>46.287563991280784</v>
       </c>
-      <c r="L575" s="10">
+      <c r="L575" s="19">
         <f t="shared" si="17"/>
         <v>-0.60853552605310623</v>
       </c>
@@ -38482,7 +38552,7 @@
       <c r="K576" s="10">
         <v>51.63023920146022</v>
       </c>
-      <c r="L576" s="10">
+      <c r="L576" s="19">
         <f t="shared" si="17"/>
         <v>-0.53126625695772511</v>
       </c>
@@ -38522,7 +38592,7 @@
       <c r="K577" s="10">
         <v>38.938715947404972</v>
       </c>
-      <c r="L577" s="10">
+      <c r="L577" s="19">
         <f t="shared" si="17"/>
         <v>-0.47058508986253789</v>
       </c>
@@ -38562,7 +38632,7 @@
       <c r="K578" s="10">
         <v>32.992166958557021</v>
       </c>
-      <c r="L578" s="10">
+      <c r="L578" s="19">
         <f t="shared" si="17"/>
         <v>-0.57827562717259395</v>
       </c>
@@ -38617,7 +38687,7 @@
       <c r="K579" s="10">
         <v>41.819650581896475</v>
       </c>
-      <c r="L579" s="10">
+      <c r="L579" s="19">
         <f t="shared" ref="L579:L642" si="19">IF(OR(K579=0,I579=G579,J579=F579),"",0.4*((3*(E579-H579)/K579)/(1+ABS(3*(E579-H579)/K579)))+0.45*((I579+G579-2*H579)/(I579-G579))+0.15*((J579+F579-2*H579)/(J579-F579)))</f>
         <v>-0.37633512027965205</v>
       </c>
@@ -38657,7 +38727,7 @@
       <c r="K580" s="10">
         <v>50.264603848036046</v>
       </c>
-      <c r="L580" s="10">
+      <c r="L580" s="19">
         <f t="shared" si="19"/>
         <v>-0.52090642588951419</v>
       </c>
@@ -38697,7 +38767,7 @@
       <c r="K581" s="10">
         <v>42.982310991380189</v>
       </c>
-      <c r="L581" s="10">
+      <c r="L581" s="19">
         <f t="shared" si="19"/>
         <v>-0.49322662267524464</v>
       </c>
@@ -38737,7 +38807,7 @@
       <c r="K582" s="10">
         <v>42.602862162618685</v>
       </c>
-      <c r="L582" s="10">
+      <c r="L582" s="19">
         <f t="shared" si="19"/>
         <v>-0.33130385553987873</v>
       </c>
@@ -38777,7 +38847,7 @@
       <c r="K583" s="10">
         <v>35.515471002867969</v>
       </c>
-      <c r="L583" s="10">
+      <c r="L583" s="19">
         <f t="shared" si="19"/>
         <v>-0.27650419555712624</v>
       </c>
@@ -38817,7 +38887,7 @@
       <c r="K584" s="10">
         <v>41.20422836194178</v>
       </c>
-      <c r="L584" s="10">
+      <c r="L584" s="19">
         <f t="shared" si="19"/>
         <v>-3.7991340439885689E-3</v>
       </c>
@@ -38857,7 +38927,7 @@
       <c r="K585" s="10">
         <v>46.305875728509086</v>
       </c>
-      <c r="L585" s="10">
+      <c r="L585" s="19">
         <f t="shared" si="19"/>
         <v>-0.17992340970708096</v>
       </c>
@@ -38897,7 +38967,7 @@
       <c r="K586" s="10">
         <v>52.28157999497369</v>
       </c>
-      <c r="L586" s="10">
+      <c r="L586" s="19">
         <f t="shared" si="19"/>
         <v>-0.1949779659474391</v>
       </c>
@@ -38937,7 +39007,7 @@
       <c r="K587" s="10">
         <v>45.246656707228858</v>
       </c>
-      <c r="L587" s="10">
+      <c r="L587" s="19">
         <f t="shared" si="19"/>
         <v>-0.42640692222375171</v>
       </c>
@@ -38977,7 +39047,7 @@
       <c r="K588" s="10">
         <v>42.836271786367632</v>
       </c>
-      <c r="L588" s="10">
+      <c r="L588" s="19">
         <f t="shared" si="19"/>
         <v>-9.8384623525616582E-2</v>
       </c>
@@ -39017,7 +39087,7 @@
       <c r="K589" s="10">
         <v>25.850229689501795</v>
       </c>
-      <c r="L589" s="10">
+      <c r="L589" s="19">
         <f t="shared" si="19"/>
         <v>0.46870144937669861</v>
       </c>
@@ -39057,7 +39127,7 @@
       <c r="K590" s="10">
         <v>29.219171788399478</v>
       </c>
-      <c r="L590" s="10">
+      <c r="L590" s="19">
         <f t="shared" si="19"/>
         <v>0.33114271987109539</v>
       </c>
@@ -39097,7 +39167,7 @@
       <c r="K591" s="10">
         <v>47.697764295090394</v>
       </c>
-      <c r="L591" s="10">
+      <c r="L591" s="19">
         <f t="shared" si="19"/>
         <v>-0.32168938923734675</v>
       </c>
@@ -39137,7 +39207,7 @@
       <c r="K592" s="10">
         <v>38.422382980352594</v>
       </c>
-      <c r="L592" s="10">
+      <c r="L592" s="19">
         <f t="shared" si="19"/>
         <v>-0.57755242856469347</v>
       </c>
@@ -39177,7 +39247,7 @@
       <c r="K593" s="10">
         <v>64.258296622360419</v>
       </c>
-      <c r="L593" s="10">
+      <c r="L593" s="19">
         <f t="shared" si="19"/>
         <v>-0.61488641492172325</v>
       </c>
@@ -39217,7 +39287,7 @@
       <c r="K594" s="10">
         <v>57.905260906954553</v>
       </c>
-      <c r="L594" s="10">
+      <c r="L594" s="19">
         <f t="shared" si="19"/>
         <v>-0.38093030814938006</v>
       </c>
@@ -39257,7 +39327,7 @@
       <c r="K595" s="10">
         <v>34.736286502733705</v>
       </c>
-      <c r="L595" s="10">
+      <c r="L595" s="19">
         <f t="shared" si="19"/>
         <v>-0.58651235380274258</v>
       </c>
@@ -39297,7 +39367,7 @@
       <c r="K596" s="10">
         <v>68.592291112048443</v>
       </c>
-      <c r="L596" s="10">
+      <c r="L596" s="19">
         <f t="shared" si="19"/>
         <v>-0.70808968222043567</v>
       </c>
@@ -39337,7 +39407,7 @@
       <c r="K597" s="10">
         <v>27.3096898737011</v>
       </c>
-      <c r="L597" s="10">
+      <c r="L597" s="19">
         <f t="shared" si="19"/>
         <v>-0.38165855060836329</v>
       </c>
@@ -39377,7 +39447,7 @@
       <c r="K598" s="10">
         <v>47.380261477684584</v>
       </c>
-      <c r="L598" s="10">
+      <c r="L598" s="19">
         <f t="shared" si="19"/>
         <v>-0.25247954426066171</v>
       </c>
@@ -39417,7 +39487,7 @@
       <c r="K599" s="10">
         <v>48.440037392978304</v>
       </c>
-      <c r="L599" s="10">
+      <c r="L599" s="19">
         <f t="shared" si="19"/>
         <v>-0.46683923478647016</v>
       </c>
@@ -39457,7 +39527,7 @@
       <c r="K600" s="10">
         <v>44.562343622567724</v>
       </c>
-      <c r="L600" s="10">
+      <c r="L600" s="19">
         <f t="shared" si="19"/>
         <v>0.64363130587470485</v>
       </c>
@@ -39497,7 +39567,7 @@
       <c r="K601" s="10">
         <v>36.623281382599032</v>
       </c>
-      <c r="L601" s="10">
+      <c r="L601" s="19">
         <f t="shared" si="19"/>
         <v>6.095079229499939E-2</v>
       </c>
@@ -39537,7 +39607,7 @@
       <c r="K602" s="10">
         <v>34.643577434597006</v>
       </c>
-      <c r="L602" s="10">
+      <c r="L602" s="19">
         <f t="shared" si="19"/>
         <v>-0.54719232179443156</v>
       </c>
@@ -39577,7 +39647,7 @@
       <c r="K603" s="10">
         <v>25.360655270394762</v>
       </c>
-      <c r="L603" s="10">
+      <c r="L603" s="19">
         <f t="shared" si="19"/>
         <v>-0.73702316972815296</v>
       </c>
@@ -39617,7 +39687,7 @@
       <c r="K604" s="10">
         <v>25.396638870684793</v>
       </c>
-      <c r="L604" s="10">
+      <c r="L604" s="19">
         <f t="shared" si="19"/>
         <v>-0.33594412137658186</v>
       </c>
@@ -39657,7 +39727,7 @@
       <c r="K605" s="10">
         <v>27.71</v>
       </c>
-      <c r="L605" s="10">
+      <c r="L605" s="19">
         <f t="shared" si="19"/>
         <v>-0.59130683154878572</v>
       </c>
@@ -39697,7 +39767,7 @@
       <c r="K606" s="10">
         <v>29.33</v>
       </c>
-      <c r="L606" s="10">
+      <c r="L606" s="19">
         <f t="shared" si="19"/>
         <v>-0.59979161843019235</v>
       </c>
@@ -39737,7 +39807,7 @@
       <c r="K607" s="10">
         <v>53.07</v>
       </c>
-      <c r="L607" s="10">
+      <c r="L607" s="19">
         <f t="shared" si="19"/>
         <v>-0.63006872234771405</v>
       </c>
@@ -39777,7 +39847,7 @@
       <c r="K608" s="10">
         <v>44.02</v>
       </c>
-      <c r="L608" s="10">
+      <c r="L608" s="19">
         <f t="shared" si="19"/>
         <v>-0.19018800957568602</v>
       </c>
@@ -39817,7 +39887,7 @@
       <c r="K609" s="10">
         <v>55.52</v>
       </c>
-      <c r="L609" s="10">
+      <c r="L609" s="19">
         <f t="shared" si="19"/>
         <v>-0.45466289269902566</v>
       </c>
@@ -39857,7 +39927,7 @@
       <c r="K610" s="10">
         <v>50.17</v>
       </c>
-      <c r="L610" s="10">
+      <c r="L610" s="19">
         <f t="shared" si="19"/>
         <v>-0.59843279905406299</v>
       </c>
@@ -39897,7 +39967,7 @@
       <c r="K611" s="10">
         <v>34.54</v>
       </c>
-      <c r="L611" s="10">
+      <c r="L611" s="19">
         <f t="shared" si="19"/>
         <v>-0.1325004440497336</v>
       </c>
@@ -39937,7 +40007,7 @@
       <c r="K612" s="10">
         <v>53.35</v>
       </c>
-      <c r="L612" s="10">
+      <c r="L612" s="19">
         <f t="shared" si="19"/>
         <v>-0.35676233183856504</v>
       </c>
@@ -39977,7 +40047,7 @@
       <c r="K613" s="10">
         <v>34.69</v>
       </c>
-      <c r="L613" s="10">
+      <c r="L613" s="19">
         <f t="shared" si="19"/>
         <v>-0.27279731781376532</v>
       </c>
@@ -40017,7 +40087,7 @@
       <c r="K614" s="10">
         <v>50.12</v>
       </c>
-      <c r="L614" s="10">
+      <c r="L614" s="19">
         <f t="shared" si="19"/>
         <v>-0.4609043951064794</v>
       </c>
@@ -40057,7 +40127,7 @@
       <c r="K615" s="10">
         <v>66.569999999999993</v>
       </c>
-      <c r="L615" s="10">
+      <c r="L615" s="19">
         <f t="shared" si="19"/>
         <v>-0.32076295507555025</v>
       </c>
@@ -40097,7 +40167,7 @@
       <c r="K616" s="10">
         <v>58.83</v>
       </c>
-      <c r="L616" s="10">
+      <c r="L616" s="19">
         <f t="shared" si="19"/>
         <v>-0.34241881443298972</v>
       </c>
@@ -40137,7 +40207,7 @@
       <c r="K617" s="10">
         <v>48.61</v>
       </c>
-      <c r="L617" s="10">
+      <c r="L617" s="19">
         <f t="shared" si="19"/>
         <v>0.1592867297089271</v>
       </c>
@@ -40177,7 +40247,7 @@
       <c r="K618" s="10">
         <v>38.979999999999997</v>
       </c>
-      <c r="L618" s="10">
+      <c r="L618" s="19">
         <f t="shared" si="19"/>
         <v>8.359939619136092E-2</v>
       </c>
@@ -40217,7 +40287,7 @@
       <c r="K619" s="10">
         <v>63.14</v>
       </c>
-      <c r="L619" s="10">
+      <c r="L619" s="19">
         <f t="shared" si="19"/>
         <v>4.1718814359494358E-2</v>
       </c>
@@ -40257,7 +40327,7 @@
       <c r="K620" s="10">
         <v>68.150000000000006</v>
       </c>
-      <c r="L620" s="10">
+      <c r="L620" s="19">
         <f t="shared" si="19"/>
         <v>-0.24940445690415114</v>
       </c>
@@ -40297,7 +40367,7 @@
       <c r="K621" s="10">
         <v>39.549999999999997</v>
       </c>
-      <c r="L621" s="10">
+      <c r="L621" s="19">
         <f t="shared" si="19"/>
         <v>0.40712056392613838</v>
       </c>
@@ -40337,7 +40407,7 @@
       <c r="K622" s="10">
         <v>54.33</v>
       </c>
-      <c r="L622" s="10">
+      <c r="L622" s="19">
         <f t="shared" si="19"/>
         <v>-0.35680022918258203</v>
       </c>
@@ -40377,7 +40447,7 @@
       <c r="K623" s="10">
         <v>53.99</v>
       </c>
-      <c r="L623" s="10">
+      <c r="L623" s="19">
         <f t="shared" si="19"/>
         <v>-0.29063764901580258</v>
       </c>
@@ -40417,7 +40487,7 @@
       <c r="K624" s="10">
         <v>39.76</v>
       </c>
-      <c r="L624" s="10">
+      <c r="L624" s="19">
         <f t="shared" si="19"/>
         <v>0.22881424853610924</v>
       </c>
@@ -40457,7 +40527,7 @@
       <c r="K625" s="10">
         <v>34.51</v>
       </c>
-      <c r="L625" s="10">
+      <c r="L625" s="19">
         <f t="shared" si="19"/>
         <v>-7.4688323372533838E-2</v>
       </c>
@@ -40497,7 +40567,7 @@
       <c r="K626" s="10">
         <v>41.63</v>
       </c>
-      <c r="L626" s="10">
+      <c r="L626" s="19">
         <f t="shared" si="19"/>
         <v>2.9377997501242779E-2</v>
       </c>
@@ -40537,7 +40607,7 @@
       <c r="K627" s="10">
         <v>34.5</v>
       </c>
-      <c r="L627" s="10">
+      <c r="L627" s="19">
         <f t="shared" si="19"/>
         <v>-0.36701673789173789</v>
       </c>
@@ -40577,7 +40647,7 @@
       <c r="K628" s="10">
         <v>39</v>
       </c>
-      <c r="L628" s="10">
+      <c r="L628" s="19">
         <f t="shared" si="19"/>
         <v>-0.4711940463805806</v>
       </c>
@@ -40617,7 +40687,7 @@
       <c r="K629" s="10">
         <v>46.74</v>
       </c>
-      <c r="L629" s="10">
+      <c r="L629" s="19">
         <f t="shared" si="19"/>
         <v>0.2207591576595814</v>
       </c>
@@ -40657,7 +40727,7 @@
       <c r="K630" s="10">
         <v>38.47</v>
       </c>
-      <c r="L630" s="10">
+      <c r="L630" s="19">
         <f t="shared" si="19"/>
         <v>-0.20589863805118222</v>
       </c>
@@ -40697,7 +40767,7 @@
       <c r="K631" s="10">
         <v>38.82</v>
       </c>
-      <c r="L631" s="10">
+      <c r="L631" s="19">
         <f t="shared" si="19"/>
         <v>-0.25040355398806285</v>
       </c>
@@ -40737,7 +40807,7 @@
       <c r="K632" s="10">
         <v>39.159999999999997</v>
       </c>
-      <c r="L632" s="10">
+      <c r="L632" s="19">
         <f t="shared" si="19"/>
         <v>-0.40463829642711596</v>
       </c>
@@ -40777,7 +40847,7 @@
       <c r="K633" s="10">
         <v>40.450000000000003</v>
       </c>
-      <c r="L633" s="10">
+      <c r="L633" s="19">
         <f t="shared" si="19"/>
         <v>-4.2433040802370647E-2</v>
       </c>
@@ -40817,7 +40887,7 @@
       <c r="K634" s="10">
         <v>32.78</v>
       </c>
-      <c r="L634" s="10">
+      <c r="L634" s="19">
         <f t="shared" si="19"/>
         <v>-0.39732813044327941</v>
       </c>
@@ -40857,7 +40927,7 @@
       <c r="K635" s="10">
         <v>38.94</v>
       </c>
-      <c r="L635" s="10">
+      <c r="L635" s="19">
         <f t="shared" si="19"/>
         <v>-8.8095459587105185E-2</v>
       </c>
@@ -40897,7 +40967,7 @@
       <c r="K636" s="10">
         <v>31.73</v>
       </c>
-      <c r="L636" s="10">
+      <c r="L636" s="19">
         <f t="shared" si="19"/>
         <v>0.25427833352442086</v>
       </c>
@@ -40937,7 +41007,7 @@
       <c r="K637" s="10">
         <v>38.53</v>
       </c>
-      <c r="L637" s="10">
+      <c r="L637" s="19">
         <f t="shared" si="19"/>
         <v>-0.47028623046743345</v>
       </c>
@@ -40977,7 +41047,7 @@
       <c r="K638" s="10">
         <v>43.57</v>
       </c>
-      <c r="L638" s="10">
+      <c r="L638" s="19">
         <f t="shared" si="19"/>
         <v>-0.56452903915761754</v>
       </c>
@@ -41017,7 +41087,7 @@
       <c r="K639" s="10">
         <v>37.619999999999997</v>
       </c>
-      <c r="L639" s="10">
+      <c r="L639" s="19">
         <f t="shared" si="19"/>
         <v>-0.46110852713178302</v>
       </c>
@@ -41057,7 +41127,7 @@
       <c r="K640" s="10">
         <v>38.020000000000003</v>
       </c>
-      <c r="L640" s="10">
+      <c r="L640" s="19">
         <f t="shared" si="19"/>
         <v>-0.3410811273302965</v>
       </c>
@@ -41097,7 +41167,7 @@
       <c r="K641" s="10">
         <v>44.58</v>
       </c>
-      <c r="L641" s="10">
+      <c r="L641" s="19">
         <f t="shared" si="19"/>
         <v>-0.15912718775772006</v>
       </c>
@@ -41137,7 +41207,7 @@
       <c r="K642" s="10">
         <v>43.37</v>
       </c>
-      <c r="L642" s="10">
+      <c r="L642" s="19">
         <f t="shared" si="19"/>
         <v>2.0875280112580292E-2</v>
       </c>
@@ -41192,7 +41262,7 @@
       <c r="K643" s="10">
         <v>64.94</v>
       </c>
-      <c r="L643" s="10">
+      <c r="L643" s="19">
         <f t="shared" ref="L643:L706" si="21">IF(OR(K643=0,I643=G643,J643=F643),"",0.4*((3*(E643-H643)/K643)/(1+ABS(3*(E643-H643)/K643)))+0.45*((I643+G643-2*H643)/(I643-G643))+0.15*((J643+F643-2*H643)/(J643-F643)))</f>
         <v>8.5105784009770022E-2</v>
       </c>
@@ -41232,7 +41302,7 @@
       <c r="K644" s="10">
         <v>45.19</v>
       </c>
-      <c r="L644" s="10">
+      <c r="L644" s="19">
         <f t="shared" si="21"/>
         <v>7.8461972175106171E-2</v>
       </c>
@@ -41272,7 +41342,7 @@
       <c r="K645" s="10">
         <v>72.86</v>
       </c>
-      <c r="L645" s="10">
+      <c r="L645" s="19">
         <f t="shared" si="21"/>
         <v>-0.26405670304763701</v>
       </c>
@@ -41312,7 +41382,7 @@
       <c r="K646" s="10">
         <v>38.96</v>
       </c>
-      <c r="L646" s="10">
+      <c r="L646" s="19">
         <f t="shared" si="21"/>
         <v>3.2625651696698038E-2</v>
       </c>
@@ -41352,7 +41422,7 @@
       <c r="K647" s="10">
         <v>33.590000000000003</v>
       </c>
-      <c r="L647" s="10">
+      <c r="L647" s="19">
         <f t="shared" si="21"/>
         <v>-0.64072599234078076</v>
       </c>
@@ -41392,7 +41462,7 @@
       <c r="K648" s="10">
         <v>48.37</v>
       </c>
-      <c r="L648" s="10">
+      <c r="L648" s="19">
         <f t="shared" si="21"/>
         <v>-0.40731304514742395</v>
       </c>
@@ -41432,7 +41502,7 @@
       <c r="K649" s="10">
         <v>73.89</v>
       </c>
-      <c r="L649" s="10">
+      <c r="L649" s="19">
         <f t="shared" si="21"/>
         <v>7.6116772075282585E-2</v>
       </c>
@@ -41472,7 +41542,7 @@
       <c r="K650" s="10">
         <v>39.99</v>
       </c>
-      <c r="L650" s="10">
+      <c r="L650" s="19">
         <f t="shared" si="21"/>
         <v>0.17640649688036913</v>
       </c>
@@ -41512,7 +41582,7 @@
       <c r="K651" s="10">
         <v>61.26</v>
       </c>
-      <c r="L651" s="10">
+      <c r="L651" s="19">
         <f t="shared" si="21"/>
         <v>-0.32054279943112729</v>
       </c>
@@ -41552,7 +41622,7 @@
       <c r="K652" s="10">
         <v>50.14</v>
       </c>
-      <c r="L652" s="10">
+      <c r="L652" s="19">
         <f t="shared" si="21"/>
         <v>0.17146167507915133</v>
       </c>
@@ -41592,7 +41662,7 @@
       <c r="K653" s="10">
         <v>63.86</v>
       </c>
-      <c r="L653" s="10">
+      <c r="L653" s="19">
         <f t="shared" si="21"/>
         <v>0.38122632873084927</v>
       </c>
@@ -41632,7 +41702,7 @@
       <c r="K654" s="10">
         <v>50.7</v>
       </c>
-      <c r="L654" s="10">
+      <c r="L654" s="19">
         <f t="shared" si="21"/>
         <v>0.22760533056163929</v>
       </c>
@@ -41672,7 +41742,7 @@
       <c r="K655" s="10">
         <v>53.3</v>
       </c>
-      <c r="L655" s="10">
+      <c r="L655" s="19">
         <f t="shared" si="21"/>
         <v>-2.5767436223716904E-2</v>
       </c>
@@ -41712,7 +41782,7 @@
       <c r="K656" s="10">
         <v>60.63</v>
       </c>
-      <c r="L656" s="10">
+      <c r="L656" s="19">
         <f t="shared" si="21"/>
         <v>-0.17572026900154653</v>
       </c>
@@ -41752,7 +41822,7 @@
       <c r="K657" s="10">
         <v>51.01</v>
       </c>
-      <c r="L657" s="10">
+      <c r="L657" s="19">
         <f t="shared" si="21"/>
         <v>0.25865986625314991</v>
       </c>
@@ -41792,7 +41862,7 @@
       <c r="K658" s="10">
         <v>45.67</v>
       </c>
-      <c r="L658" s="10">
+      <c r="L658" s="19">
         <f t="shared" si="21"/>
         <v>0.19313373451136254</v>
       </c>
@@ -41832,7 +41902,7 @@
       <c r="K659" s="10">
         <v>46.03</v>
       </c>
-      <c r="L659" s="10">
+      <c r="L659" s="19">
         <f t="shared" si="21"/>
         <v>-0.11826160773603014</v>
       </c>
@@ -41872,7 +41942,7 @@
       <c r="K660" s="10">
         <v>42.17</v>
       </c>
-      <c r="L660" s="10">
+      <c r="L660" s="19">
         <f t="shared" si="21"/>
         <v>-0.41617194570135752</v>
       </c>
@@ -41912,7 +41982,7 @@
       <c r="K661" s="10">
         <v>40.51</v>
       </c>
-      <c r="L661" s="10">
+      <c r="L661" s="19">
         <f t="shared" si="21"/>
         <v>-0.17819596531197171</v>
       </c>
@@ -41952,7 +42022,7 @@
       <c r="K662" s="10">
         <v>46.58</v>
       </c>
-      <c r="L662" s="10">
+      <c r="L662" s="19">
         <f t="shared" si="21"/>
         <v>-7.8718905576705883E-2</v>
       </c>
@@ -41992,7 +42062,7 @@
       <c r="K663" s="10">
         <v>48.78</v>
       </c>
-      <c r="L663" s="10">
+      <c r="L663" s="19">
         <f t="shared" si="21"/>
         <v>-0.13663617065678724</v>
       </c>
@@ -42032,7 +42102,7 @@
       <c r="K664" s="10">
         <v>51.87</v>
       </c>
-      <c r="L664" s="10">
+      <c r="L664" s="19">
         <f t="shared" si="21"/>
         <v>-0.29409073786707302</v>
       </c>
@@ -42072,7 +42142,7 @@
       <c r="K665" s="10">
         <v>50.84</v>
       </c>
-      <c r="L665" s="10">
+      <c r="L665" s="19">
         <f t="shared" si="21"/>
         <v>-0.39497806314962691</v>
       </c>
@@ -42112,7 +42182,7 @@
       <c r="K666" s="10">
         <v>57.44</v>
       </c>
-      <c r="L666" s="10">
+      <c r="L666" s="19">
         <f t="shared" si="21"/>
         <v>-0.38327786452862117</v>
       </c>
@@ -42152,7 +42222,7 @@
       <c r="K667" s="10">
         <v>58.85</v>
       </c>
-      <c r="L667" s="10">
+      <c r="L667" s="19">
         <f t="shared" si="21"/>
         <v>-0.1850305496431702</v>
       </c>
@@ -42192,7 +42262,7 @@
       <c r="K668" s="10">
         <v>37.44</v>
       </c>
-      <c r="L668" s="10">
+      <c r="L668" s="19">
         <f t="shared" si="21"/>
         <v>-0.60013038075254144</v>
       </c>
@@ -42232,7 +42302,7 @@
       <c r="K669" s="10">
         <v>44.35</v>
       </c>
-      <c r="L669" s="10">
+      <c r="L669" s="19">
         <f t="shared" si="21"/>
         <v>-0.64110417424899913</v>
       </c>
@@ -42272,7 +42342,7 @@
       <c r="K670" s="10">
         <v>29.9</v>
       </c>
-      <c r="L670" s="10">
+      <c r="L670" s="19">
         <f t="shared" si="21"/>
         <v>-0.57229112271540472</v>
       </c>
@@ -42312,7 +42382,7 @@
       <c r="K671" s="10">
         <v>38.32</v>
       </c>
-      <c r="L671" s="10">
+      <c r="L671" s="19">
         <f t="shared" si="21"/>
         <v>-0.61841004780257747</v>
       </c>
@@ -42352,7 +42422,7 @@
       <c r="K672" s="10">
         <v>43.11</v>
       </c>
-      <c r="L672" s="10">
+      <c r="L672" s="19">
         <f t="shared" si="21"/>
         <v>-0.13473974624343166</v>
       </c>
@@ -42392,7 +42462,7 @@
       <c r="K673" s="10">
         <v>63.69</v>
       </c>
-      <c r="L673" s="10">
+      <c r="L673" s="19">
         <f t="shared" si="21"/>
         <v>-0.25267757965507165</v>
       </c>
@@ -42432,7 +42502,7 @@
       <c r="K674" s="10">
         <v>54.45</v>
       </c>
-      <c r="L674" s="10">
+      <c r="L674" s="19">
         <f t="shared" si="21"/>
         <v>-0.35386079805056353</v>
       </c>
@@ -42472,7 +42542,7 @@
       <c r="K675" s="10">
         <v>38.76</v>
       </c>
-      <c r="L675" s="10">
+      <c r="L675" s="19">
         <f t="shared" si="21"/>
         <v>-0.23380110495873083</v>
       </c>
@@ -42512,7 +42582,7 @@
       <c r="K676" s="10">
         <v>76.66</v>
       </c>
-      <c r="L676" s="10">
+      <c r="L676" s="19">
         <f t="shared" si="21"/>
         <v>-0.23555465734501374</v>
       </c>
@@ -42552,7 +42622,7 @@
       <c r="K677" s="10">
         <v>57.55</v>
       </c>
-      <c r="L677" s="10">
+      <c r="L677" s="19">
         <f t="shared" si="21"/>
         <v>-0.17310653513371899</v>
       </c>
@@ -42592,7 +42662,7 @@
       <c r="K678" s="10">
         <v>36.67</v>
       </c>
-      <c r="L678" s="10">
+      <c r="L678" s="19">
         <f t="shared" si="21"/>
         <v>-0.27071645998897947</v>
       </c>
@@ -42632,7 +42702,7 @@
       <c r="K679" s="10">
         <v>25.39</v>
       </c>
-      <c r="L679" s="10">
+      <c r="L679" s="19">
         <f t="shared" si="21"/>
         <v>-6.4769049055086542E-2</v>
       </c>
@@ -42672,7 +42742,7 @@
       <c r="K680" s="10">
         <v>56.56</v>
       </c>
-      <c r="L680" s="10">
+      <c r="L680" s="19">
         <f t="shared" si="21"/>
         <v>-0.48490737850037163</v>
       </c>
@@ -42712,7 +42782,7 @@
       <c r="K681" s="10">
         <v>37.46</v>
       </c>
-      <c r="L681" s="10">
+      <c r="L681" s="19">
         <f t="shared" si="21"/>
         <v>-0.4932655220256677</v>
       </c>
@@ -42752,7 +42822,7 @@
       <c r="K682" s="10">
         <v>35.630000000000003</v>
       </c>
-      <c r="L682" s="10">
+      <c r="L682" s="19">
         <f t="shared" si="21"/>
         <v>-0.45533330489677531</v>
       </c>
@@ -42792,7 +42862,7 @@
       <c r="K683" s="10">
         <v>53.98</v>
       </c>
-      <c r="L683" s="10">
+      <c r="L683" s="19">
         <f t="shared" si="21"/>
         <v>-0.63623328238440957</v>
       </c>
@@ -42832,7 +42902,7 @@
       <c r="K684" s="10">
         <v>37.93</v>
       </c>
-      <c r="L684" s="10">
+      <c r="L684" s="19">
         <f t="shared" si="21"/>
         <v>-0.56426777642247261</v>
       </c>
@@ -42872,7 +42942,7 @@
       <c r="K685" s="10">
         <v>41.31</v>
       </c>
-      <c r="L685" s="10">
+      <c r="L685" s="19">
         <f t="shared" si="21"/>
         <v>-0.60366726296958861</v>
       </c>
@@ -42912,7 +42982,7 @@
       <c r="K686" s="10">
         <v>61.58</v>
       </c>
-      <c r="L686" s="10">
+      <c r="L686" s="19">
         <f t="shared" si="21"/>
         <v>-0.51312495258326385</v>
       </c>
@@ -42952,7 +43022,7 @@
       <c r="K687" s="10">
         <v>49.29</v>
       </c>
-      <c r="L687" s="10">
+      <c r="L687" s="19">
         <f t="shared" si="21"/>
         <v>-0.56058755172609276</v>
       </c>
@@ -42992,7 +43062,7 @@
       <c r="K688" s="10">
         <v>60.34</v>
       </c>
-      <c r="L688" s="10">
+      <c r="L688" s="19">
         <f t="shared" si="21"/>
         <v>-0.23059629219701158</v>
       </c>
@@ -43032,7 +43102,7 @@
       <c r="K689" s="10">
         <v>66.010000000000005</v>
       </c>
-      <c r="L689" s="10">
+      <c r="L689" s="19">
         <f t="shared" si="21"/>
         <v>-0.16307288629737607</v>
       </c>
@@ -43072,7 +43142,7 @@
       <c r="K690" s="10">
         <v>53.29</v>
       </c>
-      <c r="L690" s="10">
+      <c r="L690" s="19">
         <f t="shared" si="21"/>
         <v>-0.21130969855496906</v>
       </c>
@@ -43112,7 +43182,7 @@
       <c r="K691" s="10">
         <v>58.2</v>
       </c>
-      <c r="L691" s="10">
+      <c r="L691" s="19">
         <f t="shared" si="21"/>
         <v>-0.20341848447432198</v>
       </c>
@@ -43152,7 +43222,7 @@
       <c r="K692" s="10">
         <v>62.04</v>
       </c>
-      <c r="L692" s="10">
+      <c r="L692" s="19">
         <f t="shared" si="21"/>
         <v>-0.46521449189070246</v>
       </c>
@@ -43192,7 +43262,7 @@
       <c r="K693" s="10">
         <v>53.22</v>
       </c>
-      <c r="L693" s="10">
+      <c r="L693" s="19">
         <f t="shared" si="21"/>
         <v>-0.28991151220766226</v>
       </c>
@@ -43232,7 +43302,7 @@
       <c r="K694" s="10">
         <v>78.3</v>
       </c>
-      <c r="L694" s="10">
+      <c r="L694" s="19">
         <f t="shared" si="21"/>
         <v>-0.4241598109777589</v>
       </c>
@@ -43272,7 +43342,7 @@
       <c r="K695" s="10">
         <v>57.1</v>
       </c>
-      <c r="L695" s="10">
+      <c r="L695" s="19">
         <f t="shared" si="21"/>
         <v>-0.44262756491737787</v>
       </c>
@@ -43312,7 +43382,7 @@
       <c r="K696" s="10">
         <v>67.400000000000006</v>
       </c>
-      <c r="L696" s="10">
+      <c r="L696" s="19">
         <f t="shared" si="21"/>
         <v>-0.39075966226014164</v>
       </c>
@@ -43352,7 +43422,7 @@
       <c r="K697" s="10">
         <v>38.35</v>
       </c>
-      <c r="L697" s="10">
+      <c r="L697" s="19">
         <f t="shared" si="21"/>
         <v>-0.21162410095180667</v>
       </c>
@@ -43392,7 +43462,7 @@
       <c r="K698" s="10">
         <v>39.58</v>
       </c>
-      <c r="L698" s="10">
+      <c r="L698" s="19">
         <f t="shared" si="21"/>
         <v>-0.17322568837190391</v>
       </c>
@@ -43432,7 +43502,7 @@
       <c r="K699" s="10">
         <v>35.5</v>
       </c>
-      <c r="L699" s="10">
+      <c r="L699" s="19">
         <f t="shared" si="21"/>
         <v>-0.26708819464660677</v>
       </c>
@@ -43472,7 +43542,7 @@
       <c r="K700" s="10">
         <v>49.68</v>
       </c>
-      <c r="L700" s="10">
+      <c r="L700" s="19">
         <f t="shared" si="21"/>
         <v>-0.33979152076711738</v>
       </c>
@@ -43512,7 +43582,7 @@
       <c r="K701" s="10">
         <v>52.05</v>
       </c>
-      <c r="L701" s="10">
+      <c r="L701" s="19">
         <f t="shared" si="21"/>
         <v>-0.69216235440561924</v>
       </c>
@@ -43552,7 +43622,7 @@
       <c r="K702" s="10">
         <v>41.28</v>
       </c>
-      <c r="L702" s="10">
+      <c r="L702" s="19">
         <f t="shared" si="21"/>
         <v>-0.45190036900369002</v>
       </c>
@@ -43592,7 +43662,7 @@
       <c r="K703" s="10">
         <v>56.13</v>
       </c>
-      <c r="L703" s="10">
+      <c r="L703" s="19">
         <f t="shared" si="21"/>
         <v>-0.66667644523547553</v>
       </c>
@@ -43632,7 +43702,7 @@
       <c r="K704" s="10">
         <v>50.69</v>
       </c>
-      <c r="L704" s="10">
+      <c r="L704" s="19">
         <f t="shared" si="21"/>
         <v>-0.6528120500033352</v>
       </c>
@@ -43672,7 +43742,7 @@
       <c r="K705" s="10">
         <v>35.82</v>
       </c>
-      <c r="L705" s="10">
+      <c r="L705" s="19">
         <f t="shared" si="21"/>
         <v>-0.47331452380171241</v>
       </c>
@@ -43712,7 +43782,7 @@
       <c r="K706" s="10">
         <v>29.16</v>
       </c>
-      <c r="L706" s="10">
+      <c r="L706" s="19">
         <f t="shared" si="21"/>
         <v>-0.59767333643555154</v>
       </c>
@@ -43767,7 +43837,7 @@
       <c r="K707" s="10">
         <v>32.42</v>
       </c>
-      <c r="L707" s="10">
+      <c r="L707" s="19">
         <f t="shared" ref="L707:L770" si="23">IF(OR(K707=0,I707=G707,J707=F707),"",0.4*((3*(E707-H707)/K707)/(1+ABS(3*(E707-H707)/K707)))+0.45*((I707+G707-2*H707)/(I707-G707))+0.15*((J707+F707-2*H707)/(J707-F707)))</f>
         <v>-0.72600244926522051</v>
       </c>
@@ -43807,7 +43877,7 @@
       <c r="K708" s="10">
         <v>40.659999999999997</v>
       </c>
-      <c r="L708" s="10">
+      <c r="L708" s="19">
         <f t="shared" si="23"/>
         <v>-0.57045376418013072</v>
       </c>
@@ -43847,7 +43917,7 @@
       <c r="K709" s="10">
         <v>37.35</v>
       </c>
-      <c r="L709" s="10">
+      <c r="L709" s="19">
         <f t="shared" si="23"/>
         <v>-0.68328981723237603</v>
       </c>
@@ -43887,7 +43957,7 @@
       <c r="K710" s="10">
         <v>21.13</v>
       </c>
-      <c r="L710" s="10">
+      <c r="L710" s="19">
         <f t="shared" si="23"/>
         <v>-0.6529290574425981</v>
       </c>
@@ -43927,7 +43997,7 @@
       <c r="K711" s="10">
         <v>57.93</v>
       </c>
-      <c r="L711" s="10">
+      <c r="L711" s="19">
         <f t="shared" si="23"/>
         <v>-0.71714015151515165</v>
       </c>
@@ -43967,7 +44037,7 @@
       <c r="K712" s="10">
         <v>57.84</v>
       </c>
-      <c r="L712" s="10">
+      <c r="L712" s="19">
         <f t="shared" si="23"/>
         <v>-0.59399504191503971</v>
       </c>
@@ -44007,7 +44077,7 @@
       <c r="K713" s="10">
         <v>37.590000000000003</v>
       </c>
-      <c r="L713" s="10">
+      <c r="L713" s="19">
         <f t="shared" si="23"/>
         <v>-0.66051039697542535</v>
       </c>
@@ -44047,7 +44117,7 @@
       <c r="K714" s="10">
         <v>35.15</v>
       </c>
-      <c r="L714" s="10">
+      <c r="L714" s="19">
         <f t="shared" si="23"/>
         <v>-0.62548080196399336</v>
       </c>
@@ -44087,7 +44157,7 @@
       <c r="K715" s="10">
         <v>69.72</v>
       </c>
-      <c r="L715" s="10">
+      <c r="L715" s="19">
         <f t="shared" si="23"/>
         <v>-0.31383431195423067</v>
       </c>
@@ -44127,7 +44197,7 @@
       <c r="K716" s="10">
         <v>72.709999999999994</v>
       </c>
-      <c r="L716" s="10">
+      <c r="L716" s="19">
         <f t="shared" si="23"/>
         <v>-0.27561905683042154</v>
       </c>
@@ -44167,7 +44237,7 @@
       <c r="K717" s="10">
         <v>58.88</v>
       </c>
-      <c r="L717" s="10">
+      <c r="L717" s="19">
         <f t="shared" si="23"/>
         <v>0.25977749523204069</v>
       </c>
@@ -44207,7 +44277,7 @@
       <c r="K718" s="10">
         <v>42.67</v>
       </c>
-      <c r="L718" s="10">
+      <c r="L718" s="19">
         <f t="shared" si="23"/>
         <v>6.5480950246526226E-2</v>
       </c>
@@ -44247,7 +44317,7 @@
       <c r="K719" s="10">
         <v>34.049999999999997</v>
       </c>
-      <c r="L719" s="10">
+      <c r="L719" s="19">
         <f t="shared" si="23"/>
         <v>0.4188613861386139</v>
       </c>
@@ -44287,7 +44357,7 @@
       <c r="K720" s="10">
         <v>40.64</v>
       </c>
-      <c r="L720" s="10">
+      <c r="L720" s="19">
         <f t="shared" si="23"/>
         <v>0.12610244267198409</v>
       </c>
@@ -44327,7 +44397,7 @@
       <c r="K721" s="10">
         <v>44.54</v>
       </c>
-      <c r="L721" s="10">
+      <c r="L721" s="19">
         <f t="shared" si="23"/>
         <v>-0.10803858520900325</v>
       </c>
@@ -44367,7 +44437,7 @@
       <c r="K722" s="10">
         <v>56.57</v>
       </c>
-      <c r="L722" s="10">
+      <c r="L722" s="19">
         <f t="shared" si="23"/>
         <v>-0.11702670647987945</v>
       </c>
@@ -44407,7 +44477,7 @@
       <c r="K723" s="10">
         <v>57.95</v>
       </c>
-      <c r="L723" s="10">
+      <c r="L723" s="19">
         <f t="shared" si="23"/>
         <v>-0.19024224940914775</v>
       </c>
@@ -44447,7 +44517,7 @@
       <c r="K724" s="10">
         <v>41.89</v>
       </c>
-      <c r="L724" s="10">
+      <c r="L724" s="19">
         <f t="shared" si="23"/>
         <v>-1.0240799081638082E-2</v>
       </c>
@@ -44487,7 +44557,7 @@
       <c r="K725" s="10">
         <v>41.07</v>
       </c>
-      <c r="L725" s="10">
+      <c r="L725" s="19">
         <f t="shared" si="23"/>
         <v>0.10687212276214841</v>
       </c>
@@ -44527,7 +44597,7 @@
       <c r="K726" s="10">
         <v>49.3</v>
       </c>
-      <c r="L726" s="10">
+      <c r="L726" s="19">
         <f t="shared" si="23"/>
         <v>0.16090527314231509</v>
       </c>
@@ -44567,7 +44637,7 @@
       <c r="K727" s="10">
         <v>51.08</v>
       </c>
-      <c r="L727" s="10">
+      <c r="L727" s="19">
         <f t="shared" si="23"/>
         <v>2.414108472172986E-2</v>
       </c>
@@ -44607,7 +44677,7 @@
       <c r="K728" s="10">
         <v>43.17</v>
       </c>
-      <c r="L728" s="10">
+      <c r="L728" s="19">
         <f t="shared" si="23"/>
         <v>0.13077445109780447</v>
       </c>
@@ -44647,7 +44717,7 @@
       <c r="K729" s="10">
         <v>36.69</v>
       </c>
-      <c r="L729" s="10">
+      <c r="L729" s="19">
         <f t="shared" si="23"/>
         <v>-0.4766343132502639</v>
       </c>
@@ -44687,7 +44757,7 @@
       <c r="K730" s="10">
         <v>54.73</v>
       </c>
-      <c r="L730" s="10">
+      <c r="L730" s="19">
         <f t="shared" si="23"/>
         <v>8.2361972591544E-2</v>
       </c>
@@ -44727,7 +44797,7 @@
       <c r="K731" s="10">
         <v>37.33</v>
       </c>
-      <c r="L731" s="10">
+      <c r="L731" s="19">
         <f t="shared" si="23"/>
         <v>-0.34845722792372763</v>
       </c>
@@ -44767,7 +44837,7 @@
       <c r="K732" s="10">
         <v>43.91</v>
       </c>
-      <c r="L732" s="10">
+      <c r="L732" s="19">
         <f t="shared" si="23"/>
         <v>6.3168090459471984E-2</v>
       </c>
@@ -44807,7 +44877,7 @@
       <c r="K733" s="10">
         <v>52.64</v>
       </c>
-      <c r="L733" s="10">
+      <c r="L733" s="19">
         <f t="shared" si="23"/>
         <v>-0.18684494439473348</v>
       </c>
@@ -44847,7 +44917,7 @@
       <c r="K734" s="10">
         <v>50.49</v>
       </c>
-      <c r="L734" s="10">
+      <c r="L734" s="19">
         <f t="shared" si="23"/>
         <v>-0.24697895010395005</v>
       </c>
@@ -44887,7 +44957,7 @@
       <c r="K735" s="10">
         <v>49.38</v>
       </c>
-      <c r="L735" s="10">
+      <c r="L735" s="19">
         <f t="shared" si="23"/>
         <v>-0.59608561511762437</v>
       </c>
@@ -44927,7 +44997,7 @@
       <c r="K736" s="10">
         <v>33.909999999999997</v>
       </c>
-      <c r="L736" s="10">
+      <c r="L736" s="19">
         <f t="shared" si="23"/>
         <v>-0.46317357834616352</v>
       </c>
@@ -44967,7 +45037,7 @@
       <c r="K737" s="10">
         <v>36.130000000000003</v>
       </c>
-      <c r="L737" s="10">
+      <c r="L737" s="19">
         <f t="shared" si="23"/>
         <v>-0.50618655071639451</v>
       </c>
@@ -45007,7 +45077,7 @@
       <c r="K738" s="10">
         <v>49.4</v>
       </c>
-      <c r="L738" s="10">
+      <c r="L738" s="19">
         <f t="shared" si="23"/>
         <v>-0.5531262171937309</v>
       </c>
@@ -45047,7 +45117,7 @@
       <c r="K739" s="10">
         <v>29.1</v>
       </c>
-      <c r="L739" s="10">
+      <c r="L739" s="19">
         <f t="shared" si="23"/>
         <v>-0.35596330275229349</v>
       </c>
@@ -45087,7 +45157,7 @@
       <c r="K740" s="10">
         <v>42.31</v>
       </c>
-      <c r="L740" s="10">
+      <c r="L740" s="19">
         <f t="shared" si="23"/>
         <v>-0.4463466042154568</v>
       </c>
@@ -45127,7 +45197,7 @@
       <c r="K741" s="10">
         <v>38.44</v>
       </c>
-      <c r="L741" s="10">
+      <c r="L741" s="19">
         <f t="shared" si="23"/>
         <v>-0.26455609084652437</v>
       </c>
@@ -45167,7 +45237,7 @@
       <c r="K742" s="10">
         <v>35.47</v>
       </c>
-      <c r="L742" s="10">
+      <c r="L742" s="19">
         <f t="shared" si="23"/>
         <v>-0.52364627970393463</v>
       </c>
@@ -45207,7 +45277,7 @@
       <c r="K743" s="10">
         <v>60.47</v>
       </c>
-      <c r="L743" s="10">
+      <c r="L743" s="19">
         <f t="shared" si="23"/>
         <v>-0.26901756995705745</v>
       </c>
@@ -45247,7 +45317,7 @@
       <c r="K744" s="10">
         <v>71.73</v>
       </c>
-      <c r="L744" s="10">
+      <c r="L744" s="19">
         <f t="shared" si="23"/>
         <v>-0.22700101317122601</v>
       </c>
@@ -45287,7 +45357,7 @@
       <c r="K745" s="10">
         <v>82.7</v>
       </c>
-      <c r="L745" s="10">
+      <c r="L745" s="19">
         <f t="shared" si="23"/>
         <v>-0.24221296740172582</v>
       </c>
@@ -45327,7 +45397,7 @@
       <c r="K746" s="10">
         <v>62.62</v>
       </c>
-      <c r="L746" s="10">
+      <c r="L746" s="19">
         <f t="shared" si="23"/>
         <v>-0.24774345360202732</v>
       </c>
@@ -45367,7 +45437,7 @@
       <c r="K747" s="10">
         <v>63.41</v>
       </c>
-      <c r="L747" s="10">
+      <c r="L747" s="19">
         <f t="shared" si="23"/>
         <v>-0.19599665312096892</v>
       </c>
@@ -45407,7 +45477,7 @@
       <c r="K748" s="10">
         <v>41.56</v>
       </c>
-      <c r="L748" s="10">
+      <c r="L748" s="19">
         <f t="shared" si="23"/>
         <v>-0.3801688182720952</v>
       </c>
@@ -45447,7 +45517,7 @@
       <c r="K749" s="10">
         <v>42.48</v>
       </c>
-      <c r="L749" s="10">
+      <c r="L749" s="19">
         <f t="shared" si="23"/>
         <v>-0.64528809039985391</v>
       </c>
@@ -45487,7 +45557,7 @@
       <c r="K750" s="10">
         <v>49.64</v>
       </c>
-      <c r="L750" s="10">
+      <c r="L750" s="19">
         <f t="shared" si="23"/>
         <v>-0.1056184187042655</v>
       </c>
@@ -45527,7 +45597,7 @@
       <c r="K751" s="10">
         <v>49.7</v>
       </c>
-      <c r="L751" s="10">
+      <c r="L751" s="19">
         <f t="shared" si="23"/>
         <v>-0.17007193626046083</v>
       </c>
@@ -45567,7 +45637,7 @@
       <c r="K752" s="10">
         <v>50.26</v>
       </c>
-      <c r="L752" s="10">
+      <c r="L752" s="19">
         <f t="shared" si="23"/>
         <v>-2.2359843546284279E-2</v>
       </c>
@@ -45607,7 +45677,7 @@
       <c r="K753" s="10">
         <v>44.54</v>
       </c>
-      <c r="L753" s="10">
+      <c r="L753" s="19">
         <f t="shared" si="23"/>
         <v>0.13382852882262603</v>
       </c>
@@ -45647,7 +45717,7 @@
       <c r="K754" s="10">
         <v>44.54</v>
       </c>
-      <c r="L754" s="10">
+      <c r="L754" s="19">
         <f t="shared" si="23"/>
         <v>0.29558156375796041</v>
       </c>
@@ -45687,7 +45757,7 @@
       <c r="K755" s="10">
         <v>38.9</v>
       </c>
-      <c r="L755" s="10">
+      <c r="L755" s="19">
         <f t="shared" si="23"/>
         <v>-0.37142119396818835</v>
       </c>
@@ -45727,7 +45797,7 @@
       <c r="K756" s="10">
         <v>40.98</v>
       </c>
-      <c r="L756" s="10">
+      <c r="L756" s="19">
         <f t="shared" si="23"/>
         <v>-0.32637835103692464</v>
       </c>
@@ -45767,7 +45837,7 @@
       <c r="K757" s="10">
         <v>42.33</v>
       </c>
-      <c r="L757" s="10">
+      <c r="L757" s="19">
         <f t="shared" si="23"/>
         <v>0.11794522204958308</v>
       </c>
@@ -45807,7 +45877,7 @@
       <c r="K758" s="10">
         <v>44.19</v>
       </c>
-      <c r="L758" s="10">
+      <c r="L758" s="19">
         <f t="shared" si="23"/>
         <v>-0.62002341920374704</v>
       </c>
@@ -45847,7 +45917,7 @@
       <c r="K759" s="10">
         <v>47.07</v>
       </c>
-      <c r="L759" s="10">
+      <c r="L759" s="19">
         <f t="shared" si="23"/>
         <v>-0.22877376081967046</v>
       </c>
@@ -45887,7 +45957,7 @@
       <c r="K760" s="10">
         <v>39.11</v>
       </c>
-      <c r="L760" s="10">
+      <c r="L760" s="19">
         <f t="shared" si="23"/>
         <v>-0.51559066951717702</v>
       </c>
@@ -45927,7 +45997,7 @@
       <c r="K761" s="10">
         <v>39.85</v>
       </c>
-      <c r="L761" s="10">
+      <c r="L761" s="19">
         <f t="shared" si="23"/>
         <v>0.11647920931067304</v>
       </c>
@@ -45967,7 +46037,7 @@
       <c r="K762" s="10">
         <v>36.46</v>
       </c>
-      <c r="L762" s="10">
+      <c r="L762" s="19">
         <f t="shared" si="23"/>
         <v>0.74619269102990038</v>
       </c>
@@ -46007,7 +46077,7 @@
       <c r="K763" s="10">
         <v>53.82</v>
       </c>
-      <c r="L763" s="10">
+      <c r="L763" s="19">
         <f t="shared" si="23"/>
         <v>-0.26342580645161284</v>
       </c>
@@ -46047,7 +46117,7 @@
       <c r="K764" s="10">
         <v>50.88</v>
       </c>
-      <c r="L764" s="10">
+      <c r="L764" s="19">
         <f t="shared" si="23"/>
         <v>-0.40397115384615384</v>
       </c>
@@ -46087,7 +46157,7 @@
       <c r="K765" s="10">
         <v>29.44</v>
       </c>
-      <c r="L765" s="10" t="str">
+      <c r="L765" s="19" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -46127,7 +46197,7 @@
       <c r="K766" s="10">
         <v>44.76</v>
       </c>
-      <c r="L766" s="10">
+      <c r="L766" s="19">
         <f t="shared" si="23"/>
         <v>0.3126568679121503</v>
       </c>
@@ -46167,7 +46237,7 @@
       <c r="K767" s="10">
         <v>48.64</v>
       </c>
-      <c r="L767" s="10">
+      <c r="L767" s="19">
         <f t="shared" si="23"/>
         <v>-0.18487293038988795</v>
       </c>
@@ -46207,7 +46277,7 @@
       <c r="K768" s="10">
         <v>62.65</v>
       </c>
-      <c r="L768" s="10">
+      <c r="L768" s="19">
         <f t="shared" si="23"/>
         <v>-0.41978318002628123</v>
       </c>
@@ -46247,7 +46317,7 @@
       <c r="K769" s="10">
         <v>54.1</v>
       </c>
-      <c r="L769" s="10">
+      <c r="L769" s="19">
         <f t="shared" si="23"/>
         <v>-0.59239400272498444</v>
       </c>
@@ -46287,7 +46357,7 @@
       <c r="K770" s="10">
         <v>33.979999999999997</v>
       </c>
-      <c r="L770" s="10">
+      <c r="L770" s="19">
         <f t="shared" si="23"/>
         <v>-0.59688947557902317</v>
       </c>
@@ -46342,7 +46412,7 @@
       <c r="K771" s="10">
         <v>42.24</v>
       </c>
-      <c r="L771" s="10">
+      <c r="L771" s="19">
         <f t="shared" ref="L771:L834" si="25">IF(OR(K771=0,I771=G771,J771=F771),"",0.4*((3*(E771-H771)/K771)/(1+ABS(3*(E771-H771)/K771)))+0.45*((I771+G771-2*H771)/(I771-G771))+0.15*((J771+F771-2*H771)/(J771-F771)))</f>
         <v>-0.55061417217926645</v>
       </c>
@@ -46382,7 +46452,7 @@
       <c r="K772" s="10">
         <v>47.49</v>
       </c>
-      <c r="L772" s="10">
+      <c r="L772" s="19">
         <f t="shared" si="25"/>
         <v>-0.61546678840447389</v>
       </c>
@@ -46422,7 +46492,7 @@
       <c r="K773" s="10">
         <v>35.159999999999997</v>
       </c>
-      <c r="L773" s="10">
+      <c r="L773" s="19">
         <f t="shared" si="25"/>
         <v>0.35207286809021243</v>
       </c>
@@ -46462,7 +46532,7 @@
       <c r="K774" s="10">
         <v>39.590000000000003</v>
       </c>
-      <c r="L774" s="10">
+      <c r="L774" s="19">
         <f t="shared" si="25"/>
         <v>-0.5325180433039296</v>
       </c>
@@ -46502,7 +46572,7 @@
       <c r="K775" s="10">
         <v>39.06</v>
       </c>
-      <c r="L775" s="10">
+      <c r="L775" s="19">
         <f t="shared" si="25"/>
         <v>-0.48575620191492325</v>
       </c>
@@ -46542,7 +46612,7 @@
       <c r="K776" s="10">
         <v>43.65</v>
       </c>
-      <c r="L776" s="10">
+      <c r="L776" s="19">
         <f t="shared" si="25"/>
         <v>-0.13925564515285582</v>
       </c>
@@ -46582,7 +46652,7 @@
       <c r="K777" s="10">
         <v>50</v>
       </c>
-      <c r="L777" s="10">
+      <c r="L777" s="19">
         <f t="shared" si="25"/>
         <v>-0.61913309477086453</v>
       </c>
@@ -46622,7 +46692,7 @@
       <c r="K778" s="10">
         <v>44.2</v>
       </c>
-      <c r="L778" s="10">
+      <c r="L778" s="19">
         <f t="shared" si="25"/>
         <v>-0.20772683191482147</v>
       </c>
@@ -46662,7 +46732,7 @@
       <c r="K779" s="10">
         <v>35.25</v>
       </c>
-      <c r="L779" s="10">
+      <c r="L779" s="19">
         <f t="shared" si="25"/>
         <v>-8.3633986108145542E-2</v>
       </c>
@@ -46702,7 +46772,7 @@
       <c r="K780" s="10">
         <v>35.119999999999997</v>
       </c>
-      <c r="L780" s="10">
+      <c r="L780" s="19">
         <f t="shared" si="25"/>
         <v>-0.34556101370012071</v>
       </c>
@@ -46742,7 +46812,7 @@
       <c r="K781" s="10">
         <v>35.83</v>
       </c>
-      <c r="L781" s="10">
+      <c r="L781" s="19">
         <f t="shared" si="25"/>
         <v>-0.73900247135475183</v>
       </c>
@@ -46782,7 +46852,7 @@
       <c r="K782" s="10">
         <v>38.92</v>
       </c>
-      <c r="L782" s="10">
+      <c r="L782" s="19">
         <f t="shared" si="25"/>
         <v>-0.74427328198459541</v>
       </c>
@@ -46822,7 +46892,7 @@
       <c r="K783" s="10">
         <v>34.159999999999997</v>
       </c>
-      <c r="L783" s="10">
+      <c r="L783" s="19">
         <f t="shared" si="25"/>
         <v>-0.29977920691540633</v>
       </c>
@@ -46862,7 +46932,7 @@
       <c r="K784" s="10">
         <v>42.79</v>
       </c>
-      <c r="L784" s="10">
+      <c r="L784" s="19">
         <f t="shared" si="25"/>
         <v>-0.26176511217439946</v>
       </c>
@@ -46902,7 +46972,7 @@
       <c r="K785" s="10">
         <v>38.18</v>
       </c>
-      <c r="L785" s="10">
+      <c r="L785" s="19">
         <f t="shared" si="25"/>
         <v>-0.60766423357664234</v>
       </c>
@@ -46942,7 +47012,7 @@
       <c r="K786" s="10">
         <v>42.66</v>
       </c>
-      <c r="L786" s="10">
+      <c r="L786" s="19">
         <f t="shared" si="25"/>
         <v>-0.3112037581248569</v>
       </c>
@@ -46982,7 +47052,7 @@
       <c r="K787" s="10">
         <v>37.85</v>
       </c>
-      <c r="L787" s="10">
+      <c r="L787" s="19">
         <f t="shared" si="25"/>
         <v>4.9851990446111001E-2</v>
       </c>
@@ -47022,7 +47092,7 @@
       <c r="K788" s="10">
         <v>48.75</v>
       </c>
-      <c r="L788" s="10">
+      <c r="L788" s="19">
         <f t="shared" si="25"/>
         <v>-0.10883903647005846</v>
       </c>
@@ -47062,7 +47132,7 @@
       <c r="K789" s="10">
         <v>43.07</v>
       </c>
-      <c r="L789" s="10">
+      <c r="L789" s="19">
         <f t="shared" si="25"/>
         <v>-0.46431055690436807</v>
       </c>
@@ -47102,7 +47172,7 @@
       <c r="K790" s="10">
         <v>41.16</v>
       </c>
-      <c r="L790" s="10">
+      <c r="L790" s="19">
         <f t="shared" si="25"/>
         <v>-0.24814811568799303</v>
       </c>
@@ -47142,7 +47212,7 @@
       <c r="K791" s="10">
         <v>38.54</v>
       </c>
-      <c r="L791" s="10">
+      <c r="L791" s="19">
         <f t="shared" si="25"/>
         <v>-0.38602610369285628</v>
       </c>
@@ -47182,7 +47252,7 @@
       <c r="K792" s="10">
         <v>58.22</v>
       </c>
-      <c r="L792" s="10">
+      <c r="L792" s="19">
         <f t="shared" si="25"/>
         <v>-0.52965862289800159</v>
       </c>
@@ -47222,7 +47292,7 @@
       <c r="K793" s="10">
         <v>37.950000000000003</v>
       </c>
-      <c r="L793" s="10">
+      <c r="L793" s="19">
         <f t="shared" si="25"/>
         <v>-0.57803565422132519</v>
       </c>
@@ -47262,7 +47332,7 @@
       <c r="K794" s="10">
         <v>39.24</v>
       </c>
-      <c r="L794" s="10">
+      <c r="L794" s="19">
         <f t="shared" si="25"/>
         <v>-0.5550743036367709</v>
       </c>
@@ -47302,7 +47372,7 @@
       <c r="K795" s="10">
         <v>43.85</v>
       </c>
-      <c r="L795" s="10">
+      <c r="L795" s="19">
         <f t="shared" si="25"/>
         <v>-0.63803214192925795</v>
       </c>
@@ -47342,7 +47412,7 @@
       <c r="K796" s="10">
         <v>47.86</v>
       </c>
-      <c r="L796" s="10">
+      <c r="L796" s="19">
         <f t="shared" si="25"/>
         <v>-0.62944700460829495</v>
       </c>
@@ -47382,7 +47452,7 @@
       <c r="K797" s="10">
         <v>47.37</v>
       </c>
-      <c r="L797" s="10">
+      <c r="L797" s="19">
         <f t="shared" si="25"/>
         <v>-0.19155075796492665</v>
       </c>
@@ -47422,7 +47492,7 @@
       <c r="K798" s="10">
         <v>72.13</v>
       </c>
-      <c r="L798" s="10">
+      <c r="L798" s="19">
         <f t="shared" si="25"/>
         <v>2.3908583260133068E-2</v>
       </c>
@@ -47462,7 +47532,7 @@
       <c r="K799" s="10">
         <v>51.09</v>
       </c>
-      <c r="L799" s="10">
+      <c r="L799" s="19">
         <f t="shared" si="25"/>
         <v>0.22421771361685516</v>
       </c>
@@ -47502,7 +47572,7 @@
       <c r="K800" s="10">
         <v>52.37</v>
       </c>
-      <c r="L800" s="10">
+      <c r="L800" s="19">
         <f t="shared" si="25"/>
         <v>-0.45764209428311642</v>
       </c>
@@ -47542,7 +47612,7 @@
       <c r="K801" s="10">
         <v>33.46</v>
       </c>
-      <c r="L801" s="10">
+      <c r="L801" s="19">
         <f t="shared" si="25"/>
         <v>-0.46030456852791896</v>
       </c>
@@ -47582,7 +47652,7 @@
       <c r="K802" s="10">
         <v>33.03</v>
       </c>
-      <c r="L802" s="10">
+      <c r="L802" s="19">
         <f t="shared" si="25"/>
         <v>-0.28446301454658018</v>
       </c>
@@ -47622,7 +47692,7 @@
       <c r="K803" s="10">
         <v>37.31</v>
       </c>
-      <c r="L803" s="10">
+      <c r="L803" s="19">
         <f t="shared" si="25"/>
         <v>0.14876983329985935</v>
       </c>
@@ -47662,7 +47732,7 @@
       <c r="K804" s="10">
         <v>43.41</v>
       </c>
-      <c r="L804" s="10">
+      <c r="L804" s="19">
         <f t="shared" si="25"/>
         <v>0.33718969520180969</v>
       </c>
@@ -47702,7 +47772,7 @@
       <c r="K805" s="10">
         <v>47.38</v>
       </c>
-      <c r="L805" s="10">
+      <c r="L805" s="19">
         <f t="shared" si="25"/>
         <v>0.50541818181818199</v>
       </c>
@@ -47742,7 +47812,7 @@
       <c r="K806" s="10">
         <v>46.63</v>
       </c>
-      <c r="L806" s="10">
+      <c r="L806" s="19">
         <f t="shared" si="25"/>
         <v>0.36659807628425012</v>
       </c>
@@ -47782,7 +47852,7 @@
       <c r="K807" s="10">
         <v>59.91</v>
       </c>
-      <c r="L807" s="10">
+      <c r="L807" s="19">
         <f t="shared" si="25"/>
         <v>-0.61290380004881062</v>
       </c>
@@ -47822,7 +47892,7 @@
       <c r="K808" s="10">
         <v>78.33</v>
       </c>
-      <c r="L808" s="10">
+      <c r="L808" s="19">
         <f t="shared" si="25"/>
         <v>-0.71563989408649609</v>
       </c>
@@ -47862,7 +47932,7 @@
       <c r="K809" s="10">
         <v>61.89</v>
       </c>
-      <c r="L809" s="10">
+      <c r="L809" s="19">
         <f t="shared" si="25"/>
         <v>9.7336720691317713E-2</v>
       </c>
@@ -47902,7 +47972,7 @@
       <c r="K810" s="10">
         <v>51.45</v>
       </c>
-      <c r="L810" s="10">
+      <c r="L810" s="19">
         <f t="shared" si="25"/>
         <v>7.7946478050903573E-3</v>
       </c>
@@ -47942,7 +48012,7 @@
       <c r="K811" s="10">
         <v>38.94</v>
       </c>
-      <c r="L811" s="10">
+      <c r="L811" s="19">
         <f t="shared" si="25"/>
         <v>-0.70960762742940964</v>
       </c>
@@ -47982,7 +48052,7 @@
       <c r="K812" s="10">
         <v>42</v>
       </c>
-      <c r="L812" s="10">
+      <c r="L812" s="19">
         <f t="shared" si="25"/>
         <v>-0.62105478331970554</v>
       </c>
@@ -48022,7 +48092,7 @@
       <c r="K813" s="10">
         <v>66.02</v>
       </c>
-      <c r="L813" s="10">
+      <c r="L813" s="19">
         <f t="shared" si="25"/>
         <v>-0.76360813099943525</v>
       </c>
@@ -48062,7 +48132,7 @@
       <c r="K814" s="10">
         <v>76.22</v>
       </c>
-      <c r="L814" s="10">
+      <c r="L814" s="19">
         <f t="shared" si="25"/>
         <v>-0.44667268768378598</v>
       </c>
@@ -48102,7 +48172,7 @@
       <c r="K815" s="10">
         <v>66.22</v>
       </c>
-      <c r="L815" s="10">
+      <c r="L815" s="19">
         <f t="shared" si="25"/>
         <v>-0.37175355450236974</v>
       </c>
@@ -48142,7 +48212,7 @@
       <c r="K816" s="10">
         <v>49.17</v>
       </c>
-      <c r="L816" s="10">
+      <c r="L816" s="19">
         <f t="shared" si="25"/>
         <v>4.9385706739114014E-2</v>
       </c>
@@ -48182,7 +48252,7 @@
       <c r="K817" s="10">
         <v>40.53</v>
       </c>
-      <c r="L817" s="10">
+      <c r="L817" s="19">
         <f t="shared" si="25"/>
         <v>-0.52388985230195029</v>
       </c>
@@ -48222,7 +48292,7 @@
       <c r="K818" s="10">
         <v>72.38</v>
       </c>
-      <c r="L818" s="10">
+      <c r="L818" s="19">
         <f t="shared" si="25"/>
         <v>-0.35794277897296795</v>
       </c>
@@ -48262,7 +48332,7 @@
       <c r="K819" s="10">
         <v>71.64</v>
       </c>
-      <c r="L819" s="10">
+      <c r="L819" s="19">
         <f t="shared" si="25"/>
         <v>-0.10564284920617287</v>
       </c>
@@ -48302,7 +48372,7 @@
       <c r="K820" s="10">
         <v>72.260000000000005</v>
       </c>
-      <c r="L820" s="10">
+      <c r="L820" s="19">
         <f t="shared" si="25"/>
         <v>-0.42996345919610229</v>
       </c>
@@ -48342,7 +48412,7 @@
       <c r="K821" s="10">
         <v>70.959999999999994</v>
       </c>
-      <c r="L821" s="10">
+      <c r="L821" s="19">
         <f t="shared" si="25"/>
         <v>-0.19730169798020047</v>
       </c>
@@ -48382,7 +48452,7 @@
       <c r="K822" s="10">
         <v>60.48</v>
       </c>
-      <c r="L822" s="10">
+      <c r="L822" s="19">
         <f t="shared" si="25"/>
         <v>-0.13597053813007315</v>
       </c>
@@ -48422,7 +48492,7 @@
       <c r="K823" s="10">
         <v>65.23</v>
       </c>
-      <c r="L823" s="10">
+      <c r="L823" s="19">
         <f t="shared" si="25"/>
         <v>-0.33158171974832951</v>
       </c>
@@ -48462,7 +48532,7 @@
       <c r="K824" s="10">
         <v>21.67</v>
       </c>
-      <c r="L824" s="10">
+      <c r="L824" s="19">
         <f t="shared" si="25"/>
         <v>-1.9542083860164775E-2</v>
       </c>
@@ -48502,7 +48572,7 @@
       <c r="K825" s="10">
         <v>40.35</v>
       </c>
-      <c r="L825" s="10">
+      <c r="L825" s="19">
         <f t="shared" si="25"/>
         <v>7.1057694715914541E-2</v>
       </c>
@@ -48542,7 +48612,7 @@
       <c r="K826" s="10">
         <v>31.86</v>
       </c>
-      <c r="L826" s="10">
+      <c r="L826" s="19">
         <f t="shared" si="25"/>
         <v>-0.45256310465670074</v>
       </c>
@@ -48582,7 +48652,7 @@
       <c r="K827" s="10">
         <v>28.88</v>
       </c>
-      <c r="L827" s="10">
+      <c r="L827" s="19">
         <f t="shared" si="25"/>
         <v>-0.36993549570480883</v>
       </c>
@@ -48622,7 +48692,7 @@
       <c r="K828" s="10">
         <v>69.22</v>
       </c>
-      <c r="L828" s="10">
+      <c r="L828" s="19">
         <f t="shared" si="25"/>
         <v>-0.19824321644161394</v>
       </c>
@@ -48662,7 +48732,7 @@
       <c r="K829" s="10">
         <v>45.33</v>
       </c>
-      <c r="L829" s="10">
+      <c r="L829" s="19">
         <f t="shared" si="25"/>
         <v>0.36796573691525042</v>
       </c>
@@ -48702,7 +48772,7 @@
       <c r="K830" s="10">
         <v>58.81</v>
       </c>
-      <c r="L830" s="10">
+      <c r="L830" s="19">
         <f t="shared" si="25"/>
         <v>0.62754100551194258</v>
       </c>
@@ -48742,7 +48812,7 @@
       <c r="K831" s="10">
         <v>44.74</v>
       </c>
-      <c r="L831" s="10">
+      <c r="L831" s="19">
         <f t="shared" si="25"/>
         <v>0.66606412091670653</v>
       </c>
@@ -48782,7 +48852,7 @@
       <c r="K832" s="10">
         <v>35.08</v>
       </c>
-      <c r="L832" s="10">
+      <c r="L832" s="19">
         <f t="shared" si="25"/>
         <v>0.62706500566137946</v>
       </c>
@@ -48822,7 +48892,7 @@
       <c r="K833" s="10">
         <v>74.08</v>
       </c>
-      <c r="L833" s="10">
+      <c r="L833" s="19">
         <f t="shared" si="25"/>
         <v>-0.3293069213739393</v>
       </c>
@@ -48862,7 +48932,7 @@
       <c r="K834" s="10">
         <v>43.01</v>
       </c>
-      <c r="L834" s="10">
+      <c r="L834" s="19">
         <f t="shared" si="25"/>
         <v>-3.3781458378145855E-2</v>
       </c>
@@ -48917,7 +48987,7 @@
       <c r="K835" s="10">
         <v>50.59</v>
       </c>
-      <c r="L835" s="10">
+      <c r="L835" s="19">
         <f t="shared" ref="L835:L898" si="27">IF(OR(K835=0,I835=G835,J835=F835),"",0.4*((3*(E835-H835)/K835)/(1+ABS(3*(E835-H835)/K835)))+0.45*((I835+G835-2*H835)/(I835-G835))+0.15*((J835+F835-2*H835)/(J835-F835)))</f>
         <v>0.48186037403309506</v>
       </c>
@@ -48957,7 +49027,7 @@
       <c r="K836" s="10">
         <v>59.84</v>
       </c>
-      <c r="L836" s="10">
+      <c r="L836" s="19">
         <f t="shared" si="27"/>
         <v>0.69956456204990802</v>
       </c>
@@ -48997,7 +49067,7 @@
       <c r="K837" s="10">
         <v>51.78</v>
       </c>
-      <c r="L837" s="10">
+      <c r="L837" s="19">
         <f t="shared" si="27"/>
         <v>0.79456770944932509</v>
       </c>
@@ -49037,7 +49107,7 @@
       <c r="K838" s="10">
         <v>62.05</v>
       </c>
-      <c r="L838" s="10">
+      <c r="L838" s="19">
         <f t="shared" si="27"/>
         <v>0.53683257918552041</v>
       </c>
@@ -49077,7 +49147,7 @@
       <c r="K839" s="10">
         <v>58.93</v>
       </c>
-      <c r="L839" s="10">
+      <c r="L839" s="19">
         <f t="shared" si="27"/>
         <v>0.70215841949778435</v>
       </c>
@@ -49117,7 +49187,7 @@
       <c r="K840" s="10">
         <v>51.59</v>
       </c>
-      <c r="L840" s="10">
+      <c r="L840" s="19">
         <f t="shared" si="27"/>
         <v>-5.7130440431894691E-2</v>
       </c>
@@ -49157,7 +49227,7 @@
       <c r="K841" s="10">
         <v>50.16</v>
       </c>
-      <c r="L841" s="10">
+      <c r="L841" s="19">
         <f t="shared" si="27"/>
         <v>0.35297164787699925</v>
       </c>
@@ -49197,7 +49267,7 @@
       <c r="K842" s="10">
         <v>53.21</v>
       </c>
-      <c r="L842" s="10">
+      <c r="L842" s="19">
         <f t="shared" si="27"/>
         <v>0.39604299670398196</v>
       </c>
@@ -49237,7 +49307,7 @@
       <c r="K843" s="10">
         <v>54.24</v>
       </c>
-      <c r="L843" s="10">
+      <c r="L843" s="19">
         <f t="shared" si="27"/>
         <v>-0.16395681893136113</v>
       </c>
@@ -49277,7 +49347,7 @@
       <c r="K844" s="10">
         <v>54.27</v>
       </c>
-      <c r="L844" s="10">
+      <c r="L844" s="19">
         <f t="shared" si="27"/>
         <v>0.44986686845278911</v>
       </c>
@@ -49317,7 +49387,7 @@
       <c r="K845" s="10">
         <v>59.7</v>
       </c>
-      <c r="L845" s="10">
+      <c r="L845" s="19">
         <f t="shared" si="27"/>
         <v>0.15609993872207675</v>
       </c>
@@ -49357,7 +49427,7 @@
       <c r="K846" s="10">
         <v>60.43</v>
       </c>
-      <c r="L846" s="10">
+      <c r="L846" s="19">
         <f t="shared" si="27"/>
         <v>3.1949340838394305E-2</v>
       </c>
@@ -49397,7 +49467,7 @@
       <c r="K847" s="10">
         <v>60.04</v>
       </c>
-      <c r="L847" s="10">
+      <c r="L847" s="19">
         <f t="shared" si="27"/>
         <v>-0.16253110179604077</v>
       </c>
@@ -49437,7 +49507,7 @@
       <c r="K848" s="10">
         <v>70.459999999999994</v>
       </c>
-      <c r="L848" s="10">
+      <c r="L848" s="19">
         <f t="shared" si="27"/>
         <v>-9.8346095879874515E-2</v>
       </c>
@@ -49477,7 +49547,7 @@
       <c r="K849" s="10">
         <v>60.97</v>
       </c>
-      <c r="L849" s="10">
+      <c r="L849" s="19">
         <f t="shared" si="27"/>
         <v>0.27490379615184607</v>
       </c>
@@ -49517,7 +49587,7 @@
       <c r="K850" s="10">
         <v>66.88</v>
       </c>
-      <c r="L850" s="10">
+      <c r="L850" s="19">
         <f t="shared" si="27"/>
         <v>0.29385019815106106</v>
       </c>
@@ -49557,7 +49627,7 @@
       <c r="K851" s="10">
         <v>58.96</v>
       </c>
-      <c r="L851" s="10">
+      <c r="L851" s="19">
         <f t="shared" si="27"/>
         <v>-4.3663491081099029E-2</v>
       </c>
@@ -49597,7 +49667,7 @@
       <c r="K852" s="10">
         <v>59.65</v>
       </c>
-      <c r="L852" s="10">
+      <c r="L852" s="19">
         <f t="shared" si="27"/>
         <v>0.57121448745219106</v>
       </c>
@@ -49637,7 +49707,7 @@
       <c r="K853" s="10">
         <v>55.43</v>
       </c>
-      <c r="L853" s="10">
+      <c r="L853" s="19">
         <f t="shared" si="27"/>
         <v>-5.8123158687103348E-2</v>
       </c>
@@ -49677,7 +49747,7 @@
       <c r="K854" s="10">
         <v>54.08</v>
       </c>
-      <c r="L854" s="10">
+      <c r="L854" s="19">
         <f t="shared" si="27"/>
         <v>0.10129615559945292</v>
       </c>
@@ -49717,7 +49787,7 @@
       <c r="K855" s="10">
         <v>59.48</v>
       </c>
-      <c r="L855" s="10">
+      <c r="L855" s="19">
         <f t="shared" si="27"/>
         <v>-1.8471750411604142E-2</v>
       </c>
@@ -49757,7 +49827,7 @@
       <c r="K856" s="10">
         <v>54.63</v>
       </c>
-      <c r="L856" s="10">
+      <c r="L856" s="19">
         <f t="shared" si="27"/>
         <v>0.25922268907563023</v>
       </c>
@@ -49797,7 +49867,7 @@
       <c r="K857" s="10">
         <v>60.66</v>
       </c>
-      <c r="L857" s="10">
+      <c r="L857" s="19">
         <f t="shared" si="27"/>
         <v>-5.8900885337940051E-2</v>
       </c>
@@ -49837,7 +49907,7 @@
       <c r="K858" s="10">
         <v>56.55</v>
       </c>
-      <c r="L858" s="10">
+      <c r="L858" s="19">
         <f t="shared" si="27"/>
         <v>-6.5994397759103679E-2</v>
       </c>
@@ -49877,7 +49947,7 @@
       <c r="K859" s="10">
         <v>50.1</v>
       </c>
-      <c r="L859" s="10">
+      <c r="L859" s="19">
         <f t="shared" si="27"/>
         <v>-2.7816255534471871E-2</v>
       </c>
@@ -49917,7 +49987,7 @@
       <c r="K860" s="10">
         <v>50.27</v>
       </c>
-      <c r="L860" s="10">
+      <c r="L860" s="19">
         <f t="shared" si="27"/>
         <v>-0.20721352709846821</v>
       </c>
@@ -49957,7 +50027,7 @@
       <c r="K861" s="10">
         <v>48.94</v>
       </c>
-      <c r="L861" s="10">
+      <c r="L861" s="19">
         <f t="shared" si="27"/>
         <v>0.12154895760249894</v>
       </c>
@@ -49997,7 +50067,7 @@
       <c r="K862" s="10">
         <v>53.8</v>
       </c>
-      <c r="L862" s="10">
+      <c r="L862" s="19">
         <f t="shared" si="27"/>
         <v>0.254807040254515</v>
       </c>
@@ -50037,7 +50107,7 @@
       <c r="K863" s="10">
         <v>46.68</v>
       </c>
-      <c r="L863" s="10">
+      <c r="L863" s="19">
         <f t="shared" si="27"/>
         <v>0.26500528563209541</v>
       </c>
@@ -50077,7 +50147,7 @@
       <c r="K864" s="10">
         <v>53.9</v>
       </c>
-      <c r="L864" s="10">
+      <c r="L864" s="19">
         <f t="shared" si="27"/>
         <v>0.24193109075309704</v>
       </c>
@@ -50117,7 +50187,7 @@
       <c r="K865" s="10">
         <v>39.74</v>
       </c>
-      <c r="L865" s="10">
+      <c r="L865" s="19">
         <f t="shared" si="27"/>
         <v>-0.26906898934403112</v>
       </c>
@@ -50157,7 +50227,7 @@
       <c r="K866" s="10">
         <v>58.85</v>
       </c>
-      <c r="L866" s="10">
+      <c r="L866" s="19">
         <f t="shared" si="27"/>
         <v>0.40140673280208161</v>
       </c>
@@ -50197,7 +50267,7 @@
       <c r="K867" s="10">
         <v>45.01</v>
       </c>
-      <c r="L867" s="10">
+      <c r="L867" s="19">
         <f t="shared" si="27"/>
         <v>-2.2193293885601487E-2</v>
       </c>
@@ -50237,7 +50307,7 @@
       <c r="K868" s="10">
         <v>44.29</v>
       </c>
-      <c r="L868" s="10">
+      <c r="L868" s="19">
         <f t="shared" si="27"/>
         <v>-0.44958996379557131</v>
       </c>
@@ -50277,7 +50347,7 @@
       <c r="K869" s="10">
         <v>44.25</v>
       </c>
-      <c r="L869" s="10">
+      <c r="L869" s="19">
         <f t="shared" si="27"/>
         <v>-0.41063560592635567</v>
       </c>
@@ -50317,7 +50387,7 @@
       <c r="K870" s="10">
         <v>47.28</v>
       </c>
-      <c r="L870" s="10">
+      <c r="L870" s="19">
         <f t="shared" si="27"/>
         <v>0.30876520955385317</v>
       </c>
@@ -50357,7 +50427,7 @@
       <c r="K871" s="10">
         <v>71.14</v>
       </c>
-      <c r="L871" s="10">
+      <c r="L871" s="19">
         <f t="shared" si="27"/>
         <v>-4.9204103110540187E-2</v>
       </c>
@@ -50397,7 +50467,7 @@
       <c r="K872" s="10">
         <v>69.319999999999993</v>
       </c>
-      <c r="L872" s="10">
+      <c r="L872" s="19">
         <f t="shared" si="27"/>
         <v>-8.6581573407392753E-2</v>
       </c>
@@ -50437,7 +50507,7 @@
       <c r="K873" s="10">
         <v>63.44</v>
       </c>
-      <c r="L873" s="10">
+      <c r="L873" s="19">
         <f t="shared" si="27"/>
         <v>0.122069938842716</v>
       </c>
@@ -50477,7 +50547,7 @@
       <c r="K874" s="10">
         <v>66.69</v>
       </c>
-      <c r="L874" s="10">
+      <c r="L874" s="19">
         <f t="shared" si="27"/>
         <v>-0.4310304648622405</v>
       </c>
@@ -50517,7 +50587,7 @@
       <c r="K875" s="10">
         <v>57.12</v>
       </c>
-      <c r="L875" s="10">
+      <c r="L875" s="19">
         <f t="shared" si="27"/>
         <v>-3.195590840943164E-2</v>
       </c>
@@ -50557,7 +50627,7 @@
       <c r="K876" s="10">
         <v>49.69</v>
       </c>
-      <c r="L876" s="10">
+      <c r="L876" s="19">
         <f t="shared" si="27"/>
         <v>-0.22165900389342041</v>
       </c>
@@ -50597,7 +50667,7 @@
       <c r="K877" s="10">
         <v>45.38</v>
       </c>
-      <c r="L877" s="10">
+      <c r="L877" s="19">
         <f t="shared" si="27"/>
         <v>-0.22389686703642631</v>
       </c>
@@ -50637,7 +50707,7 @@
       <c r="K878" s="10">
         <v>64.83</v>
       </c>
-      <c r="L878" s="10">
+      <c r="L878" s="19">
         <f t="shared" si="27"/>
         <v>-0.18029131180595265</v>
       </c>
@@ -50677,7 +50747,7 @@
       <c r="K879" s="10">
         <v>39.61</v>
       </c>
-      <c r="L879" s="10">
+      <c r="L879" s="19">
         <f t="shared" si="27"/>
         <v>0.11670631706823253</v>
       </c>
@@ -50717,7 +50787,7 @@
       <c r="K880" s="10">
         <v>56.93</v>
       </c>
-      <c r="L880" s="10">
+      <c r="L880" s="19">
         <f t="shared" si="27"/>
         <v>-0.31174551696101899</v>
       </c>
@@ -50757,7 +50827,7 @@
       <c r="K881" s="10">
         <v>43.05</v>
       </c>
-      <c r="L881" s="10">
+      <c r="L881" s="19">
         <f t="shared" si="27"/>
         <v>-0.10307859132510928</v>
       </c>
@@ -50797,7 +50867,7 @@
       <c r="K882" s="10">
         <v>50.84</v>
       </c>
-      <c r="L882" s="10">
+      <c r="L882" s="19">
         <f t="shared" si="27"/>
         <v>-5.0591754627153644E-2</v>
       </c>
@@ -50837,7 +50907,7 @@
       <c r="K883" s="10">
         <v>48.49</v>
       </c>
-      <c r="L883" s="10">
+      <c r="L883" s="19">
         <f t="shared" si="27"/>
         <v>2.1802937522082892E-2</v>
       </c>
@@ -50877,7 +50947,7 @@
       <c r="K884" s="10">
         <v>52.21</v>
       </c>
-      <c r="L884" s="10">
+      <c r="L884" s="19">
         <f t="shared" si="27"/>
         <v>-2.4207072855193322E-2</v>
       </c>
@@ -50917,7 +50987,7 @@
       <c r="K885" s="10">
         <v>59.12</v>
       </c>
-      <c r="L885" s="10">
+      <c r="L885" s="19">
         <f t="shared" si="27"/>
         <v>-0.1901971975939587</v>
       </c>
@@ -50957,7 +51027,7 @@
       <c r="K886" s="10">
         <v>40.46</v>
       </c>
-      <c r="L886" s="10">
+      <c r="L886" s="19">
         <f t="shared" si="27"/>
         <v>8.0552913207634219E-2</v>
       </c>
@@ -50997,7 +51067,7 @@
       <c r="K887" s="10">
         <v>56.21</v>
       </c>
-      <c r="L887" s="10">
+      <c r="L887" s="19">
         <f t="shared" si="27"/>
         <v>-6.3445661055728131E-2</v>
       </c>
@@ -51037,7 +51107,7 @@
       <c r="K888" s="10">
         <v>45.51</v>
       </c>
-      <c r="L888" s="10">
+      <c r="L888" s="19">
         <f t="shared" si="27"/>
         <v>-3.6688982539407784E-3</v>
       </c>
@@ -51077,7 +51147,7 @@
       <c r="K889" s="10">
         <v>54.14</v>
       </c>
-      <c r="L889" s="10">
+      <c r="L889" s="19">
         <f t="shared" si="27"/>
         <v>-8.0013593882752643E-2</v>
       </c>
@@ -51117,7 +51187,7 @@
       <c r="K890" s="10">
         <v>50.49</v>
       </c>
-      <c r="L890" s="10">
+      <c r="L890" s="19">
         <f t="shared" si="27"/>
         <v>-0.12997082228116713</v>
       </c>
@@ -51157,7 +51227,7 @@
       <c r="K891" s="10">
         <v>44.26</v>
       </c>
-      <c r="L891" s="10">
+      <c r="L891" s="19">
         <f t="shared" si="27"/>
         <v>-0.57429588380575591</v>
       </c>
@@ -51197,7 +51267,7 @@
       <c r="K892" s="10">
         <v>44.69</v>
       </c>
-      <c r="L892" s="10">
+      <c r="L892" s="19">
         <f t="shared" si="27"/>
         <v>-0.21627233202096666</v>
       </c>
@@ -51237,7 +51307,7 @@
       <c r="K893" s="10">
         <v>36.340000000000003</v>
       </c>
-      <c r="L893" s="10">
+      <c r="L893" s="19">
         <f t="shared" si="27"/>
         <v>-0.36997341839447118</v>
       </c>
@@ -51277,7 +51347,7 @@
       <c r="K894" s="10">
         <v>72.739999999999995</v>
       </c>
-      <c r="L894" s="10">
+      <c r="L894" s="19">
         <f t="shared" si="27"/>
         <v>-0.13329456237746434</v>
       </c>
@@ -51317,7 +51387,7 @@
       <c r="K895" s="10">
         <v>63.43</v>
       </c>
-      <c r="L895" s="10">
+      <c r="L895" s="19">
         <f t="shared" si="27"/>
         <v>-0.29657642526345041</v>
       </c>
@@ -51357,7 +51427,7 @@
       <c r="K896" s="10">
         <v>67.22</v>
       </c>
-      <c r="L896" s="10">
+      <c r="L896" s="19">
         <f t="shared" si="27"/>
         <v>-0.38622902051327596</v>
       </c>
@@ -51397,7 +51467,7 @@
       <c r="K897" s="10">
         <v>79.38</v>
       </c>
-      <c r="L897" s="10">
+      <c r="L897" s="19">
         <f t="shared" si="27"/>
         <v>-0.41785241367750592</v>
       </c>
@@ -51437,7 +51507,7 @@
       <c r="K898" s="10">
         <v>63.6</v>
       </c>
-      <c r="L898" s="10">
+      <c r="L898" s="19">
         <f t="shared" si="27"/>
         <v>-0.34095656735438229</v>
       </c>
@@ -51492,7 +51562,7 @@
       <c r="K899" s="10">
         <v>70.89</v>
       </c>
-      <c r="L899" s="10">
+      <c r="L899" s="19">
         <f t="shared" ref="L899:L962" si="29">IF(OR(K899=0,I899=G899,J899=F899),"",0.4*((3*(E899-H899)/K899)/(1+ABS(3*(E899-H899)/K899)))+0.45*((I899+G899-2*H899)/(I899-G899))+0.15*((J899+F899-2*H899)/(J899-F899)))</f>
         <v>-0.27933783573979198</v>
       </c>
@@ -51532,7 +51602,7 @@
       <c r="K900" s="10">
         <v>64.010000000000005</v>
       </c>
-      <c r="L900" s="10">
+      <c r="L900" s="19">
         <f t="shared" si="29"/>
         <v>-0.3147385153426337</v>
       </c>
@@ -51572,7 +51642,7 @@
       <c r="K901" s="10">
         <v>53.81</v>
       </c>
-      <c r="L901" s="10">
+      <c r="L901" s="19">
         <f t="shared" si="29"/>
         <v>-0.44763092936471788</v>
       </c>
@@ -51612,7 +51682,7 @@
       <c r="K902" s="10">
         <v>60.53</v>
       </c>
-      <c r="L902" s="10">
+      <c r="L902" s="19">
         <f t="shared" si="29"/>
         <v>-0.48285201793721977</v>
       </c>
@@ -51652,7 +51722,7 @@
       <c r="K903" s="10">
         <v>74.3</v>
       </c>
-      <c r="L903" s="10">
+      <c r="L903" s="19">
         <f t="shared" si="29"/>
         <v>-0.314490731020514</v>
       </c>
@@ -51692,7 +51762,7 @@
       <c r="K904" s="10">
         <v>70.16</v>
       </c>
-      <c r="L904" s="10">
+      <c r="L904" s="19">
         <f t="shared" si="29"/>
         <v>-0.40840242980895697</v>
       </c>
@@ -51732,7 +51802,7 @@
       <c r="K905" s="10">
         <v>60.7</v>
       </c>
-      <c r="L905" s="10">
+      <c r="L905" s="19">
         <f t="shared" si="29"/>
         <v>3.6958387064051273E-2</v>
       </c>
@@ -51772,7 +51842,7 @@
       <c r="K906" s="10">
         <v>73.540000000000006</v>
       </c>
-      <c r="L906" s="10">
+      <c r="L906" s="19">
         <f t="shared" si="29"/>
         <v>-0.2472585056864533</v>
       </c>
@@ -51812,7 +51882,7 @@
       <c r="K907" s="10">
         <v>71.180000000000007</v>
       </c>
-      <c r="L907" s="10">
+      <c r="L907" s="19">
         <f t="shared" si="29"/>
         <v>-0.18535931320536317</v>
       </c>
@@ -51852,7 +51922,7 @@
       <c r="K908" s="10">
         <v>52.63</v>
       </c>
-      <c r="L908" s="10">
+      <c r="L908" s="19">
         <f t="shared" si="29"/>
         <v>0.26956142598092586</v>
       </c>
@@ -51892,7 +51962,7 @@
       <c r="K909" s="10">
         <v>70.599999999999994</v>
       </c>
-      <c r="L909" s="10">
+      <c r="L909" s="19">
         <f t="shared" si="29"/>
         <v>-9.4115245419588295E-2</v>
       </c>
@@ -51932,7 +52002,7 @@
       <c r="K910" s="10">
         <v>68.56</v>
       </c>
-      <c r="L910" s="10">
+      <c r="L910" s="19">
         <f t="shared" si="29"/>
         <v>-0.1425366266398625</v>
       </c>
@@ -51972,7 +52042,7 @@
       <c r="K911" s="14">
         <v>64.95</v>
       </c>
-      <c r="L911" s="10">
+      <c r="L911" s="19">
         <f t="shared" si="29"/>
         <v>-0.45071555146016445</v>
       </c>
@@ -52012,7 +52082,7 @@
       <c r="K912" s="10">
         <v>71.14</v>
       </c>
-      <c r="L912" s="10">
+      <c r="L912" s="19">
         <f t="shared" si="29"/>
         <v>-0.29367803740308424</v>
       </c>
@@ -52052,7 +52122,7 @@
       <c r="K913" s="10">
         <v>69.78</v>
       </c>
-      <c r="L913" s="10">
+      <c r="L913" s="19">
         <f t="shared" si="29"/>
         <v>-0.49032421196326631</v>
       </c>
@@ -52092,7 +52162,7 @@
       <c r="K914" s="14">
         <v>49.87</v>
       </c>
-      <c r="L914" s="10">
+      <c r="L914" s="19">
         <f t="shared" si="29"/>
         <v>-0.5047806811644131</v>
       </c>
@@ -52132,7 +52202,7 @@
       <c r="K915" s="10">
         <v>48.43</v>
       </c>
-      <c r="L915" s="10">
+      <c r="L915" s="19">
         <f t="shared" si="29"/>
         <v>-0.39250353606789262</v>
       </c>
@@ -52172,7 +52242,7 @@
       <c r="K916" s="10">
         <v>68.19</v>
       </c>
-      <c r="L916" s="10">
+      <c r="L916" s="19">
         <f t="shared" si="29"/>
         <v>-0.38233990870324253</v>
       </c>
@@ -52212,7 +52282,7 @@
       <c r="K917" s="10">
         <v>43.94</v>
       </c>
-      <c r="L917" s="10">
+      <c r="L917" s="19">
         <f t="shared" si="29"/>
         <v>-0.36505637870416868</v>
       </c>
@@ -52252,7 +52322,7 @@
       <c r="K918" s="10">
         <v>71.66</v>
       </c>
-      <c r="L918" s="10">
+      <c r="L918" s="19">
         <f t="shared" si="29"/>
         <v>-0.48688912429378534</v>
       </c>
@@ -52292,7 +52362,7 @@
       <c r="K919" s="10">
         <v>70.540000000000006</v>
       </c>
-      <c r="L919" s="10">
+      <c r="L919" s="19">
         <f t="shared" si="29"/>
         <v>-0.42270661657779934</v>
       </c>
@@ -52332,7 +52402,7 @@
       <c r="K920" s="10">
         <v>67.72</v>
       </c>
-      <c r="L920" s="10">
+      <c r="L920" s="19">
         <f t="shared" si="29"/>
         <v>-0.60302862800392332</v>
       </c>
@@ -52372,7 +52442,7 @@
       <c r="K921" s="10">
         <v>40.520000000000003</v>
       </c>
-      <c r="L921" s="10">
+      <c r="L921" s="19">
         <f t="shared" si="29"/>
         <v>-0.25088611173942554</v>
       </c>
@@ -52412,7 +52482,7 @@
       <c r="K922" s="10">
         <v>42.93</v>
       </c>
-      <c r="L922" s="10">
+      <c r="L922" s="19">
         <f t="shared" si="29"/>
         <v>-0.57439402028830755</v>
       </c>
@@ -52452,7 +52522,7 @@
       <c r="K923" s="10">
         <v>87.34</v>
       </c>
-      <c r="L923" s="10">
+      <c r="L923" s="19">
         <f t="shared" si="29"/>
         <v>-0.71098382749326139</v>
       </c>
@@ -52492,7 +52562,7 @@
       <c r="K924" s="10">
         <v>63.8</v>
       </c>
-      <c r="L924" s="10">
+      <c r="L924" s="19">
         <f t="shared" si="29"/>
         <v>-0.60726875732708108</v>
       </c>
@@ -52532,7 +52602,7 @@
       <c r="K925" s="10">
         <v>43.54</v>
       </c>
-      <c r="L925" s="10">
+      <c r="L925" s="19">
         <f t="shared" si="29"/>
         <v>-0.5971349683287317</v>
       </c>
@@ -52572,7 +52642,7 @@
       <c r="K926" s="10">
         <v>45.2</v>
       </c>
-      <c r="L926" s="10">
+      <c r="L926" s="19">
         <f t="shared" si="29"/>
         <v>-0.35412111017661901</v>
       </c>
@@ -52612,7 +52682,7 @@
       <c r="K927" s="10">
         <v>71.209999999999994</v>
       </c>
-      <c r="L927" s="10">
+      <c r="L927" s="19">
         <f t="shared" si="29"/>
         <v>-0.61386947023484439</v>
       </c>
@@ -52652,7 +52722,7 @@
       <c r="K928" s="10">
         <v>31.21</v>
       </c>
-      <c r="L928" s="10">
+      <c r="L928" s="19">
         <f t="shared" si="29"/>
         <v>-0.29134189031505259</v>
       </c>
@@ -52692,7 +52762,7 @@
       <c r="K929" s="10">
         <v>68.209999999999994</v>
       </c>
-      <c r="L929" s="10">
+      <c r="L929" s="19">
         <f t="shared" si="29"/>
         <v>-0.6887544376136463</v>
       </c>
@@ -52732,7 +52802,7 @@
       <c r="K930" s="10">
         <v>65.73</v>
       </c>
-      <c r="L930" s="10">
+      <c r="L930" s="19">
         <f t="shared" si="29"/>
         <v>-0.20666460525601557</v>
       </c>
@@ -52772,7 +52842,7 @@
       <c r="K931" s="10">
         <v>71.42</v>
       </c>
-      <c r="L931" s="10">
+      <c r="L931" s="19">
         <f t="shared" si="29"/>
         <v>-0.36906144802291113</v>
       </c>
@@ -52812,7 +52882,7 @@
       <c r="K932" s="10">
         <v>70.790000000000006</v>
       </c>
-      <c r="L932" s="10">
+      <c r="L932" s="19">
         <f t="shared" si="29"/>
         <v>-0.62008952123490801</v>
       </c>
@@ -52852,7 +52922,7 @@
       <c r="K933" s="10">
         <v>76</v>
       </c>
-      <c r="L933" s="10">
+      <c r="L933" s="19">
         <f t="shared" si="29"/>
         <v>-0.3763156276424014</v>
       </c>
@@ -52892,7 +52962,7 @@
       <c r="K934" s="10">
         <v>59.39</v>
       </c>
-      <c r="L934" s="10">
+      <c r="L934" s="19">
         <f t="shared" si="29"/>
         <v>-0.61966013688930854</v>
       </c>
@@ -52932,7 +53002,7 @@
       <c r="K935" s="10">
         <v>71.739999999999995</v>
       </c>
-      <c r="L935" s="10">
+      <c r="L935" s="19">
         <f t="shared" si="29"/>
         <v>-0.64905038946052507</v>
       </c>
@@ -52972,7 +53042,7 @@
       <c r="K936" s="10">
         <v>72.540000000000006</v>
       </c>
-      <c r="L936" s="10">
+      <c r="L936" s="19">
         <f t="shared" si="29"/>
         <v>-0.17614263667121738</v>
       </c>
@@ -53012,7 +53082,7 @@
       <c r="K937" s="10">
         <v>78.959999999999994</v>
       </c>
-      <c r="L937" s="10">
+      <c r="L937" s="19">
         <f t="shared" si="29"/>
         <v>-3.7341800721149281E-2</v>
       </c>
@@ -53052,7 +53122,7 @@
       <c r="K938" s="10">
         <v>90.94</v>
       </c>
-      <c r="L938" s="10">
+      <c r="L938" s="19">
         <f t="shared" si="29"/>
         <v>-0.38280098716046196</v>
       </c>
@@ -53092,7 +53162,7 @@
       <c r="K939" s="10">
         <v>56.33</v>
       </c>
-      <c r="L939" s="10">
+      <c r="L939" s="19">
         <f t="shared" si="29"/>
         <v>-0.48223186499549864</v>
       </c>
@@ -53132,7 +53202,7 @@
       <c r="K940" s="10">
         <v>74.87</v>
       </c>
-      <c r="L940" s="10">
+      <c r="L940" s="19">
         <f t="shared" si="29"/>
         <v>-0.59820295690223024</v>
       </c>
@@ -53172,7 +53242,7 @@
       <c r="K941" s="10">
         <v>58.35</v>
       </c>
-      <c r="L941" s="10">
+      <c r="L941" s="19">
         <f t="shared" si="29"/>
         <v>-0.56882489162598793</v>
       </c>
@@ -53212,7 +53282,7 @@
       <c r="K942" s="10">
         <v>55.2</v>
       </c>
-      <c r="L942" s="10">
+      <c r="L942" s="19">
         <f t="shared" si="29"/>
         <v>6.6364460562103308E-2</v>
       </c>
@@ -53252,7 +53322,7 @@
       <c r="K943" s="10">
         <v>71.989999999999995</v>
       </c>
-      <c r="L943" s="10">
+      <c r="L943" s="19">
         <f t="shared" si="29"/>
         <v>-0.42786048923995246</v>
       </c>
@@ -53292,7 +53362,7 @@
       <c r="K944" s="10">
         <v>71.55</v>
       </c>
-      <c r="L944" s="10">
+      <c r="L944" s="19">
         <f t="shared" si="29"/>
         <v>-0.65933583959899744</v>
       </c>
@@ -53332,7 +53402,7 @@
       <c r="K945" s="10">
         <v>54.03</v>
       </c>
-      <c r="L945" s="10">
+      <c r="L945" s="19">
         <f t="shared" si="29"/>
         <v>-0.4799137655701054</v>
       </c>
@@ -53372,7 +53442,7 @@
       <c r="K946" s="10">
         <v>62.38</v>
       </c>
-      <c r="L946" s="10">
+      <c r="L946" s="19">
         <f t="shared" si="29"/>
         <v>-0.53888527414115561</v>
       </c>
@@ -53412,7 +53482,7 @@
       <c r="K947" s="10">
         <v>60.29</v>
       </c>
-      <c r="L947" s="10">
+      <c r="L947" s="19">
         <f t="shared" si="29"/>
         <v>-0.29729634002361277</v>
       </c>
@@ -53452,7 +53522,7 @@
       <c r="K948" s="10">
         <v>89.06</v>
       </c>
-      <c r="L948" s="10">
+      <c r="L948" s="19">
         <f t="shared" si="29"/>
         <v>-0.57166282864383433</v>
       </c>
@@ -53492,7 +53562,7 @@
       <c r="K949" s="10">
         <v>67.78</v>
       </c>
-      <c r="L949" s="10">
+      <c r="L949" s="19">
         <f t="shared" si="29"/>
         <v>-0.66753284102716337</v>
       </c>
@@ -53532,7 +53602,7 @@
       <c r="K950" s="10">
         <v>76.260000000000005</v>
       </c>
-      <c r="L950" s="10">
+      <c r="L950" s="19">
         <f t="shared" si="29"/>
         <v>-0.69432849364791283</v>
       </c>
@@ -53572,7 +53642,7 @@
       <c r="K951" s="10">
         <v>70.38</v>
       </c>
-      <c r="L951" s="10">
+      <c r="L951" s="19">
         <f t="shared" si="29"/>
         <v>-0.28741042952489104</v>
       </c>
@@ -53612,7 +53682,7 @@
       <c r="K952" s="10">
         <v>70.66</v>
       </c>
-      <c r="L952" s="10">
+      <c r="L952" s="19">
         <f t="shared" si="29"/>
         <v>-0.46615259870265069</v>
       </c>
@@ -53652,7 +53722,7 @@
       <c r="K953" s="10">
         <v>69.36</v>
       </c>
-      <c r="L953" s="10">
+      <c r="L953" s="19">
         <f t="shared" si="29"/>
         <v>-0.44206978722177381</v>
       </c>
@@ -53692,7 +53762,7 @@
       <c r="K954" s="10">
         <v>75.61</v>
       </c>
-      <c r="L954" s="10">
+      <c r="L954" s="19">
         <f t="shared" si="29"/>
         <v>-0.32088253550501539</v>
       </c>
@@ -53732,7 +53802,7 @@
       <c r="K955" s="10">
         <v>56.15</v>
       </c>
-      <c r="L955" s="10">
+      <c r="L955" s="19">
         <f t="shared" si="29"/>
         <v>-0.50582877680886162</v>
       </c>
@@ -53772,7 +53842,7 @@
       <c r="K956" s="10">
         <v>54.22</v>
       </c>
-      <c r="L956" s="10">
+      <c r="L956" s="19">
         <f t="shared" si="29"/>
         <v>-0.63098579273075917</v>
       </c>
@@ -53812,7 +53882,7 @@
       <c r="K957" s="10">
         <v>70.319999999999993</v>
       </c>
-      <c r="L957" s="10">
+      <c r="L957" s="19">
         <f t="shared" si="29"/>
         <v>-0.64622055937193335</v>
       </c>
@@ -53852,7 +53922,7 @@
       <c r="K958" s="10">
         <v>75.64</v>
       </c>
-      <c r="L958" s="10">
+      <c r="L958" s="19">
         <f t="shared" si="29"/>
         <v>-0.36617724288840264</v>
       </c>
@@ -53892,7 +53962,7 @@
       <c r="K959" s="10">
         <v>60.95</v>
       </c>
-      <c r="L959" s="10">
+      <c r="L959" s="19">
         <f t="shared" si="29"/>
         <v>-0.45766133002290194</v>
       </c>
@@ -53932,7 +54002,7 @@
       <c r="K960" s="10">
         <v>56.27</v>
       </c>
-      <c r="L960" s="10">
+      <c r="L960" s="19">
         <f t="shared" si="29"/>
         <v>-0.43652475766308613</v>
       </c>
@@ -53972,7 +54042,7 @@
       <c r="K961" s="10">
         <v>66.66</v>
       </c>
-      <c r="L961" s="10">
+      <c r="L961" s="19">
         <f t="shared" si="29"/>
         <v>-0.45973220117570218</v>
       </c>
@@ -54012,7 +54082,7 @@
       <c r="K962" s="10">
         <v>55.21</v>
       </c>
-      <c r="L962" s="10">
+      <c r="L962" s="19">
         <f t="shared" si="29"/>
         <v>-0.6157369773869833</v>
       </c>
@@ -54067,7 +54137,7 @@
       <c r="K963" s="10">
         <v>44.97</v>
       </c>
-      <c r="L963" s="10">
+      <c r="L963" s="19">
         <f t="shared" ref="L963:L1026" si="31">IF(OR(K963=0,I963=G963,J963=F963),"",0.4*((3*(E963-H963)/K963)/(1+ABS(3*(E963-H963)/K963)))+0.45*((I963+G963-2*H963)/(I963-G963))+0.15*((J963+F963-2*H963)/(J963-F963)))</f>
         <v>3.6008165581600804E-2</v>
       </c>
@@ -54107,7 +54177,7 @@
       <c r="K964" s="10">
         <v>65.58</v>
       </c>
-      <c r="L964" s="10">
+      <c r="L964" s="19">
         <f t="shared" si="31"/>
         <v>-0.47844649581112958</v>
       </c>
@@ -54147,7 +54217,7 @@
       <c r="K965" s="10">
         <v>50.55</v>
       </c>
-      <c r="L965" s="10">
+      <c r="L965" s="19">
         <f t="shared" si="31"/>
         <v>-0.50817200970522958</v>
       </c>
@@ -54187,7 +54257,7 @@
       <c r="K966" s="10">
         <v>55.02</v>
       </c>
-      <c r="L966" s="10">
+      <c r="L966" s="19">
         <f t="shared" si="31"/>
         <v>-0.6953125</v>
       </c>
@@ -54227,7 +54297,7 @@
       <c r="K967" s="10">
         <v>72.16</v>
       </c>
-      <c r="L967" s="10">
+      <c r="L967" s="19">
         <f t="shared" si="31"/>
         <v>-0.49240096128976635</v>
       </c>
@@ -54267,7 +54337,7 @@
       <c r="K968" s="10">
         <v>90.01</v>
       </c>
-      <c r="L968" s="10">
+      <c r="L968" s="19">
         <f t="shared" si="31"/>
         <v>-0.55236738544405062</v>
       </c>
@@ -54307,7 +54377,7 @@
       <c r="K969" s="10">
         <v>55.05</v>
       </c>
-      <c r="L969" s="10">
+      <c r="L969" s="19">
         <f t="shared" si="31"/>
         <v>-0.43237336973005769</v>
       </c>
@@ -54347,7 +54417,7 @@
       <c r="K970" s="10">
         <v>58.09</v>
       </c>
-      <c r="L970" s="10">
+      <c r="L970" s="19">
         <f t="shared" si="31"/>
         <v>-0.58905225751779866</v>
       </c>
@@ -54387,7 +54457,7 @@
       <c r="K971" s="10">
         <v>45.88</v>
       </c>
-      <c r="L971" s="10">
+      <c r="L971" s="19">
         <f t="shared" si="31"/>
         <v>-0.33633570143326924</v>
       </c>
@@ -54427,7 +54497,7 @@
       <c r="K972" s="10">
         <v>65.86</v>
       </c>
-      <c r="L972" s="10">
+      <c r="L972" s="19">
         <f t="shared" si="31"/>
         <v>-0.68053485049545781</v>
       </c>
@@ -54467,7 +54537,7 @@
       <c r="K973" s="10">
         <v>54.2</v>
       </c>
-      <c r="L973" s="10">
+      <c r="L973" s="19">
         <f t="shared" si="31"/>
         <v>-0.42786714685375693</v>
       </c>
@@ -54507,7 +54577,7 @@
       <c r="K974" s="10">
         <v>52.44</v>
       </c>
-      <c r="L974" s="10">
+      <c r="L974" s="19">
         <f t="shared" si="31"/>
         <v>-0.52093122943211545</v>
       </c>
@@ -54547,7 +54617,7 @@
       <c r="K975" s="10">
         <v>49.61</v>
       </c>
-      <c r="L975" s="10">
+      <c r="L975" s="19">
         <f t="shared" si="31"/>
         <v>-0.61601170679792472</v>
       </c>
@@ -54587,7 +54657,7 @@
       <c r="K976" s="10">
         <v>51.43</v>
       </c>
-      <c r="L976" s="10">
+      <c r="L976" s="19">
         <f t="shared" si="31"/>
         <v>-0.45221076249039954</v>
       </c>
@@ -54627,7 +54697,7 @@
       <c r="K977" s="10">
         <v>69.739999999999995</v>
       </c>
-      <c r="L977" s="10">
+      <c r="L977" s="19">
         <f t="shared" si="31"/>
         <v>-0.4946304196413025</v>
       </c>
@@ -54667,7 +54737,7 @@
       <c r="K978" s="10">
         <v>70.47</v>
       </c>
-      <c r="L978" s="10">
+      <c r="L978" s="19">
         <f t="shared" si="31"/>
         <v>-0.53133018773215546</v>
       </c>
@@ -54707,7 +54777,7 @@
       <c r="K979" s="10">
         <v>53.55</v>
       </c>
-      <c r="L979" s="10">
+      <c r="L979" s="19">
         <f t="shared" si="31"/>
         <v>-0.46885250937052725</v>
       </c>
@@ -54747,7 +54817,7 @@
       <c r="K980" s="10">
         <v>54.17</v>
       </c>
-      <c r="L980" s="10">
+      <c r="L980" s="19">
         <f t="shared" si="31"/>
         <v>-0.56335767983442164</v>
       </c>
@@ -54787,7 +54857,7 @@
       <c r="K981" s="10">
         <v>83.68</v>
       </c>
-      <c r="L981" s="10">
+      <c r="L981" s="19">
         <f t="shared" si="31"/>
         <v>-0.24812275630842684</v>
       </c>
@@ -54827,7 +54897,7 @@
       <c r="K982" s="10">
         <v>60.04</v>
       </c>
-      <c r="L982" s="10">
+      <c r="L982" s="19">
         <f t="shared" si="31"/>
         <v>0.34050486837360261</v>
       </c>
@@ -54867,7 +54937,7 @@
       <c r="K983" s="10">
         <v>65.53</v>
       </c>
-      <c r="L983" s="10">
+      <c r="L983" s="19">
         <f t="shared" si="31"/>
         <v>-0.31181735574738756</v>
       </c>
@@ -54907,7 +54977,7 @@
       <c r="K984" s="10">
         <v>50.87</v>
       </c>
-      <c r="L984" s="10">
+      <c r="L984" s="19">
         <f t="shared" si="31"/>
         <v>-0.2886082838231333</v>
       </c>
@@ -54947,7 +55017,7 @@
       <c r="K985" s="10">
         <v>77.239999999999995</v>
       </c>
-      <c r="L985" s="10">
+      <c r="L985" s="19">
         <f t="shared" si="31"/>
         <v>3.6086091328026829E-2</v>
       </c>
@@ -54987,7 +55057,7 @@
       <c r="K986" s="10">
         <v>51.46</v>
       </c>
-      <c r="L986" s="10">
+      <c r="L986" s="19">
         <f t="shared" si="31"/>
         <v>-0.34918338513704439</v>
       </c>
@@ -55027,7 +55097,7 @@
       <c r="K987" s="10">
         <v>65.03</v>
       </c>
-      <c r="L987" s="10">
+      <c r="L987" s="19">
         <f t="shared" si="31"/>
         <v>-0.33617616520535298</v>
       </c>
@@ -55067,7 +55137,7 @@
       <c r="K988" s="10">
         <v>60.35</v>
       </c>
-      <c r="L988" s="10">
+      <c r="L988" s="19">
         <f t="shared" si="31"/>
         <v>-0.4567984976914064</v>
       </c>
@@ -55107,7 +55177,7 @@
       <c r="K989" s="10">
         <v>53.2</v>
       </c>
-      <c r="L989" s="10">
+      <c r="L989" s="19">
         <f t="shared" si="31"/>
         <v>-0.58033083198100566</v>
       </c>
@@ -55147,7 +55217,7 @@
       <c r="K990" s="10">
         <v>67.680000000000007</v>
       </c>
-      <c r="L990" s="10">
+      <c r="L990" s="19">
         <f t="shared" si="31"/>
         <v>-0.7045798729848558</v>
       </c>
@@ -55187,7 +55257,7 @@
       <c r="K991" s="10">
         <v>73.680000000000007</v>
       </c>
-      <c r="L991" s="10">
+      <c r="L991" s="19">
         <f t="shared" si="31"/>
         <v>-0.69053699284009551</v>
       </c>
@@ -55227,7 +55297,7 @@
       <c r="K992" s="10">
         <v>52.15</v>
       </c>
-      <c r="L992" s="10">
+      <c r="L992" s="19">
         <f t="shared" si="31"/>
         <v>-0.59239735650725911</v>
       </c>
@@ -55267,7 +55337,7 @@
       <c r="K993" s="10">
         <v>72.73</v>
       </c>
-      <c r="L993" s="10">
+      <c r="L993" s="19">
         <f t="shared" si="31"/>
         <v>-0.63789578051430651</v>
       </c>
@@ -55307,7 +55377,7 @@
       <c r="K994" s="10">
         <v>54.77</v>
       </c>
-      <c r="L994" s="10">
+      <c r="L994" s="19">
         <f t="shared" si="31"/>
         <v>-0.48977052927729919</v>
       </c>
@@ -55347,7 +55417,7 @@
       <c r="K995" s="10">
         <v>69.709999999999994</v>
       </c>
-      <c r="L995" s="10">
+      <c r="L995" s="19">
         <f t="shared" si="31"/>
         <v>-0.67349824118336787</v>
       </c>
@@ -55387,7 +55457,7 @@
       <c r="K996" s="10">
         <v>57.22</v>
       </c>
-      <c r="L996" s="10">
+      <c r="L996" s="19">
         <f t="shared" si="31"/>
         <v>-0.49730895963746691</v>
       </c>
@@ -55427,7 +55497,7 @@
       <c r="K997" s="10">
         <v>64.98</v>
       </c>
-      <c r="L997" s="10">
+      <c r="L997" s="19">
         <f t="shared" si="31"/>
         <v>-0.57484794613576862</v>
       </c>
@@ -55467,7 +55537,7 @@
       <c r="K998" s="10">
         <v>64.89</v>
       </c>
-      <c r="L998" s="10">
+      <c r="L998" s="19">
         <f t="shared" si="31"/>
         <v>-0.67862551393330295</v>
       </c>
@@ -55507,7 +55577,7 @@
       <c r="K999" s="10">
         <v>35.96</v>
       </c>
-      <c r="L999" s="10">
+      <c r="L999" s="19">
         <f t="shared" si="31"/>
         <v>-0.5451250529885544</v>
       </c>
@@ -55547,7 +55617,7 @@
       <c r="K1000" s="10">
         <v>69.55</v>
       </c>
-      <c r="L1000" s="10">
+      <c r="L1000" s="19">
         <f t="shared" si="31"/>
         <v>-0.67786488407213286</v>
       </c>
@@ -55587,7 +55657,7 @@
       <c r="K1001" s="10">
         <v>44.79</v>
       </c>
-      <c r="L1001" s="10">
+      <c r="L1001" s="19">
         <f t="shared" si="31"/>
         <v>-0.49410011918951124</v>
       </c>
@@ -55627,7 +55697,7 @@
       <c r="K1002" s="10">
         <v>44.7</v>
       </c>
-      <c r="L1002" s="10">
+      <c r="L1002" s="19">
         <f t="shared" si="31"/>
         <v>-0.57859744990892537</v>
       </c>
@@ -55667,7 +55737,7 @@
       <c r="K1003" s="10">
         <v>63.56</v>
       </c>
-      <c r="L1003" s="10">
+      <c r="L1003" s="19">
         <f t="shared" si="31"/>
         <v>-0.71102928799865339</v>
       </c>
@@ -55707,7 +55777,7 @@
       <c r="K1004" s="10">
         <v>71.06</v>
       </c>
-      <c r="L1004" s="10">
+      <c r="L1004" s="19">
         <f t="shared" si="31"/>
         <v>-0.67285771311984388</v>
       </c>
@@ -55747,7 +55817,7 @@
       <c r="K1005" s="10">
         <v>71.959999999999994</v>
       </c>
-      <c r="L1005" s="10">
+      <c r="L1005" s="19">
         <f t="shared" si="31"/>
         <v>-0.68040448674371168</v>
       </c>
@@ -55787,7 +55857,7 @@
       <c r="K1006" s="10">
         <v>66.77</v>
       </c>
-      <c r="L1006" s="10">
+      <c r="L1006" s="19">
         <f t="shared" si="31"/>
         <v>-0.65281813975011582</v>
       </c>
@@ -55827,7 +55897,7 @@
       <c r="K1007" s="10">
         <v>71.13</v>
       </c>
-      <c r="L1007" s="10">
+      <c r="L1007" s="19">
         <f t="shared" si="31"/>
         <v>-0.70469802555168415</v>
       </c>
@@ -55867,7 +55937,7 @@
       <c r="K1008" s="10">
         <v>69.27</v>
       </c>
-      <c r="L1008" s="10">
+      <c r="L1008" s="19">
         <f t="shared" si="31"/>
         <v>-0.68522845275181732</v>
       </c>
@@ -55907,7 +55977,7 @@
       <c r="K1009" s="10">
         <v>50.98</v>
       </c>
-      <c r="L1009" s="10">
+      <c r="L1009" s="19">
         <f t="shared" si="31"/>
         <v>-0.68839887931929034</v>
       </c>
@@ -55947,7 +56017,7 @@
       <c r="K1010" s="10">
         <v>52.1</v>
       </c>
-      <c r="L1010" s="10">
+      <c r="L1010" s="19">
         <f t="shared" si="31"/>
         <v>-0.64287476866132032</v>
       </c>
@@ -55987,7 +56057,7 @@
       <c r="K1011" s="10">
         <v>55.36</v>
       </c>
-      <c r="L1011" s="10">
+      <c r="L1011" s="19">
         <f t="shared" si="31"/>
         <v>0.1600740832201506</v>
       </c>
@@ -56027,7 +56097,7 @@
       <c r="K1012" s="10">
         <v>40.86</v>
       </c>
-      <c r="L1012" s="10">
+      <c r="L1012" s="19">
         <f t="shared" si="31"/>
         <v>-0.61876061120543291</v>
       </c>
@@ -56067,7 +56137,7 @@
       <c r="K1013" s="10">
         <v>39.42</v>
       </c>
-      <c r="L1013" s="10">
+      <c r="L1013" s="19">
         <f t="shared" si="31"/>
         <v>-0.64200633161851994</v>
       </c>
@@ -56107,7 +56177,7 @@
       <c r="K1014" s="10">
         <v>51.59</v>
       </c>
-      <c r="L1014" s="10">
+      <c r="L1014" s="19">
         <f t="shared" si="31"/>
         <v>-0.67547600913937544</v>
       </c>
@@ -56147,7 +56217,7 @@
       <c r="K1015" s="10">
         <v>50.29</v>
       </c>
-      <c r="L1015" s="10">
+      <c r="L1015" s="19">
         <f t="shared" si="31"/>
         <v>-0.60020489258661369</v>
       </c>
@@ -56187,7 +56257,7 @@
       <c r="K1016" s="10">
         <v>47.59</v>
       </c>
-      <c r="L1016" s="10">
+      <c r="L1016" s="19">
         <f t="shared" si="31"/>
         <v>-0.48307632999229005</v>
       </c>
@@ -56227,7 +56297,7 @@
       <c r="K1017" s="10">
         <v>45.89</v>
       </c>
-      <c r="L1017" s="10">
+      <c r="L1017" s="19">
         <f t="shared" si="31"/>
         <v>-0.54319266055045878</v>
       </c>
@@ -56267,7 +56337,7 @@
       <c r="K1018" s="10">
         <v>46.38</v>
       </c>
-      <c r="L1018" s="10">
+      <c r="L1018" s="19">
         <f t="shared" si="31"/>
         <v>-0.43267326732673261</v>
       </c>
@@ -56307,7 +56377,7 @@
       <c r="K1019" s="10">
         <v>49.27</v>
       </c>
-      <c r="L1019" s="10">
+      <c r="L1019" s="19">
         <f t="shared" si="31"/>
         <v>-0.54220677807277839</v>
       </c>
@@ -56347,7 +56417,7 @@
       <c r="K1020" s="10">
         <v>48.97</v>
       </c>
-      <c r="L1020" s="10">
+      <c r="L1020" s="19">
         <f t="shared" si="31"/>
         <v>-0.57088914220575659</v>
       </c>
@@ -56387,7 +56457,7 @@
       <c r="K1021" s="10">
         <v>50.86</v>
       </c>
-      <c r="L1021" s="10">
+      <c r="L1021" s="19">
         <f t="shared" si="31"/>
         <v>-0.49741767764298095</v>
       </c>
@@ -56427,7 +56497,7 @@
       <c r="K1022" s="10">
         <v>50.37</v>
       </c>
-      <c r="L1022" s="10">
+      <c r="L1022" s="19">
         <f t="shared" si="31"/>
         <v>-0.22680461982675643</v>
       </c>
@@ -56467,7 +56537,7 @@
       <c r="K1023" s="10">
         <v>60.31</v>
       </c>
-      <c r="L1023" s="10">
+      <c r="L1023" s="19">
         <f t="shared" si="31"/>
         <v>-0.6708759085642052</v>
       </c>
@@ -56507,7 +56577,7 @@
       <c r="K1024" s="10">
         <v>46.41</v>
       </c>
-      <c r="L1024" s="10">
+      <c r="L1024" s="19">
         <f t="shared" si="31"/>
         <v>-0.57966360856269117</v>
       </c>
@@ -56547,7 +56617,7 @@
       <c r="K1025" s="10">
         <v>64.569999999999993</v>
       </c>
-      <c r="L1025" s="10">
+      <c r="L1025" s="19">
         <f t="shared" si="31"/>
         <v>-0.63736949803333964</v>
       </c>
@@ -56587,7 +56657,7 @@
       <c r="K1026" s="10">
         <v>63.52</v>
       </c>
-      <c r="L1026" s="10">
+      <c r="L1026" s="19">
         <f t="shared" si="31"/>
         <v>-0.71620716574903442</v>
       </c>
@@ -56642,8 +56712,8 @@
       <c r="K1027" s="10">
         <v>47.62</v>
       </c>
-      <c r="L1027" s="10">
-        <f t="shared" ref="L1027:L1044" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
+      <c r="L1027" s="19">
+        <f t="shared" ref="L1027:L1045" si="33">IF(OR(K1027=0,I1027=G1027,J1027=F1027),"",0.4*((3*(E1027-H1027)/K1027)/(1+ABS(3*(E1027-H1027)/K1027)))+0.45*((I1027+G1027-2*H1027)/(I1027-G1027))+0.15*((J1027+F1027-2*H1027)/(J1027-F1027)))</f>
         <v>-0.56220481668637778</v>
       </c>
     </row>
@@ -56682,7 +56752,7 @@
       <c r="K1028" s="10">
         <v>64.84</v>
       </c>
-      <c r="L1028" s="10">
+      <c r="L1028" s="19">
         <f t="shared" si="33"/>
         <v>-0.69401995524058191</v>
       </c>
@@ -56722,7 +56792,7 @@
       <c r="K1029" s="10">
         <v>49.98</v>
       </c>
-      <c r="L1029" s="10">
+      <c r="L1029" s="19">
         <f t="shared" si="33"/>
         <v>-0.62586447168889914</v>
       </c>
@@ -56762,7 +56832,7 @@
       <c r="K1030" s="10">
         <v>62.78</v>
       </c>
-      <c r="L1030" s="10">
+      <c r="L1030" s="19">
         <f t="shared" si="33"/>
         <v>-0.50039742468802162</v>
       </c>
@@ -56802,7 +56872,7 @@
       <c r="K1031" s="10">
         <v>68.13</v>
       </c>
-      <c r="L1031" s="10">
+      <c r="L1031" s="19">
         <f t="shared" si="33"/>
         <v>-0.65365583694375962</v>
       </c>
@@ -56857,7 +56927,7 @@
       <c r="K1032" s="10">
         <v>47.03</v>
       </c>
-      <c r="L1032" s="10">
+      <c r="L1032" s="19">
         <f t="shared" si="33"/>
         <v>-0.37056933931508074</v>
       </c>
@@ -56897,7 +56967,7 @@
       <c r="K1033" s="10">
         <v>55.64</v>
       </c>
-      <c r="L1033" s="10">
+      <c r="L1033" s="19">
         <f t="shared" si="33"/>
         <v>-0.40553691617377119</v>
       </c>
@@ -56952,7 +57022,7 @@
       <c r="K1034" s="10">
         <v>51.31</v>
       </c>
-      <c r="L1034" s="10">
+      <c r="L1034" s="19">
         <f t="shared" si="33"/>
         <v>-0.13670539223038852</v>
       </c>
@@ -56992,7 +57062,7 @@
       <c r="K1035" s="10">
         <v>68.87</v>
       </c>
-      <c r="L1035" s="10">
+      <c r="L1035" s="19">
         <f t="shared" si="33"/>
         <v>-0.46311752988047816</v>
       </c>
@@ -57032,7 +57102,7 @@
       <c r="K1036" s="10">
         <v>51.9</v>
       </c>
-      <c r="L1036" s="10">
+      <c r="L1036" s="19">
         <f t="shared" si="33"/>
         <v>-0.55107991360691133</v>
       </c>
@@ -57087,7 +57157,7 @@
       <c r="K1037" s="10">
         <v>48.61</v>
       </c>
-      <c r="L1037" s="10">
+      <c r="L1037" s="19">
         <f t="shared" si="33"/>
         <v>-0.59082688875669243</v>
       </c>
@@ -57127,7 +57197,7 @@
       <c r="K1038" s="10">
         <v>43.28</v>
       </c>
-      <c r="L1038" s="10">
+      <c r="L1038" s="19">
         <f t="shared" si="33"/>
         <v>-0.52501407921907262</v>
       </c>
@@ -57167,7 +57237,7 @@
       <c r="K1039" s="10">
         <v>68.17</v>
       </c>
-      <c r="L1039" s="10">
+      <c r="L1039" s="19">
         <f t="shared" si="33"/>
         <v>-0.67710547038943258</v>
       </c>
@@ -57222,7 +57292,7 @@
       <c r="K1040" s="10">
         <v>55.01</v>
       </c>
-      <c r="L1040" s="10">
+      <c r="L1040" s="19">
         <f t="shared" si="33"/>
         <v>-0.55290861601424091</v>
       </c>
@@ -57262,7 +57332,7 @@
       <c r="K1041" s="10">
         <v>47.62</v>
       </c>
-      <c r="L1041" s="10">
+      <c r="L1041" s="19">
         <f t="shared" si="33"/>
         <v>-0.48683508102955197</v>
       </c>
@@ -57317,7 +57387,7 @@
       <c r="K1042" s="10">
         <v>72.069999999999993</v>
       </c>
-      <c r="L1042" s="10">
+      <c r="L1042" s="19">
         <f t="shared" si="33"/>
         <v>-0.18535438877962951</v>
       </c>
@@ -57357,7 +57427,7 @@
       <c r="K1043" s="10">
         <v>53.3</v>
       </c>
-      <c r="L1043" s="10">
+      <c r="L1043" s="19">
         <f t="shared" si="33"/>
         <v>-0.2806141069130893</v>
       </c>
@@ -57397,9 +57467,64 @@
       <c r="K1044" s="10">
         <v>49.11</v>
       </c>
-      <c r="L1044" s="10">
+      <c r="L1044" s="19">
         <f t="shared" si="33"/>
         <v>-0.58850184083828949</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:12">
+      <c r="A1045" s="8">
+        <v>46197</v>
+      </c>
+      <c r="B1045" s="8">
+        <v>46198</v>
+      </c>
+      <c r="C1045" s="9">
+        <v>0.41666666666674601</v>
+      </c>
+      <c r="D1045" s="8" t="str">
+        <f t="shared" ref="D1045" si="39">IF(
+ AND(
+  B1045 &gt;= IF(
+         YEAR(B1045)&gt;=2007,
+         DATE(YEAR(B1045),3,14)-WEEKDAY(DATE(YEAR(B1045),3,14),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1045),4,7)-WEEKDAY(DATE(YEAR(B1045),4,7),1)+1 + TIME(2,0,0)
+       ),
+  B1045 &lt;  IF(
+         YEAR(B1045)&gt;=2007,
+         DATE(YEAR(B1045),11,7)-WEEKDAY(DATE(YEAR(B1045),11,7),1)+1 + TIME(2,0,0),
+         DATE(YEAR(B1045),10,31)-WEEKDAY(DATE(YEAR(B1045),10,31),1) + TIME(2,0,0)
+       )
+ ),
+ "UTC-4",
+ "UTC-5"
+)</f>
+        <v>UTC-4</v>
+      </c>
+      <c r="E1045" s="10">
+        <v>98.59</v>
+      </c>
+      <c r="F1045" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="G1045" s="10">
+        <v>85.5</v>
+      </c>
+      <c r="H1045" s="12">
+        <v>99</v>
+      </c>
+      <c r="I1045" s="12">
+        <v>100</v>
+      </c>
+      <c r="J1045" s="12">
+        <v>200</v>
+      </c>
+      <c r="K1045" s="10">
+        <v>43.91</v>
+      </c>
+      <c r="L1045" s="19">
+        <f t="shared" si="33"/>
+        <v>-0.397178806845285</v>
       </c>
     </row>
   </sheetData>
@@ -57422,29 +57547,89 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44703C2A-D4C6-BD4F-B5E9-874C8C9CFE9E}">
-  <dimension ref="B2:C3"/>
+  <dimension ref="B2:D11"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="2" spans="2:3">
-      <c r="B2" t="s">
+    <row r="2" spans="2:4">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="2:3">
-      <c r="B3" t="s">
+    <row r="3" spans="2:4">
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4">
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="B11" t="s">
         <v>8</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C11" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" xr:uid="{A82A1AB3-CBB7-F444-B7E1-7D406688AF01}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{A82A1AB3-CBB7-F444-B7E1-7D406688AF01}"/>
+    <hyperlink ref="D5" r:id="rId2" xr:uid="{113F6732-0185-4C2B-AA6C-637F02D708EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
